--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="24">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -29,19 +29,7 @@
     <t>BSBAS1</t>
   </si>
   <si>
-    <t>BSCLTH1</t>
-  </si>
-  <si>
-    <t>BSCLTH4</t>
-  </si>
-  <si>
-    <t>BSCLUG</t>
-  </si>
-  <si>
     <t>BSECOM</t>
-  </si>
-  <si>
-    <t>BSTOY1</t>
   </si>
   <si>
     <t>Total</t>
@@ -101,13 +89,7 @@
     <t>SP-PERFUME</t>
   </si>
   <si>
-    <t>SPACC</t>
-  </si>
-  <si>
     <t>SPAIS1</t>
-  </si>
-  <si>
-    <t>SPAIS2</t>
   </si>
 </sst>
 </file>
@@ -497,18 +479,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,20 +504,8 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -545,18 +513,14 @@
         <v>21092</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
@@ -564,332 +528,146 @@
         <v>21469</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B4" s="2">
-        <v>21075</v>
+        <v>21085</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B5" s="2">
-        <v>21533</v>
+        <v>21088</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B6" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21515</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B8" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>1015</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>1015</v>
+      </c>
+      <c r="B10" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
         <v>5</v>
       </c>
-      <c r="G5" s="3">
-        <v>18</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>1016</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C11" s="3">
+        <v>196</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="4">
+        <v>196</v>
+      </c>
+      <c r="D12" s="4">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>2</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>2</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3">
-        <v>6</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B10" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>10</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B12" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C12" s="3">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3">
-        <v>11</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B13" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C13" s="3">
-        <v>46</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>145</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B14" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C14" s="3">
-        <v>67</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>108</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B15" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B16" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3">
-        <v>5</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B17" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C17" s="3">
-        <v>285</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>48</v>
-      </c>
-      <c r="I17" s="3">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4">
-        <v>406</v>
-      </c>
-      <c r="D18" s="4">
-        <v>2</v>
-      </c>
-      <c r="E18" s="4">
-        <v>4</v>
-      </c>
-      <c r="F18" s="4">
-        <v>292</v>
-      </c>
-      <c r="G18" s="4">
-        <v>42</v>
-      </c>
-      <c r="H18" s="4">
-        <v>54</v>
-      </c>
-      <c r="I18" s="4">
-        <v>800</v>
+      <c r="E12" s="4">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +677,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -922,34 +700,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -964,14 +742,14 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3">
-        <v>70</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -986,14 +764,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3">
-        <v>84</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1008,88 +786,88 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3">
-        <v>84</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>60139</v>
+        <v>60134</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3">
+        <v>169</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3">
-        <v>23</v>
-      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>60272</v>
+        <v>60135</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3">
+        <v>99</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>17</v>
-      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3">
-        <v>17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>60129</v>
+        <v>60306</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="3">
+        <v>152</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>32</v>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>32</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>60130</v>
+        <v>60132</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -1097,21 +875,21 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>11</v>
-      </c>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>376</v>
+      </c>
       <c r="L8" s="3">
-        <v>11</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>60131</v>
+        <v>60135</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1119,219 +897,221 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>20</v>
-      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>134</v>
+      </c>
       <c r="L9" s="3">
-        <v>20</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>60134</v>
+        <v>60139</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3">
-        <v>213</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>160</v>
+      </c>
       <c r="L10" s="3">
-        <v>213</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>60127</v>
+      </c>
+      <c r="C11" s="3">
+        <v>38</v>
+      </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>129</v>
-      </c>
+      <c r="E11" s="3">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>129</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3">
-        <v>195</v>
-      </c>
+        <v>60132</v>
+      </c>
+      <c r="C12" s="3">
+        <v>115</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>195</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
-        <v>60</v>
-      </c>
-      <c r="E13" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C13" s="3">
+        <v>47</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>3</v>
-      </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="3">
-        <v>568</v>
-      </c>
+      <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>632</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3">
-        <v>29</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3">
+        <v>263</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3">
-        <v>222</v>
-      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>64</v>
+      </c>
+      <c r="K14" s="3"/>
       <c r="L14" s="3">
-        <v>253</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2">
+        <v>60136</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>13</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>13</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
         <v>26</v>
-      </c>
-      <c r="B15" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
-        <v>24</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3">
-        <v>231</v>
-      </c>
-      <c r="L15" s="3">
-        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2">
-        <v>60130</v>
+        <v>60140</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="3">
-        <v>23</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3">
+        <v>30</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>1</v>
-      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>12</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
-        <v>60272</v>
+        <v>60203</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="3">
-        <v>7</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3">
+        <v>32</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>9</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3">
-        <v>6</v>
-      </c>
-      <c r="E18" s="3"/>
+        <v>60134</v>
+      </c>
+      <c r="C18" s="3">
+        <v>218</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -1339,89 +1119,91 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3">
-        <v>6</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C19" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C19" s="3">
+        <v>247</v>
+      </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3">
-        <v>75</v>
-      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3">
-        <v>75</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C20" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C20" s="3">
+        <v>183</v>
+      </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="3">
+        <v>3</v>
+      </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="3">
-        <v>62</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3">
-        <v>62</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C21" s="3"/>
+        <v>60140</v>
+      </c>
+      <c r="C21" s="3">
+        <v>80</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3">
-        <v>31</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>60127</v>
+        <v>60203</v>
       </c>
       <c r="C22" s="3">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="3">
-        <v>6</v>
-      </c>
+      <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1429,25 +1211,21 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3">
-        <v>165</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2">
-        <v>60132</v>
+        <v>60355</v>
       </c>
       <c r="C23" s="3">
-        <v>229</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1455,517 +1233,505 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3">
-        <v>231</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C24" s="3">
-        <v>79</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3">
-        <v>2</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="K24" s="3">
+        <v>314</v>
+      </c>
       <c r="L24" s="3">
-        <v>81</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2">
-        <v>60355</v>
+        <v>60306</v>
       </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>38</v>
+      </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3">
-        <v>263</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>64</v>
-      </c>
-      <c r="K25" s="3"/>
+      <c r="I25" s="3">
+        <v>2</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3">
+        <v>453</v>
+      </c>
       <c r="L25" s="3">
-        <v>327</v>
+        <v>493</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2">
-        <v>60136</v>
+        <v>60355</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>22</v>
+      </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="3">
-        <v>13</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3">
-        <v>13</v>
-      </c>
-      <c r="K26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3">
+        <v>499</v>
+      </c>
       <c r="L26" s="3">
-        <v>26</v>
+        <v>521</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2">
-        <v>60140</v>
+        <v>60136</v>
       </c>
       <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>2</v>
+      </c>
       <c r="E27" s="3"/>
-      <c r="F27" s="3">
-        <v>30</v>
-      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3">
-        <v>12</v>
-      </c>
-      <c r="K27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3">
+        <v>52</v>
+      </c>
       <c r="L27" s="3">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2">
-        <v>60203</v>
+        <v>60140</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>4</v>
+      </c>
       <c r="E28" s="3"/>
-      <c r="F28" s="3">
-        <v>32</v>
-      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3">
-        <v>9</v>
-      </c>
-      <c r="K28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3">
+        <v>122</v>
+      </c>
       <c r="L28" s="3">
-        <v>41</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C29" s="3">
-        <v>218</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3">
-        <v>2</v>
-      </c>
+        <v>60127</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="H29" s="3">
+        <v>25</v>
+      </c>
+      <c r="I29" s="3">
+        <v>2</v>
+      </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3">
-        <v>220</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C30" s="3">
-        <v>247</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3">
-        <v>2</v>
-      </c>
+        <v>60132</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="H30" s="3">
+        <v>111</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3">
-        <v>249</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C31" s="3">
-        <v>183</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3">
+        <v>60139</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
         <v>3</v>
       </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3">
+        <v>53</v>
+      </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3">
-        <v>186</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B32" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C32" s="3">
-        <v>80</v>
-      </c>
-      <c r="D32" s="3"/>
+        <v>60134</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="H32" s="3">
+        <v>78</v>
+      </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2">
-        <v>60203</v>
-      </c>
-      <c r="C33" s="3">
-        <v>39</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="3">
+        <v>122</v>
+      </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3">
-        <v>39</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B34" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C34" s="3">
-        <v>167</v>
-      </c>
-      <c r="D34" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="H34" s="3">
+        <v>155</v>
+      </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="2">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B35" s="2">
-        <v>60134</v>
+        <v>60355</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="3">
-        <v>12</v>
-      </c>
+      <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+      <c r="H35" s="3">
+        <v>232</v>
+      </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="3">
-        <v>339</v>
-      </c>
+      <c r="K35" s="3"/>
       <c r="L35" s="3">
-        <v>351</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B36" s="2">
-        <v>60306</v>
+        <v>60136</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="3">
-        <v>38</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3">
-        <v>2</v>
-      </c>
+      <c r="H36" s="3">
+        <v>44</v>
+      </c>
+      <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="3">
-        <v>480</v>
-      </c>
+      <c r="K36" s="3"/>
       <c r="L36" s="3">
-        <v>520</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B37" s="2">
-        <v>60355</v>
+        <v>60140</v>
       </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="3">
-        <v>22</v>
-      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
+      <c r="H37" s="3">
+        <v>73</v>
+      </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="3">
-        <v>531</v>
-      </c>
+      <c r="K37" s="3"/>
       <c r="L37" s="3">
-        <v>553</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B38" s="2">
-        <v>60136</v>
+        <v>60203</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
+      <c r="H38" s="3">
+        <v>58</v>
+      </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3">
-        <v>52</v>
-      </c>
+      <c r="K38" s="3"/>
       <c r="L38" s="3">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B39" s="2">
-        <v>60140</v>
+        <v>60132</v>
       </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="3">
-        <v>4</v>
-      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="I39" s="3">
+        <v>284</v>
+      </c>
       <c r="J39" s="3"/>
-      <c r="K39" s="3">
-        <v>122</v>
-      </c>
+      <c r="K39" s="3"/>
       <c r="L39" s="3">
-        <v>126</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B40" s="2">
-        <v>60127</v>
+        <v>60134</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="3">
-        <v>2</v>
-      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3">
-        <v>48</v>
-      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="3">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3">
-        <v>52</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B41" s="2">
-        <v>60132</v>
+        <v>60135</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3">
-        <v>2</v>
-      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3">
-        <v>242</v>
-      </c>
+      <c r="H41" s="3"/>
       <c r="I41" s="3">
-        <v>1</v>
+        <v>244</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B42" s="2">
-        <v>60139</v>
+        <v>60140</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>3</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3">
-        <v>95</v>
-      </c>
-      <c r="I42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3">
+        <v>41</v>
+      </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3">
-        <v>98</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B43" s="2">
-        <v>60134</v>
+        <v>60203</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3">
-        <v>1</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3">
-        <v>112</v>
-      </c>
-      <c r="I43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3">
+        <v>51</v>
+      </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3">
-        <v>113</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B44" s="2">
-        <v>60135</v>
+        <v>60306</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3">
-        <v>155</v>
-      </c>
-      <c r="I44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3">
+        <v>215</v>
+      </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3">
-        <v>155</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2">
-        <v>60306</v>
+        <v>60132</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3">
@@ -1973,157 +1739,159 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3">
-        <v>217</v>
-      </c>
-      <c r="I45" s="3"/>
+      <c r="G45" s="3">
+        <v>955</v>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3">
+        <v>2</v>
+      </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3">
-        <v>218</v>
+        <v>958</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B46" s="2">
-        <v>60355</v>
+        <v>60134</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3">
-        <v>348</v>
-      </c>
+      <c r="G46" s="3">
+        <v>419</v>
+      </c>
+      <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3">
-        <v>348</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2">
-        <v>60136</v>
+        <v>60355</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="G47" s="3">
+        <v>620</v>
+      </c>
       <c r="H47" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3">
-        <v>44</v>
+        <v>621</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B48" s="2">
-        <v>60140</v>
+        <v>60306</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3">
-        <v>73</v>
-      </c>
+      <c r="G48" s="3">
+        <v>453</v>
+      </c>
+      <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3">
-        <v>73</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B49" s="2">
-        <v>60203</v>
+        <v>60136</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="3">
-        <v>1</v>
-      </c>
+      <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3">
-        <v>58</v>
-      </c>
+      <c r="G49" s="3">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B50" s="2">
-        <v>60132</v>
+        <v>60140</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
+      <c r="G50" s="3">
+        <v>105</v>
+      </c>
       <c r="H50" s="3"/>
-      <c r="I50" s="3">
-        <v>339</v>
-      </c>
+      <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3">
-        <v>339</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2">
-        <v>60134</v>
+        <v>60203</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="G51" s="3">
+        <v>65</v>
+      </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="3">
-        <v>277</v>
-      </c>
+      <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3">
-        <v>277</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B52" s="2">
-        <v>60135</v>
+        <v>60128</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -2132,20 +1900,20 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3">
-        <v>273</v>
+        <v>2</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3">
-        <v>273</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B53" s="2">
-        <v>60140</v>
+        <v>60129</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -2154,216 +1922,220 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
+      <c r="K53" s="3">
+        <v>1</v>
+      </c>
       <c r="L53" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B54" s="2">
-        <v>60203</v>
+        <v>60131</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3">
+        <v>2</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3">
-        <v>61</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B55" s="2">
-        <v>60306</v>
+        <v>60132</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
+      <c r="H55" s="3">
+        <v>2</v>
+      </c>
       <c r="I55" s="3">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3">
-        <v>255</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B56" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="3">
-        <v>1</v>
-      </c>
+      <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3">
-        <v>955</v>
-      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3">
-        <v>958</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B57" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C57" s="3"/>
+        <v>60136</v>
+      </c>
+      <c r="C57" s="3">
+        <v>11</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3">
-        <v>419</v>
-      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3">
-        <v>419</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B58" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C58" s="3"/>
+        <v>60137</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3">
-        <v>620</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1</v>
-      </c>
-      <c r="I58" s="3"/>
+      <c r="F58" s="3">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3">
+        <v>3</v>
+      </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3">
-        <v>621</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>60306</v>
+        <v>60138</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="3">
-        <v>453</v>
-      </c>
-      <c r="H59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3">
-        <v>453</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>60136</v>
+        <v>60215</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3">
-        <v>19</v>
-      </c>
-      <c r="H60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3">
+        <v>5</v>
+      </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>60140</v>
+        <v>60224</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="3">
-        <v>105</v>
-      </c>
+      <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="I61" s="3">
+        <v>2</v>
+      </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3">
-        <v>105</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>60203</v>
+        <v>60227</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3">
-        <v>65</v>
-      </c>
+      <c r="F62" s="3">
+        <v>2</v>
+      </c>
+      <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -2371,7 +2143,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="2">
-        <v>60128</v>
+        <v>60296</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -2380,12 +2152,12 @@
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -2393,7 +2165,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="2">
-        <v>60129</v>
+        <v>60448</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -2402,14 +2174,12 @@
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J64" s="3"/>
-      <c r="K64" s="3">
-        <v>1</v>
-      </c>
+      <c r="K64" s="3"/>
       <c r="L64" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -2417,7 +2187,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="2">
-        <v>60131</v>
+        <v>60496</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -2427,13 +2197,11 @@
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
-      <c r="I65" s="3">
-        <v>2</v>
-      </c>
+      <c r="I65" s="3"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -2441,307 +2209,59 @@
         <v>60</v>
       </c>
       <c r="B66" s="2">
-        <v>60132</v>
+        <v>60507</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3">
+        <v>1</v>
+      </c>
       <c r="G66" s="3"/>
-      <c r="H66" s="3">
-        <v>2</v>
-      </c>
+      <c r="H66" s="3"/>
       <c r="I66" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="2">
-        <v>60</v>
-      </c>
-      <c r="B67" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3">
-        <v>1</v>
-      </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" s="2">
-        <v>60</v>
-      </c>
-      <c r="B68" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C68" s="3">
-        <v>11</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" s="2">
-        <v>60</v>
-      </c>
-      <c r="B69" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C69" s="3">
-        <v>1</v>
-      </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3">
-        <v>3</v>
-      </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" s="2">
-        <v>60</v>
-      </c>
-      <c r="B70" s="2">
-        <v>60138</v>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3">
-        <v>1</v>
-      </c>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="2">
-        <v>60</v>
-      </c>
-      <c r="B71" s="2">
-        <v>60215</v>
-      </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3">
-        <v>5</v>
-      </c>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="2">
-        <v>60</v>
-      </c>
-      <c r="B72" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3">
-        <v>2</v>
-      </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" s="2">
-        <v>60</v>
-      </c>
-      <c r="B73" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3">
-        <v>2</v>
-      </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="2">
-        <v>60</v>
-      </c>
-      <c r="B74" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3">
+      <c r="A67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="2">
-        <v>60</v>
-      </c>
-      <c r="B75" s="2">
-        <v>60448</v>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3">
-        <v>2</v>
-      </c>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" s="2">
-        <v>60</v>
-      </c>
-      <c r="B76" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3">
-        <v>2</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" s="2">
-        <v>60</v>
-      </c>
-      <c r="B77" s="2">
-        <v>60507</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3">
-        <v>1</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3">
-        <v>1</v>
-      </c>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="4">
-        <v>1413</v>
-      </c>
-      <c r="D78" s="4">
-        <v>239</v>
-      </c>
-      <c r="E78" s="4">
+      <c r="B67" s="2"/>
+      <c r="C67" s="4">
+        <v>1146</v>
+      </c>
+      <c r="D67" s="4">
+        <v>90</v>
+      </c>
+      <c r="E67" s="4">
         <v>16</v>
       </c>
-      <c r="F78" s="4">
-        <v>883</v>
-      </c>
-      <c r="G78" s="4">
-        <v>3042</v>
-      </c>
-      <c r="H78" s="4">
-        <v>1406</v>
-      </c>
-      <c r="I78" s="4">
-        <v>1389</v>
-      </c>
-      <c r="J78" s="4">
+      <c r="F67" s="4">
+        <v>766</v>
+      </c>
+      <c r="G67" s="4">
+        <v>2723</v>
+      </c>
+      <c r="H67" s="4">
+        <v>960</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1123</v>
+      </c>
+      <c r="J67" s="4">
         <v>98</v>
       </c>
-      <c r="K78" s="4">
-        <v>2546</v>
-      </c>
-      <c r="L78" s="4">
-        <v>11032</v>
+      <c r="K67" s="4">
+        <v>2111</v>
+      </c>
+      <c r="L67" s="4">
+        <v>9033</v>
       </c>
     </row>
   </sheetData>
@@ -2751,7 +2271,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2767,16 +2287,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2786,15 +2306,13 @@
       <c r="B2" s="2">
         <v>21082</v>
       </c>
-      <c r="C2" s="3">
-        <v>68</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3">
-        <v>83</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2804,15 +2322,13 @@
       <c r="B3" s="2">
         <v>21234</v>
       </c>
-      <c r="C3" s="3">
-        <v>51</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3">
-        <v>72</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2824,11 +2340,11 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2840,11 +2356,11 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2865,52 +2381,36 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B7" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
+        <v>21246</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B8" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4">
+        <v>54</v>
+      </c>
+      <c r="E8" s="4">
         <v>7</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="4">
-        <v>133</v>
-      </c>
-      <c r="D9" s="4">
-        <v>74</v>
-      </c>
-      <c r="E9" s="4">
-        <v>36</v>
-      </c>
-      <c r="F9" s="4">
-        <v>243</v>
+      <c r="F8" s="4">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2937,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2959,7 +2459,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="4">
@@ -2976,19 +2476,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2996,34 +2495,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>3004</v>
       </c>
@@ -3031,32 +2524,24 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D2" s="3">
         <v>21</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="3">
-        <v>36</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" s="3">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="I2" s="3">
-        <v>210</v>
-      </c>
-      <c r="J2" s="3">
-        <v>42</v>
-      </c>
-      <c r="K2" s="3">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
@@ -3064,32 +2549,24 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D3" s="3">
         <v>60</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>42</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="I3" s="3">
-        <v>221</v>
-      </c>
-      <c r="J3" s="3">
-        <v>74</v>
-      </c>
-      <c r="K3" s="3">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2">
         <v>3006</v>
       </c>
@@ -3103,22 +2580,20 @@
         <v>23</v>
       </c>
       <c r="E4" s="3">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3">
+        <v>14</v>
+      </c>
       <c r="I4" s="3">
-        <v>14</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>3006</v>
       </c>
@@ -3132,94 +2607,44 @@
         <v>20</v>
       </c>
       <c r="E5" s="3">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="F5" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>4</v>
+      </c>
       <c r="I5" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>6</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4">
-        <v>266</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B6" s="2"/>
+      <c r="C6" s="4">
+        <v>181</v>
+      </c>
+      <c r="D6" s="4">
         <v>124</v>
       </c>
-      <c r="E8" s="4">
-        <v>153</v>
-      </c>
-      <c r="F8" s="4">
-        <v>139</v>
-      </c>
-      <c r="G8" s="4">
-        <v>19</v>
-      </c>
-      <c r="H8" s="4">
-        <v>157</v>
-      </c>
-      <c r="I8" s="4">
-        <v>456</v>
-      </c>
-      <c r="J8" s="4">
-        <v>116</v>
-      </c>
-      <c r="K8" s="4">
-        <v>1430</v>
+      <c r="E6" s="4">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4">
+        <v>53</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>155</v>
+      </c>
+      <c r="I6" s="4">
+        <v>529</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="22">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -80,13 +80,7 @@
     <t>SP-HLIN</t>
   </si>
   <si>
-    <t>SP-HMEN</t>
-  </si>
-  <si>
     <t>SP-HWNTR</t>
-  </si>
-  <si>
-    <t>SP-PERFUME</t>
   </si>
   <si>
     <t>SPAIS1</t>
@@ -648,11 +642,11 @@
         <v>21090</v>
       </c>
       <c r="C11" s="3">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3">
-        <v>196</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -661,13 +655,13 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="D12" s="4">
         <v>23</v>
       </c>
       <c r="E12" s="4">
-        <v>219</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -878,10 +872,10 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="L8" s="3">
-        <v>376</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -900,10 +894,10 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L9" s="3">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -922,10 +916,10 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="L10" s="3">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -936,7 +930,7 @@
         <v>60127</v>
       </c>
       <c r="C11" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3">
@@ -949,7 +943,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -960,11 +954,9 @@
         <v>60132</v>
       </c>
       <c r="C12" s="3">
-        <v>115</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3">
         <v>1</v>
       </c>
@@ -975,7 +967,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -986,7 +978,7 @@
         <v>60139</v>
       </c>
       <c r="C13" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3">
@@ -999,7 +991,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1254,10 +1246,10 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L24" s="3">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1280,10 +1272,10 @@
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="L25" s="3">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1304,10 +1296,10 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="L26" s="3">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1373,7 +1365,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I29" s="3">
         <v>2</v>
@@ -1381,7 +1373,7 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1399,7 +1391,7 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I30" s="3">
         <v>1</v>
@@ -1407,7 +1399,7 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1425,13 +1417,13 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1449,13 +1441,13 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1471,13 +1463,13 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1495,13 +1487,13 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1517,13 +1509,13 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1608,12 +1600,12 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1630,12 +1622,12 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1652,12 +1644,12 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -1674,12 +1666,12 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -1696,12 +1688,12 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -1718,12 +1710,12 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3">
-        <v>215</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2234,10 +2226,10 @@
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="4">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="D67" s="4">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E67" s="4">
         <v>16</v>
@@ -2249,19 +2241,19 @@
         <v>2723</v>
       </c>
       <c r="H67" s="4">
-        <v>960</v>
+        <v>916</v>
       </c>
       <c r="I67" s="4">
-        <v>1123</v>
+        <v>1094</v>
       </c>
       <c r="J67" s="4">
         <v>98</v>
       </c>
       <c r="K67" s="4">
-        <v>2111</v>
+        <v>2052</v>
       </c>
       <c r="L67" s="4">
-        <v>9033</v>
+        <v>8883</v>
       </c>
     </row>
   </sheetData>
@@ -2309,10 +2301,10 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2325,10 +2317,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2340,11 +2332,11 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2356,11 +2348,11 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2404,13 +2396,13 @@
         <v>14</v>
       </c>
       <c r="D8" s="4">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E8" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2476,18 +2468,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="2" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2507,16 +2498,10 @@
         <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>3004</v>
       </c>
@@ -2524,24 +2509,20 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3">
         <v>21</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3">
+        <v>70</v>
+      </c>
       <c r="G2" s="3">
-        <v>2</v>
-      </c>
-      <c r="H2" s="3">
-        <v>78</v>
-      </c>
-      <c r="I2" s="3">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
@@ -2549,24 +2530,20 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3">
+        <v>55</v>
+      </c>
       <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <v>59</v>
-      </c>
-      <c r="I3" s="3">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>3006</v>
       </c>
@@ -2580,20 +2557,16 @@
         <v>23</v>
       </c>
       <c r="E4" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3">
-        <v>32</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
         <v>14</v>
       </c>
-      <c r="I4" s="3">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="G4" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>3006</v>
       </c>
@@ -2607,44 +2580,34 @@
         <v>20</v>
       </c>
       <c r="E5" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
         <v>4</v>
       </c>
-      <c r="I5" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="G5" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="D6" s="4">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="4">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="G6" s="4">
-        <v>3</v>
-      </c>
-      <c r="H6" s="4">
-        <v>155</v>
-      </c>
-      <c r="I6" s="4">
-        <v>529</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -18,15 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
   <si>
     <t>WAVE_NBR</t>
   </si>
   <si>
     <t>DEST_ID</t>
-  </si>
-  <si>
-    <t>BSBAS1</t>
   </si>
   <si>
     <t>BSECOM</t>
@@ -39,9 +36,6 @@
   </si>
   <si>
     <t>MCHL</t>
-  </si>
-  <si>
-    <t>MCOS1</t>
   </si>
   <si>
     <t>MFTA</t>
@@ -68,9 +62,6 @@
     <t>SMKID</t>
   </si>
   <si>
-    <t>SMLAD</t>
-  </si>
-  <si>
     <t>SXDMF1</t>
   </si>
   <si>
@@ -78,9 +69,6 @@
   </si>
   <si>
     <t>SP-HLIN</t>
-  </si>
-  <si>
-    <t>SP-HWNTR</t>
   </si>
   <si>
     <t>SPAIS1</t>
@@ -473,16 +461,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,173 +483,143 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
       <c r="B2" s="2">
         <v>21092</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
       <c r="B3" s="2">
         <v>21469</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
         <v>1006</v>
       </c>
       <c r="B4" s="2">
         <v>21085</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
       <c r="D4" s="3">
         <v>2</v>
       </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>1006</v>
       </c>
       <c r="B5" s="2">
         <v>21088</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2">
         <v>1007</v>
       </c>
       <c r="B6" s="2">
         <v>21086</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
       <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="2">
         <v>1007</v>
       </c>
       <c r="B7" s="2">
         <v>21515</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
       <c r="D7" s="3">
         <v>6</v>
       </c>
-      <c r="E7" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>1008</v>
       </c>
       <c r="B8" s="2">
         <v>21087</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>1015</v>
       </c>
       <c r="B9" s="2">
         <v>21089</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
       <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>1015</v>
       </c>
       <c r="B10" s="2">
         <v>21234</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>5</v>
+      </c>
       <c r="D10" s="3">
         <v>5</v>
       </c>
-      <c r="E10" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C11" s="3">
-        <v>166</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4">
-        <v>166</v>
-      </c>
-      <c r="D12" s="4">
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4">
         <v>23</v>
       </c>
-      <c r="E12" s="4">
-        <v>189</v>
+      <c r="D11" s="4">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -671,22 +629,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="8" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="4" max="7" width="6.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,37 +650,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>4</v>
       </c>
@@ -734,19 +687,18 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3">
-        <v>21</v>
-      </c>
+      <c r="F2" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="K2" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>4</v>
       </c>
@@ -756,19 +708,18 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>29</v>
-      </c>
+      <c r="F3" s="3">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="K3" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -778,19 +729,18 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>37</v>
-      </c>
+      <c r="F4" s="3">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="K4" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>14</v>
       </c>
@@ -799,20 +749,19 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
-        <v>169</v>
-      </c>
+      <c r="E5" s="3">
+        <v>114</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="K5" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>14</v>
       </c>
@@ -821,20 +770,19 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
-        <v>99</v>
-      </c>
+      <c r="E6" s="3">
+        <v>66</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="K6" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>14</v>
       </c>
@@ -843,20 +791,19 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>152</v>
-      </c>
+      <c r="E7" s="3">
+        <v>106</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="K7" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>26</v>
       </c>
@@ -870,15 +817,14 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="3">
+        <v>233</v>
+      </c>
       <c r="K8" s="3">
-        <v>353</v>
-      </c>
-      <c r="L8" s="3">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>26</v>
       </c>
@@ -892,15 +838,14 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="J9" s="3">
+        <v>94</v>
+      </c>
       <c r="K9" s="3">
-        <v>132</v>
-      </c>
-      <c r="L9" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>26</v>
       </c>
@@ -914,15 +859,14 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="J10" s="3">
+        <v>120</v>
+      </c>
       <c r="K10" s="3">
-        <v>153</v>
-      </c>
-      <c r="L10" s="3">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
         <v>34</v>
       </c>
@@ -930,23 +874,20 @@
         <v>60127</v>
       </c>
       <c r="C11" s="3">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>6</v>
-      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="K11" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>34</v>
       </c>
@@ -954,23 +895,20 @@
         <v>60132</v>
       </c>
       <c r="C12" s="3">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
+      <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="K12" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>34</v>
       </c>
@@ -978,23 +916,20 @@
         <v>60139</v>
       </c>
       <c r="C13" s="3">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="K13" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>35</v>
       </c>
@@ -1003,22 +938,21 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
         <v>263</v>
       </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
         <v>64</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3">
+      <c r="J14" s="3"/>
+      <c r="K14" s="3">
         <v>327</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>36</v>
       </c>
@@ -1027,22 +961,21 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3">
+      <c r="E15" s="3">
         <v>13</v>
       </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3">
+      <c r="I15" s="3">
         <v>13</v>
       </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3">
+      <c r="J15" s="3"/>
+      <c r="K15" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>36</v>
       </c>
@@ -1051,22 +984,21 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3">
+      <c r="E16" s="3">
         <v>30</v>
       </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3">
+      <c r="I16" s="3">
         <v>12</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
         <v>36</v>
       </c>
@@ -1075,22 +1007,21 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3">
+      <c r="E17" s="3">
         <v>32</v>
       </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3">
+      <c r="I17" s="3">
         <v>9</v>
       </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
         <v>37</v>
       </c>
@@ -1101,20 +1032,17 @@
         <v>218</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="3">
-        <v>2</v>
-      </c>
+      <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="K18" s="3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
         <v>37</v>
       </c>
@@ -1125,20 +1053,17 @@
         <v>247</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="K19" s="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
         <v>37</v>
       </c>
@@ -1149,20 +1074,17 @@
         <v>183</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="3">
-        <v>3</v>
-      </c>
+      <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20" s="3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2">
         <v>38</v>
       </c>
@@ -1179,12 +1101,11 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3">
+      <c r="K21" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:11">
       <c r="A22" s="2">
         <v>38</v>
       </c>
@@ -1201,12 +1122,11 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3">
+      <c r="K22" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:11">
       <c r="A23" s="2">
         <v>38</v>
       </c>
@@ -1223,12 +1143,11 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3">
+      <c r="K23" s="3">
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:11">
       <c r="A24" s="2">
         <v>39</v>
       </c>
@@ -1244,15 +1163,14 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
+      <c r="J24" s="3">
+        <v>249</v>
+      </c>
       <c r="K24" s="3">
-        <v>307</v>
-      </c>
-      <c r="L24" s="3">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2">
         <v>39</v>
       </c>
@@ -1266,19 +1184,18 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3">
+      <c r="H25" s="3">
         <v>2</v>
       </c>
-      <c r="J25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3">
+        <v>376</v>
+      </c>
       <c r="K25" s="3">
-        <v>443</v>
-      </c>
-      <c r="L25" s="3">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="2">
         <v>39</v>
       </c>
@@ -1294,15 +1211,14 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+      <c r="J26" s="3">
+        <v>429</v>
+      </c>
       <c r="K26" s="3">
-        <v>489</v>
-      </c>
-      <c r="L26" s="3">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="2">
         <v>49</v>
       </c>
@@ -1318,15 +1234,14 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="3">
+        <v>52</v>
+      </c>
       <c r="K27" s="3">
-        <v>52</v>
-      </c>
-      <c r="L27" s="3">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:11">
       <c r="A28" s="2">
         <v>49</v>
       </c>
@@ -1342,188 +1257,172 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
+      <c r="J28" s="3">
+        <v>122</v>
+      </c>
       <c r="K28" s="3">
-        <v>122</v>
-      </c>
-      <c r="L28" s="3">
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2">
-        <v>60127</v>
+        <v>60134</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3">
-        <v>22</v>
-      </c>
-      <c r="I29" s="3">
-        <v>2</v>
-      </c>
+      <c r="G29" s="3">
+        <v>69</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="K29" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2">
-        <v>60132</v>
+        <v>60135</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="3">
-        <v>2</v>
-      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3">
-        <v>100</v>
-      </c>
-      <c r="I30" s="3">
-        <v>1</v>
-      </c>
+      <c r="G30" s="3">
+        <v>101</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="K30" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3">
-        <v>45</v>
-      </c>
+      <c r="G31" s="3">
+        <v>134</v>
+      </c>
+      <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="K31" s="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" s="2">
-        <v>60134</v>
+        <v>60355</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
+      <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3">
-        <v>75</v>
-      </c>
+      <c r="G32" s="3">
+        <v>116</v>
+      </c>
+      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="K32" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B33" s="2">
-        <v>60135</v>
+        <v>60136</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3">
-        <v>120</v>
-      </c>
+      <c r="G33" s="3">
+        <v>44</v>
+      </c>
+      <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="K33" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B34" s="2">
-        <v>60306</v>
+        <v>60140</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
+      <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3">
-        <v>149</v>
-      </c>
+      <c r="G34" s="3">
+        <v>73</v>
+      </c>
+      <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="K34" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" s="2">
-        <v>60355</v>
+        <v>60203</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3">
-        <v>221</v>
-      </c>
+      <c r="G35" s="3">
+        <v>58</v>
+      </c>
+      <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="K35" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" s="2">
-        <v>60136</v>
+        <v>60132</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -1531,21 +1430,20 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="K36" s="3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B37" s="2">
-        <v>60140</v>
+        <v>60134</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -1553,523 +1451,498 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="K37" s="3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2">
-        <v>60203</v>
+        <v>60135</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
+      <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="K38" s="3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39" s="2">
-        <v>60132</v>
+        <v>60140</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3">
-        <v>280</v>
-      </c>
+      <c r="H39" s="3">
+        <v>29</v>
+      </c>
+      <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="K39" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B40" s="2">
-        <v>60134</v>
+        <v>60203</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3">
-        <v>255</v>
-      </c>
+      <c r="H40" s="3">
+        <v>33</v>
+      </c>
+      <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="K40" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B41" s="2">
-        <v>60135</v>
+        <v>60306</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3">
-        <v>240</v>
-      </c>
+      <c r="H41" s="3">
+        <v>162</v>
+      </c>
+      <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="K41" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B42" s="2">
-        <v>60140</v>
+        <v>60132</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3">
+        <v>915</v>
+      </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3">
-        <v>40</v>
-      </c>
+      <c r="H42" s="3">
+        <v>2</v>
+      </c>
+      <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="K42" s="3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B43" s="2">
-        <v>60203</v>
+        <v>60134</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3">
+        <v>408</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="3">
-        <v>49</v>
-      </c>
+      <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="K43" s="3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="F44" s="3">
+        <v>589</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1</v>
+      </c>
       <c r="H44" s="3"/>
-      <c r="I44" s="3">
-        <v>198</v>
-      </c>
+      <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="K44" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B45" s="2">
-        <v>60132</v>
+        <v>60306</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="3">
-        <v>1</v>
-      </c>
+      <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3">
-        <v>955</v>
-      </c>
+      <c r="F45" s="3">
+        <v>453</v>
+      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="3">
-        <v>2</v>
-      </c>
+      <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="K45" s="3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B46" s="2">
-        <v>60134</v>
+        <v>60136</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3">
-        <v>419</v>
-      </c>
+      <c r="F46" s="3">
+        <v>19</v>
+      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="K46" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2">
-        <v>60355</v>
+        <v>60140</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3">
-        <v>620</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1</v>
-      </c>
+      <c r="F47" s="3">
+        <v>105</v>
+      </c>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="K47" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B48" s="2">
-        <v>60306</v>
+        <v>60203</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3">
-        <v>453</v>
-      </c>
+      <c r="F48" s="3">
+        <v>65</v>
+      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="K48" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B49" s="2">
-        <v>60136</v>
+        <v>60128</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="3">
-        <v>19</v>
-      </c>
-      <c r="H49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3">
+        <v>2</v>
+      </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="K49" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B50" s="2">
-        <v>60140</v>
+        <v>60129</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3">
-        <v>105</v>
-      </c>
-      <c r="H50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3">
+        <v>5</v>
+      </c>
       <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="J50" s="3">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B51" s="2">
-        <v>60203</v>
+        <v>60131</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="E51" s="3">
+        <v>2</v>
+      </c>
       <c r="F51" s="3"/>
-      <c r="G51" s="3">
-        <v>65</v>
-      </c>
-      <c r="H51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3">
+        <v>2</v>
+      </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="K51" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="2">
         <v>60</v>
       </c>
       <c r="B52" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3">
+      <c r="G52" s="3">
         <v>2</v>
       </c>
+      <c r="H52" s="3">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="K52" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="2">
         <v>60</v>
       </c>
       <c r="B53" s="2">
-        <v>60129</v>
+        <v>60134</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3">
-        <v>5</v>
-      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3">
         <v>1</v>
       </c>
-      <c r="L53" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="2">
         <v>60</v>
       </c>
       <c r="B54" s="2">
-        <v>60131</v>
-      </c>
-      <c r="C54" s="3"/>
+        <v>60136</v>
+      </c>
+      <c r="C54" s="3">
+        <v>11</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3">
-        <v>2</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="3">
-        <v>2</v>
-      </c>
+      <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="K54" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="2">
         <v>60</v>
       </c>
       <c r="B55" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C55" s="3"/>
+        <v>60137</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1</v>
+      </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
+      <c r="E55" s="3">
+        <v>1</v>
+      </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3">
-        <v>2</v>
-      </c>
-      <c r="I55" s="3">
         <v>3</v>
       </c>
+      <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3">
+      <c r="K55" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:11">
       <c r="A56" s="2">
         <v>60</v>
       </c>
       <c r="B56" s="2">
-        <v>60134</v>
+        <v>60138</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="G56" s="3">
+        <v>1</v>
+      </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="3">
-        <v>1</v>
-      </c>
+      <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="K56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="2">
         <v>60</v>
       </c>
       <c r="B57" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C57" s="3">
-        <v>11</v>
-      </c>
+        <v>60215</v>
+      </c>
+      <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="G57" s="3">
+        <v>5</v>
+      </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="K57" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="2">
         <v>60</v>
       </c>
       <c r="B58" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C58" s="3">
-        <v>1</v>
-      </c>
+        <v>60224</v>
+      </c>
+      <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="3">
-        <v>1</v>
-      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3">
-        <v>3</v>
-      </c>
+      <c r="H58" s="3">
+        <v>2</v>
+      </c>
+      <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="K58" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="2">
         <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>60138</v>
+        <v>60227</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+      <c r="E59" s="3">
+        <v>2</v>
+      </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="3">
-        <v>1</v>
-      </c>
+      <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="K59" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="2">
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>60215</v>
+        <v>60296</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -2077,183 +1950,110 @@
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="K60" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>60224</v>
+        <v>60448</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3">
+      <c r="H61" s="3">
         <v>2</v>
       </c>
+      <c r="I61" s="3"/>
       <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3">
+      <c r="K61" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:11">
       <c r="A62" s="2">
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>60227</v>
+        <v>60496</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3">
+      <c r="E62" s="3">
         <v>2</v>
       </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3">
+      <c r="K62" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:11">
       <c r="A63" s="2">
         <v>60</v>
       </c>
       <c r="B63" s="2">
-        <v>60296</v>
+        <v>60507</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
+      <c r="E63" s="3">
+        <v>1</v>
+      </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3">
-        <v>4</v>
-      </c>
+      <c r="H63" s="3">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="2">
-        <v>60</v>
-      </c>
-      <c r="B64" s="2">
-        <v>60448</v>
-      </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3">
+      <c r="K63" s="3">
         <v>2</v>
       </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="2">
-        <v>60</v>
-      </c>
-      <c r="B65" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3">
-        <v>2</v>
-      </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="2">
-        <v>60</v>
-      </c>
-      <c r="B66" s="2">
-        <v>60507</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="4">
-        <v>1129</v>
-      </c>
-      <c r="D67" s="4">
-        <v>89</v>
-      </c>
-      <c r="E67" s="4">
-        <v>16</v>
-      </c>
-      <c r="F67" s="4">
-        <v>766</v>
-      </c>
-      <c r="G67" s="4">
-        <v>2723</v>
-      </c>
-      <c r="H67" s="4">
-        <v>916</v>
-      </c>
-      <c r="I67" s="4">
-        <v>1094</v>
-      </c>
-      <c r="J67" s="4">
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="4">
+        <v>974</v>
+      </c>
+      <c r="D64" s="4">
+        <v>82</v>
+      </c>
+      <c r="E64" s="4">
+        <v>632</v>
+      </c>
+      <c r="F64" s="4">
+        <v>2586</v>
+      </c>
+      <c r="G64" s="4">
+        <v>604</v>
+      </c>
+      <c r="H64" s="4">
+        <v>959</v>
+      </c>
+      <c r="I64" s="4">
         <v>98</v>
       </c>
-      <c r="K67" s="4">
-        <v>2052</v>
-      </c>
-      <c r="L67" s="4">
-        <v>8883</v>
+      <c r="J64" s="4">
+        <v>1676</v>
+      </c>
+      <c r="K64" s="4">
+        <v>7611</v>
       </c>
     </row>
   </sheetData>
@@ -2263,15 +2063,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="6" width="7.7109375" customWidth="1"/>
+    <col min="3" max="5" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2279,130 +2079,73 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B2" s="2">
-        <v>21082</v>
+        <v>21083</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
       <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>21195</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>2008</v>
+        <v>2019</v>
       </c>
       <c r="B4" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C6" s="3">
+        <v>21246</v>
+      </c>
+      <c r="C4" s="3">
         <v>7</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C7" s="3">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4">
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4">
         <v>14</v>
       </c>
-      <c r="D8" s="4">
-        <v>45</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4">
-        <v>61</v>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2172,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2451,7 +2194,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="4">
@@ -2468,17 +2211,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2486,43 +2228,35 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>3004</v>
       </c>
       <c r="B2" s="2">
         <v>21082</v>
       </c>
-      <c r="C2" s="3">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <v>12</v>
+      </c>
       <c r="F2" s="3">
-        <v>70</v>
-      </c>
-      <c r="G2" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
@@ -2530,20 +2264,17 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3">
-        <v>59</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>18</v>
+      </c>
       <c r="F3" s="3">
-        <v>55</v>
-      </c>
-      <c r="G3" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>3006</v>
       </c>
@@ -2551,22 +2282,19 @@
         <v>21083</v>
       </c>
       <c r="C4" s="3">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D4" s="3">
         <v>23</v>
       </c>
       <c r="E4" s="3">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>3006</v>
       </c>
@@ -2574,40 +2302,34 @@
         <v>21457</v>
       </c>
       <c r="C5" s="3">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3">
         <v>20</v>
       </c>
       <c r="E5" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3">
-        <v>4</v>
-      </c>
-      <c r="G5" s="3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="D6" s="4">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="E6" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6" s="4">
-        <v>143</v>
-      </c>
-      <c r="G6" s="4">
-        <v>468</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -7,29 +7,22 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Babyshop" sheetId="1" r:id="rId1"/>
-    <sheet name="Max" sheetId="2" r:id="rId2"/>
-    <sheet name="Shoe Mart" sheetId="3" r:id="rId3"/>
-    <sheet name="Shoexpress" sheetId="4" r:id="rId4"/>
-    <sheet name="Splash" sheetId="5" r:id="rId5"/>
+    <sheet name="Max" sheetId="1" r:id="rId1"/>
+    <sheet name="Shoe Mart" sheetId="2" r:id="rId2"/>
+    <sheet name="Shoexpress" sheetId="3" r:id="rId3"/>
+    <sheet name="Splash" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="14">
   <si>
     <t>WAVE_NBR</t>
   </si>
   <si>
     <t>DEST_ID</t>
-  </si>
-  <si>
-    <t>BSECOM</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
   <si>
     <t>MACC01</t>
@@ -56,19 +49,13 @@
     <t>MXKIDS</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>SMACC</t>
   </si>
   <si>
-    <t>SMKID</t>
-  </si>
-  <si>
     <t>SXDMF1</t>
-  </si>
-  <si>
-    <t>SP-HLAD</t>
-  </si>
-  <si>
-    <t>SP-HLIN</t>
   </si>
   <si>
     <t>SPAIS1</t>
@@ -461,175 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="B2" s="2">
-        <v>21092</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21469</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B8" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C9" s="3">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B10" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="4">
-        <v>23</v>
-      </c>
-      <c r="D11" s="4">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -650,67 +469,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2">
-        <v>60130</v>
+        <v>60134</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3">
-        <v>9</v>
-      </c>
+      <c r="E2" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2">
         <v>60135</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="3">
         <v>7</v>
       </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -721,181 +540,189 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
-        <v>16</v>
-      </c>
+      <c r="E4" s="3">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2">
-        <v>60134</v>
+        <v>60132</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>114</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3">
+        <v>46</v>
+      </c>
       <c r="K5" s="3">
-        <v>114</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2">
         <v>60135</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3">
-        <v>66</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>23</v>
+      </c>
       <c r="K6" s="3">
-        <v>66</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2">
-        <v>60306</v>
+        <v>60139</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>106</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="3">
+        <v>31</v>
+      </c>
       <c r="K7" s="3">
-        <v>106</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2">
-        <v>60132</v>
+        <v>60355</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="E8" s="3">
+        <v>263</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>233</v>
-      </c>
+      <c r="I8" s="3">
+        <v>64</v>
+      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>233</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2">
-        <v>60135</v>
+        <v>60136</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3">
+        <v>13</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3">
-        <v>94</v>
-      </c>
+      <c r="I9" s="3">
+        <v>13</v>
+      </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>94</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2">
-        <v>60139</v>
+        <v>60140</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3">
+        <v>30</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3">
-        <v>120</v>
-      </c>
+      <c r="I10" s="3">
+        <v>12</v>
+      </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>120</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C11" s="3">
-        <v>12</v>
-      </c>
+        <v>60203</v>
+      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3">
+        <v>32</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3">
+        <v>9</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C12" s="3">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -905,18 +732,18 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>10</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2">
-        <v>60139</v>
+        <v>60135</v>
       </c>
       <c r="C13" s="3">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -926,350 +753,342 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3">
-        <v>6</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C14" s="3">
+        <v>141</v>
+      </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="3">
-        <v>263</v>
-      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>64</v>
-      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3">
-        <v>327</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>60140</v>
+      </c>
+      <c r="C15" s="3">
+        <v>80</v>
+      </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>13</v>
-      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>13</v>
-      </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>60203</v>
+      </c>
+      <c r="C16" s="3">
+        <v>39</v>
+      </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="3">
-        <v>30</v>
-      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3">
-        <v>12</v>
-      </c>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2">
-        <v>60203</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C17" s="3">
+        <v>167</v>
+      </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>32</v>
-      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="3">
-        <v>9</v>
-      </c>
+      <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3">
-        <v>41</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2">
         <v>60134</v>
       </c>
-      <c r="C18" s="3">
-        <v>218</v>
-      </c>
-      <c r="D18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3">
+        <v>12</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="3">
+        <v>99</v>
+      </c>
       <c r="K18" s="3">
-        <v>218</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C19" s="3">
-        <v>247</v>
-      </c>
-      <c r="D19" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
+        <v>38</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3">
+        <v>2</v>
+      </c>
       <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3">
+        <v>164</v>
+      </c>
       <c r="K19" s="3">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C20" s="3">
-        <v>183</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3">
+        <v>22</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3">
+        <v>182</v>
+      </c>
       <c r="K20" s="3">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C21" s="3">
-        <v>80</v>
-      </c>
-      <c r="D21" s="3"/>
+        <v>60136</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3">
+        <v>2</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="J21" s="3">
+        <v>52</v>
+      </c>
       <c r="K21" s="3">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2">
-        <v>60203</v>
-      </c>
-      <c r="C22" s="3">
-        <v>39</v>
-      </c>
-      <c r="D22" s="3"/>
+        <v>60140</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
+        <v>4</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="3">
+        <v>122</v>
+      </c>
       <c r="K22" s="3">
-        <v>39</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C23" s="3">
-        <v>167</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3">
+        <v>11</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3">
-        <v>167</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2">
-        <v>60134</v>
+        <v>60135</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="3">
-        <v>12</v>
-      </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3">
+        <v>23</v>
+      </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3">
-        <v>249</v>
-      </c>
+      <c r="J24" s="3"/>
       <c r="K24" s="3">
-        <v>261</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2">
         <v>60306</v>
       </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="3">
-        <v>38</v>
-      </c>
+      <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3">
-        <v>2</v>
-      </c>
+      <c r="G25" s="3">
+        <v>21</v>
+      </c>
+      <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>376</v>
-      </c>
+      <c r="J25" s="3"/>
       <c r="K25" s="3">
-        <v>416</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2">
         <v>60355</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="3">
-        <v>22</v>
-      </c>
+      <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3">
+        <v>73</v>
+      </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3">
-        <v>429</v>
-      </c>
+      <c r="J26" s="3"/>
       <c r="K26" s="3">
-        <v>451</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2">
         <v>60136</v>
       </c>
       <c r="C27" s="3"/>
-      <c r="D27" s="3">
-        <v>2</v>
-      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3">
+        <v>44</v>
+      </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3">
-        <v>52</v>
-      </c>
+      <c r="J27" s="3"/>
       <c r="K27" s="3">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2">
         <v>60140</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="3">
-        <v>4</v>
-      </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3">
+        <v>72</v>
+      </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3">
-        <v>122</v>
-      </c>
+      <c r="J28" s="3"/>
       <c r="K28" s="3">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2">
-        <v>60134</v>
+        <v>60203</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3">
@@ -1278,169 +1097,169 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B30" s="2">
-        <v>60135</v>
+        <v>60132</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3">
-        <v>101</v>
-      </c>
-      <c r="H30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3">
+        <v>198</v>
+      </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3">
-        <v>101</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>60306</v>
+        <v>60134</v>
       </c>
       <c r="C31" s="3"/>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3">
-        <v>134</v>
-      </c>
-      <c r="H31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3">
+        <v>160</v>
+      </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B32" s="2">
-        <v>60355</v>
+        <v>60135</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3">
-        <v>116</v>
-      </c>
-      <c r="H32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3">
+        <v>150</v>
+      </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3">
-        <v>116</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2">
-        <v>60136</v>
+        <v>60140</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3">
-        <v>44</v>
-      </c>
-      <c r="H33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3">
+        <v>21</v>
+      </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2">
-        <v>60140</v>
+        <v>60203</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3">
-        <v>73</v>
-      </c>
-      <c r="H34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3">
+        <v>28</v>
+      </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3">
-        <v>73</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B35" s="2">
-        <v>60203</v>
+        <v>60306</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="3">
-        <v>1</v>
-      </c>
+      <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="3">
-        <v>58</v>
-      </c>
-      <c r="H35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3">
+        <v>135</v>
+      </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3">
-        <v>59</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2">
         <v>60132</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3">
+        <v>773</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3">
-        <v>261</v>
+        <v>2</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3">
-        <v>261</v>
+        <v>776</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B37" s="2">
         <v>60134</v>
@@ -1448,252 +1267,254 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3">
+        <v>335</v>
+      </c>
       <c r="G37" s="3"/>
-      <c r="H37" s="3">
-        <v>235</v>
-      </c>
+      <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3">
-        <v>235</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B38" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3">
-        <v>210</v>
-      </c>
+      <c r="F38" s="3">
+        <v>520</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3">
-        <v>210</v>
+        <v>521</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B39" s="2">
-        <v>60140</v>
+        <v>60306</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3">
+        <v>453</v>
+      </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="3">
-        <v>29</v>
-      </c>
+      <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3">
-        <v>29</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B40" s="2">
-        <v>60203</v>
+        <v>60136</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3">
+        <v>19</v>
+      </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="3">
-        <v>33</v>
-      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B41" s="2">
-        <v>60306</v>
+        <v>60140</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3">
+        <v>105</v>
+      </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="3">
-        <v>162</v>
-      </c>
+      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3">
-        <v>162</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2">
-        <v>60132</v>
+        <v>60203</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3">
-        <v>915</v>
+        <v>65</v>
       </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3">
-        <v>2</v>
-      </c>
+      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3">
-        <v>918</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B43" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>408</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="3">
+        <v>2</v>
+      </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3">
-        <v>408</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B44" s="2">
-        <v>60355</v>
+        <v>60129</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3">
-        <v>589</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3">
         <v>1</v>
       </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
       <c r="K44" s="3">
-        <v>590</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B45" s="2">
-        <v>60306</v>
+        <v>60131</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3">
-        <v>453</v>
-      </c>
+      <c r="E45" s="3">
+        <v>2</v>
+      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
+      <c r="H45" s="3">
+        <v>2</v>
+      </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3">
-        <v>453</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B46" s="2">
-        <v>60136</v>
+        <v>60132</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="3">
-        <v>19</v>
-      </c>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3">
+        <v>2</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3</v>
+      </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B47" s="2">
-        <v>60140</v>
+        <v>60134</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="3">
-        <v>105</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3">
-        <v>105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B48" s="2">
-        <v>60203</v>
-      </c>
-      <c r="C48" s="3"/>
+        <v>60136</v>
+      </c>
+      <c r="C48" s="3">
+        <v>11</v>
+      </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3">
-        <v>65</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -1701,20 +1522,24 @@
         <v>60</v>
       </c>
       <c r="B49" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C49" s="3"/>
+        <v>60137</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="E49" s="3">
+        <v>1</v>
+      </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -1722,22 +1547,20 @@
         <v>60</v>
       </c>
       <c r="B50" s="2">
-        <v>60129</v>
+        <v>60138</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3">
-        <v>5</v>
-      </c>
+      <c r="G50" s="3">
+        <v>1</v>
+      </c>
+      <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3">
+      <c r="J50" s="3"/>
+      <c r="K50" s="3">
         <v>1</v>
-      </c>
-      <c r="K50" s="3">
-        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -1745,22 +1568,20 @@
         <v>60</v>
       </c>
       <c r="B51" s="2">
-        <v>60131</v>
+        <v>60215</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="3">
-        <v>2</v>
-      </c>
+      <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3">
-        <v>2</v>
-      </c>
+      <c r="G51" s="3">
+        <v>5</v>
+      </c>
+      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -1768,22 +1589,20 @@
         <v>60</v>
       </c>
       <c r="B52" s="2">
-        <v>60132</v>
+        <v>60224</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-      <c r="G52" s="3">
+      <c r="G52" s="3"/>
+      <c r="H52" s="3">
         <v>2</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -1791,20 +1610,20 @@
         <v>60</v>
       </c>
       <c r="B53" s="2">
-        <v>60134</v>
+        <v>60227</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+      <c r="E53" s="3">
+        <v>2</v>
+      </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3">
-        <v>1</v>
-      </c>
+      <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -1812,20 +1631,20 @@
         <v>60</v>
       </c>
       <c r="B54" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C54" s="3">
-        <v>11</v>
-      </c>
+        <v>60296</v>
+      </c>
+      <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
+      <c r="H54" s="3">
+        <v>4</v>
+      </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -1833,24 +1652,20 @@
         <v>60</v>
       </c>
       <c r="B55" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C55" s="3">
-        <v>1</v>
-      </c>
+        <v>60448</v>
+      </c>
+      <c r="C55" s="3"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="3">
-        <v>1</v>
-      </c>
+      <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -1858,20 +1673,20 @@
         <v>60</v>
       </c>
       <c r="B56" s="2">
-        <v>60138</v>
+        <v>60496</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
+      <c r="E56" s="3">
+        <v>2</v>
+      </c>
       <c r="F56" s="3"/>
-      <c r="G56" s="3">
-        <v>1</v>
-      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -1879,181 +1694,124 @@
         <v>60</v>
       </c>
       <c r="B57" s="2">
-        <v>60215</v>
+        <v>60507</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
+      <c r="E57" s="3">
+        <v>1</v>
+      </c>
       <c r="F57" s="3"/>
-      <c r="G57" s="3">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="2">
-        <v>60</v>
-      </c>
-      <c r="B58" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3">
-        <v>2</v>
-      </c>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" s="2">
-        <v>60</v>
-      </c>
-      <c r="B59" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3">
-        <v>2</v>
-      </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" s="2">
-        <v>60</v>
-      </c>
-      <c r="B60" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" s="2">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2">
-        <v>60448</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3">
-        <v>2</v>
-      </c>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="A62" s="2">
-        <v>60</v>
-      </c>
-      <c r="B62" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3">
-        <v>2</v>
-      </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="2">
-        <v>60</v>
-      </c>
-      <c r="B63" s="2">
-        <v>60507</v>
-      </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3">
+      <c r="A58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="4">
+        <v>791</v>
+      </c>
+      <c r="D58" s="4">
+        <v>80</v>
+      </c>
+      <c r="E58" s="4">
+        <v>369</v>
+      </c>
+      <c r="F58" s="4">
+        <v>2270</v>
+      </c>
+      <c r="G58" s="4">
+        <v>309</v>
+      </c>
+      <c r="H58" s="4">
+        <v>721</v>
+      </c>
+      <c r="I58" s="4">
+        <v>98</v>
+      </c>
+      <c r="J58" s="4">
+        <v>720</v>
+      </c>
+      <c r="K58" s="4">
+        <v>5358</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="4" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3">
-        <v>1</v>
-      </c>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="4">
-        <v>974</v>
-      </c>
-      <c r="D64" s="4">
-        <v>82</v>
-      </c>
-      <c r="E64" s="4">
-        <v>632</v>
-      </c>
-      <c r="F64" s="4">
-        <v>2586</v>
-      </c>
-      <c r="G64" s="4">
-        <v>604</v>
-      </c>
-      <c r="H64" s="4">
-        <v>959</v>
-      </c>
-      <c r="I64" s="4">
-        <v>98</v>
-      </c>
-      <c r="J64" s="4">
-        <v>1676</v>
-      </c>
-      <c r="K64" s="4">
-        <v>7611</v>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B2" s="2">
+        <v>21195</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2062,98 +1820,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="5" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B2" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C3" s="3">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C4" s="3">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2172,10 +1838,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2194,7 +1860,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="4">
@@ -2209,18 +1875,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2228,35 +1894,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
         <v>3004</v>
       </c>
       <c r="B2" s="2">
         <v>21082</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3">
+      <c r="C2" s="3">
         <v>12</v>
       </c>
-      <c r="F2" s="3">
+      <c r="D2" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
@@ -2264,17 +1922,13 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
         <v>18</v>
       </c>
-      <c r="F3" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="D3" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
         <v>3006</v>
       </c>
@@ -2282,19 +1936,13 @@
         <v>21083</v>
       </c>
       <c r="C4" s="3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3">
         <v>14</v>
       </c>
-      <c r="F4" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>3006</v>
       </c>
@@ -2302,34 +1950,22 @@
         <v>21457</v>
       </c>
       <c r="C5" s="3">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="3">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="D6" s="4">
-        <v>43</v>
-      </c>
-      <c r="E6" s="4">
         <v>48</v>
-      </c>
-      <c r="F6" s="4">
-        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -10,14 +10,13 @@
     <sheet name="Max" sheetId="1" r:id="rId1"/>
     <sheet name="Shoe Mart" sheetId="2" r:id="rId2"/>
     <sheet name="Shoexpress" sheetId="3" r:id="rId3"/>
-    <sheet name="Splash" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="13">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -56,9 +55,6 @@
   </si>
   <si>
     <t>SXDMF1</t>
-  </si>
-  <si>
-    <t>SPAIS1</t>
   </si>
 </sst>
 </file>
@@ -448,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -498,15 +494,15 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2">
-        <v>60134</v>
+        <v>60355</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -514,464 +510,460 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2">
-        <v>60135</v>
+        <v>60136</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>13</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2">
-        <v>60306</v>
+        <v>60140</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>12</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2">
-        <v>60132</v>
+        <v>60203</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="3">
+        <v>32</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>46</v>
-      </c>
+      <c r="I5" s="3">
+        <v>9</v>
+      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>60134</v>
+      </c>
+      <c r="C6" s="3">
+        <v>68</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3">
-        <v>23</v>
-      </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="3">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C7" s="3">
+        <v>68</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>31</v>
-      </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="3">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C8" s="3">
+        <v>47</v>
+      </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="3">
-        <v>263</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>64</v>
-      </c>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>327</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>60140</v>
+      </c>
+      <c r="C9" s="3">
+        <v>80</v>
+      </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="3">
-        <v>13</v>
-      </c>
+      <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>13</v>
-      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>60203</v>
+      </c>
+      <c r="C10" s="3">
+        <v>39</v>
+      </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="3">
-        <v>30</v>
-      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3">
-        <v>12</v>
-      </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2">
-        <v>60203</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C11" s="3">
+        <v>167</v>
+      </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>32</v>
-      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>9</v>
-      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3">
-        <v>41</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2">
         <v>60134</v>
       </c>
-      <c r="C12" s="3">
-        <v>180</v>
-      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="3">
+        <v>28</v>
+      </c>
       <c r="K12" s="3">
-        <v>180</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C13" s="3">
-        <v>172</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3">
+        <v>3</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3">
+        <v>2</v>
+      </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3">
+        <v>48</v>
+      </c>
       <c r="K13" s="3">
-        <v>172</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C14" s="3">
-        <v>141</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>58</v>
+      </c>
       <c r="K14" s="3">
-        <v>141</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C15" s="3">
-        <v>80</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>60136</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3">
+        <v>38</v>
+      </c>
       <c r="K15" s="3">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
-        <v>60203</v>
-      </c>
-      <c r="C16" s="3">
-        <v>39</v>
-      </c>
+        <v>60140</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>98</v>
+      </c>
       <c r="K16" s="3">
-        <v>39</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C17" s="3">
-        <v>167</v>
-      </c>
+        <v>60136</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3">
+        <v>12</v>
+      </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3">
-        <v>167</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
-        <v>60134</v>
+        <v>60140</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="3">
-        <v>12</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3">
+        <v>19</v>
+      </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3">
-        <v>99</v>
-      </c>
+      <c r="J18" s="3"/>
       <c r="K18" s="3">
-        <v>111</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
-        <v>60306</v>
+        <v>60203</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3">
-        <v>2</v>
-      </c>
+      <c r="G19" s="3">
+        <v>12</v>
+      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="3">
-        <v>164</v>
-      </c>
+      <c r="J19" s="3"/>
       <c r="K19" s="3">
-        <v>204</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2">
-        <v>60355</v>
+        <v>60132</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3">
-        <v>22</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="3">
+        <v>90</v>
+      </c>
       <c r="I20" s="3"/>
-      <c r="J20" s="3">
-        <v>182</v>
-      </c>
+      <c r="J20" s="3"/>
       <c r="K20" s="3">
-        <v>204</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B21" s="2">
-        <v>60136</v>
+        <v>60134</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="3">
-        <v>2</v>
-      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="3">
+        <v>99</v>
+      </c>
       <c r="I21" s="3"/>
-      <c r="J21" s="3">
-        <v>52</v>
-      </c>
+      <c r="J21" s="3"/>
       <c r="K21" s="3">
-        <v>54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2">
-        <v>60140</v>
+        <v>60135</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="3">
-        <v>4</v>
-      </c>
+      <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="3">
+        <v>78</v>
+      </c>
       <c r="I22" s="3"/>
-      <c r="J22" s="3">
-        <v>122</v>
-      </c>
+      <c r="J22" s="3"/>
       <c r="K22" s="3">
-        <v>126</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2">
-        <v>60134</v>
+        <v>60140</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
         <v>11</v>
       </c>
-      <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3">
@@ -980,28 +972,28 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2">
-        <v>60135</v>
+        <v>60203</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3">
-        <v>23</v>
-      </c>
-      <c r="H24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
+        <v>14</v>
+      </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2">
         <v>60306</v>
@@ -1010,171 +1002,175 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3">
-        <v>21</v>
-      </c>
-      <c r="H25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
+        <v>64</v>
+      </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2">
-        <v>60355</v>
+        <v>60132</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3">
-        <v>73</v>
-      </c>
-      <c r="H26" s="3"/>
+      <c r="F26" s="3">
+        <v>624</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
+        <v>2</v>
+      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3">
-        <v>73</v>
+        <v>627</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2">
-        <v>60136</v>
+        <v>60134</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3">
-        <v>44</v>
-      </c>
+      <c r="F27" s="3">
+        <v>281</v>
+      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3">
-        <v>44</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2">
-        <v>60140</v>
+        <v>60355</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3">
+        <v>387</v>
+      </c>
       <c r="G28" s="3">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3">
-        <v>72</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2">
-        <v>60203</v>
+        <v>60306</v>
       </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
+      <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3">
-        <v>56</v>
-      </c>
+      <c r="F29" s="3">
+        <v>377</v>
+      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3">
-        <v>57</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2">
-        <v>60132</v>
+        <v>60136</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3">
+        <v>17</v>
+      </c>
       <c r="G30" s="3"/>
-      <c r="H30" s="3">
-        <v>198</v>
-      </c>
+      <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3">
-        <v>198</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2">
-        <v>60134</v>
+        <v>60140</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3">
+        <v>91</v>
+      </c>
       <c r="G31" s="3"/>
-      <c r="H31" s="3">
-        <v>160</v>
-      </c>
+      <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3">
-        <v>160</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2">
-        <v>60135</v>
+        <v>60203</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3">
+        <v>57</v>
+      </c>
       <c r="G32" s="3"/>
-      <c r="H32" s="3">
-        <v>150</v>
-      </c>
+      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3">
-        <v>150</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2">
-        <v>60140</v>
+        <v>60128</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1182,20 +1178,20 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B34" s="2">
-        <v>60203</v>
+        <v>60129</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -1203,63 +1199,65 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="J34" s="3">
+        <v>1</v>
+      </c>
       <c r="K34" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B35" s="2">
-        <v>60306</v>
+        <v>60131</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="E35" s="3">
+        <v>2</v>
+      </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3">
-        <v>135</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B36" s="2">
         <v>60132</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3">
-        <v>773</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3">
+        <v>2</v>
+      </c>
       <c r="H36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3">
-        <v>776</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B37" s="2">
         <v>60134</v>
@@ -1267,122 +1265,124 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3">
-        <v>335</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
+      <c r="H37" s="3">
+        <v>1</v>
+      </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3">
-        <v>335</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B38" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C38" s="3"/>
+        <v>60136</v>
+      </c>
+      <c r="C38" s="3">
+        <v>11</v>
+      </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="3">
-        <v>520</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3">
-        <v>521</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B39" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C39" s="3"/>
+        <v>60137</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1</v>
+      </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3">
-        <v>453</v>
-      </c>
+      <c r="E39" s="3">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
+      <c r="H39" s="3">
+        <v>3</v>
+      </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3">
-        <v>453</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B40" s="2">
-        <v>60136</v>
+        <v>60138</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>19</v>
-      </c>
-      <c r="G40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B41" s="2">
-        <v>60140</v>
+        <v>60215</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>105</v>
-      </c>
-      <c r="G41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3">
+        <v>5</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B42" s="2">
-        <v>60203</v>
+        <v>60224</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>65</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="3">
+        <v>2</v>
+      </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1390,16 +1390,16 @@
         <v>60</v>
       </c>
       <c r="B43" s="2">
-        <v>60128</v>
+        <v>60227</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="E43" s="3">
+        <v>2</v>
+      </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3">
-        <v>2</v>
-      </c>
+      <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3">
@@ -1411,7 +1411,7 @@
         <v>60</v>
       </c>
       <c r="B44" s="2">
-        <v>60129</v>
+        <v>60296</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -1419,14 +1419,12 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I44" s="3"/>
-      <c r="J44" s="3">
-        <v>1</v>
-      </c>
+      <c r="J44" s="3"/>
       <c r="K44" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -1434,13 +1432,11 @@
         <v>60</v>
       </c>
       <c r="B45" s="2">
-        <v>60131</v>
+        <v>60448</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="3">
-        <v>2</v>
-      </c>
+      <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3">
@@ -1449,7 +1445,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -1457,22 +1453,20 @@
         <v>60</v>
       </c>
       <c r="B46" s="2">
-        <v>60132</v>
+        <v>60496</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="E46" s="3">
+        <v>2</v>
+      </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="3">
-        <v>2</v>
-      </c>
-      <c r="H46" s="3">
-        <v>3</v>
-      </c>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -1480,11 +1474,13 @@
         <v>60</v>
       </c>
       <c r="B47" s="2">
-        <v>60134</v>
+        <v>60507</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="E47" s="3">
+        <v>1</v>
+      </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3">
@@ -1493,256 +1489,40 @@
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="2">
-        <v>60</v>
-      </c>
-      <c r="B48" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C48" s="3">
-        <v>11</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="2">
-        <v>60</v>
-      </c>
-      <c r="B49" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C49" s="3">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="2">
-        <v>60</v>
-      </c>
-      <c r="B50" s="2">
-        <v>60138</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3">
-        <v>1</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="2">
-        <v>60</v>
-      </c>
-      <c r="B51" s="2">
-        <v>60215</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3">
-        <v>5</v>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="2">
-        <v>60</v>
-      </c>
-      <c r="B52" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3">
-        <v>2</v>
-      </c>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="2">
-        <v>60</v>
-      </c>
-      <c r="B53" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3">
-        <v>2</v>
-      </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="2">
-        <v>60</v>
-      </c>
-      <c r="B54" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="2">
-        <v>60</v>
-      </c>
-      <c r="B55" s="2">
-        <v>60448</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3">
-        <v>2</v>
-      </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="2">
-        <v>60</v>
-      </c>
-      <c r="B56" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3">
-        <v>2</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="2">
-        <v>60</v>
-      </c>
-      <c r="B57" s="2">
-        <v>60507</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3">
-        <v>1</v>
-      </c>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" s="2" t="s">
+      <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="4">
-        <v>791</v>
-      </c>
-      <c r="D58" s="4">
-        <v>80</v>
-      </c>
-      <c r="E58" s="4">
-        <v>369</v>
-      </c>
-      <c r="F58" s="4">
-        <v>2270</v>
-      </c>
-      <c r="G58" s="4">
-        <v>309</v>
-      </c>
-      <c r="H58" s="4">
-        <v>721</v>
-      </c>
-      <c r="I58" s="4">
-        <v>98</v>
-      </c>
-      <c r="J58" s="4">
-        <v>720</v>
-      </c>
-      <c r="K58" s="4">
-        <v>5358</v>
+      <c r="B48" s="2"/>
+      <c r="C48" s="4">
+        <v>481</v>
+      </c>
+      <c r="D48" s="4">
+        <v>8</v>
+      </c>
+      <c r="E48" s="4">
+        <v>243</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1834</v>
+      </c>
+      <c r="G48" s="4">
+        <v>52</v>
+      </c>
+      <c r="H48" s="4">
+        <v>385</v>
+      </c>
+      <c r="I48" s="4">
+        <v>34</v>
+      </c>
+      <c r="J48" s="4">
+        <v>271</v>
+      </c>
+      <c r="K48" s="4">
+        <v>3308</v>
       </c>
     </row>
   </sheetData>
@@ -1873,102 +1653,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2">
-        <v>3004</v>
-      </c>
-      <c r="B2" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C2" s="3">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
-        <v>3004</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C3" s="3">
-        <v>18</v>
-      </c>
-      <c r="D3" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2">
-        <v>3006</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C4" s="3">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2">
-        <v>3006</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="46">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>MFTA</t>
-  </si>
-  <si>
-    <t>MHOM</t>
   </si>
   <si>
     <t>MHOM1</t>
@@ -726,13 +723,13 @@
         <v>21082</v>
       </c>
       <c r="C6" s="3">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="D6" s="3">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E6" s="3">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="F6" s="3">
         <v>5</v>
@@ -746,16 +743,14 @@
       <c r="I6" s="3">
         <v>49</v>
       </c>
-      <c r="J6" s="3">
-        <v>6</v>
-      </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3">
         <v>99</v>
       </c>
       <c r="N6" s="3">
-        <v>1592</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -766,13 +761,13 @@
         <v>21469</v>
       </c>
       <c r="C7" s="3">
-        <v>748</v>
+        <v>726</v>
       </c>
       <c r="D7" s="3">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E7" s="3">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -786,16 +781,14 @@
       <c r="I7" s="3">
         <v>6</v>
       </c>
-      <c r="J7" s="3">
-        <v>14</v>
-      </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3">
         <v>37</v>
       </c>
       <c r="N7" s="3">
-        <v>1600</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -882,14 +875,14 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L10" s="3">
         <v>9</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -934,12 +927,12 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -950,7 +943,7 @@
         <v>21085</v>
       </c>
       <c r="C13" s="3">
-        <v>550</v>
+        <v>511</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -961,7 +954,7 @@
         <v>12</v>
       </c>
       <c r="H13" s="3">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="I13" s="3">
         <v>17</v>
@@ -970,10 +963,10 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N13" s="3">
-        <v>669</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -984,7 +977,7 @@
         <v>21088</v>
       </c>
       <c r="C14" s="3">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -995,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="3">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3">
         <v>21</v>
@@ -1004,10 +997,10 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N14" s="3">
-        <v>467</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1018,7 +1011,7 @@
         <v>21087</v>
       </c>
       <c r="C15" s="3">
-        <v>349</v>
+        <v>242</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1030,14 +1023,14 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3">
-        <v>369</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1048,7 +1041,7 @@
         <v>21229</v>
       </c>
       <c r="C16" s="3">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1060,14 +1053,14 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3">
-        <v>262</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1136,7 +1129,7 @@
         <v>119</v>
       </c>
       <c r="E19" s="3">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F19" s="3">
         <v>2</v>
@@ -1159,7 +1152,7 @@
         <v>25</v>
       </c>
       <c r="N19" s="3">
-        <v>1480</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1176,7 +1169,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1191,7 +1184,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3">
-        <v>299</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1552,13 +1545,13 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="4">
-        <v>6474</v>
+        <v>6204</v>
       </c>
       <c r="D31" s="4">
-        <v>1430</v>
+        <v>1403</v>
       </c>
       <c r="E31" s="4">
-        <v>2031</v>
+        <v>1918</v>
       </c>
       <c r="F31" s="4">
         <v>84</v>
@@ -1567,25 +1560,25 @@
         <v>44</v>
       </c>
       <c r="H31" s="4">
-        <v>4604</v>
+        <v>4532</v>
       </c>
       <c r="I31" s="4">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="J31" s="4">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="K31" s="4">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L31" s="4">
         <v>10</v>
       </c>
       <c r="M31" s="4">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="N31" s="4">
-        <v>15615</v>
+        <v>15057</v>
       </c>
     </row>
   </sheetData>
@@ -1648,7 +1641,7 @@
         <v>21087</v>
       </c>
       <c r="C2" s="3">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -1659,7 +1652,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3">
-        <v>212</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1672,16 +1665,14 @@
       <c r="C3" s="3">
         <v>21</v>
       </c>
-      <c r="D3" s="3">
-        <v>21</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1760,13 +1751,13 @@
         <v>21229</v>
       </c>
       <c r="C7" s="3">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="D7" s="3">
         <v>37</v>
       </c>
       <c r="E7" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
@@ -1775,7 +1766,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>536</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1794,16 +1785,14 @@
       <c r="E8" s="3">
         <v>19</v>
       </c>
-      <c r="F8" s="3">
-        <v>6</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3">
         <v>8</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1851,7 +1840,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G10" s="3">
         <v>5</v>
@@ -1859,7 +1848,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1883,11 +1872,9 @@
         <v>6</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>9</v>
-      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1912,10 +1899,10 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3">
-        <v>300</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1941,11 +1928,9 @@
         <v>2</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="3">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1969,11 +1954,11 @@
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3">
-        <v>351</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1997,13 +1982,13 @@
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3">
         <v>3</v>
       </c>
       <c r="J15" s="3">
-        <v>863</v>
+        <v>855</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2086,10 +2071,10 @@
         <v>40</v>
       </c>
       <c r="I18" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J18" s="3">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2224,28 +2209,28 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="4">
-        <v>3050</v>
+        <v>2947</v>
       </c>
       <c r="D24" s="4">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="E24" s="4">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="F24" s="4">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="G24" s="4">
         <v>51</v>
       </c>
       <c r="H24" s="4">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="I24" s="4">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="J24" s="4">
-        <v>5045</v>
+        <v>4776</v>
       </c>
     </row>
   </sheetData>
@@ -2255,7 +2240,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2263,16 +2248,16 @@
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="6.7109375" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="7" width="6.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="10" width="6.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2310,13 +2295,10 @@
         <v>30</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -2334,15 +2316,14 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="L2" s="3">
+        <v>106</v>
+      </c>
       <c r="M2" s="3">
-        <v>135</v>
-      </c>
-      <c r="N2" s="3">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2360,15 +2341,14 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>130</v>
+      </c>
       <c r="M3" s="3">
-        <v>215</v>
-      </c>
-      <c r="N3" s="3">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -2384,19 +2364,18 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3">
+      <c r="J4" s="3">
         <v>1</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
+        <v>87</v>
+      </c>
       <c r="M4" s="3">
-        <v>158</v>
-      </c>
-      <c r="N4" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2414,15 +2393,14 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>178</v>
+      </c>
       <c r="M5" s="3">
-        <v>199</v>
-      </c>
-      <c r="N5" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -2440,15 +2418,14 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>184</v>
+      </c>
       <c r="M6" s="3">
-        <v>230</v>
-      </c>
-      <c r="N6" s="3">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2466,15 +2443,14 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>154</v>
+      </c>
       <c r="M7" s="3">
-        <v>179</v>
-      </c>
-      <c r="N7" s="3">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -2486,19 +2462,18 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>118</v>
-      </c>
+      <c r="H8" s="3">
+        <v>71</v>
+      </c>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="M8" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -2510,19 +2485,18 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>65</v>
-      </c>
+      <c r="H9" s="3">
+        <v>47</v>
+      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="M9" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="2">
         <v>4</v>
       </c>
@@ -2534,19 +2508,18 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3">
-        <v>69</v>
-      </c>
+      <c r="H10" s="3">
+        <v>40</v>
+      </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="M10" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2">
         <v>5</v>
       </c>
@@ -2558,21 +2531,20 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>172</v>
-      </c>
+      <c r="H11" s="3">
+        <v>160</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
       <c r="M11" s="3">
-        <v>1</v>
-      </c>
-      <c r="N11" s="3">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2">
         <v>5</v>
       </c>
@@ -2584,21 +2556,20 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>237</v>
+      </c>
       <c r="I12" s="3">
-        <v>257</v>
-      </c>
-      <c r="J12" s="3">
         <v>1</v>
       </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="M12" s="3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2">
         <v>5</v>
       </c>
@@ -2612,21 +2583,20 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>133</v>
-      </c>
+      <c r="H13" s="3">
+        <v>116</v>
+      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
       <c r="M13" s="3">
-        <v>1</v>
-      </c>
-      <c r="N13" s="3">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2">
         <v>6</v>
       </c>
@@ -2638,19 +2608,18 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
         <v>207</v>
       </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3">
+      <c r="M14" s="3">
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:13">
       <c r="A15" s="2">
         <v>6</v>
       </c>
@@ -2662,19 +2631,18 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
+      <c r="H15" s="3">
         <v>184</v>
       </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3">
+      <c r="M15" s="3">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:13">
       <c r="A16" s="2">
         <v>6</v>
       </c>
@@ -2686,19 +2654,18 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3">
+      <c r="H16" s="3">
         <v>216</v>
       </c>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3">
+      <c r="M16" s="3">
         <v>216</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:13">
       <c r="A17" s="2">
         <v>7</v>
       </c>
@@ -2712,17 +2679,16 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3">
-        <v>55</v>
-      </c>
+      <c r="J17" s="3">
+        <v>48</v>
+      </c>
+      <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="M17" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2">
         <v>7</v>
       </c>
@@ -2736,17 +2702,16 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3">
-        <v>36</v>
-      </c>
+      <c r="J18" s="3">
+        <v>34</v>
+      </c>
+      <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="M18" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2">
         <v>7</v>
       </c>
@@ -2758,21 +2723,20 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3">
+      <c r="H19" s="3">
         <v>1</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3">
-        <v>181</v>
-      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3">
+        <v>159</v>
+      </c>
+      <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="M19" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2">
         <v>8</v>
       </c>
@@ -2786,17 +2750,16 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3">
-        <v>53</v>
-      </c>
+      <c r="J20" s="3">
+        <v>51</v>
+      </c>
+      <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="M20" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2">
         <v>8</v>
       </c>
@@ -2810,17 +2773,16 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3">
-        <v>95</v>
-      </c>
+      <c r="J21" s="3">
+        <v>93</v>
+      </c>
+      <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="M21" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2">
         <v>8</v>
       </c>
@@ -2834,17 +2796,16 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3">
-        <v>168</v>
-      </c>
+      <c r="J22" s="3">
+        <v>158</v>
+      </c>
+      <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="M22" s="3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2">
         <v>9</v>
       </c>
@@ -2858,17 +2819,16 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3">
+      <c r="J23" s="3">
         <v>215</v>
       </c>
+      <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3">
+      <c r="M23" s="3">
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:13">
       <c r="A24" s="2">
         <v>9</v>
       </c>
@@ -2882,17 +2842,16 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3">
+      <c r="J24" s="3">
         <v>251</v>
       </c>
+      <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3">
+      <c r="M24" s="3">
         <v>251</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:13">
       <c r="A25" s="2">
         <v>9</v>
       </c>
@@ -2906,17 +2865,16 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3">
+      <c r="J25" s="3">
         <v>126</v>
       </c>
+      <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3">
+      <c r="M25" s="3">
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:13">
       <c r="A26" s="2">
         <v>10</v>
       </c>
@@ -2929,20 +2887,19 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3">
+        <v>211</v>
+      </c>
       <c r="J26" s="3">
-        <v>266</v>
-      </c>
-      <c r="K26" s="3">
         <v>3</v>
       </c>
+      <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="M26" s="3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2">
         <v>10</v>
       </c>
@@ -2955,18 +2912,17 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3">
-        <v>115</v>
-      </c>
+      <c r="I27" s="3">
+        <v>80</v>
+      </c>
+      <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="M27" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2">
         <v>10</v>
       </c>
@@ -2979,18 +2935,17 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3">
-        <v>86</v>
-      </c>
+      <c r="I28" s="3">
+        <v>70</v>
+      </c>
+      <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="M28" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="2">
         <v>11</v>
       </c>
@@ -3003,18 +2958,17 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3">
-        <v>172</v>
-      </c>
+      <c r="I29" s="3">
+        <v>167</v>
+      </c>
+      <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="M29" s="3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2">
         <v>11</v>
       </c>
@@ -3029,18 +2983,17 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3">
-        <v>306</v>
-      </c>
+      <c r="I30" s="3">
+        <v>289</v>
+      </c>
+      <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="M30" s="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2">
         <v>11</v>
       </c>
@@ -3053,18 +3006,17 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3">
-        <v>187</v>
-      </c>
+      <c r="I31" s="3">
+        <v>175</v>
+      </c>
+      <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="M31" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2">
         <v>12</v>
       </c>
@@ -3077,20 +3029,19 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="I32" s="3">
+        <v>186</v>
+      </c>
       <c r="J32" s="3">
-        <v>186</v>
-      </c>
-      <c r="K32" s="3">
         <v>1</v>
       </c>
+      <c r="K32" s="3"/>
       <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3">
+      <c r="M32" s="3">
         <v>187</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:13">
       <c r="A33" s="2">
         <v>12</v>
       </c>
@@ -3103,18 +3054,17 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3">
+      <c r="I33" s="3">
         <v>154</v>
       </c>
+      <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3">
+      <c r="M33" s="3">
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:13">
       <c r="A34" s="2">
         <v>12</v>
       </c>
@@ -3127,20 +3077,19 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="I34" s="3">
+        <v>165</v>
+      </c>
       <c r="J34" s="3">
-        <v>165</v>
-      </c>
-      <c r="K34" s="3">
         <v>1</v>
       </c>
+      <c r="K34" s="3"/>
       <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3">
+      <c r="M34" s="3">
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:13">
       <c r="A35" s="2">
         <v>13</v>
       </c>
@@ -3151,7 +3100,7 @@
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -3159,12 +3108,11 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="M35" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2">
         <v>13</v>
       </c>
@@ -3175,7 +3123,7 @@
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -3183,12 +3131,11 @@
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="M36" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2">
         <v>13</v>
       </c>
@@ -3199,7 +3146,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -3207,12 +3154,11 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="M37" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2">
         <v>14</v>
       </c>
@@ -3223,22 +3169,21 @@
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3">
+      <c r="K38" s="3">
         <v>28</v>
       </c>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="L38" s="3"/>
+      <c r="M38" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2">
         <v>14</v>
       </c>
@@ -3249,22 +3194,21 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3">
+      <c r="K39" s="3">
         <v>37</v>
       </c>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2">
         <v>14</v>
       </c>
@@ -3275,22 +3219,21 @@
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3">
+      <c r="K40" s="3">
         <v>26</v>
       </c>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2">
         <v>15</v>
       </c>
@@ -3307,16 +3250,15 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3">
+      <c r="K41" s="3">
         <v>30</v>
       </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3">
+      <c r="L41" s="3"/>
+      <c r="M41" s="3">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:13">
       <c r="A42" s="2">
         <v>15</v>
       </c>
@@ -3333,16 +3275,15 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3">
+      <c r="K42" s="3">
         <v>20</v>
       </c>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3">
+      <c r="L42" s="3"/>
+      <c r="M42" s="3">
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:13">
       <c r="A43" s="2">
         <v>15</v>
       </c>
@@ -3359,16 +3300,15 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3">
+      <c r="K43" s="3">
         <v>19</v>
       </c>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3">
+      <c r="L43" s="3"/>
+      <c r="M43" s="3">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:13">
       <c r="A44" s="2">
         <v>16</v>
       </c>
@@ -3376,7 +3316,7 @@
         <v>60137</v>
       </c>
       <c r="C44" s="3">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3">
@@ -3389,12 +3329,11 @@
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="M44" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2">
         <v>16</v>
       </c>
@@ -3402,7 +3341,7 @@
         <v>60224</v>
       </c>
       <c r="C45" s="3">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3">
@@ -3415,12 +3354,11 @@
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="M45" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2">
         <v>16</v>
       </c>
@@ -3428,7 +3366,7 @@
         <v>60227</v>
       </c>
       <c r="C46" s="3">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3439,12 +3377,11 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="M46" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2">
         <v>17</v>
       </c>
@@ -3465,12 +3402,11 @@
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3">
+      <c r="M47" s="3">
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:13">
       <c r="A48" s="2">
         <v>17</v>
       </c>
@@ -3491,12 +3427,11 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3">
+      <c r="M48" s="3">
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:13">
       <c r="A49" s="2">
         <v>17</v>
       </c>
@@ -3515,12 +3450,11 @@
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3">
+      <c r="M49" s="3">
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:13">
       <c r="A50" s="2">
         <v>18</v>
       </c>
@@ -3541,12 +3475,11 @@
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3">
+      <c r="M50" s="3">
         <v>252</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:13">
       <c r="A51" s="2">
         <v>18</v>
       </c>
@@ -3565,12 +3498,11 @@
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3">
+      <c r="M51" s="3">
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:13">
       <c r="A52" s="2">
         <v>18</v>
       </c>
@@ -3591,291 +3523,279 @@
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3">
+      <c r="M52" s="3">
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:13">
       <c r="A53" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B53" s="2">
-        <v>60127</v>
+        <v>60138</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="M53" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B54" s="2">
-        <v>60128</v>
+        <v>60224</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="M54" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B55" s="2">
-        <v>60496</v>
+        <v>60127</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
+      <c r="K55" s="3">
+        <v>4</v>
+      </c>
       <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="M55" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B56" s="2">
-        <v>60138</v>
+        <v>60128</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="3">
-        <v>4</v>
-      </c>
+      <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
+      <c r="K56" s="3">
+        <v>6</v>
+      </c>
       <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="M56" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B57" s="2">
-        <v>60224</v>
+        <v>60129</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3">
-        <v>7</v>
-      </c>
+      <c r="G57" s="3">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
+      <c r="K57" s="3">
+        <v>6</v>
+      </c>
       <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="M57" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="2">
         <v>22</v>
       </c>
       <c r="B58" s="2">
-        <v>60127</v>
+        <v>60131</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3">
+      <c r="G58" s="3">
         <v>3</v>
       </c>
+      <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3">
+      <c r="K58" s="3">
         <v>8</v>
       </c>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3">
+      <c r="L58" s="3"/>
+      <c r="M58" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:13">
       <c r="A59" s="2">
         <v>22</v>
       </c>
       <c r="B59" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+      <c r="G59" s="3">
+        <v>6</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3">
-        <v>13</v>
-      </c>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="K59" s="3">
+        <v>16</v>
+      </c>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="2">
         <v>22</v>
       </c>
       <c r="B60" s="2">
-        <v>60129</v>
+        <v>60134</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3">
-        <v>5</v>
-      </c>
+      <c r="G60" s="3">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3">
-        <v>10</v>
-      </c>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3">
+      <c r="K60" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="L60" s="3"/>
+      <c r="M60" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B61" s="2">
-        <v>60131</v>
+        <v>60130</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="3">
-        <v>3</v>
-      </c>
+      <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3">
-        <v>8</v>
-      </c>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="K61" s="3">
+        <v>27</v>
+      </c>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B62" s="2">
-        <v>60132</v>
+        <v>60135</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3">
-        <v>6</v>
-      </c>
+      <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3">
-        <v>24</v>
-      </c>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="K62" s="3">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B63" s="2">
-        <v>60134</v>
+        <v>60139</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
-      <c r="H63" s="3">
-        <v>4</v>
-      </c>
+      <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3">
-        <v>15</v>
-      </c>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="K63" s="3">
+        <v>32</v>
+      </c>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="2">
         <v>23</v>
       </c>
       <c r="B64" s="2">
-        <v>60130</v>
+        <v>60306</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -3885,21 +3805,20 @@
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3">
-        <v>27</v>
-      </c>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="K64" s="3">
+        <v>18</v>
+      </c>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="2">
         <v>23</v>
       </c>
       <c r="B65" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -3909,24 +3828,25 @@
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3">
-        <v>16</v>
-      </c>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="K65" s="3">
+        <v>11</v>
+      </c>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B66" s="2">
-        <v>60139</v>
+        <v>60128</v>
       </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3">
+        <v>6</v>
+      </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -3935,46 +3855,50 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3">
-        <v>32</v>
-      </c>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <v>133</v>
+      </c>
+      <c r="M66" s="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B67" s="2">
-        <v>60306</v>
+        <v>60132</v>
       </c>
       <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3">
+        <v>26</v>
+      </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
+      <c r="J67" s="3">
+        <v>1</v>
+      </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3">
-        <v>18</v>
-      </c>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <v>682</v>
+      </c>
+      <c r="M67" s="3">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B68" s="2">
-        <v>60355</v>
+        <v>60134</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>8</v>
+      </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -3983,96 +3907,86 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3">
-        <v>11</v>
-      </c>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <v>171</v>
+      </c>
+      <c r="M68" s="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B69" s="2">
         <v>60128</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="3">
-        <v>6</v>
-      </c>
+      <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+      <c r="H69" s="3">
+        <v>108</v>
+      </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3">
-        <v>144</v>
-      </c>
-      <c r="N69" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B70" s="2">
         <v>60132</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="3">
-        <v>26</v>
-      </c>
+      <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+      <c r="H70" s="3">
+        <v>374</v>
+      </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
-      <c r="K70" s="3">
-        <v>1</v>
-      </c>
-      <c r="L70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3">
+        <v>2</v>
+      </c>
       <c r="M70" s="3">
-        <v>716</v>
-      </c>
-      <c r="N70" s="3">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B71" s="2">
         <v>60134</v>
       </c>
       <c r="C71" s="3"/>
-      <c r="D71" s="3">
-        <v>8</v>
-      </c>
+      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
+      <c r="H71" s="3">
+        <v>196</v>
+      </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3">
-        <v>183</v>
-      </c>
-      <c r="N71" s="3">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B72" s="2">
         <v>60128</v>
@@ -4083,20 +3997,19 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="3">
-        <v>108</v>
-      </c>
-      <c r="J72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3">
+        <v>140</v>
+      </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="M72" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B73" s="2">
         <v>60132</v>
@@ -4107,22 +4020,19 @@
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
-      <c r="I73" s="3">
-        <v>374</v>
-      </c>
-      <c r="J73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3">
+        <v>136</v>
+      </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3">
-        <v>2</v>
-      </c>
-      <c r="N73" s="3">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B74" s="2">
         <v>60134</v>
@@ -4133,20 +4043,19 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="3">
-        <v>196</v>
-      </c>
-      <c r="J74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3">
+        <v>99</v>
+      </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="M74" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B75" s="2">
         <v>60128</v>
@@ -4157,20 +4066,19 @@
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="I75" s="3">
+        <v>112</v>
+      </c>
       <c r="J75" s="3"/>
-      <c r="K75" s="3">
-        <v>140</v>
-      </c>
+      <c r="K75" s="3"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="M75" s="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B76" s="2">
         <v>60132</v>
@@ -4181,44 +4089,44 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+      <c r="I76" s="3">
+        <v>564</v>
+      </c>
       <c r="J76" s="3"/>
-      <c r="K76" s="3">
-        <v>136</v>
-      </c>
+      <c r="K76" s="3"/>
       <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="M76" s="3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B77" s="2">
         <v>60134</v>
       </c>
       <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
+      <c r="D77" s="3">
+        <v>2</v>
+      </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="I77" s="3">
+        <v>143</v>
+      </c>
       <c r="J77" s="3"/>
-      <c r="K77" s="3">
-        <v>99</v>
-      </c>
+      <c r="K77" s="3"/>
       <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="M77" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B78" s="2">
         <v>60128</v>
@@ -4226,23 +4134,24 @@
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3">
+        <v>27</v>
+      </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
-      <c r="J78" s="3">
-        <v>112</v>
-      </c>
-      <c r="K78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3">
+        <v>15</v>
+      </c>
       <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="M78" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B79" s="2">
         <v>60132</v>
@@ -4250,136 +4159,131 @@
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
+      <c r="F79" s="3">
+        <v>139</v>
+      </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
-      <c r="J79" s="3">
-        <v>564</v>
-      </c>
-      <c r="K79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3">
+        <v>77</v>
+      </c>
       <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="M79" s="3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B80" s="2">
         <v>60134</v>
       </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="3">
-        <v>2</v>
-      </c>
+      <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3">
+        <v>97</v>
+      </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
-      <c r="J80" s="3">
+      <c r="J80" s="3"/>
+      <c r="K80" s="3">
+        <v>46</v>
+      </c>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3">
         <v>143</v>
       </c>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B81" s="2">
         <v>60128</v>
       </c>
-      <c r="C81" s="3"/>
+      <c r="C81" s="3">
+        <v>94</v>
+      </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="F81" s="3">
-        <v>27</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
-      <c r="L81" s="3">
-        <v>15</v>
-      </c>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
+      <c r="L81" s="3"/>
+      <c r="M81" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B82" s="2">
         <v>60132</v>
       </c>
-      <c r="C82" s="3"/>
+      <c r="C82" s="3">
+        <v>414</v>
+      </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="F82" s="3">
-        <v>139</v>
-      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-      <c r="L82" s="3">
-        <v>77</v>
-      </c>
-      <c r="M82" s="3"/>
-      <c r="N82" s="3">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B83" s="2">
         <v>60134</v>
       </c>
-      <c r="C83" s="3"/>
+      <c r="C83" s="3">
+        <v>188</v>
+      </c>
       <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3">
-        <v>97</v>
-      </c>
+      <c r="E83" s="3">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
-      <c r="L83" s="3">
-        <v>46</v>
-      </c>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="L83" s="3"/>
+      <c r="M83" s="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B84" s="2">
-        <v>60128</v>
+        <v>60135</v>
       </c>
       <c r="C84" s="3">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
+      <c r="E84" s="3">
+        <v>1</v>
+      </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
@@ -4387,20 +4291,19 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
+      <c r="M84" s="3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B85" s="2">
-        <v>60132</v>
+        <v>60139</v>
       </c>
       <c r="C85" s="3">
-        <v>414</v>
+        <v>179</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -4411,25 +4314,22 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="M85" s="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B86" s="2">
-        <v>60134</v>
+        <v>60306</v>
       </c>
       <c r="C86" s="3">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D86" s="3"/>
-      <c r="E86" s="3">
-        <v>1</v>
-      </c>
+      <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
@@ -4437,24 +4337,23 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-      <c r="N86" s="3">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="M86" s="3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B87" s="2">
-        <v>60135</v>
+        <v>60130</v>
       </c>
       <c r="C87" s="3">
-        <v>137</v>
+        <v>268</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -4463,20 +4362,19 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="M87" s="3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B88" s="2">
-        <v>60139</v>
+        <v>60355</v>
       </c>
       <c r="C88" s="3">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -4487,22 +4385,21 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="M88" s="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B89" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C89" s="3">
-        <v>169</v>
-      </c>
-      <c r="D89" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3">
+        <v>11</v>
+      </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -4510,49 +4407,49 @@
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="L89" s="3">
+        <v>284</v>
+      </c>
+      <c r="M89" s="3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B90" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C90" s="3">
-        <v>268</v>
-      </c>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3">
-        <v>5</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3">
+        <v>10</v>
+      </c>
+      <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="L90" s="3">
+        <v>330</v>
+      </c>
+      <c r="M90" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
       <c r="A91" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B91" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C91" s="3">
-        <v>170</v>
-      </c>
-      <c r="D91" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3">
+        <v>5</v>
+      </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
@@ -4560,22 +4457,23 @@
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="L91" s="3">
+        <v>220</v>
+      </c>
+      <c r="M91" s="3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
       <c r="A92" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B92" s="2">
-        <v>60135</v>
+        <v>60130</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -4584,24 +4482,23 @@
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
+      <c r="L92" s="3">
+        <v>248</v>
+      </c>
       <c r="M92" s="3">
-        <v>284</v>
-      </c>
-      <c r="N92" s="3">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13">
       <c r="A93" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B93" s="2">
-        <v>60139</v>
+        <v>60355</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -4610,252 +4507,238 @@
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
+      <c r="L93" s="3">
+        <v>356</v>
+      </c>
       <c r="M93" s="3">
-        <v>330</v>
-      </c>
-      <c r="N93" s="3">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13">
       <c r="A94" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B94" s="2">
-        <v>60306</v>
+        <v>60139</v>
       </c>
       <c r="C94" s="3"/>
-      <c r="D94" s="3">
-        <v>5</v>
-      </c>
+      <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3">
+        <v>80</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
+      <c r="K94" s="3">
+        <v>19</v>
+      </c>
       <c r="L94" s="3"/>
       <c r="M94" s="3">
-        <v>220</v>
-      </c>
-      <c r="N94" s="3">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
       <c r="A95" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B95" s="2">
-        <v>60130</v>
+        <v>60306</v>
       </c>
       <c r="C95" s="3"/>
-      <c r="D95" s="3">
-        <v>5</v>
-      </c>
+      <c r="D95" s="3"/>
       <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
+      <c r="F95" s="3">
+        <v>78</v>
+      </c>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
+      <c r="K95" s="3">
+        <v>26</v>
+      </c>
       <c r="L95" s="3"/>
       <c r="M95" s="3">
-        <v>248</v>
-      </c>
-      <c r="N95" s="3">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B96" s="2">
         <v>60355</v>
       </c>
       <c r="C96" s="3"/>
-      <c r="D96" s="3">
-        <v>15</v>
-      </c>
+      <c r="D96" s="3"/>
       <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
+      <c r="F96" s="3">
+        <v>91</v>
+      </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
+      <c r="K96" s="3">
+        <v>37</v>
+      </c>
       <c r="L96" s="3"/>
       <c r="M96" s="3">
-        <v>356</v>
-      </c>
-      <c r="N96" s="3">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B97" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3">
-        <v>19</v>
-      </c>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="K97" s="3">
+        <v>27</v>
+      </c>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B98" s="2">
-        <v>60306</v>
+        <v>60135</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3">
-        <v>26</v>
-      </c>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="K98" s="3">
+        <v>13</v>
+      </c>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B99" s="2">
-        <v>60355</v>
+        <v>60135</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
-      <c r="F99" s="3">
-        <v>91</v>
-      </c>
+      <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
+      <c r="I99" s="3">
+        <v>172</v>
+      </c>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
-      <c r="L99" s="3">
-        <v>37</v>
-      </c>
-      <c r="M99" s="3"/>
-      <c r="N99" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="L99" s="3"/>
+      <c r="M99" s="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13">
       <c r="A100" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B100" s="2">
-        <v>60130</v>
+        <v>60139</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
-      <c r="F100" s="3">
-        <v>51</v>
-      </c>
+      <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
+      <c r="I100" s="3">
+        <v>185</v>
+      </c>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
-      <c r="L100" s="3">
-        <v>27</v>
-      </c>
-      <c r="M100" s="3"/>
-      <c r="N100" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="L100" s="3"/>
+      <c r="M100" s="3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13">
       <c r="A101" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B101" s="2">
-        <v>60135</v>
+        <v>60306</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
-      <c r="F101" s="3">
-        <v>45</v>
-      </c>
+      <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
+      <c r="I101" s="3">
+        <v>215</v>
+      </c>
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
-      <c r="L101" s="3">
-        <v>13</v>
-      </c>
-      <c r="M101" s="3"/>
-      <c r="N101" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
+      <c r="L101" s="3"/>
+      <c r="M101" s="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B102" s="2">
-        <v>60135</v>
+        <v>60130</v>
       </c>
       <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
+      <c r="D102" s="3">
+        <v>1</v>
+      </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3">
-        <v>172</v>
-      </c>
+      <c r="I102" s="3">
+        <v>204</v>
+      </c>
+      <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
-      <c r="N102" s="3">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="M102" s="3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
       <c r="A103" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B103" s="2">
-        <v>60139</v>
+        <v>60355</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -4863,23 +4746,22 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3">
-        <v>185</v>
-      </c>
+      <c r="I103" s="3">
+        <v>282</v>
+      </c>
+      <c r="J103" s="3"/>
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="M103" s="3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
       <c r="A104" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B104" s="2">
-        <v>60306</v>
+        <v>60135</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -4889,47 +4771,43 @@
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
-      <c r="M104" s="3"/>
-      <c r="N104" s="3">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="M104" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
       <c r="A105" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B105" s="2">
-        <v>60130</v>
+        <v>60139</v>
       </c>
       <c r="C105" s="3"/>
-      <c r="D105" s="3">
-        <v>1</v>
-      </c>
+      <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
-      <c r="M105" s="3"/>
-      <c r="N105" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
+      <c r="M105" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B106" s="2">
-        <v>60355</v>
+        <v>60306</v>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
@@ -4939,21 +4817,20 @@
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
-      <c r="M106" s="3"/>
-      <c r="N106" s="3">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
+      <c r="M106" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B107" s="2">
-        <v>60135</v>
+        <v>60130</v>
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
@@ -4962,19 +4839,18 @@
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
-      <c r="J107" s="3"/>
-      <c r="K107" s="3">
-        <v>80</v>
-      </c>
+      <c r="J107" s="3">
+        <v>102</v>
+      </c>
+      <c r="K107" s="3"/>
       <c r="L107" s="3"/>
-      <c r="M107" s="3"/>
-      <c r="N107" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
+      <c r="M107" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B108" s="2">
         <v>60139</v>
@@ -4984,21 +4860,20 @@
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
+      <c r="H108" s="3">
+        <v>205</v>
+      </c>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
-      <c r="K108" s="3">
-        <v>71</v>
-      </c>
+      <c r="K108" s="3"/>
       <c r="L108" s="3"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="M108" s="3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B109" s="2">
         <v>60306</v>
@@ -5008,202 +4883,123 @@
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
+      <c r="H109" s="3">
+        <v>200</v>
+      </c>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
-      <c r="K109" s="3">
-        <v>72</v>
-      </c>
+      <c r="K109" s="3"/>
       <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="M109" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B110" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
+      <c r="H110" s="3">
+        <v>342</v>
+      </c>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
-      <c r="K110" s="3">
-        <v>102</v>
-      </c>
+      <c r="K110" s="3"/>
       <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
+      <c r="M110" s="3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B111" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3">
-        <v>205</v>
-      </c>
+      <c r="H111" s="3">
+        <v>124</v>
+      </c>
+      <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
+      <c r="M111" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
       <c r="A112" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B112" s="2">
-        <v>60306</v>
+        <v>60135</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3">
-        <v>200</v>
-      </c>
+      <c r="H112" s="3">
+        <v>149</v>
+      </c>
+      <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
       <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" s="2">
-        <v>53</v>
-      </c>
-      <c r="B113" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3">
-        <v>342</v>
-      </c>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="A114" s="2">
-        <v>54</v>
-      </c>
-      <c r="B114" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3">
-        <v>124</v>
-      </c>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="3"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
-      <c r="A115" s="2">
-        <v>54</v>
-      </c>
-      <c r="B115" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3">
+      <c r="M112" s="3">
         <v>149</v>
       </c>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" s="2" t="s">
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B116" s="2"/>
-      <c r="C116" s="4">
-        <v>2922</v>
-      </c>
-      <c r="D116" s="4">
+      <c r="B113" s="2"/>
+      <c r="C113" s="4">
+        <v>2828</v>
+      </c>
+      <c r="D113" s="4">
         <v>172</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E113" s="4">
         <v>18</v>
       </c>
-      <c r="F116" s="4">
-        <v>971</v>
-      </c>
-      <c r="G116" s="4">
-        <v>5</v>
-      </c>
-      <c r="H116" s="4">
+      <c r="F113" s="4">
+        <v>932</v>
+      </c>
+      <c r="G113" s="4">
         <v>32</v>
       </c>
-      <c r="I116" s="4">
-        <v>3120</v>
-      </c>
-      <c r="J116" s="4">
-        <v>3515</v>
-      </c>
-      <c r="K116" s="4">
-        <v>1887</v>
-      </c>
-      <c r="L116" s="4">
-        <v>602</v>
-      </c>
-      <c r="M116" s="4">
-        <v>3601</v>
-      </c>
-      <c r="N116" s="4">
-        <v>16845</v>
+      <c r="H113" s="4">
+        <v>2977</v>
+      </c>
+      <c r="I113" s="4">
+        <v>3375</v>
+      </c>
+      <c r="J113" s="4">
+        <v>1842</v>
+      </c>
+      <c r="K113" s="4">
+        <v>579</v>
+      </c>
+      <c r="L113" s="4">
+        <v>3267</v>
+      </c>
+      <c r="M113" s="4">
+        <v>16022</v>
       </c>
     </row>
   </sheetData>
@@ -5213,17 +5009,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="6" width="7.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="3" max="7" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5231,25 +5025,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>2000</v>
       </c>
@@ -5258,18 +5049,15 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>2000</v>
       </c>
@@ -5278,16 +5066,15 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="G3" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>2001</v>
       </c>
@@ -5306,12 +5093,11 @@
       <c r="F4" s="3">
         <v>17</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="3">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>2001</v>
       </c>
@@ -5330,12 +5116,11 @@
       <c r="F5" s="3">
         <v>17</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="3">
         <v>499</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>2002</v>
       </c>
@@ -5354,36 +5139,32 @@
       <c r="F6" s="3">
         <v>8</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="3">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>2003</v>
       </c>
       <c r="B7" s="2">
         <v>21087</v>
       </c>
-      <c r="C7" s="3">
-        <v>17</v>
-      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3">
         <v>29</v>
       </c>
       <c r="E7" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F7" s="3">
-        <v>32</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>2004</v>
       </c>
@@ -5402,12 +5183,11 @@
       <c r="F8" s="3">
         <v>53</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="G8" s="3">
         <v>350</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9" s="2">
         <v>2004</v>
       </c>
@@ -5426,12 +5206,11 @@
       <c r="F9" s="3">
         <v>4</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
+      <c r="G9" s="3">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>2005</v>
       </c>
@@ -5450,12 +5229,11 @@
       <c r="F10" s="3">
         <v>14</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3">
+      <c r="G10" s="3">
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11" s="2">
         <v>2005</v>
       </c>
@@ -5474,12 +5252,11 @@
       <c r="F11" s="3">
         <v>26</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3">
+      <c r="G11" s="3">
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>2006</v>
       </c>
@@ -5496,12 +5273,11 @@
       <c r="F12" s="3">
         <v>4</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3">
+      <c r="G12" s="3">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13" s="2">
         <v>2007</v>
       </c>
@@ -5520,12 +5296,11 @@
       <c r="F13" s="3">
         <v>42</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3">
+      <c r="G13" s="3">
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14" s="2">
         <v>2007</v>
       </c>
@@ -5544,12 +5319,11 @@
       <c r="F14" s="3">
         <v>7</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15" s="2">
         <v>2008</v>
       </c>
@@ -5566,12 +5340,11 @@
       <c r="F15" s="3">
         <v>9</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3">
+      <c r="G15" s="3">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16" s="2">
         <v>2008</v>
       </c>
@@ -5590,12 +5363,11 @@
       <c r="F16" s="3">
         <v>6</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3">
+      <c r="G16" s="3">
         <v>459</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17" s="2">
         <v>2009</v>
       </c>
@@ -5614,12 +5386,11 @@
       <c r="F17" s="3">
         <v>25</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3">
+      <c r="G17" s="3">
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -5638,12 +5409,11 @@
       <c r="F18" s="3">
         <v>14</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3">
+      <c r="G18" s="3">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19" s="2">
         <v>2010</v>
       </c>
@@ -5662,12 +5432,11 @@
       <c r="F19" s="3">
         <v>4</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3">
+      <c r="G19" s="3">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20" s="2">
         <v>2012</v>
       </c>
@@ -5680,12 +5449,11 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3">
+      <c r="G20" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21" s="2">
         <v>2015</v>
       </c>
@@ -5698,33 +5466,29 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3">
+      <c r="G21" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="4">
-        <v>2415</v>
+        <v>2398</v>
       </c>
       <c r="D22" s="4">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E22" s="4">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="F22" s="4">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G22" s="4">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4">
-        <v>3335</v>
+        <v>3296</v>
       </c>
     </row>
   </sheetData>
@@ -5751,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>
@@ -5852,34 +5616,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>13</v>
@@ -5897,13 +5661,13 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="J2" s="3">
         <v>12</v>
@@ -5915,7 +5679,7 @@
         <v>11</v>
       </c>
       <c r="M2" s="3">
-        <v>266</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5930,25 +5694,25 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J3" s="3">
         <v>14</v>
       </c>
       <c r="K3" s="3">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="L3" s="3">
         <v>10</v>
       </c>
       <c r="M3" s="3">
-        <v>155</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5969,7 +5733,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
@@ -5979,7 +5743,7 @@
         <v>11</v>
       </c>
       <c r="M4" s="3">
-        <v>101</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6000,7 +5764,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -6008,7 +5772,7 @@
         <v>9</v>
       </c>
       <c r="M5" s="3">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6018,30 +5782,26 @@
       <c r="B6" s="2">
         <v>21092</v>
       </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3">
         <v>9</v>
       </c>
       <c r="F6" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3">
         <v>13</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>14</v>
-      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3">
         <v>2</v>
       </c>
       <c r="M6" s="3">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6057,22 +5817,20 @@
         <v>8</v>
       </c>
       <c r="F7" s="3">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>8</v>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3">
         <v>3</v>
       </c>
       <c r="M7" s="3">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6092,7 +5850,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="3">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3">
         <v>81</v>
@@ -6104,7 +5862,7 @@
         <v>124</v>
       </c>
       <c r="J8" s="3">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K8" s="3">
         <v>175</v>
@@ -6113,7 +5871,7 @@
         <v>11</v>
       </c>
       <c r="M8" s="3">
-        <v>787</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6133,7 +5891,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3">
         <v>32</v>
@@ -6143,7 +5901,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" s="3">
         <v>63</v>
@@ -6152,7 +5910,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="3">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6422,7 +6180,7 @@
         <v>68</v>
       </c>
       <c r="J16" s="3">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K16" s="3">
         <v>129</v>
@@ -6431,7 +6189,7 @@
         <v>11</v>
       </c>
       <c r="M16" s="3">
-        <v>712</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -6461,7 +6219,7 @@
         <v>67</v>
       </c>
       <c r="J17" s="3">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="K17" s="3">
         <v>148</v>
@@ -6470,7 +6228,7 @@
         <v>17</v>
       </c>
       <c r="M17" s="3">
-        <v>1052</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -6551,37 +6309,37 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="4">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D20" s="4">
         <v>988</v>
       </c>
       <c r="E20" s="4">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="F20" s="4">
-        <v>1146</v>
+        <v>1106</v>
       </c>
       <c r="G20" s="4">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H20" s="4">
         <v>7</v>
       </c>
       <c r="I20" s="4">
-        <v>1136</v>
+        <v>1001</v>
       </c>
       <c r="J20" s="4">
-        <v>1606</v>
+        <v>1572</v>
       </c>
       <c r="K20" s="4">
-        <v>1509</v>
+        <v>1473</v>
       </c>
       <c r="L20" s="4">
         <v>119</v>
       </c>
       <c r="M20" s="4">
-        <v>7757</v>
+        <v>7461</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="43">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -51,12 +51,6 @@
     <t>BSLIQ</t>
   </si>
   <si>
-    <t>BSNUF1</t>
-  </si>
-  <si>
-    <t>BSNUF2</t>
-  </si>
-  <si>
     <t>BSTOY1</t>
   </si>
   <si>
@@ -79,9 +73,6 @@
   </si>
   <si>
     <t>LSHFU</t>
-  </si>
-  <si>
-    <t>LSTEEN</t>
   </si>
   <si>
     <t>MACC01</t>
@@ -546,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -555,11 +546,11 @@
     <col min="5" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,14 +587,8 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -625,13 +610,11 @@
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3">
+      <c r="L2" s="3">
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:12">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
@@ -655,13 +638,11 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3">
+      <c r="L3" s="3">
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
         <v>1001</v>
       </c>
@@ -683,13 +664,11 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3">
+      <c r="L4" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
@@ -709,13 +688,11 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="L5" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
@@ -723,13 +700,13 @@
         <v>21082</v>
       </c>
       <c r="C6" s="3">
-        <v>542</v>
+        <v>489</v>
       </c>
       <c r="D6" s="3">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3">
         <v>5</v>
@@ -738,22 +715,20 @@
         <v>12</v>
       </c>
       <c r="H6" s="3">
-        <v>466</v>
+        <v>397</v>
       </c>
       <c r="I6" s="3">
         <v>49</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3">
-        <v>99</v>
-      </c>
-      <c r="N6" s="3">
-        <v>1527</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="K6" s="3">
+        <v>97</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2">
         <v>1002</v>
       </c>
@@ -761,13 +736,13 @@
         <v>21469</v>
       </c>
       <c r="C7" s="3">
-        <v>726</v>
+        <v>600</v>
       </c>
       <c r="D7" s="3">
-        <v>153</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -776,22 +751,20 @@
         <v>2</v>
       </c>
       <c r="H7" s="3">
-        <v>418</v>
+        <v>350</v>
       </c>
       <c r="I7" s="3">
         <v>6</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3">
-        <v>37</v>
-      </c>
-      <c r="N7" s="3">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="K7" s="3">
+        <v>36</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2">
         <v>1003</v>
       </c>
@@ -819,13 +792,11 @@
         <v>4</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
+      <c r="L8" s="3">
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:12">
       <c r="A9" s="2">
         <v>1003</v>
       </c>
@@ -850,257 +821,239 @@
       <c r="J9" s="3">
         <v>21</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3">
+      <c r="K9" s="3">
         <v>60</v>
       </c>
-      <c r="N9" s="3">
+      <c r="L9" s="3">
         <v>866</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:12">
       <c r="A10" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>21085</v>
+      </c>
+      <c r="C10" s="3">
+        <v>196</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="F10" s="3">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>12</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3">
-        <v>14</v>
-      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>9</v>
-      </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B11" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>21088</v>
+      </c>
+      <c r="C11" s="3">
+        <v>150</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="F11" s="3">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
+      <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>1</v>
-      </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="2">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B12" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>21087</v>
+      </c>
+      <c r="C12" s="3">
+        <v>50</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="2">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B13" s="2">
-        <v>21085</v>
+        <v>21229</v>
       </c>
       <c r="C13" s="3">
-        <v>511</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3">
-        <v>12</v>
-      </c>
-      <c r="H13" s="3">
-        <v>29</v>
-      </c>
-      <c r="I13" s="3">
-        <v>17</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3">
-        <v>7</v>
-      </c>
-      <c r="N13" s="3">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B14" s="2">
-        <v>21088</v>
+        <v>21085</v>
       </c>
       <c r="C14" s="3">
-        <v>284</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D14" s="3">
+        <v>21</v>
+      </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
-        <v>47</v>
-      </c>
-      <c r="I14" s="3">
-        <v>21</v>
-      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3">
-        <v>11</v>
-      </c>
-      <c r="N14" s="3">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B15" s="2">
-        <v>21087</v>
+        <v>21088</v>
       </c>
       <c r="C15" s="3">
-        <v>242</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D15" s="3">
+        <v>44</v>
+      </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>10</v>
-      </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="L15" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B16" s="2">
-        <v>21229</v>
+        <v>21086</v>
       </c>
       <c r="C16" s="3">
-        <v>184</v>
-      </c>
-      <c r="D16" s="3"/>
+        <v>763</v>
+      </c>
+      <c r="D16" s="3">
+        <v>119</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="3">
-        <v>6</v>
-      </c>
-      <c r="H16" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>433</v>
+      </c>
       <c r="I16" s="3">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="K16" s="3">
+        <v>25</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B17" s="2">
-        <v>21085</v>
+        <v>21515</v>
       </c>
       <c r="C17" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D17" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="3">
+        <v>241</v>
+      </c>
+      <c r="I17" s="3">
+        <v>6</v>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="2">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B18" s="2">
-        <v>21088</v>
+        <v>21087</v>
       </c>
       <c r="C18" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D18" s="3">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1109,476 +1062,344 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="L18" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B19" s="2">
-        <v>21086</v>
+        <v>21229</v>
       </c>
       <c r="C19" s="3">
-        <v>763</v>
+        <v>7</v>
       </c>
       <c r="D19" s="3">
-        <v>119</v>
-      </c>
-      <c r="E19" s="3">
-        <v>22</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3">
-        <v>2</v>
-      </c>
-      <c r="H19" s="3">
-        <v>433</v>
-      </c>
-      <c r="I19" s="3">
-        <v>56</v>
-      </c>
-      <c r="J19" s="3">
-        <v>19</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3">
-        <v>25</v>
-      </c>
-      <c r="N19" s="3">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="L19" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B20" s="2">
-        <v>21515</v>
+        <v>21195</v>
       </c>
       <c r="C20" s="3">
+        <v>709</v>
+      </c>
+      <c r="D20" s="3">
+        <v>137</v>
+      </c>
+      <c r="E20" s="3">
+        <v>259</v>
+      </c>
+      <c r="F20" s="3">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>330</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3">
+        <v>31</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C21" s="3">
+        <v>592</v>
+      </c>
+      <c r="D21" s="3">
+        <v>102</v>
+      </c>
+      <c r="E21" s="3">
+        <v>224</v>
+      </c>
+      <c r="F21" s="3">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3">
+        <v>359</v>
+      </c>
+      <c r="I21" s="3">
+        <v>11</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3">
+        <v>37</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C22" s="3">
+        <v>11</v>
+      </c>
+      <c r="D22" s="3">
+        <v>52</v>
+      </c>
+      <c r="E22" s="3">
+        <v>113</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
+        <v>266</v>
+      </c>
+      <c r="I22" s="3">
         <v>17</v>
       </c>
-      <c r="D20" s="3">
-        <v>19</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3">
-        <v>241</v>
-      </c>
-      <c r="I20" s="3">
-        <v>6</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B21" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C21" s="3">
-        <v>5</v>
-      </c>
-      <c r="D21" s="3">
-        <v>21</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B22" s="2">
-        <v>21229</v>
-      </c>
-      <c r="C22" s="3">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3">
-        <v>31</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L22" s="3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B23" s="2">
-        <v>21195</v>
+        <v>21457</v>
       </c>
       <c r="C23" s="3">
-        <v>709</v>
+        <v>24</v>
       </c>
       <c r="D23" s="3">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="E23" s="3">
-        <v>259</v>
+        <v>76</v>
       </c>
       <c r="F23" s="3">
-        <v>11</v>
-      </c>
-      <c r="G23" s="3">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>243</v>
+      </c>
+      <c r="I23" s="3">
+        <v>12</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C24" s="3">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>22</v>
+      </c>
+      <c r="E24" s="3">
+        <v>74</v>
+      </c>
+      <c r="F24" s="3">
         <v>1</v>
       </c>
-      <c r="H23" s="3">
-        <v>330</v>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3">
-        <v>30</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3">
-        <v>31</v>
-      </c>
-      <c r="N23" s="3">
-        <v>1508</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B24" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C24" s="3">
-        <v>592</v>
-      </c>
-      <c r="D24" s="3">
-        <v>102</v>
-      </c>
-      <c r="E24" s="3">
-        <v>224</v>
-      </c>
-      <c r="F24" s="3">
-        <v>10</v>
-      </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
       <c r="H24" s="3">
-        <v>359</v>
+        <v>182</v>
       </c>
       <c r="I24" s="3">
-        <v>11</v>
-      </c>
-      <c r="J24" s="3">
-        <v>47</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3">
-        <v>37</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="L24" s="3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B25" s="2">
-        <v>21083</v>
+        <v>21234</v>
       </c>
       <c r="C25" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" s="3">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="F25" s="3">
-        <v>4</v>
-      </c>
-      <c r="G25" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
       <c r="H25" s="3">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I25" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="L25" s="3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B26" s="2">
-        <v>21457</v>
+        <v>21081</v>
       </c>
       <c r="C26" s="3">
-        <v>24</v>
+        <v>551</v>
       </c>
       <c r="D26" s="3">
-        <v>42</v>
+        <v>161</v>
       </c>
       <c r="E26" s="3">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="F26" s="3">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
       <c r="H26" s="3">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="I26" s="3">
-        <v>12</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>17</v>
+      </c>
+      <c r="J26" s="3">
+        <v>45</v>
+      </c>
+      <c r="K26" s="3">
+        <v>46</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B27" s="2">
-        <v>21089</v>
+        <v>21090</v>
       </c>
       <c r="C27" s="3">
-        <v>4</v>
+        <v>476</v>
       </c>
       <c r="D27" s="3">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="E27" s="3">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="3">
         <v>1</v>
       </c>
       <c r="H27" s="3">
-        <v>182</v>
+        <v>301</v>
       </c>
       <c r="I27" s="3">
+        <v>19</v>
+      </c>
+      <c r="J27" s="3">
         <v>3</v>
       </c>
-      <c r="J27" s="3">
-        <v>2</v>
-      </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B28" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C28" s="3">
-        <v>12</v>
-      </c>
-      <c r="D28" s="3">
-        <v>59</v>
-      </c>
-      <c r="E28" s="3">
-        <v>67</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3">
-        <v>1</v>
-      </c>
-      <c r="H28" s="3">
-        <v>256</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="K27" s="3">
         <v>20</v>
       </c>
-      <c r="J28" s="3">
-        <v>5</v>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B29" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C29" s="3">
-        <v>551</v>
-      </c>
-      <c r="D29" s="3">
-        <v>161</v>
-      </c>
-      <c r="E29" s="3">
-        <v>258</v>
-      </c>
-      <c r="F29" s="3">
-        <v>7</v>
-      </c>
-      <c r="G29" s="3">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3">
-        <v>325</v>
-      </c>
-      <c r="I29" s="3">
-        <v>17</v>
-      </c>
-      <c r="J29" s="3">
-        <v>45</v>
-      </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3">
-        <v>46</v>
-      </c>
-      <c r="N29" s="3">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B30" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C30" s="3">
-        <v>476</v>
-      </c>
-      <c r="D30" s="3">
-        <v>108</v>
-      </c>
-      <c r="E30" s="3">
-        <v>167</v>
-      </c>
-      <c r="F30" s="3">
-        <v>2</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1</v>
-      </c>
-      <c r="H30" s="3">
-        <v>301</v>
-      </c>
-      <c r="I30" s="3">
-        <v>19</v>
-      </c>
-      <c r="J30" s="3">
-        <v>3</v>
-      </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3">
-        <v>20</v>
-      </c>
-      <c r="N30" s="3">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="4">
-        <v>6204</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1403</v>
-      </c>
-      <c r="E31" s="4">
-        <v>1918</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="L27" s="3">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="4">
+        <v>5267</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1183</v>
+      </c>
+      <c r="E28" s="4">
+        <v>1566</v>
+      </c>
+      <c r="F28" s="4">
         <v>84</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G28" s="4">
         <v>44</v>
       </c>
-      <c r="H31" s="4">
-        <v>4532</v>
-      </c>
-      <c r="I31" s="4">
-        <v>294</v>
-      </c>
-      <c r="J31" s="4">
-        <v>176</v>
-      </c>
-      <c r="K31" s="4">
-        <v>19</v>
-      </c>
-      <c r="L31" s="4">
-        <v>10</v>
-      </c>
-      <c r="M31" s="4">
-        <v>373</v>
-      </c>
-      <c r="N31" s="4">
-        <v>15057</v>
+      <c r="H28" s="4">
+        <v>4319</v>
+      </c>
+      <c r="I28" s="4">
+        <v>233</v>
+      </c>
+      <c r="J28" s="4">
+        <v>73</v>
+      </c>
+      <c r="K28" s="4">
+        <v>352</v>
+      </c>
+      <c r="L28" s="4">
+        <v>13121</v>
       </c>
     </row>
   </sheetData>
@@ -1588,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1596,12 +1417,10 @@
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="5" width="7.7109375" customWidth="1"/>
     <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="7" max="9" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,628 +1428,530 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>4000</v>
       </c>
       <c r="B2" s="2">
-        <v>21087</v>
+        <v>21088</v>
       </c>
       <c r="C2" s="3">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="I2" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="B3" s="2">
-        <v>21088</v>
+        <v>21092</v>
       </c>
       <c r="C3" s="3">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
+      </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="I3" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="B4" s="2">
-        <v>21469</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+        <v>21176</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3">
+        <v>23</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>2</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="I4" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>4001</v>
       </c>
       <c r="B5" s="2">
-        <v>21092</v>
+        <v>21229</v>
       </c>
       <c r="C5" s="3">
-        <v>30</v>
-      </c>
-      <c r="D5" s="3">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3">
-        <v>7</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="I5" s="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B6" s="2">
-        <v>21176</v>
+        <v>21085</v>
       </c>
       <c r="C6" s="3">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>8</v>
+      </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="I6" s="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B7" s="2">
-        <v>21229</v>
+        <v>21086</v>
       </c>
       <c r="C7" s="3">
-        <v>409</v>
+        <v>108</v>
       </c>
       <c r="D7" s="3">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3">
         <v>37</v>
       </c>
-      <c r="E7" s="3">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="I7" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2">
         <v>4002</v>
       </c>
       <c r="B8" s="2">
-        <v>21085</v>
+        <v>21515</v>
       </c>
       <c r="C8" s="3">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="D8" s="3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2">
+        <v>4003</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21081</v>
+      </c>
+      <c r="C9" s="3">
+        <v>61</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>6</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2">
+        <v>4004</v>
+      </c>
+      <c r="B10" s="2">
+        <v>21195</v>
+      </c>
+      <c r="C10" s="3">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3">
         <v>8</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2">
-        <v>4002</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C9" s="3">
-        <v>108</v>
-      </c>
-      <c r="D9" s="3">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>35</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E10" s="3">
+        <v>53</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2">
+        <v>4004</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C11" s="3">
+        <v>130</v>
+      </c>
+      <c r="D11" s="3">
         <v>37</v>
       </c>
-      <c r="G9" s="3">
-        <v>11</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2">
-        <v>4002</v>
-      </c>
-      <c r="B10" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C10" s="3">
-        <v>108</v>
-      </c>
-      <c r="D10" s="3">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3">
-        <v>16</v>
-      </c>
-      <c r="G10" s="3">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2">
-        <v>4003</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C11" s="3">
-        <v>61</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46</v>
-      </c>
       <c r="E11" s="3">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="I11" s="3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B12" s="2">
-        <v>21195</v>
+        <v>21083</v>
       </c>
       <c r="C12" s="3">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D12" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E12" s="3">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>99</v>
-      </c>
-      <c r="J12" s="3">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B13" s="2">
-        <v>21246</v>
+        <v>21234</v>
       </c>
       <c r="C13" s="3">
-        <v>130</v>
+        <v>721</v>
       </c>
       <c r="D13" s="3">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E13" s="3">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
-        <v>21</v>
-      </c>
-      <c r="G13" s="3">
-        <v>2</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="I13" s="3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2">
         <v>4005</v>
       </c>
       <c r="B14" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C14" s="3">
-        <v>122</v>
+        <v>330</v>
       </c>
       <c r="D14" s="3">
         <v>30</v>
       </c>
       <c r="E14" s="3">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F14" s="3">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3">
-        <v>27</v>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>58</v>
+      </c>
+      <c r="I14" s="3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="B15" s="2">
-        <v>21234</v>
+        <v>21523</v>
       </c>
       <c r="C15" s="3">
-        <v>721</v>
-      </c>
-      <c r="D15" s="3">
-        <v>23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>75</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
+        <v>24</v>
+      </c>
+      <c r="I15" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2">
+        <v>4007</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21082</v>
+      </c>
+      <c r="C16" s="3">
         <v>31</v>
       </c>
-      <c r="I15" s="3">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2">
-        <v>4005</v>
-      </c>
-      <c r="B16" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C16" s="3">
-        <v>330</v>
-      </c>
       <c r="D16" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3">
-        <v>34</v>
-      </c>
-      <c r="G16" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="G16" s="3">
+        <v>10</v>
+      </c>
       <c r="H16" s="3">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I16" s="3">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="B17" s="2">
-        <v>21523</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
+        <v>21089</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>40</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3">
-        <v>24</v>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>59</v>
+      </c>
+      <c r="I17" s="3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="B18" s="2">
-        <v>21082</v>
+        <v>21090</v>
       </c>
       <c r="C18" s="3">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="D18" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3">
-        <v>104</v>
-      </c>
-      <c r="G18" s="3">
-        <v>10</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I18" s="3">
-        <v>14</v>
-      </c>
-      <c r="J18" s="3">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B19" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C19" s="3"/>
+        <v>21075</v>
+      </c>
+      <c r="C19" s="3">
+        <v>117</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3">
-        <v>59</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>13</v>
+      </c>
+      <c r="I19" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B20" s="2">
-        <v>21090</v>
+        <v>21094</v>
       </c>
       <c r="C20" s="3">
-        <v>194</v>
-      </c>
-      <c r="D20" s="3">
-        <v>26</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3">
-        <v>85</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3">
-        <v>42</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="H20" s="3"/>
+      <c r="I20" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2">
         <v>4011</v>
       </c>
       <c r="B21" s="2">
-        <v>21075</v>
+        <v>21533</v>
       </c>
       <c r="C21" s="3">
-        <v>117</v>
-      </c>
-      <c r="D21" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="D21" s="3">
+        <v>25</v>
+      </c>
       <c r="E21" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3">
-        <v>13</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B22" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C22" s="3">
-        <v>44</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B23" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C23" s="3">
-        <v>241</v>
-      </c>
-      <c r="D23" s="3">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>8</v>
-      </c>
-      <c r="F23" s="3">
-        <v>24</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3">
         <v>16</v>
       </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3">
+      <c r="I21" s="3">
         <v>314</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="4">
-        <v>2947</v>
-      </c>
-      <c r="D24" s="4">
-        <v>433</v>
-      </c>
-      <c r="E24" s="4">
-        <v>321</v>
-      </c>
-      <c r="F24" s="4">
-        <v>597</v>
-      </c>
-      <c r="G24" s="4">
-        <v>51</v>
-      </c>
-      <c r="H24" s="4">
-        <v>310</v>
-      </c>
-      <c r="I24" s="4">
-        <v>117</v>
-      </c>
-      <c r="J24" s="4">
-        <v>4776</v>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="4">
+        <v>2592</v>
+      </c>
+      <c r="D22" s="4">
+        <v>396</v>
+      </c>
+      <c r="E22" s="4">
+        <v>272</v>
+      </c>
+      <c r="F22" s="4">
+        <v>467</v>
+      </c>
+      <c r="G22" s="4">
+        <v>42</v>
+      </c>
+      <c r="H22" s="4">
+        <v>252</v>
+      </c>
+      <c r="I22" s="4">
+        <v>4021</v>
       </c>
     </row>
   </sheetData>
@@ -2240,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2265,37 +1986,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2307,7 +2028,7 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -2316,11 +2037,9 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3">
-        <v>106</v>
-      </c>
+      <c r="L2" s="3"/>
       <c r="M2" s="3">
-        <v>122</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2332,7 +2051,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -2341,11 +2060,9 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3">
-        <v>130</v>
-      </c>
+      <c r="L3" s="3"/>
       <c r="M3" s="3">
-        <v>149</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2357,7 +2074,7 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -2368,11 +2085,9 @@
         <v>1</v>
       </c>
       <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>87</v>
-      </c>
+      <c r="L4" s="3"/>
       <c r="M4" s="3">
-        <v>104</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2394,10 +2109,10 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="M5" s="3">
-        <v>189</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2419,10 +2134,10 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="M6" s="3">
-        <v>193</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2444,10 +2159,10 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="M7" s="3">
-        <v>164</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2463,14 +2178,14 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2486,14 +2201,14 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2509,14 +2224,14 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2532,7 +2247,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -2541,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="3">
-        <v>161</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2557,7 +2272,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
@@ -2566,7 +2281,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>238</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2584,7 +2299,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -2593,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="3">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2609,14 +2324,14 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2632,14 +2347,14 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2655,14 +2370,14 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2680,12 +2395,12 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2703,12 +2418,12 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -2728,12 +2443,12 @@
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3">
-        <v>160</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2751,12 +2466,12 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2774,12 +2489,12 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2797,12 +2512,12 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3">
-        <v>158</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2888,7 +2603,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="J26" s="3">
         <v>3</v>
@@ -2896,7 +2611,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3">
-        <v>214</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -2913,13 +2628,13 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3">
-        <v>80</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -2936,13 +2651,13 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3">
-        <v>70</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -2959,13 +2674,13 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2984,13 +2699,13 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
-        <v>290</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -3007,13 +2722,13 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3">
-        <v>175</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -3100,7 +2815,7 @@
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -3109,7 +2824,7 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -3123,7 +2838,7 @@
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -3132,7 +2847,7 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -3146,7 +2861,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -3155,7 +2870,7 @@
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -3168,19 +2883,17 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="3">
-        <v>6</v>
-      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -3193,19 +2906,17 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3">
-        <v>9</v>
-      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -3218,19 +2929,17 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>5</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -3316,7 +3025,7 @@
         <v>60137</v>
       </c>
       <c r="C44" s="3">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3">
@@ -3330,7 +3039,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -3341,7 +3050,7 @@
         <v>60224</v>
       </c>
       <c r="C45" s="3">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3">
@@ -3355,7 +3064,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -3366,7 +3075,7 @@
         <v>60227</v>
       </c>
       <c r="C46" s="3">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3378,7 +3087,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3">
-        <v>87</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -3389,7 +3098,7 @@
         <v>60138</v>
       </c>
       <c r="C47" s="3">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3">
@@ -3403,7 +3112,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3">
-        <v>134</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -3414,7 +3123,7 @@
         <v>60496</v>
       </c>
       <c r="C48" s="3">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3">
@@ -3428,7 +3137,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3">
-        <v>125</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -3439,7 +3148,7 @@
         <v>60507</v>
       </c>
       <c r="C49" s="3">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -3451,7 +3160,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3">
-        <v>93</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -3462,7 +3171,7 @@
         <v>60127</v>
       </c>
       <c r="C50" s="3">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3">
@@ -3476,7 +3185,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -3487,7 +3196,7 @@
         <v>60129</v>
       </c>
       <c r="C51" s="3">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -3499,7 +3208,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -3510,7 +3219,7 @@
         <v>60131</v>
       </c>
       <c r="C52" s="3">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3">
@@ -3524,7 +3233,7 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -3590,12 +3299,10 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3">
-        <v>4</v>
-      </c>
+      <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -3603,22 +3310,22 @@
         <v>22</v>
       </c>
       <c r="B56" s="2">
-        <v>60128</v>
+        <v>60129</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="G56" s="3">
+        <v>5</v>
+      </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3">
-        <v>6</v>
-      </c>
+      <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -3626,24 +3333,22 @@
         <v>22</v>
       </c>
       <c r="B57" s="2">
-        <v>60129</v>
+        <v>60131</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3">
-        <v>6</v>
-      </c>
+      <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -3651,24 +3356,22 @@
         <v>22</v>
       </c>
       <c r="B58" s="2">
-        <v>60131</v>
+        <v>60132</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="3">
-        <v>8</v>
-      </c>
+      <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -3676,49 +3379,47 @@
         <v>22</v>
       </c>
       <c r="B59" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B60" s="2">
-        <v>60134</v>
+        <v>60130</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3">
-        <v>4</v>
-      </c>
+      <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -3726,7 +3427,7 @@
         <v>23</v>
       </c>
       <c r="B61" s="2">
-        <v>60130</v>
+        <v>60135</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
@@ -3737,11 +3438,11 @@
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -3749,7 +3450,7 @@
         <v>23</v>
       </c>
       <c r="B62" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -3760,11 +3461,11 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L62" s="3"/>
       <c r="M62" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -3772,7 +3473,7 @@
         <v>23</v>
       </c>
       <c r="B63" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -3783,11 +3484,11 @@
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L63" s="3"/>
       <c r="M63" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -3795,7 +3496,7 @@
         <v>23</v>
       </c>
       <c r="B64" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -3806,34 +3507,36 @@
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L64" s="3"/>
       <c r="M64" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B65" s="2">
-        <v>60355</v>
+        <v>60128</v>
       </c>
       <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3">
+        <v>6</v>
+      </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-      <c r="K65" s="3">
-        <v>11</v>
-      </c>
-      <c r="L65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3">
+        <v>121</v>
+      </c>
       <c r="M65" s="3">
-        <v>11</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -3841,24 +3544,26 @@
         <v>26</v>
       </c>
       <c r="B66" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
+      <c r="J66" s="3">
+        <v>1</v>
+      </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3">
-        <v>133</v>
+        <v>585</v>
       </c>
       <c r="M66" s="3">
-        <v>139</v>
+        <v>612</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -3866,51 +3571,47 @@
         <v>26</v>
       </c>
       <c r="B67" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
-      <c r="J67" s="3">
-        <v>1</v>
-      </c>
+      <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3">
-        <v>682</v>
+        <v>142</v>
       </c>
       <c r="M67" s="3">
-        <v>709</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B68" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3">
-        <v>8</v>
-      </c>
+      <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="H68" s="3">
+        <v>108</v>
+      </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
-      <c r="L68" s="3">
-        <v>171</v>
-      </c>
+      <c r="L68" s="3"/>
       <c r="M68" s="3">
-        <v>179</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -3918,7 +3619,7 @@
         <v>27</v>
       </c>
       <c r="B69" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
@@ -3926,14 +3627,16 @@
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3">
-        <v>108</v>
+        <v>374</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
+      <c r="L69" s="3">
+        <v>2</v>
+      </c>
       <c r="M69" s="3">
-        <v>108</v>
+        <v>376</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -3941,7 +3644,7 @@
         <v>27</v>
       </c>
       <c r="B70" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -3949,39 +3652,37 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3">
-        <v>374</v>
+        <v>196</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
-      <c r="L70" s="3">
-        <v>2</v>
-      </c>
+      <c r="L70" s="3"/>
       <c r="M70" s="3">
-        <v>376</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B71" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="3">
-        <v>196</v>
-      </c>
+      <c r="H71" s="3"/>
       <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
+      <c r="J71" s="3">
+        <v>140</v>
+      </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3">
-        <v>196</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -3989,7 +3690,7 @@
         <v>28</v>
       </c>
       <c r="B72" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -3999,12 +3700,12 @@
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -4012,7 +3713,7 @@
         <v>28</v>
       </c>
       <c r="B73" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
@@ -4022,20 +3723,20 @@
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B74" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
@@ -4043,14 +3744,14 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3">
-        <v>99</v>
-      </c>
+      <c r="I74" s="3">
+        <v>112</v>
+      </c>
+      <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -4058,7 +3759,7 @@
         <v>29</v>
       </c>
       <c r="B75" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
@@ -4067,13 +3768,13 @@
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3">
-        <v>112</v>
+        <v>564</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3">
-        <v>112</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -4081,47 +3782,49 @@
         <v>29</v>
       </c>
       <c r="B76" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
+      <c r="D76" s="3">
+        <v>2</v>
+      </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3">
-        <v>564</v>
+        <v>143</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3">
-        <v>564</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B77" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C77" s="3"/>
-      <c r="D77" s="3">
-        <v>2</v>
-      </c>
+      <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3">
+        <v>27</v>
+      </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
-      <c r="I77" s="3">
-        <v>143</v>
-      </c>
+      <c r="I77" s="3"/>
       <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
+      <c r="K77" s="3">
+        <v>15</v>
+      </c>
       <c r="L77" s="3"/>
       <c r="M77" s="3">
-        <v>145</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -4129,24 +3832,24 @@
         <v>30</v>
       </c>
       <c r="B78" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="L78" s="3"/>
       <c r="M78" s="3">
-        <v>42</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -4154,49 +3857,47 @@
         <v>30</v>
       </c>
       <c r="B79" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="L79" s="3"/>
       <c r="M79" s="3">
-        <v>216</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B80" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C80" s="3"/>
+        <v>60128</v>
+      </c>
+      <c r="C80" s="3">
+        <v>94</v>
+      </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="3">
-        <v>97</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
-      <c r="K80" s="3">
-        <v>46</v>
-      </c>
+      <c r="K80" s="3"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3">
-        <v>143</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -4204,10 +3905,10 @@
         <v>31</v>
       </c>
       <c r="B81" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C81" s="3">
-        <v>94</v>
+        <v>414</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -4219,7 +3920,7 @@
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3">
-        <v>94</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -4227,13 +3928,15 @@
         <v>31</v>
       </c>
       <c r="B82" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C82" s="3">
-        <v>414</v>
+        <v>188</v>
       </c>
       <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
+      <c r="E82" s="3">
+        <v>1</v>
+      </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
@@ -4242,18 +3945,18 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3">
-        <v>414</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B83" s="2">
-        <v>60134</v>
+        <v>60135</v>
       </c>
       <c r="C83" s="3">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3">
@@ -4267,7 +3970,7 @@
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -4275,15 +3978,13 @@
         <v>32</v>
       </c>
       <c r="B84" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C84" s="3">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="D84" s="3"/>
-      <c r="E84" s="3">
-        <v>1</v>
-      </c>
+      <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
@@ -4292,7 +3993,7 @@
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3">
-        <v>138</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -4300,10 +4001,10 @@
         <v>32</v>
       </c>
       <c r="B85" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C85" s="3">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -4315,21 +4016,23 @@
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
       <c r="M85" s="3">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B86" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C86" s="3">
-        <v>169</v>
+        <v>268</v>
       </c>
       <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
+      <c r="E86" s="3">
+        <v>5</v>
+      </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
@@ -4338,7 +4041,7 @@
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3">
-        <v>169</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -4346,15 +4049,13 @@
         <v>33</v>
       </c>
       <c r="B87" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C87" s="3">
-        <v>268</v>
+        <v>170</v>
       </c>
       <c r="D87" s="3"/>
-      <c r="E87" s="3">
-        <v>5</v>
-      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
@@ -4363,20 +4064,20 @@
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3">
-        <v>273</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B88" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C88" s="3">
-        <v>170</v>
-      </c>
-      <c r="D88" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3">
+        <v>11</v>
+      </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -4384,9 +4085,11 @@
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
+      <c r="L88" s="3">
+        <v>284</v>
+      </c>
       <c r="M88" s="3">
-        <v>170</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -4394,11 +4097,11 @@
         <v>34</v>
       </c>
       <c r="B89" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -4408,10 +4111,10 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="M89" s="3">
-        <v>295</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -4419,11 +4122,11 @@
         <v>34</v>
       </c>
       <c r="B90" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -4433,18 +4136,18 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="M90" s="3">
-        <v>340</v>
+        <v>225</v>
       </c>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B91" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3">
@@ -4458,10 +4161,10 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="M91" s="3">
-        <v>225</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -4469,11 +4172,11 @@
         <v>35</v>
       </c>
       <c r="B92" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -4483,35 +4186,35 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="3">
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="M92" s="3">
-        <v>253</v>
+        <v>371</v>
       </c>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B93" s="2">
-        <v>60355</v>
+        <v>60139</v>
       </c>
       <c r="C93" s="3"/>
-      <c r="D93" s="3">
-        <v>15</v>
-      </c>
+      <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3">
+        <v>80</v>
+      </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3">
-        <v>356</v>
-      </c>
+      <c r="K93" s="3">
+        <v>19</v>
+      </c>
+      <c r="L93" s="3"/>
       <c r="M93" s="3">
-        <v>371</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -4519,24 +4222,24 @@
         <v>36</v>
       </c>
       <c r="B94" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L94" s="3"/>
       <c r="M94" s="3">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -4544,49 +4247,49 @@
         <v>36</v>
       </c>
       <c r="B95" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L95" s="3"/>
       <c r="M95" s="3">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B96" s="2">
-        <v>60355</v>
+        <v>60130</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="3">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L96" s="3"/>
       <c r="M96" s="3">
-        <v>128</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -4594,29 +4297,29 @@
         <v>37</v>
       </c>
       <c r="B97" s="2">
-        <v>60130</v>
+        <v>60135</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L97" s="3"/>
       <c r="M97" s="3">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B98" s="2">
         <v>60135</v>
@@ -4624,19 +4327,17 @@
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="3">
-        <v>45</v>
-      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
+      <c r="I98" s="3">
+        <v>172</v>
+      </c>
       <c r="J98" s="3"/>
-      <c r="K98" s="3">
-        <v>13</v>
-      </c>
+      <c r="K98" s="3"/>
       <c r="L98" s="3"/>
       <c r="M98" s="3">
-        <v>58</v>
+        <v>172</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -4644,7 +4345,7 @@
         <v>38</v>
       </c>
       <c r="B99" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
@@ -4653,13 +4354,13 @@
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
       <c r="I99" s="3">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
       <c r="M99" s="3">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -4667,7 +4368,7 @@
         <v>38</v>
       </c>
       <c r="B100" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -4676,36 +4377,38 @@
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
       <c r="M100" s="3">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B101" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
+      <c r="D101" s="3">
+        <v>1</v>
+      </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101" s="3"/>
       <c r="M101" s="3">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -4713,32 +4416,30 @@
         <v>39</v>
       </c>
       <c r="B102" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C102" s="3"/>
-      <c r="D102" s="3">
-        <v>1</v>
-      </c>
+      <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3">
-        <v>205</v>
+        <v>282</v>
       </c>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B103" s="2">
-        <v>60355</v>
+        <v>60135</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -4746,14 +4447,14 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
-      <c r="I103" s="3">
-        <v>282</v>
-      </c>
-      <c r="J103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3">
+        <v>80</v>
+      </c>
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
       <c r="M103" s="3">
-        <v>282</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -4761,7 +4462,7 @@
         <v>51</v>
       </c>
       <c r="B104" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -4771,12 +4472,12 @@
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
       <c r="M104" s="3">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -4784,7 +4485,7 @@
         <v>51</v>
       </c>
       <c r="B105" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
@@ -4794,20 +4495,20 @@
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
       <c r="M105" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B106" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
@@ -4817,35 +4518,35 @@
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
       <c r="M106" s="3">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B107" s="2">
-        <v>60130</v>
+        <v>60139</v>
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
+      <c r="H107" s="3">
+        <v>205</v>
+      </c>
       <c r="I107" s="3"/>
-      <c r="J107" s="3">
-        <v>102</v>
-      </c>
+      <c r="J107" s="3"/>
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
       <c r="M107" s="3">
-        <v>102</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -4853,7 +4554,7 @@
         <v>53</v>
       </c>
       <c r="B108" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -4861,14 +4562,14 @@
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
       <c r="L108" s="3"/>
       <c r="M108" s="3">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -4876,7 +4577,7 @@
         <v>53</v>
       </c>
       <c r="B109" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
@@ -4884,22 +4585,22 @@
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3">
-        <v>200</v>
+        <v>342</v>
       </c>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
       <c r="M109" s="3">
-        <v>200</v>
+        <v>342</v>
       </c>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B110" s="2">
-        <v>60355</v>
+        <v>60130</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -4907,14 +4608,14 @@
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3">
-        <v>342</v>
+        <v>124</v>
       </c>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
       <c r="M110" s="3">
-        <v>342</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -4922,7 +4623,7 @@
         <v>54</v>
       </c>
       <c r="B111" s="2">
-        <v>60130</v>
+        <v>60135</v>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
@@ -4930,76 +4631,53 @@
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3">
-        <v>124</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="2">
-        <v>54</v>
-      </c>
-      <c r="B112" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3">
-        <v>149</v>
-      </c>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13">
-      <c r="A113" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" s="4">
-        <v>2828</v>
-      </c>
-      <c r="D113" s="4">
-        <v>172</v>
-      </c>
-      <c r="E113" s="4">
+      <c r="A112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" s="2"/>
+      <c r="C112" s="4">
+        <v>2583</v>
+      </c>
+      <c r="D112" s="4">
+        <v>143</v>
+      </c>
+      <c r="E112" s="4">
         <v>18</v>
       </c>
-      <c r="F113" s="4">
-        <v>932</v>
-      </c>
-      <c r="G113" s="4">
+      <c r="F112" s="4">
+        <v>847</v>
+      </c>
+      <c r="G112" s="4">
         <v>32</v>
       </c>
-      <c r="H113" s="4">
-        <v>2977</v>
-      </c>
-      <c r="I113" s="4">
-        <v>3375</v>
-      </c>
-      <c r="J113" s="4">
-        <v>1842</v>
-      </c>
-      <c r="K113" s="4">
-        <v>579</v>
-      </c>
-      <c r="L113" s="4">
-        <v>3267</v>
-      </c>
-      <c r="M113" s="4">
-        <v>16022</v>
+      <c r="H112" s="4">
+        <v>2750</v>
+      </c>
+      <c r="I112" s="4">
+        <v>2913</v>
+      </c>
+      <c r="J112" s="4">
+        <v>1669</v>
+      </c>
+      <c r="K112" s="4">
+        <v>452</v>
+      </c>
+      <c r="L112" s="4">
+        <v>2636</v>
+      </c>
+      <c r="M112" s="4">
+        <v>14043</v>
       </c>
     </row>
   </sheetData>
@@ -5025,19 +4703,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5049,12 +4727,12 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5066,12 +4744,12 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5111,13 +4789,13 @@
         <v>32</v>
       </c>
       <c r="E5" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3">
         <v>17</v>
       </c>
       <c r="G5" s="3">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5133,14 +4811,10 @@
       <c r="D6" s="3">
         <v>6</v>
       </c>
-      <c r="E6" s="3">
-        <v>9</v>
-      </c>
-      <c r="F6" s="3">
-        <v>8</v>
-      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5154,14 +4828,10 @@
       <c r="D7" s="3">
         <v>29</v>
       </c>
-      <c r="E7" s="3">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3">
-        <v>25</v>
-      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5472,23 +5142,23 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="4">
         <v>2398</v>
       </c>
       <c r="D22" s="4">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="E22" s="4">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="F22" s="4">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="G22" s="4">
-        <v>3296</v>
+        <v>3182</v>
       </c>
     </row>
   </sheetData>
@@ -5515,10 +5185,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5557,10 +5227,10 @@
         <v>17183</v>
       </c>
       <c r="C4" s="3">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5579,14 +5249,14 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4">
-        <v>118</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -5596,7 +5266,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5616,37 +5286,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -5656,30 +5326,22 @@
       <c r="B2" s="2">
         <v>21088</v>
       </c>
-      <c r="C2" s="3">
-        <v>11</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3">
-        <v>31</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3">
-        <v>22</v>
-      </c>
-      <c r="J2" s="3">
-        <v>12</v>
-      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
       <c r="K2" s="3">
         <v>105</v>
       </c>
       <c r="L2" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M2" s="3">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5689,657 +5351,519 @@
       <c r="B3" s="2">
         <v>21469</v>
       </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>9</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>20</v>
-      </c>
-      <c r="J3" s="3">
-        <v>14</v>
-      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M3" s="3">
-        <v>86</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2">
-        <v>3001</v>
+        <v>3003</v>
       </c>
       <c r="B4" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C4" s="3">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>21081</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>95</v>
+      </c>
       <c r="E4" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="3">
+        <v>63</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
       <c r="I4" s="3">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="J4" s="3">
-        <v>3</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>11</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="K4" s="3">
+        <v>135</v>
+      </c>
+      <c r="L4" s="3"/>
       <c r="M4" s="3">
-        <v>65</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>3001</v>
+        <v>3003</v>
       </c>
       <c r="B5" s="2">
-        <v>21229</v>
-      </c>
-      <c r="C5" s="3">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>21515</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>71</v>
+      </c>
       <c r="E5" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>28</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>8</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>9</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="J5" s="3">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3">
+        <v>48</v>
+      </c>
+      <c r="L5" s="3"/>
       <c r="M5" s="3">
-        <v>42</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="B6" s="2">
-        <v>21092</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>162</v>
+      </c>
       <c r="E6" s="3">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F6" s="3">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="G6" s="3">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>85</v>
+      </c>
+      <c r="J6" s="3">
+        <v>137</v>
+      </c>
+      <c r="K6" s="3">
+        <v>175</v>
+      </c>
       <c r="L6" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M6" s="3">
-        <v>42</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="B7" s="2">
-        <v>21176</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+        <v>21234</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>84</v>
+      </c>
       <c r="E7" s="3">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="I7" s="3">
+        <v>77</v>
+      </c>
+      <c r="J7" s="3">
+        <v>72</v>
+      </c>
+      <c r="K7" s="3">
+        <v>126</v>
+      </c>
       <c r="L7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" s="3">
-        <v>95</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2">
-        <v>3003</v>
+        <v>3006</v>
       </c>
       <c r="B8" s="2">
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
       </c>
       <c r="D8" s="3">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="G8" s="3">
-        <v>81</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L8" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M8" s="3">
-        <v>765</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2">
-        <v>3003</v>
+        <v>3006</v>
       </c>
       <c r="B9" s="2">
-        <v>21515</v>
+        <v>21457</v>
       </c>
       <c r="C9" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3">
         <v>20</v>
       </c>
       <c r="F9" s="3">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="J9" s="3">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="K9" s="3">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="L9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" s="3">
-        <v>375</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>3004</v>
+        <v>3008</v>
       </c>
       <c r="B10" s="2">
-        <v>21082</v>
+        <v>21195</v>
       </c>
       <c r="C10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="G10" s="3">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="H10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="J10" s="3">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="K10" s="3">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L10" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M10" s="3">
-        <v>800</v>
+        <v>911</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>3004</v>
+        <v>3008</v>
       </c>
       <c r="B11" s="2">
-        <v>21234</v>
+        <v>21246</v>
       </c>
       <c r="C11" s="3">
         <v>6</v>
       </c>
       <c r="D11" s="3">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="G11" s="3">
-        <v>48</v>
-      </c>
-      <c r="H11" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
       <c r="I11" s="3">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J11" s="3">
-        <v>72</v>
+        <v>278</v>
       </c>
       <c r="K11" s="3">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="L11" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" s="3">
-        <v>516</v>
+        <v>772</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>3006</v>
+        <v>3009</v>
       </c>
       <c r="B12" s="2">
-        <v>21083</v>
+        <v>21085</v>
       </c>
       <c r="C12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="3">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="E12" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="G12" s="3">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J12" s="3">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="K12" s="3">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L12" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M12" s="3">
-        <v>386</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>3006</v>
+        <v>3009</v>
       </c>
       <c r="B13" s="2">
-        <v>21457</v>
+        <v>21086</v>
       </c>
       <c r="C13" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" s="3">
-        <v>38</v>
+        <v>153</v>
       </c>
       <c r="E13" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F13" s="3">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="G13" s="3">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="J13" s="3">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="K13" s="3">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L13" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M13" s="3">
-        <v>286</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>3008</v>
+        <v>3011</v>
       </c>
       <c r="B14" s="2">
-        <v>21195</v>
+        <v>21089</v>
       </c>
       <c r="C14" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>60</v>
-      </c>
-      <c r="E14" s="3">
-        <v>13</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="3">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="G14" s="3">
-        <v>157</v>
-      </c>
-      <c r="H14" s="3">
-        <v>3</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="J14" s="3">
-        <v>230</v>
+        <v>26</v>
       </c>
       <c r="K14" s="3">
-        <v>110</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>911</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>3008</v>
+        <v>3011</v>
       </c>
       <c r="B15" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C15" s="3">
-        <v>6</v>
-      </c>
+        <v>21090</v>
+      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="3">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" s="3">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3">
-        <v>52</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>278</v>
+        <v>37</v>
       </c>
       <c r="K15" s="3">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="L15" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M15" s="3">
-        <v>772</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="2">
-        <v>3009</v>
-      </c>
-      <c r="B16" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>174</v>
-      </c>
-      <c r="E16" s="3">
-        <v>6</v>
-      </c>
-      <c r="F16" s="3">
-        <v>109</v>
-      </c>
-      <c r="G16" s="3">
-        <v>71</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3">
-        <v>68</v>
-      </c>
-      <c r="J16" s="3">
-        <v>131</v>
-      </c>
-      <c r="K16" s="3">
-        <v>129</v>
-      </c>
-      <c r="L16" s="3">
+      <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M16" s="3">
+      <c r="B16" s="2"/>
+      <c r="C16" s="4">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4">
+        <v>988</v>
+      </c>
+      <c r="E16" s="4">
+        <v>216</v>
+      </c>
+      <c r="F16" s="4">
+        <v>900</v>
+      </c>
+      <c r="G16" s="4">
         <v>700</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="2">
-        <v>3009</v>
-      </c>
-      <c r="B17" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>153</v>
-      </c>
-      <c r="E17" s="3">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3">
-        <v>151</v>
-      </c>
-      <c r="G17" s="3">
-        <v>110</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3">
-        <v>67</v>
-      </c>
-      <c r="J17" s="3">
-        <v>354</v>
-      </c>
-      <c r="K17" s="3">
-        <v>148</v>
-      </c>
-      <c r="L17" s="3">
-        <v>17</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B18" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3">
-        <v>9</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3">
-        <v>19</v>
-      </c>
-      <c r="G18" s="3">
-        <v>17</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3">
-        <v>58</v>
-      </c>
-      <c r="J18" s="3">
-        <v>26</v>
-      </c>
-      <c r="K18" s="3">
-        <v>26</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B19" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
-        <v>30</v>
-      </c>
-      <c r="E19" s="3">
-        <v>12</v>
-      </c>
-      <c r="F19" s="3">
-        <v>48</v>
-      </c>
-      <c r="G19" s="3">
-        <v>36</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3">
-        <v>40</v>
-      </c>
-      <c r="J19" s="3">
-        <v>37</v>
-      </c>
-      <c r="K19" s="3">
-        <v>34</v>
-      </c>
-      <c r="L19" s="3">
-        <v>2</v>
-      </c>
-      <c r="M19" s="3">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4">
-        <v>120</v>
-      </c>
-      <c r="D20" s="4">
-        <v>988</v>
-      </c>
-      <c r="E20" s="4">
-        <v>312</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1106</v>
-      </c>
-      <c r="G20" s="4">
-        <v>763</v>
-      </c>
-      <c r="H20" s="4">
+      <c r="H16" s="4">
         <v>7</v>
       </c>
-      <c r="I20" s="4">
-        <v>1001</v>
-      </c>
-      <c r="J20" s="4">
-        <v>1572</v>
-      </c>
-      <c r="K20" s="4">
-        <v>1473</v>
-      </c>
-      <c r="L20" s="4">
-        <v>119</v>
-      </c>
-      <c r="M20" s="4">
-        <v>7461</v>
+      <c r="I16" s="4">
+        <v>937</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1192</v>
+      </c>
+      <c r="K16" s="4">
+        <v>1370</v>
+      </c>
+      <c r="L16" s="4">
+        <v>69</v>
+      </c>
+      <c r="M16" s="4">
+        <v>6415</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -537,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -611,7 +611,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3">
-        <v>211</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -631,15 +631,15 @@
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="I3" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3">
-        <v>245</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -700,14 +700,10 @@
         <v>21082</v>
       </c>
       <c r="C6" s="3">
-        <v>489</v>
-      </c>
-      <c r="D6" s="3">
-        <v>32</v>
-      </c>
-      <c r="E6" s="3">
-        <v>75</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="3">
         <v>5</v>
       </c>
@@ -715,17 +711,13 @@
         <v>12</v>
       </c>
       <c r="H6" s="3">
-        <v>397</v>
-      </c>
-      <c r="I6" s="3">
-        <v>49</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3">
-        <v>97</v>
-      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3">
-        <v>1156</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -736,14 +728,10 @@
         <v>21469</v>
       </c>
       <c r="C7" s="3">
-        <v>600</v>
-      </c>
-      <c r="D7" s="3">
-        <v>39</v>
-      </c>
-      <c r="E7" s="3">
-        <v>67</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
       <c r="F7" s="3">
         <v>1</v>
       </c>
@@ -751,17 +739,13 @@
         <v>2</v>
       </c>
       <c r="H7" s="3">
-        <v>350</v>
-      </c>
-      <c r="I7" s="3">
-        <v>6</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3">
-        <v>36</v>
-      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>1101</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -836,7 +820,7 @@
         <v>21085</v>
       </c>
       <c r="C10" s="3">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -851,7 +835,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>211</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -862,7 +846,7 @@
         <v>21088</v>
       </c>
       <c r="C11" s="3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -877,7 +861,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>159</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -887,9 +871,7 @@
       <c r="B12" s="2">
         <v>21087</v>
       </c>
-      <c r="C12" s="3">
-        <v>50</v>
-      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3">
@@ -903,7 +885,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -913,9 +895,7 @@
       <c r="B13" s="2">
         <v>21229</v>
       </c>
-      <c r="C13" s="3">
-        <v>67</v>
-      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3">
@@ -929,7 +909,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1053,7 +1033,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1063,7 +1043,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1077,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1087,7 +1067,7 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1304,7 +1284,7 @@
         <v>161</v>
       </c>
       <c r="E26" s="3">
-        <v>218</v>
+        <v>89</v>
       </c>
       <c r="F26" s="3">
         <v>7</v>
@@ -1318,14 +1298,12 @@
       <c r="I26" s="3">
         <v>17</v>
       </c>
-      <c r="J26" s="3">
-        <v>45</v>
-      </c>
+      <c r="J26" s="3"/>
       <c r="K26" s="3">
         <v>46</v>
       </c>
       <c r="L26" s="3">
-        <v>1371</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1342,7 +1320,7 @@
         <v>108</v>
       </c>
       <c r="E27" s="3">
-        <v>137</v>
+        <v>66</v>
       </c>
       <c r="F27" s="3">
         <v>2</v>
@@ -1356,50 +1334,70 @@
       <c r="I27" s="3">
         <v>19</v>
       </c>
-      <c r="J27" s="3">
-        <v>3</v>
-      </c>
+      <c r="J27" s="3"/>
       <c r="K27" s="3">
         <v>20</v>
       </c>
       <c r="L27" s="3">
-        <v>1067</v>
+        <v>993</v>
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="2">
+        <v>1016</v>
+      </c>
+      <c r="B28" s="2">
+        <v>21253</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="4">
-        <v>5267</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1183</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1566</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="B29" s="2"/>
+      <c r="C29" s="4">
+        <v>4780</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1066</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1224</v>
+      </c>
+      <c r="F29" s="4">
         <v>84</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G29" s="4">
         <v>44</v>
       </c>
-      <c r="H28" s="4">
-        <v>4319</v>
-      </c>
-      <c r="I28" s="4">
-        <v>233</v>
-      </c>
-      <c r="J28" s="4">
-        <v>73</v>
-      </c>
-      <c r="K28" s="4">
-        <v>352</v>
-      </c>
-      <c r="L28" s="4">
-        <v>13121</v>
+      <c r="H29" s="4">
+        <v>3717</v>
+      </c>
+      <c r="I29" s="4">
+        <v>175</v>
+      </c>
+      <c r="J29" s="4">
+        <v>25</v>
+      </c>
+      <c r="K29" s="4">
+        <v>219</v>
+      </c>
+      <c r="L29" s="4">
+        <v>11334</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1451,13 +1449,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="B2" s="2">
-        <v>21088</v>
+        <v>21092</v>
       </c>
       <c r="C2" s="3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -1465,7 +1463,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1473,60 +1471,66 @@
         <v>4001</v>
       </c>
       <c r="B3" s="2">
-        <v>21092</v>
+        <v>21176</v>
       </c>
       <c r="C3" s="3">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3">
-        <v>20</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B4" s="2">
-        <v>21176</v>
+        <v>21085</v>
       </c>
       <c r="C4" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3">
+        <v>8</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B5" s="2">
-        <v>21229</v>
+        <v>21086</v>
       </c>
       <c r="C5" s="3">
-        <v>215</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="D5" s="3">
+        <v>27</v>
+      </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="3">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3">
+        <v>11</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>215</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1534,147 +1538,139 @@
         <v>4002</v>
       </c>
       <c r="B6" s="2">
-        <v>21085</v>
+        <v>21515</v>
       </c>
       <c r="C6" s="3">
-        <v>47</v>
-      </c>
-      <c r="D6" s="3">
-        <v>34</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="B7" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C7" s="3">
-        <v>108</v>
-      </c>
+        <v>21081</v>
+      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3">
-        <v>17</v>
-      </c>
-      <c r="F7" s="3">
-        <v>37</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>200</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="B8" s="2">
-        <v>21515</v>
+        <v>21195</v>
       </c>
       <c r="C8" s="3">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>5</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>157</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="B9" s="2">
-        <v>21081</v>
+        <v>21246</v>
       </c>
       <c r="C9" s="3">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="D9" s="3">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3">
-        <v>128</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B10" s="2">
-        <v>21195</v>
+        <v>21083</v>
       </c>
       <c r="C10" s="3">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3">
-        <v>53</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>82</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3">
-        <v>122</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B11" s="2">
-        <v>21246</v>
+        <v>21234</v>
       </c>
       <c r="C11" s="3">
-        <v>130</v>
+        <v>721</v>
       </c>
       <c r="D11" s="3">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3">
-        <v>36</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3">
         <v>2</v>
       </c>
+      <c r="F11" s="3">
+        <v>75</v>
+      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>205</v>
+        <v>821</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1682,178 +1678,164 @@
         <v>4005</v>
       </c>
       <c r="B12" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C12" s="3">
-        <v>122</v>
+        <v>330</v>
       </c>
       <c r="D12" s="3">
         <v>30</v>
       </c>
       <c r="E12" s="3">
-        <v>35</v>
-      </c>
-      <c r="F12" s="3">
-        <v>126</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>313</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="B13" s="2">
-        <v>21234</v>
+        <v>21523</v>
       </c>
       <c r="C13" s="3">
-        <v>721</v>
-      </c>
-      <c r="D13" s="3">
-        <v>23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>75</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3">
+        <v>24</v>
+      </c>
       <c r="I13" s="3">
-        <v>821</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2">
-        <v>4005</v>
+        <v>4007</v>
       </c>
       <c r="B14" s="2">
-        <v>21457</v>
+        <v>21082</v>
       </c>
       <c r="C14" s="3">
-        <v>330</v>
+        <v>31</v>
       </c>
       <c r="D14" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>10</v>
+      </c>
       <c r="H14" s="3">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I14" s="3">
-        <v>426</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="B15" s="2">
-        <v>21523</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
+        <v>21089</v>
+      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3">
-        <v>48</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="I15" s="3">
-        <v>73</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="B16" s="2">
-        <v>21082</v>
+        <v>21090</v>
       </c>
       <c r="C16" s="3">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="D16" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3">
-        <v>57</v>
-      </c>
-      <c r="G16" s="3">
-        <v>10</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
       <c r="H16" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I16" s="3">
-        <v>205</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B17" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>21075</v>
+      </c>
+      <c r="C17" s="3">
+        <v>117</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="I17" s="3">
-        <v>104</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B18" s="2">
-        <v>21090</v>
+        <v>21094</v>
       </c>
       <c r="C18" s="3">
-        <v>194</v>
-      </c>
-      <c r="D18" s="3">
-        <v>26</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>75</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3">
-        <v>42</v>
-      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3">
-        <v>339</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1861,97 +1843,53 @@
         <v>4011</v>
       </c>
       <c r="B19" s="2">
-        <v>21075</v>
+        <v>21533</v>
       </c>
       <c r="C19" s="3">
-        <v>117</v>
-      </c>
-      <c r="D19" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="D19" s="3">
+        <v>25</v>
+      </c>
       <c r="E19" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I19" s="3">
-        <v>162</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B20" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C20" s="3">
-        <v>44</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B21" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C21" s="3">
-        <v>241</v>
-      </c>
-      <c r="D21" s="3">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="2" t="s">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4">
-        <v>2592</v>
-      </c>
-      <c r="D22" s="4">
-        <v>396</v>
-      </c>
-      <c r="E22" s="4">
-        <v>272</v>
-      </c>
-      <c r="F22" s="4">
-        <v>467</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="B20" s="2"/>
+      <c r="C20" s="4">
+        <v>2129</v>
+      </c>
+      <c r="D20" s="4">
+        <v>298</v>
+      </c>
+      <c r="E20" s="4">
+        <v>234</v>
+      </c>
+      <c r="F20" s="4">
+        <v>288</v>
+      </c>
+      <c r="G20" s="4">
         <v>42</v>
       </c>
-      <c r="H22" s="4">
-        <v>252</v>
-      </c>
-      <c r="I22" s="4">
-        <v>4021</v>
+      <c r="H20" s="4">
+        <v>181</v>
+      </c>
+      <c r="I20" s="4">
+        <v>3172</v>
       </c>
     </row>
   </sheetData>
@@ -1961,7 +1899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2021,15 +1959,13 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>60138</v>
+        <v>60127</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3">
-        <v>6</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -2037,22 +1973,22 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="L2" s="3">
+        <v>54</v>
+      </c>
       <c r="M2" s="3">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>60496</v>
+        <v>60129</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="3">
-        <v>8</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -2060,117 +1996,119 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>46</v>
+      </c>
       <c r="M3" s="3">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>60507</v>
+        <v>60131</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>8</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>41</v>
+      </c>
       <c r="M4" s="3">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>60127</v>
+        <v>60138</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3">
-        <v>11</v>
-      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>89</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="M5" s="3">
-        <v>135</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>60129</v>
+        <v>60496</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="3">
-        <v>9</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="3">
+        <v>121</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>120</v>
-      </c>
+      <c r="L6" s="3"/>
       <c r="M6" s="3">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>60131</v>
+        <v>60507</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>57</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3">
-        <v>112</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>60137</v>
+        <v>60127</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -2178,22 +2116,22 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>47</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>60224</v>
+        <v>60129</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -2201,22 +2139,22 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>28</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>60227</v>
+        <v>60131</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -2224,19 +2162,19 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3">
-        <v>32</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2">
         <v>60138</v>
@@ -2246,22 +2184,20 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3">
-        <v>120</v>
-      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3">
+        <v>42</v>
+      </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <v>1</v>
-      </c>
+      <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>121</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2">
         <v>60496</v>
@@ -2271,49 +2207,43 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3">
-        <v>171</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3">
+        <v>66</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>172</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>60507</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>88</v>
-      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3">
+        <v>118</v>
+      </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>90</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>60127</v>
@@ -2323,20 +2253,20 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3">
-        <v>192</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>215</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>192</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2">
         <v>60129</v>
@@ -2346,20 +2276,20 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3">
-        <v>168</v>
-      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3">
+        <v>251</v>
+      </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3">
-        <v>168</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2">
         <v>60131</v>
@@ -2369,23 +2299,23 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>205</v>
-      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>126</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3">
-        <v>205</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2">
-        <v>60137</v>
+        <v>60138</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -2393,70 +2323,70 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3">
-        <v>33</v>
-      </c>
+      <c r="I17" s="3">
+        <v>87</v>
+      </c>
+      <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3">
-        <v>33</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2">
-        <v>60224</v>
+        <v>60496</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3">
-        <v>18</v>
-      </c>
+      <c r="I18" s="3">
+        <v>145</v>
+      </c>
+      <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3">
-        <v>18</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B19" s="2">
-        <v>60227</v>
+        <v>60507</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3">
-        <v>1</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3">
-        <v>84</v>
-      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
+        <v>90</v>
+      </c>
+      <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B20" s="2">
-        <v>60138</v>
+        <v>60127</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -2464,22 +2394,24 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="I20" s="3">
+        <v>165</v>
+      </c>
       <c r="J20" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B21" s="2">
-        <v>60496</v>
+        <v>60129</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -2487,22 +2419,22 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3">
-        <v>72</v>
-      </c>
+      <c r="I21" s="3">
+        <v>133</v>
+      </c>
+      <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3">
-        <v>72</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2">
-        <v>60507</v>
+        <v>60131</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -2510,19 +2442,21 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="I22" s="3">
+        <v>142</v>
+      </c>
       <c r="J22" s="3">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3">
-        <v>120</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2">
         <v>60127</v>
@@ -2530,22 +2464,24 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3">
+        <v>58</v>
+      </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3">
-        <v>215</v>
-      </c>
-      <c r="K23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3">
+        <v>30</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3">
-        <v>215</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2">
         <v>60129</v>
@@ -2553,22 +2489,24 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3">
+        <v>55</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3">
-        <v>251</v>
-      </c>
-      <c r="K24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3">
+        <v>20</v>
+      </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3">
-        <v>251</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2">
         <v>60131</v>
@@ -2576,332 +2514,330 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3">
+        <v>39</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>126</v>
-      </c>
-      <c r="K25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3">
+        <v>19</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3">
-        <v>126</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C26" s="3"/>
+        <v>60138</v>
+      </c>
+      <c r="C26" s="3">
+        <v>41</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="3">
-        <v>26</v>
-      </c>
-      <c r="J26" s="3">
-        <v>3</v>
-      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B27" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C27" s="3"/>
+        <v>60496</v>
+      </c>
+      <c r="C27" s="3">
+        <v>38</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3">
-        <v>15</v>
-      </c>
+      <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B28" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C28" s="3"/>
+        <v>60507</v>
+      </c>
+      <c r="C28" s="3">
+        <v>28</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="3">
-        <v>10</v>
-      </c>
+      <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B29" s="2">
-        <v>60138</v>
-      </c>
-      <c r="C29" s="3"/>
+        <v>60127</v>
+      </c>
+      <c r="C29" s="3">
+        <v>184</v>
+      </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3">
-        <v>139</v>
-      </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3">
-        <v>139</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
+        <v>60129</v>
+      </c>
+      <c r="C30" s="3">
+        <v>115</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3">
-        <v>208</v>
-      </c>
+      <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
-        <v>209</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B31" s="2">
-        <v>60507</v>
-      </c>
-      <c r="C31" s="3"/>
+        <v>60131</v>
+      </c>
+      <c r="C31" s="3">
+        <v>134</v>
+      </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3">
+        <v>4</v>
+      </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="3">
-        <v>132</v>
-      </c>
+      <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B32" s="2">
-        <v>60127</v>
+        <v>60138</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3">
+        <v>4</v>
+      </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="3">
-        <v>186</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1</v>
-      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
-        <v>187</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B33" s="2">
-        <v>60129</v>
+        <v>60224</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="G33" s="3">
+        <v>7</v>
+      </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="3">
-        <v>154</v>
-      </c>
+      <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3">
-        <v>154</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2">
-        <v>60131</v>
+        <v>60127</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="G34" s="3">
+        <v>3</v>
+      </c>
       <c r="H34" s="3"/>
-      <c r="I34" s="3">
-        <v>165</v>
-      </c>
-      <c r="J34" s="3">
-        <v>1</v>
-      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
-        <v>166</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2">
-        <v>60137</v>
+        <v>60129</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="3">
-        <v>11</v>
-      </c>
-      <c r="G35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3">
+        <v>5</v>
+      </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B36" s="2">
-        <v>60224</v>
+        <v>60131</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3">
-        <v>8</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3">
+        <v>3</v>
+      </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2">
-        <v>60227</v>
+        <v>60132</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3">
-        <v>8</v>
-      </c>
-      <c r="G37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3">
+        <v>6</v>
+      </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B38" s="2">
-        <v>60138</v>
+        <v>60134</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="G38" s="3">
+        <v>4</v>
+      </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3">
-        <v>5</v>
-      </c>
+      <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2">
-        <v>60496</v>
+        <v>60130</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -2912,19 +2848,19 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B40" s="2">
-        <v>60507</v>
+        <v>60139</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -2935,501 +2871,505 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B41" s="2">
-        <v>60127</v>
+        <v>60306</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>78</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3">
-        <v>108</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B42" s="2">
-        <v>60129</v>
+        <v>60128</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3">
+        <v>6</v>
+      </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>74</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3">
-        <v>20</v>
-      </c>
-      <c r="L42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>60</v>
+      </c>
       <c r="M42" s="3">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B43" s="2">
-        <v>60131</v>
+        <v>60132</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3">
+        <v>26</v>
+      </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>60</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3">
-        <v>19</v>
-      </c>
-      <c r="L43" s="3"/>
+      <c r="J43" s="3">
+        <v>1</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3">
+        <v>317</v>
+      </c>
       <c r="M43" s="3">
-        <v>79</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B44" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C44" s="3">
-        <v>23</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="L44" s="3">
+        <v>82</v>
+      </c>
       <c r="M44" s="3">
-        <v>24</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B45" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C45" s="3">
-        <v>50</v>
-      </c>
+        <v>60128</v>
+      </c>
+      <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="3">
-        <v>2</v>
-      </c>
+      <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
+      <c r="H45" s="3">
+        <v>108</v>
+      </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3">
-        <v>52</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B46" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C46" s="3">
-        <v>49</v>
-      </c>
+        <v>60132</v>
+      </c>
+      <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
+      <c r="H46" s="3">
+        <v>374</v>
+      </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
+      <c r="L46" s="3">
+        <v>2</v>
+      </c>
       <c r="M46" s="3">
-        <v>49</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B47" s="2">
-        <v>60138</v>
-      </c>
-      <c r="C47" s="3">
-        <v>85</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="3">
-        <v>1</v>
-      </c>
+      <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="3">
+        <v>196</v>
+      </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3">
-        <v>86</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B48" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C48" s="3">
-        <v>79</v>
-      </c>
+        <v>60128</v>
+      </c>
+      <c r="C48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="3">
-        <v>2</v>
-      </c>
+      <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
+      <c r="J48" s="3">
+        <v>140</v>
+      </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3">
-        <v>81</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B49" s="2">
-        <v>60507</v>
-      </c>
-      <c r="C49" s="3">
-        <v>52</v>
-      </c>
+        <v>60132</v>
+      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
+      <c r="J49" s="3">
+        <v>136</v>
+      </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3">
-        <v>52</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B50" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C50" s="3">
-        <v>243</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="3">
-        <v>1</v>
-      </c>
+      <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
+      <c r="J50" s="3">
+        <v>99</v>
+      </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3">
-        <v>244</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B51" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C51" s="3">
-        <v>167</v>
-      </c>
+        <v>60128</v>
+      </c>
+      <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="I51" s="3">
+        <v>106</v>
+      </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3">
-        <v>167</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B52" s="2">
-        <v>60131</v>
-      </c>
-      <c r="C52" s="3">
-        <v>216</v>
-      </c>
+        <v>60132</v>
+      </c>
+      <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="3">
-        <v>4</v>
-      </c>
+      <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+      <c r="I52" s="3">
+        <v>522</v>
+      </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3">
-        <v>220</v>
+        <v>522</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B53" s="2">
-        <v>60138</v>
+        <v>60134</v>
       </c>
       <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="D53" s="3">
+        <v>2</v>
+      </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <v>4</v>
-      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="I53" s="3">
+        <v>131</v>
+      </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3">
-        <v>4</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B54" s="2">
-        <v>60224</v>
+        <v>60128</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3">
-        <v>7</v>
-      </c>
+      <c r="F54" s="3">
+        <v>27</v>
+      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
+      <c r="K54" s="3">
+        <v>15</v>
+      </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B55" s="2">
-        <v>60127</v>
+        <v>60132</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3">
-        <v>3</v>
-      </c>
+      <c r="F55" s="3">
+        <v>130</v>
+      </c>
+      <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
+      <c r="K55" s="3">
+        <v>77</v>
+      </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3">
-        <v>3</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B56" s="2">
-        <v>60129</v>
+        <v>60134</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3">
-        <v>5</v>
-      </c>
+      <c r="F56" s="3">
+        <v>82</v>
+      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
+      <c r="K56" s="3">
+        <v>46</v>
+      </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B57" s="2">
-        <v>60131</v>
-      </c>
-      <c r="C57" s="3"/>
+        <v>60128</v>
+      </c>
+      <c r="C57" s="3">
+        <v>94</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3">
-        <v>3</v>
-      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B58" s="2">
         <v>60132</v>
       </c>
-      <c r="C58" s="3"/>
+      <c r="C58" s="3">
+        <v>414</v>
+      </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3">
-        <v>6</v>
-      </c>
+      <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3">
-        <v>6</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B59" s="2">
         <v>60134</v>
       </c>
-      <c r="C59" s="3"/>
+      <c r="C59" s="3">
+        <v>188</v>
+      </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+      <c r="E59" s="3">
+        <v>1</v>
+      </c>
       <c r="F59" s="3"/>
-      <c r="G59" s="3">
-        <v>4</v>
-      </c>
+      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
-      <c r="K59" s="3">
-        <v>2</v>
-      </c>
+      <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3">
-        <v>6</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B60" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C60" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C60" s="3">
+        <v>137</v>
+      </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
+      <c r="E60" s="3">
+        <v>1</v>
+      </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
-      <c r="K60" s="3">
-        <v>27</v>
-      </c>
+      <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3">
-        <v>27</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B61" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C61" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C61" s="3">
+        <v>179</v>
+      </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3437,22 +3377,22 @@
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
-      <c r="K61" s="3">
-        <v>16</v>
-      </c>
+      <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3">
-        <v>16</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B62" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C62" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C62" s="3">
+        <v>169</v>
+      </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3460,45 +3400,47 @@
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
-      <c r="K62" s="3">
-        <v>32</v>
-      </c>
+      <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3">
-        <v>32</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B63" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C63" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C63" s="3">
+        <v>268</v>
+      </c>
       <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
+      <c r="E63" s="3">
+        <v>5</v>
+      </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="3">
-        <v>18</v>
-      </c>
+      <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3">
-        <v>18</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B64" s="2">
         <v>60355</v>
       </c>
-      <c r="C64" s="3"/>
+      <c r="C64" s="3">
+        <v>170</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3506,24 +3448,22 @@
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="3">
-        <v>11</v>
-      </c>
+      <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3">
-        <v>11</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B65" s="2">
-        <v>60128</v>
+        <v>60135</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3533,49 +3473,47 @@
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="M65" s="3">
-        <v>127</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B66" s="2">
-        <v>60132</v>
+        <v>60139</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="3">
-        <v>1</v>
-      </c>
+      <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3">
-        <v>585</v>
+        <v>260</v>
       </c>
       <c r="M66" s="3">
-        <v>612</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B67" s="2">
-        <v>60134</v>
+        <v>60306</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3585,181 +3523,193 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="M67" s="3">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B68" s="2">
-        <v>60128</v>
+        <v>60130</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>5</v>
+      </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3">
-        <v>108</v>
-      </c>
+      <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
+      <c r="L68" s="3">
+        <v>248</v>
+      </c>
       <c r="M68" s="3">
-        <v>108</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B69" s="2">
-        <v>60132</v>
+        <v>60355</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3">
+        <v>15</v>
+      </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="3">
-        <v>374</v>
-      </c>
+      <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3">
-        <v>2</v>
+        <v>356</v>
       </c>
       <c r="M69" s="3">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B70" s="2">
-        <v>60134</v>
+        <v>60139</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3">
+        <v>80</v>
+      </c>
       <c r="G70" s="3"/>
-      <c r="H70" s="3">
-        <v>196</v>
-      </c>
+      <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+      <c r="K70" s="3">
+        <v>19</v>
+      </c>
       <c r="L70" s="3"/>
       <c r="M70" s="3">
-        <v>196</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B71" s="2">
-        <v>60128</v>
+        <v>60306</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3">
+        <v>78</v>
+      </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
-      <c r="J71" s="3">
-        <v>140</v>
-      </c>
-      <c r="K71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3">
+        <v>26</v>
+      </c>
       <c r="L71" s="3"/>
       <c r="M71" s="3">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B72" s="2">
-        <v>60132</v>
+        <v>60355</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3">
+        <v>91</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
-      <c r="J72" s="3">
-        <v>136</v>
-      </c>
-      <c r="K72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3">
+        <v>37</v>
+      </c>
       <c r="L72" s="3"/>
       <c r="M72" s="3">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B73" s="2">
-        <v>60134</v>
+        <v>60130</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3">
+        <v>51</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
-      <c r="J73" s="3">
-        <v>99</v>
-      </c>
-      <c r="K73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3">
+        <v>27</v>
+      </c>
       <c r="L73" s="3"/>
       <c r="M73" s="3">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B74" s="2">
-        <v>60128</v>
+        <v>60135</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3">
+        <v>45</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="3">
-        <v>112</v>
-      </c>
+      <c r="I74" s="3"/>
       <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
+      <c r="K74" s="3">
+        <v>13</v>
+      </c>
       <c r="L74" s="3"/>
       <c r="M74" s="3">
-        <v>112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B75" s="2">
-        <v>60132</v>
+        <v>60135</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
@@ -3768,916 +3718,353 @@
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3">
-        <v>564</v>
+        <v>172</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3">
-        <v>564</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B76" s="2">
-        <v>60134</v>
+        <v>60139</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="3">
-        <v>2</v>
-      </c>
+      <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3">
-        <v>145</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B77" s="2">
-        <v>60128</v>
+        <v>60306</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="3">
-        <v>27</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="I77" s="3">
+        <v>215</v>
+      </c>
       <c r="J77" s="3"/>
-      <c r="K77" s="3">
-        <v>15</v>
-      </c>
+      <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3">
-        <v>42</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B78" s="2">
-        <v>60132</v>
+        <v>60130</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
+      <c r="D78" s="3">
+        <v>1</v>
+      </c>
       <c r="E78" s="3"/>
-      <c r="F78" s="3">
-        <v>139</v>
-      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="I78" s="3">
+        <v>204</v>
+      </c>
       <c r="J78" s="3"/>
-      <c r="K78" s="3">
-        <v>77</v>
-      </c>
+      <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B79" s="2">
-        <v>60134</v>
+        <v>60355</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="3">
-        <v>97</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="I79" s="3">
+        <v>282</v>
+      </c>
       <c r="J79" s="3"/>
-      <c r="K79" s="3">
-        <v>46</v>
-      </c>
+      <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3">
-        <v>143</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B80" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C80" s="3">
-        <v>94</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
+      <c r="J80" s="3">
+        <v>80</v>
+      </c>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B81" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C81" s="3">
-        <v>414</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
+      <c r="J81" s="3">
+        <v>71</v>
+      </c>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3">
-        <v>414</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B82" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C82" s="3">
-        <v>188</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C82" s="3"/>
       <c r="D82" s="3"/>
-      <c r="E82" s="3">
-        <v>1</v>
-      </c>
+      <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
+      <c r="J82" s="3">
+        <v>72</v>
+      </c>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3">
-        <v>189</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="2">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B83" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C83" s="3">
-        <v>137</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C83" s="3"/>
       <c r="D83" s="3"/>
-      <c r="E83" s="3">
-        <v>1</v>
-      </c>
+      <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
+      <c r="J83" s="3">
+        <v>102</v>
+      </c>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3">
-        <v>138</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="2">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B84" s="2">
         <v>60139</v>
       </c>
-      <c r="C84" s="3">
-        <v>179</v>
-      </c>
+      <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
+      <c r="H84" s="3">
+        <v>205</v>
+      </c>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3">
-        <v>179</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="2">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B85" s="2">
         <v>60306</v>
       </c>
-      <c r="C85" s="3">
-        <v>169</v>
-      </c>
+      <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
+      <c r="H85" s="3">
+        <v>200</v>
+      </c>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
       <c r="M85" s="3">
-        <v>169</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="2">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B86" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C86" s="3">
-        <v>268</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C86" s="3"/>
       <c r="D86" s="3"/>
-      <c r="E86" s="3">
-        <v>5</v>
-      </c>
+      <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
+      <c r="H86" s="3">
+        <v>342</v>
+      </c>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="2">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B87" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C87" s="3">
-        <v>170</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
+      <c r="H87" s="3">
+        <v>124</v>
+      </c>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3">
-        <v>170</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B88" s="2">
         <v>60135</v>
       </c>
       <c r="C88" s="3"/>
-      <c r="D88" s="3">
-        <v>11</v>
-      </c>
+      <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
+      <c r="H88" s="3">
+        <v>149</v>
+      </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
-      <c r="L88" s="3">
-        <v>284</v>
-      </c>
+      <c r="L88" s="3"/>
       <c r="M88" s="3">
-        <v>295</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="2">
-        <v>34</v>
-      </c>
-      <c r="B89" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3">
-        <v>10</v>
-      </c>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3">
-        <v>330</v>
-      </c>
-      <c r="M89" s="3">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="2">
-        <v>34</v>
-      </c>
-      <c r="B90" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3">
-        <v>5</v>
-      </c>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3">
-        <v>220</v>
-      </c>
-      <c r="M90" s="3">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="2">
-        <v>35</v>
-      </c>
-      <c r="B91" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3">
-        <v>248</v>
-      </c>
-      <c r="M91" s="3">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="2">
-        <v>35</v>
-      </c>
-      <c r="B92" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3">
-        <v>15</v>
-      </c>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3">
-        <v>356</v>
-      </c>
-      <c r="M92" s="3">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13">
-      <c r="A93" s="2">
-        <v>36</v>
-      </c>
-      <c r="B93" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3">
-        <v>80</v>
-      </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3">
-        <v>19</v>
-      </c>
-      <c r="L93" s="3"/>
-      <c r="M93" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13">
-      <c r="A94" s="2">
-        <v>36</v>
-      </c>
-      <c r="B94" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3">
-        <v>78</v>
-      </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3">
-        <v>26</v>
-      </c>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13">
-      <c r="A95" s="2">
-        <v>36</v>
-      </c>
-      <c r="B95" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3">
+      <c r="A89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="4">
+        <v>2159</v>
+      </c>
+      <c r="D89" s="4">
         <v>91</v>
       </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3">
-        <v>37</v>
-      </c>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13">
-      <c r="A96" s="2">
-        <v>37</v>
-      </c>
-      <c r="B96" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3">
-        <v>51</v>
-      </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3">
-        <v>27</v>
-      </c>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13">
-      <c r="A97" s="2">
-        <v>37</v>
-      </c>
-      <c r="B97" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3">
-        <v>45</v>
-      </c>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3">
-        <v>13</v>
-      </c>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13">
-      <c r="A98" s="2">
-        <v>38</v>
-      </c>
-      <c r="B98" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3">
-        <v>172</v>
-      </c>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13">
-      <c r="A99" s="2">
-        <v>38</v>
-      </c>
-      <c r="B99" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3">
-        <v>185</v>
-      </c>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13">
-      <c r="A100" s="2">
-        <v>38</v>
-      </c>
-      <c r="B100" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3">
-        <v>215</v>
-      </c>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-      <c r="M100" s="3">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
-      <c r="A101" s="2">
-        <v>39</v>
-      </c>
-      <c r="B101" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3">
-        <v>1</v>
-      </c>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3">
-        <v>204</v>
-      </c>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13">
-      <c r="A102" s="2">
-        <v>39</v>
-      </c>
-      <c r="B102" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3">
-        <v>282</v>
-      </c>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13">
-      <c r="A103" s="2">
-        <v>51</v>
-      </c>
-      <c r="B103" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3">
-        <v>80</v>
-      </c>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13">
-      <c r="A104" s="2">
-        <v>51</v>
-      </c>
-      <c r="B104" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3">
-        <v>71</v>
-      </c>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3"/>
-      <c r="M104" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="A105" s="2">
-        <v>51</v>
-      </c>
-      <c r="B105" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="3">
-        <v>72</v>
-      </c>
-      <c r="K105" s="3"/>
-      <c r="L105" s="3"/>
-      <c r="M105" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13">
-      <c r="A106" s="2">
-        <v>52</v>
-      </c>
-      <c r="B106" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3">
-        <v>102</v>
-      </c>
-      <c r="K106" s="3"/>
-      <c r="L106" s="3"/>
-      <c r="M106" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="A107" s="2">
-        <v>53</v>
-      </c>
-      <c r="B107" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3">
-        <v>205</v>
-      </c>
-      <c r="I107" s="3"/>
-      <c r="J107" s="3"/>
-      <c r="K107" s="3"/>
-      <c r="L107" s="3"/>
-      <c r="M107" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13">
-      <c r="A108" s="2">
-        <v>53</v>
-      </c>
-      <c r="B108" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3">
-        <v>200</v>
-      </c>
-      <c r="I108" s="3"/>
-      <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
-      <c r="L108" s="3"/>
-      <c r="M108" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13">
-      <c r="A109" s="2">
-        <v>53</v>
-      </c>
-      <c r="B109" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3">
-        <v>342</v>
-      </c>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13">
-      <c r="A110" s="2">
-        <v>54</v>
-      </c>
-      <c r="B110" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3">
-        <v>124</v>
-      </c>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13">
-      <c r="A111" s="2">
-        <v>54</v>
-      </c>
-      <c r="B111" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3">
-        <v>149</v>
-      </c>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13">
-      <c r="A112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B112" s="2"/>
-      <c r="C112" s="4">
-        <v>2583</v>
-      </c>
-      <c r="D112" s="4">
-        <v>143</v>
-      </c>
-      <c r="E112" s="4">
-        <v>18</v>
-      </c>
-      <c r="F112" s="4">
-        <v>847</v>
-      </c>
-      <c r="G112" s="4">
+      <c r="E89" s="4">
+        <v>12</v>
+      </c>
+      <c r="F89" s="4">
+        <v>736</v>
+      </c>
+      <c r="G89" s="4">
         <v>32</v>
       </c>
-      <c r="H112" s="4">
-        <v>2750</v>
-      </c>
-      <c r="I112" s="4">
-        <v>2913</v>
-      </c>
-      <c r="J112" s="4">
-        <v>1669</v>
-      </c>
-      <c r="K112" s="4">
-        <v>452</v>
-      </c>
-      <c r="L112" s="4">
-        <v>2636</v>
-      </c>
-      <c r="M112" s="4">
-        <v>14043</v>
+      <c r="H89" s="4">
+        <v>2448</v>
+      </c>
+      <c r="I89" s="4">
+        <v>2580</v>
+      </c>
+      <c r="J89" s="4">
+        <v>1521</v>
+      </c>
+      <c r="K89" s="4">
+        <v>363</v>
+      </c>
+      <c r="L89" s="4">
+        <v>1849</v>
+      </c>
+      <c r="M89" s="4">
+        <v>11791</v>
       </c>
     </row>
   </sheetData>
@@ -4687,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4723,33 +4110,35 @@
         <v>2000</v>
       </c>
       <c r="B2" s="2">
-        <v>21088</v>
+        <v>21469</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B3" s="2">
-        <v>21469</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>21176</v>
+      </c>
+      <c r="C3" s="3">
+        <v>36</v>
+      </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4757,81 +4146,77 @@
         <v>2001</v>
       </c>
       <c r="B4" s="2">
-        <v>21176</v>
+        <v>21229</v>
       </c>
       <c r="C4" s="3">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3">
-        <v>17</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>66</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B5" s="2">
-        <v>21229</v>
+        <v>21092</v>
       </c>
       <c r="C5" s="3">
-        <v>433</v>
+        <v>61</v>
       </c>
       <c r="D5" s="3">
-        <v>32</v>
-      </c>
-      <c r="E5" s="3">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3">
-        <v>17</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>490</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B6" s="2">
-        <v>21092</v>
-      </c>
-      <c r="C6" s="3">
-        <v>61</v>
-      </c>
+        <v>21087</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B7" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>21086</v>
+      </c>
+      <c r="C7" s="3">
+        <v>243</v>
+      </c>
       <c r="D7" s="3">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>53</v>
+      </c>
       <c r="G7" s="3">
-        <v>29</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4839,45 +4224,45 @@
         <v>2004</v>
       </c>
       <c r="B8" s="2">
-        <v>21086</v>
+        <v>21515</v>
       </c>
       <c r="C8" s="3">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3">
-        <v>350</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B9" s="2">
-        <v>21515</v>
+        <v>21081</v>
       </c>
       <c r="C9" s="3">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3">
         <v>14</v>
       </c>
-      <c r="E9" s="3">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4</v>
-      </c>
       <c r="G9" s="3">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4885,66 +4270,66 @@
         <v>2005</v>
       </c>
       <c r="B10" s="2">
-        <v>21081</v>
+        <v>21085</v>
       </c>
       <c r="C10" s="3">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="D10" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G10" s="3">
-        <v>90</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B11" s="2">
-        <v>21085</v>
+        <v>21089</v>
       </c>
       <c r="C11" s="3">
-        <v>221</v>
-      </c>
-      <c r="D11" s="3">
         <v>50</v>
       </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3">
-        <v>315</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B12" s="2">
-        <v>21089</v>
+        <v>21082</v>
       </c>
       <c r="C12" s="3">
-        <v>50</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>252</v>
+      </c>
+      <c r="D12" s="3">
+        <v>28</v>
+      </c>
       <c r="E12" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F12" s="3">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3">
-        <v>58</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4952,45 +4337,43 @@
         <v>2007</v>
       </c>
       <c r="B13" s="2">
-        <v>21082</v>
+        <v>21234</v>
       </c>
       <c r="C13" s="3">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D13" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F13" s="3">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G13" s="3">
-        <v>358</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B14" s="2">
-        <v>21234</v>
+        <v>21083</v>
       </c>
       <c r="C14" s="3">
-        <v>235</v>
-      </c>
-      <c r="D14" s="3">
-        <v>42</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F14" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G14" s="3">
-        <v>317</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4998,43 +4381,45 @@
         <v>2008</v>
       </c>
       <c r="B15" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C15" s="3">
-        <v>64</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>420</v>
+      </c>
+      <c r="D15" s="3">
+        <v>22</v>
+      </c>
       <c r="E15" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G15" s="3">
-        <v>85</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B16" s="2">
-        <v>21457</v>
+        <v>21195</v>
       </c>
       <c r="C16" s="3">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="D16" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E16" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F16" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G16" s="3">
-        <v>459</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5042,123 +4427,100 @@
         <v>2009</v>
       </c>
       <c r="B17" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C17" s="3">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D17" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E17" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B18" s="2">
-        <v>21246</v>
+        <v>21090</v>
       </c>
       <c r="C18" s="3">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D18" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F18" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G18" s="3">
-        <v>122</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B19" s="2">
-        <v>21090</v>
+        <v>21533</v>
       </c>
       <c r="C19" s="3">
-        <v>34</v>
-      </c>
-      <c r="D19" s="3">
-        <v>3</v>
-      </c>
-      <c r="E19" s="3">
-        <v>8</v>
-      </c>
-      <c r="F19" s="3">
-        <v>4</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B20" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C20" s="3">
-        <v>30</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>21085</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B21" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="2" t="s">
+      <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4">
+      <c r="B21" s="2"/>
+      <c r="C21" s="4">
         <v>2398</v>
       </c>
-      <c r="D22" s="4">
-        <v>339</v>
-      </c>
-      <c r="E22" s="4">
-        <v>203</v>
-      </c>
-      <c r="F22" s="4">
-        <v>242</v>
-      </c>
-      <c r="G22" s="4">
-        <v>3182</v>
+      <c r="D21" s="4">
+        <v>311</v>
+      </c>
+      <c r="E21" s="4">
+        <v>175</v>
+      </c>
+      <c r="F21" s="4">
+        <v>208</v>
+      </c>
+      <c r="G21" s="4">
+        <v>3092</v>
       </c>
     </row>
   </sheetData>
@@ -5168,7 +4530,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5199,10 +4561,10 @@
         <v>17056</v>
       </c>
       <c r="C2" s="3">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5221,42 +4583,28 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="B4" s="2">
-        <v>17183</v>
+        <v>21094</v>
       </c>
       <c r="C4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2">
-        <v>5003</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4">
-        <v>68</v>
-      </c>
-      <c r="D6" s="4">
-        <v>68</v>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4">
+        <v>29</v>
+      </c>
+      <c r="D5" s="4">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -5266,7 +4614,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5333,15 +4681,15 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
       <c r="K2" s="3">
         <v>105</v>
       </c>
-      <c r="L2" s="3">
-        <v>5</v>
-      </c>
+      <c r="L2" s="3"/>
       <c r="M2" s="3">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5362,11 +4710,9 @@
       <c r="K3" s="3">
         <v>3</v>
       </c>
-      <c r="L3" s="3">
-        <v>5</v>
-      </c>
+      <c r="L3" s="3"/>
       <c r="M3" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5378,14 +4724,14 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3">
         <v>20</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
@@ -5393,15 +4739,13 @@
       <c r="I4" s="3">
         <v>124</v>
       </c>
-      <c r="J4" s="3">
-        <v>58</v>
-      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3">
-        <v>497</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5413,28 +4757,26 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3">
         <v>20</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
         <v>69</v>
       </c>
-      <c r="J5" s="3">
-        <v>28</v>
-      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3">
-        <v>264</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5612,7 +4954,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="G10" s="3">
         <v>157</v>
@@ -5627,13 +4969,13 @@
         <v>230</v>
       </c>
       <c r="K10" s="3">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="L10" s="3">
         <v>3</v>
       </c>
       <c r="M10" s="3">
-        <v>911</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5653,7 +4995,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="G11" s="3">
         <v>52</v>
@@ -5668,13 +5010,13 @@
         <v>278</v>
       </c>
       <c r="K11" s="3">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="L11" s="3">
         <v>6</v>
       </c>
       <c r="M11" s="3">
-        <v>772</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5688,32 +5030,32 @@
         <v>1</v>
       </c>
       <c r="D12" s="3">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="E12" s="3">
         <v>6</v>
       </c>
       <c r="F12" s="3">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="G12" s="3">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
         <v>68</v>
       </c>
       <c r="J12" s="3">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="K12" s="3">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="L12" s="3">
         <v>11</v>
       </c>
       <c r="M12" s="3">
-        <v>618</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5727,143 +5069,233 @@
         <v>5</v>
       </c>
       <c r="D13" s="3">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="E13" s="3">
         <v>28</v>
       </c>
       <c r="F13" s="3">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3">
         <v>67</v>
       </c>
       <c r="J13" s="3">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="K13" s="3">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="L13" s="3">
         <v>17</v>
       </c>
       <c r="M13" s="3">
-        <v>852</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B14" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
+        <v>21081</v>
+      </c>
+      <c r="C14" s="3"/>
       <c r="D14" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3">
-        <v>19</v>
-      </c>
-      <c r="G14" s="3">
-        <v>17</v>
-      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>58</v>
-      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3">
-        <v>26</v>
-      </c>
-      <c r="K14" s="3">
-        <v>26</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>156</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
+        <v>3010</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="2">
+        <v>3010</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3">
+        <v>4</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2">
+        <v>3010</v>
+      </c>
+      <c r="B17" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2">
         <v>3011</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B18" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3">
+        <v>19</v>
+      </c>
+      <c r="G18" s="3">
+        <v>17</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3">
+        <v>58</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3">
+        <v>26</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="2">
+        <v>3011</v>
+      </c>
+      <c r="B19" s="2">
         <v>21090</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
         <v>30</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E19" s="3">
         <v>12</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F19" s="3">
         <v>48</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G19" s="3">
         <v>36</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
         <v>40</v>
       </c>
-      <c r="J15" s="3">
-        <v>37</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="J19" s="3"/>
+      <c r="K19" s="3">
         <v>34</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L19" s="3">
         <v>2</v>
       </c>
-      <c r="M15" s="3">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="2" t="s">
+      <c r="M19" s="3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4">
+      <c r="B20" s="2"/>
+      <c r="C20" s="4">
         <v>36</v>
       </c>
-      <c r="D16" s="4">
-        <v>988</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D20" s="4">
+        <v>860</v>
+      </c>
+      <c r="E20" s="4">
         <v>216</v>
       </c>
-      <c r="F16" s="4">
-        <v>900</v>
-      </c>
-      <c r="G16" s="4">
-        <v>700</v>
-      </c>
-      <c r="H16" s="4">
+      <c r="F20" s="4">
+        <v>635</v>
+      </c>
+      <c r="G20" s="4">
+        <v>542</v>
+      </c>
+      <c r="H20" s="4">
         <v>7</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I20" s="4">
         <v>937</v>
       </c>
-      <c r="J16" s="4">
-        <v>1192</v>
-      </c>
-      <c r="K16" s="4">
-        <v>1370</v>
-      </c>
-      <c r="L16" s="4">
-        <v>69</v>
-      </c>
-      <c r="M16" s="4">
-        <v>6415</v>
+      <c r="J20" s="4">
+        <v>855</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1017</v>
+      </c>
+      <c r="L20" s="4">
+        <v>59</v>
+      </c>
+      <c r="M20" s="4">
+        <v>5164</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="44">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>BSLIQ</t>
+  </si>
+  <si>
+    <t>BSNUF1</t>
   </si>
   <si>
     <t>BSTOY1</t>
@@ -537,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -546,11 +549,11 @@
     <col min="5" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="11" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,8 +590,11 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -602,84 +608,71 @@
         <v>2</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="3">
-        <v>106</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
       <c r="B3" s="2">
         <v>21176</v>
       </c>
-      <c r="C3" s="3">
-        <v>6</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3">
         <v>2</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>118</v>
-      </c>
-      <c r="I3" s="3">
-        <v>12</v>
-      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
         <v>1001</v>
       </c>
       <c r="B4" s="2">
         <v>21092</v>
       </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
       <c r="B5" s="2">
         <v>21176</v>
       </c>
-      <c r="C5" s="3">
-        <v>5</v>
-      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -688,11 +681,12 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" s="3"/>
+      <c r="M5" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
@@ -700,27 +694,26 @@
         <v>21082</v>
       </c>
       <c r="C6" s="3">
-        <v>450</v>
+        <v>396</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3">
-        <v>12</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" s="3"/>
+      <c r="M6" s="3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
         <v>1002</v>
       </c>
@@ -728,27 +721,26 @@
         <v>21469</v>
       </c>
       <c r="C7" s="3">
-        <v>504</v>
+        <v>397</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="3">
-        <v>2</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" s="3"/>
+      <c r="M7" s="3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2">
         <v>1003</v>
       </c>
@@ -776,11 +768,12 @@
         <v>4</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="3">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3">
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="2">
         <v>1003</v>
       </c>
@@ -805,599 +798,473 @@
       <c r="J9" s="3">
         <v>21</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
         <v>60</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>866</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="B10" s="2">
-        <v>21085</v>
+        <v>21086</v>
       </c>
       <c r="C10" s="3">
-        <v>43</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>763</v>
+      </c>
+      <c r="D10" s="3">
+        <v>119</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>12</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
+        <v>433</v>
+      </c>
+      <c r="I10" s="3">
+        <v>56</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>25</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="2">
-        <v>21088</v>
+        <v>21515</v>
       </c>
       <c r="C11" s="3">
-        <v>65</v>
-      </c>
-      <c r="D11" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="D11" s="3">
+        <v>19</v>
+      </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>5</v>
-      </c>
-      <c r="G11" s="3">
-        <v>4</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3">
+        <v>241</v>
+      </c>
+      <c r="I11" s="3">
+        <v>6</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="B12" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+        <v>21195</v>
+      </c>
+      <c r="C12" s="3">
+        <v>709</v>
+      </c>
+      <c r="D12" s="3">
+        <v>137</v>
+      </c>
+      <c r="E12" s="3">
+        <v>221</v>
+      </c>
       <c r="F12" s="3">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3">
+        <v>330</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>31</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="B13" s="2">
-        <v>21229</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+        <v>21246</v>
+      </c>
+      <c r="C13" s="3">
+        <v>592</v>
+      </c>
+      <c r="D13" s="3">
+        <v>102</v>
+      </c>
+      <c r="E13" s="3">
+        <v>200</v>
+      </c>
       <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3">
-        <v>6</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
+        <v>359</v>
+      </c>
+      <c r="I13" s="3">
+        <v>11</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>37</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="B14" s="2">
-        <v>21085</v>
+        <v>21083</v>
       </c>
       <c r="C14" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D14" s="3">
-        <v>21</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="E14" s="3">
+        <v>113</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4</v>
+      </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="3">
+        <v>266</v>
+      </c>
+      <c r="I14" s="3">
+        <v>17</v>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="L14" s="3"/>
+      <c r="M14" s="3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="B15" s="2">
-        <v>21088</v>
+        <v>21457</v>
       </c>
       <c r="C15" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D15" s="3">
-        <v>44</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E15" s="3">
+        <v>76</v>
+      </c>
+      <c r="F15" s="3">
+        <v>8</v>
+      </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="3">
+        <v>243</v>
+      </c>
+      <c r="I15" s="3">
+        <v>12</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="L15" s="3"/>
+      <c r="M15" s="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B16" s="2">
-        <v>21086</v>
+        <v>21089</v>
       </c>
       <c r="C16" s="3">
-        <v>763</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3">
-        <v>119</v>
-      </c>
-      <c r="E16" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="E16" s="3">
+        <v>74</v>
+      </c>
       <c r="F16" s="3">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3">
-        <v>433</v>
+        <v>182</v>
       </c>
       <c r="I16" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="3">
-        <v>25</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B17" s="2">
-        <v>21515</v>
+        <v>21234</v>
       </c>
       <c r="C17" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E17" s="3">
+        <v>67</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="I17" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="3">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="L17" s="3"/>
+      <c r="M17" s="3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B18" s="2">
-        <v>21087</v>
+        <v>21081</v>
       </c>
       <c r="C18" s="3">
-        <v>5</v>
+        <v>551</v>
       </c>
       <c r="D18" s="3">
-        <v>3</v>
+        <v>161</v>
       </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3">
+        <v>7</v>
+      </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="3">
+        <v>325</v>
+      </c>
+      <c r="I18" s="3">
+        <v>17</v>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>46</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B19" s="2">
-        <v>21229</v>
+        <v>21090</v>
       </c>
       <c r="C19" s="3">
-        <v>7</v>
+        <v>476</v>
       </c>
       <c r="D19" s="3">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>301</v>
+      </c>
+      <c r="I19" s="3">
+        <v>19</v>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>20</v>
+      </c>
+      <c r="M19" s="3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B20" s="2">
-        <v>21195</v>
+        <v>21253</v>
       </c>
       <c r="C20" s="3">
-        <v>709</v>
-      </c>
-      <c r="D20" s="3">
-        <v>137</v>
-      </c>
-      <c r="E20" s="3">
-        <v>259</v>
-      </c>
-      <c r="F20" s="3">
-        <v>11</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <v>330</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3">
-        <v>31</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B21" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C21" s="3">
-        <v>592</v>
-      </c>
-      <c r="D21" s="3">
-        <v>102</v>
-      </c>
-      <c r="E21" s="3">
-        <v>224</v>
-      </c>
-      <c r="F21" s="3">
-        <v>10</v>
-      </c>
+        <v>21085</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3">
-        <v>359</v>
-      </c>
-      <c r="I21" s="3">
-        <v>11</v>
-      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3">
-        <v>37</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>2</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="B22" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C22" s="3">
+        <v>21088</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3">
+        <v>6</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="2">
+        <v>1020</v>
+      </c>
+      <c r="B23" s="2">
+        <v>88887</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3">
         <v>11</v>
       </c>
-      <c r="D22" s="3">
-        <v>52</v>
-      </c>
-      <c r="E22" s="3">
-        <v>113</v>
-      </c>
-      <c r="F22" s="3">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3">
-        <v>266</v>
-      </c>
-      <c r="I22" s="3">
-        <v>17</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B23" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C23" s="3">
-        <v>24</v>
-      </c>
-      <c r="D23" s="3">
-        <v>42</v>
-      </c>
-      <c r="E23" s="3">
-        <v>76</v>
-      </c>
-      <c r="F23" s="3">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3">
-        <v>243</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3"/>
+      <c r="M23" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B24" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C24" s="3">
-        <v>4</v>
-      </c>
-      <c r="D24" s="3">
-        <v>22</v>
-      </c>
-      <c r="E24" s="3">
-        <v>74</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="B24" s="2"/>
+      <c r="C24" s="4">
+        <v>4469</v>
+      </c>
+      <c r="D24" s="4">
+        <v>979</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1007</v>
+      </c>
+      <c r="F24" s="4">
+        <v>68</v>
+      </c>
+      <c r="G24" s="4">
         <v>1</v>
       </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3">
-        <v>182</v>
-      </c>
-      <c r="I24" s="3">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B25" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C25" s="3">
-        <v>12</v>
-      </c>
-      <c r="D25" s="3">
-        <v>59</v>
-      </c>
-      <c r="E25" s="3">
-        <v>67</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3">
-        <v>256</v>
-      </c>
-      <c r="I25" s="3">
-        <v>20</v>
-      </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B26" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C26" s="3">
-        <v>551</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="H24" s="4">
+        <v>3255</v>
+      </c>
+      <c r="I24" s="4">
         <v>161</v>
       </c>
-      <c r="E26" s="3">
-        <v>89</v>
-      </c>
-      <c r="F26" s="3">
-        <v>7</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3">
-        <v>325</v>
-      </c>
-      <c r="I26" s="3">
-        <v>17</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3">
-        <v>46</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B27" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C27" s="3">
-        <v>476</v>
-      </c>
-      <c r="D27" s="3">
-        <v>108</v>
-      </c>
-      <c r="E27" s="3">
-        <v>66</v>
-      </c>
-      <c r="F27" s="3">
-        <v>2</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3">
-        <v>301</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J24" s="4">
+        <v>25</v>
+      </c>
+      <c r="K24" s="4">
         <v>19</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3">
-        <v>20</v>
-      </c>
-      <c r="L27" s="3">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B28" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C28" s="3">
-        <v>3</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="4">
-        <v>4780</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1066</v>
-      </c>
-      <c r="E29" s="4">
-        <v>1224</v>
-      </c>
-      <c r="F29" s="4">
-        <v>84</v>
-      </c>
-      <c r="G29" s="4">
-        <v>44</v>
-      </c>
-      <c r="H29" s="4">
-        <v>3717</v>
-      </c>
-      <c r="I29" s="4">
-        <v>175</v>
-      </c>
-      <c r="J29" s="4">
-        <v>25</v>
-      </c>
-      <c r="K29" s="4">
+      <c r="L24" s="4">
         <v>219</v>
       </c>
-      <c r="L29" s="4">
-        <v>11334</v>
+      <c r="M24" s="4">
+        <v>10203</v>
       </c>
     </row>
   </sheetData>
@@ -1426,25 +1293,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1455,7 +1322,7 @@
         <v>21092</v>
       </c>
       <c r="C2" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -1463,7 +1330,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1474,7 +1341,7 @@
         <v>21176</v>
       </c>
       <c r="C3" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -1482,7 +1349,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1492,12 +1359,8 @@
       <c r="B4" s="2">
         <v>21085</v>
       </c>
-      <c r="C4" s="3">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3">
-        <v>17</v>
-      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
@@ -1505,7 +1368,7 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1515,9 +1378,7 @@
       <c r="B5" s="2">
         <v>21086</v>
       </c>
-      <c r="C5" s="3">
-        <v>37</v>
-      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3">
         <v>27</v>
       </c>
@@ -1530,7 +1391,7 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1540,9 +1401,7 @@
       <c r="B6" s="2">
         <v>21515</v>
       </c>
-      <c r="C6" s="3">
-        <v>40</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1551,7 +1410,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1562,17 +1421,15 @@
         <v>21081</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>46</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1588,14 +1445,12 @@
       <c r="D8" s="3">
         <v>8</v>
       </c>
-      <c r="E8" s="3">
-        <v>53</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>122</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1605,14 +1460,12 @@
       <c r="B9" s="2">
         <v>21246</v>
       </c>
-      <c r="C9" s="3">
-        <v>130</v>
-      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="3">
         <v>37</v>
       </c>
       <c r="E9" s="3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
@@ -1620,7 +1473,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3">
-        <v>205</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1639,13 +1492,11 @@
       <c r="E10" s="3">
         <v>35</v>
       </c>
-      <c r="F10" s="3">
-        <v>82</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3">
-        <v>269</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1739,11 +1590,9 @@
       <c r="G14" s="3">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
-        <v>27</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1758,15 +1607,13 @@
       <c r="E15" s="3">
         <v>5</v>
       </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
         <v>59</v>
       </c>
       <c r="I15" s="3">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1788,10 +1635,10 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3">
-        <v>264</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1867,29 +1714,29 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="4">
-        <v>2129</v>
+        <v>1876</v>
       </c>
       <c r="D20" s="4">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="E20" s="4">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="F20" s="4">
-        <v>288</v>
+        <v>166</v>
       </c>
       <c r="G20" s="4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H20" s="4">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="I20" s="4">
-        <v>3172</v>
+        <v>2588</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1924,37 +1771,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1974,10 +1821,10 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="M2" s="3">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1997,10 +1844,10 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="M3" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2020,10 +1867,10 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="M4" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2039,7 +1886,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -2048,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="3">
-        <v>90</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2064,7 +1911,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -2073,7 +1920,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3">
-        <v>122</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2091,7 +1938,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -2100,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="3">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2116,14 +1963,14 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>158</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2139,14 +1986,14 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>144</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2162,14 +2009,14 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3">
-        <v>181</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2256,12 +2103,12 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>215</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2279,12 +2126,12 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3">
-        <v>251</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2302,12 +2149,12 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2324,13 +2171,13 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2349,13 +2196,13 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3">
-        <v>146</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -2372,13 +2219,13 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2395,7 +2242,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="J20" s="3">
         <v>1</v>
@@ -2403,7 +2250,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2420,13 +2267,13 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3">
-        <v>133</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2443,7 +2290,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="J22" s="3">
         <v>1</v>
@@ -2451,7 +2298,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3">
-        <v>143</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2465,7 +2312,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -2476,7 +2323,7 @@
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3">
-        <v>88</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -2490,7 +2337,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -2501,7 +2348,7 @@
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2515,7 +2362,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -2526,7 +2373,7 @@
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2537,7 +2384,7 @@
         <v>60138</v>
       </c>
       <c r="C26" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2549,18 +2396,18 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2">
-        <v>60496</v>
+        <v>60127</v>
       </c>
       <c r="C27" s="3">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2572,18 +2419,18 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3">
-        <v>38</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2">
-        <v>60507</v>
+        <v>60129</v>
       </c>
       <c r="C28" s="3">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2595,7 +2442,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -2603,15 +2450,13 @@
         <v>18</v>
       </c>
       <c r="B29" s="2">
-        <v>60127</v>
+        <v>60131</v>
       </c>
       <c r="C29" s="3">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="3">
-        <v>1</v>
-      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -2620,70 +2465,68 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3">
-        <v>185</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C30" s="3">
-        <v>115</v>
-      </c>
+        <v>60127</v>
+      </c>
+      <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3">
+        <v>3</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
-        <v>115</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2">
-        <v>60131</v>
-      </c>
-      <c r="C31" s="3">
-        <v>134</v>
-      </c>
+        <v>60129</v>
+      </c>
+      <c r="C31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="3">
-        <v>4</v>
-      </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3">
+        <v>3</v>
+      </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3">
-        <v>138</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2">
-        <v>60138</v>
+        <v>60131</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -2691,22 +2534,22 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2">
-        <v>60224</v>
+        <v>60132</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2714,7 +2557,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2722,14 +2565,14 @@
         <v>22</v>
       </c>
       <c r="B34" s="2">
-        <v>60127</v>
+        <v>60134</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -2737,153 +2580,163 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B35" s="2">
-        <v>60129</v>
+        <v>60128</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3">
+        <v>6</v>
+      </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="3">
-        <v>5</v>
-      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
+      <c r="L35" s="3">
+        <v>39</v>
+      </c>
       <c r="M35" s="3">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2">
-        <v>60131</v>
+        <v>60132</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3">
+        <v>26</v>
+      </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
-      <c r="G36" s="3">
-        <v>3</v>
-      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+      <c r="J36" s="3">
+        <v>1</v>
+      </c>
       <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+      <c r="L36" s="3">
+        <v>183</v>
+      </c>
       <c r="M36" s="3">
-        <v>3</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3">
+        <v>8</v>
+      </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="3">
-        <v>6</v>
-      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+      <c r="L37" s="3">
+        <v>38</v>
+      </c>
       <c r="M37" s="3">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="3">
-        <v>4</v>
-      </c>
-      <c r="H38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3">
+        <v>88</v>
+      </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3">
-        <v>4</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2">
-        <v>60130</v>
+        <v>60132</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
+      <c r="H39" s="3">
+        <v>303</v>
+      </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3">
-        <v>27</v>
-      </c>
-      <c r="L39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3">
+        <v>2</v>
+      </c>
       <c r="M39" s="3">
-        <v>27</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2">
-        <v>60139</v>
+        <v>60134</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
+      <c r="H40" s="3">
+        <v>170</v>
+      </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3">
-        <v>4</v>
-      </c>
+      <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
-        <v>4</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2">
-        <v>60306</v>
+        <v>60128</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -2892,387 +2745,381 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3">
-        <v>3</v>
-      </c>
+      <c r="J41" s="3">
+        <v>140</v>
+      </c>
+      <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3">
-        <v>3</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>6</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
+      <c r="J42" s="3">
+        <v>136</v>
+      </c>
       <c r="K42" s="3"/>
-      <c r="L42" s="3">
-        <v>60</v>
-      </c>
+      <c r="L42" s="3"/>
       <c r="M42" s="3">
-        <v>66</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B43" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3">
-        <v>26</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="K43" s="3"/>
-      <c r="L43" s="3">
-        <v>317</v>
-      </c>
+      <c r="L43" s="3"/>
       <c r="M43" s="3">
-        <v>344</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="3">
-        <v>8</v>
-      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="I44" s="3">
+        <v>100</v>
+      </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
-      <c r="L44" s="3">
-        <v>82</v>
-      </c>
+      <c r="L44" s="3"/>
       <c r="M44" s="3">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B45" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3">
-        <v>108</v>
-      </c>
-      <c r="I45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3">
+        <v>454</v>
+      </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3">
-        <v>108</v>
+        <v>454</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B46" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="D46" s="3">
+        <v>2</v>
+      </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3">
-        <v>374</v>
-      </c>
-      <c r="I46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3">
+        <v>117</v>
+      </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
-      <c r="L46" s="3">
-        <v>2</v>
-      </c>
+      <c r="L46" s="3"/>
       <c r="M46" s="3">
-        <v>376</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B47" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3">
+        <v>13</v>
+      </c>
       <c r="G47" s="3"/>
-      <c r="H47" s="3">
-        <v>196</v>
-      </c>
+      <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
+      <c r="K47" s="3">
+        <v>15</v>
+      </c>
       <c r="L47" s="3"/>
       <c r="M47" s="3">
-        <v>196</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B48" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+      <c r="F48" s="3">
+        <v>60</v>
+      </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="3">
-        <v>140</v>
-      </c>
-      <c r="K48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3">
+        <v>77</v>
+      </c>
       <c r="L48" s="3"/>
       <c r="M48" s="3">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B49" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3">
+        <v>42</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="3">
-        <v>136</v>
-      </c>
-      <c r="K49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3">
+        <v>46</v>
+      </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3">
-        <v>136</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B50" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C50" s="3"/>
+        <v>60128</v>
+      </c>
+      <c r="C50" s="3">
+        <v>94</v>
+      </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3">
-        <v>99</v>
-      </c>
+      <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B51" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C51" s="3"/>
+        <v>60132</v>
+      </c>
+      <c r="C51" s="3">
+        <v>414</v>
+      </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="3">
-        <v>106</v>
-      </c>
+      <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3">
-        <v>106</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B52" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C52" s="3"/>
+        <v>60134</v>
+      </c>
+      <c r="C52" s="3">
+        <v>188</v>
+      </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="3">
-        <v>522</v>
-      </c>
+      <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3">
-        <v>522</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B53" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3">
-        <v>2</v>
-      </c>
-      <c r="E53" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C53" s="3">
+        <v>137</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3">
+        <v>1</v>
+      </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="3">
-        <v>131</v>
-      </c>
+      <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B54" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C54" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C54" s="3">
+        <v>179</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3">
-        <v>27</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3">
-        <v>15</v>
-      </c>
+      <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3">
-        <v>42</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B55" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C55" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C55" s="3">
+        <v>169</v>
+      </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3">
-        <v>130</v>
-      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3">
-        <v>77</v>
-      </c>
+      <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3">
-        <v>207</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B56" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C56" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C56" s="3">
+        <v>268</v>
+      </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3">
-        <v>82</v>
-      </c>
+      <c r="E56" s="3">
+        <v>5</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3">
-        <v>46</v>
-      </c>
+      <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3">
-        <v>128</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B57" s="2">
-        <v>60128</v>
+        <v>60355</v>
       </c>
       <c r="C57" s="3">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3284,20 +3131,20 @@
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3">
-        <v>94</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B58" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C58" s="3">
-        <v>414</v>
-      </c>
-      <c r="D58" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3">
+        <v>11</v>
+      </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -3305,72 +3152,74 @@
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
+      <c r="L58" s="3">
+        <v>139</v>
+      </c>
       <c r="M58" s="3">
-        <v>414</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B59" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C59" s="3">
-        <v>188</v>
-      </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3">
-        <v>1</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
+      <c r="L59" s="3">
+        <v>148</v>
+      </c>
       <c r="M59" s="3">
-        <v>189</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B60" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C60" s="3">
-        <v>137</v>
-      </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3">
-        <v>1</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
+      <c r="L60" s="3">
+        <v>90</v>
+      </c>
       <c r="M60" s="3">
-        <v>138</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B61" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C61" s="3">
-        <v>179</v>
-      </c>
-      <c r="D61" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3">
+        <v>5</v>
+      </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -3378,22 +3227,24 @@
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
+      <c r="L61" s="3">
+        <v>248</v>
+      </c>
       <c r="M61" s="3">
-        <v>179</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B62" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C62" s="3">
-        <v>169</v>
-      </c>
-      <c r="D62" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3">
+        <v>15</v>
+      </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -3401,237 +3252,235 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
+      <c r="L62" s="3">
+        <v>356</v>
+      </c>
       <c r="M62" s="3">
-        <v>169</v>
+        <v>371</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B63" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C63" s="3">
-        <v>268</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="3">
-        <v>5</v>
-      </c>
-      <c r="F63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3">
+        <v>80</v>
+      </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
+      <c r="K63" s="3">
+        <v>19</v>
+      </c>
       <c r="L63" s="3"/>
       <c r="M63" s="3">
-        <v>273</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B64" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C64" s="3">
-        <v>170</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="3">
+        <v>78</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
+      <c r="K64" s="3">
+        <v>26</v>
+      </c>
       <c r="L64" s="3"/>
       <c r="M64" s="3">
-        <v>170</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B65" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C65" s="3"/>
-      <c r="D65" s="3">
-        <v>11</v>
-      </c>
+      <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3">
+        <v>91</v>
+      </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3">
-        <v>229</v>
-      </c>
+      <c r="K65" s="3">
+        <v>37</v>
+      </c>
+      <c r="L65" s="3"/>
       <c r="M65" s="3">
-        <v>240</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B66" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="3">
-        <v>10</v>
-      </c>
+      <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3">
+        <v>51</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3">
-        <v>260</v>
-      </c>
+      <c r="K66" s="3">
+        <v>27</v>
+      </c>
+      <c r="L66" s="3"/>
       <c r="M66" s="3">
-        <v>270</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B67" s="2">
-        <v>60306</v>
+        <v>60135</v>
       </c>
       <c r="C67" s="3"/>
-      <c r="D67" s="3">
-        <v>5</v>
-      </c>
+      <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3">
+        <v>45</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3">
-        <v>152</v>
-      </c>
+      <c r="K67" s="3">
+        <v>13</v>
+      </c>
+      <c r="L67" s="3"/>
       <c r="M67" s="3">
-        <v>157</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B68" s="2">
-        <v>60130</v>
+        <v>60135</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3">
-        <v>5</v>
-      </c>
+      <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="I68" s="3">
+        <v>172</v>
+      </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
-      <c r="L68" s="3">
-        <v>248</v>
-      </c>
+      <c r="L68" s="3"/>
       <c r="M68" s="3">
-        <v>253</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B69" s="2">
-        <v>60355</v>
+        <v>60139</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="3">
-        <v>15</v>
-      </c>
+      <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="I69" s="3">
+        <v>185</v>
+      </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
-      <c r="L69" s="3">
-        <v>356</v>
-      </c>
+      <c r="L69" s="3"/>
       <c r="M69" s="3">
-        <v>371</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B70" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="3">
-        <v>80</v>
-      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="I70" s="3">
+        <v>215</v>
+      </c>
       <c r="J70" s="3"/>
-      <c r="K70" s="3">
-        <v>19</v>
-      </c>
+      <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3">
-        <v>99</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B71" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
+      <c r="D71" s="3">
+        <v>1</v>
+      </c>
       <c r="E71" s="3"/>
-      <c r="F71" s="3">
-        <v>78</v>
-      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="I71" s="3">
+        <v>204</v>
+      </c>
       <c r="J71" s="3"/>
-      <c r="K71" s="3">
-        <v>26</v>
-      </c>
+      <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3">
-        <v>104</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B72" s="2">
         <v>60355</v>
@@ -3639,24 +3488,22 @@
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="3">
-        <v>91</v>
-      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="I72" s="3">
+        <v>282</v>
+      </c>
       <c r="J72" s="3"/>
-      <c r="K72" s="3">
-        <v>37</v>
-      </c>
+      <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3">
-        <v>128</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B73" s="2">
         <v>60130</v>
@@ -3664,207 +3511,203 @@
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="3">
-        <v>51</v>
-      </c>
-      <c r="G73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3">
+        <v>3</v>
+      </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
-      <c r="K73" s="3">
-        <v>27</v>
-      </c>
+      <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3">
-        <v>78</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B74" s="2">
-        <v>60135</v>
+        <v>60132</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
-      <c r="K74" s="3">
-        <v>13</v>
-      </c>
+      <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B75" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
+      <c r="G75" s="3">
+        <v>3</v>
+      </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="3">
-        <v>172</v>
-      </c>
+      <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3">
-        <v>172</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B76" s="2">
-        <v>60139</v>
+        <v>60202</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="G76" s="3">
+        <v>3</v>
+      </c>
       <c r="H76" s="3"/>
-      <c r="I76" s="3">
-        <v>185</v>
-      </c>
+      <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3">
-        <v>185</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B77" s="2">
-        <v>60306</v>
+        <v>60215</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
+      <c r="G77" s="3">
+        <v>3</v>
+      </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="3">
-        <v>215</v>
-      </c>
+      <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3">
-        <v>215</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B78" s="2">
-        <v>60130</v>
+        <v>60272</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="3">
-        <v>1</v>
-      </c>
+      <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
+      <c r="G78" s="3">
+        <v>3</v>
+      </c>
       <c r="H78" s="3"/>
-      <c r="I78" s="3">
-        <v>204</v>
-      </c>
+      <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3">
-        <v>205</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B79" s="2">
-        <v>60355</v>
+        <v>60296</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
+      <c r="G79" s="3">
+        <v>3</v>
+      </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="3">
-        <v>282</v>
-      </c>
+      <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3">
-        <v>282</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B80" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3">
+        <v>1</v>
+      </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
-      <c r="J80" s="3">
-        <v>80</v>
-      </c>
+      <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B81" s="2">
-        <v>60139</v>
+        <v>60496</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
+      <c r="H81" s="3">
+        <v>3</v>
+      </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3">
-        <v>71</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -3872,7 +3715,7 @@
         <v>51</v>
       </c>
       <c r="B82" s="2">
-        <v>60306</v>
+        <v>60135</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -3882,20 +3725,20 @@
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B83" s="2">
-        <v>60130</v>
+        <v>60139</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
@@ -3905,58 +3748,58 @@
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B84" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="3">
-        <v>205</v>
-      </c>
+      <c r="H84" s="3"/>
       <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
+      <c r="J84" s="3">
+        <v>72</v>
+      </c>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3">
-        <v>205</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B85" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="3">
-        <v>200</v>
-      </c>
+      <c r="H85" s="3"/>
       <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
+      <c r="J85" s="3">
+        <v>102</v>
+      </c>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
       <c r="M85" s="3">
-        <v>200</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3964,7 +3807,7 @@
         <v>53</v>
       </c>
       <c r="B86" s="2">
-        <v>60355</v>
+        <v>60139</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
@@ -3972,22 +3815,22 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3">
-        <v>342</v>
+        <v>205</v>
       </c>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3">
-        <v>342</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B87" s="2">
-        <v>60130</v>
+        <v>60306</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
@@ -3995,22 +3838,22 @@
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3">
-        <v>124</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B88" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -4018,53 +3861,99 @@
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
       <c r="M88" s="3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="2">
+        <v>54</v>
+      </c>
+      <c r="B89" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3">
+        <v>124</v>
+      </c>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="2">
+        <v>54</v>
+      </c>
+      <c r="B90" s="2">
+        <v>60135</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3">
         <v>149</v>
       </c>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="4">
-        <v>2159</v>
-      </c>
-      <c r="D89" s="4">
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" s="4">
+        <v>1860</v>
+      </c>
+      <c r="D91" s="4">
         <v>91</v>
       </c>
-      <c r="E89" s="4">
-        <v>12</v>
-      </c>
-      <c r="F89" s="4">
-        <v>736</v>
-      </c>
-      <c r="G89" s="4">
-        <v>32</v>
-      </c>
-      <c r="H89" s="4">
-        <v>2448</v>
-      </c>
-      <c r="I89" s="4">
-        <v>2580</v>
-      </c>
-      <c r="J89" s="4">
-        <v>1521</v>
-      </c>
-      <c r="K89" s="4">
-        <v>363</v>
-      </c>
-      <c r="L89" s="4">
-        <v>1849</v>
-      </c>
-      <c r="M89" s="4">
-        <v>11791</v>
+      <c r="E91" s="4">
+        <v>6</v>
+      </c>
+      <c r="F91" s="4">
+        <v>513</v>
+      </c>
+      <c r="G91" s="4">
+        <v>37</v>
+      </c>
+      <c r="H91" s="4">
+        <v>1955</v>
+      </c>
+      <c r="I91" s="4">
+        <v>2249</v>
+      </c>
+      <c r="J91" s="4">
+        <v>1414</v>
+      </c>
+      <c r="K91" s="4">
+        <v>329</v>
+      </c>
+      <c r="L91" s="4">
+        <v>1266</v>
+      </c>
+      <c r="M91" s="4">
+        <v>9720</v>
       </c>
     </row>
   </sheetData>
@@ -4074,7 +3963,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4090,19 +3979,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4110,13 +3999,13 @@
         <v>2000</v>
       </c>
       <c r="B2" s="2">
-        <v>21469</v>
+        <v>21085</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
         <v>1</v>
@@ -4130,7 +4019,7 @@
         <v>21176</v>
       </c>
       <c r="C3" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3">
         <v>5</v>
@@ -4138,7 +4027,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4149,7 +4038,7 @@
         <v>21229</v>
       </c>
       <c r="C4" s="3">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="D4" s="3">
         <v>32</v>
@@ -4157,7 +4046,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>465</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4181,19 +4070,23 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B6" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>21086</v>
+      </c>
+      <c r="C6" s="3">
+        <v>243</v>
+      </c>
       <c r="D6" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3">
+        <v>53</v>
+      </c>
       <c r="G6" s="3">
-        <v>29</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4201,45 +4094,43 @@
         <v>2004</v>
       </c>
       <c r="B7" s="2">
-        <v>21086</v>
+        <v>21515</v>
       </c>
       <c r="C7" s="3">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3">
-        <v>8</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3">
-        <v>341</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B8" s="2">
-        <v>21515</v>
+        <v>21081</v>
       </c>
       <c r="C8" s="3">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D8" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="3">
-        <v>4</v>
-      </c>
       <c r="G8" s="3">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4247,66 +4138,66 @@
         <v>2005</v>
       </c>
       <c r="B9" s="2">
-        <v>21081</v>
+        <v>21085</v>
       </c>
       <c r="C9" s="3">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="D9" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F9" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3">
-        <v>90</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B10" s="2">
-        <v>21085</v>
+        <v>21089</v>
       </c>
       <c r="C10" s="3">
-        <v>221</v>
-      </c>
-      <c r="D10" s="3">
         <v>50</v>
       </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3">
-        <v>315</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B11" s="2">
-        <v>21089</v>
+        <v>21082</v>
       </c>
       <c r="C11" s="3">
-        <v>50</v>
-      </c>
-      <c r="D11" s="3"/>
+        <v>252</v>
+      </c>
+      <c r="D11" s="3">
+        <v>28</v>
+      </c>
       <c r="E11" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F11" s="3">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G11" s="3">
-        <v>58</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4314,45 +4205,43 @@
         <v>2007</v>
       </c>
       <c r="B12" s="2">
-        <v>21082</v>
+        <v>21234</v>
       </c>
       <c r="C12" s="3">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D12" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E12" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F12" s="3">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G12" s="3">
-        <v>358</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B13" s="2">
-        <v>21234</v>
+        <v>21083</v>
       </c>
       <c r="C13" s="3">
-        <v>235</v>
-      </c>
-      <c r="D13" s="3">
-        <v>42</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F13" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" s="3">
-        <v>317</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4360,43 +4249,45 @@
         <v>2008</v>
       </c>
       <c r="B14" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C14" s="3">
-        <v>64</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>420</v>
+      </c>
+      <c r="D14" s="3">
+        <v>22</v>
+      </c>
       <c r="E14" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G14" s="3">
-        <v>85</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B15" s="2">
-        <v>21457</v>
+        <v>21195</v>
       </c>
       <c r="C15" s="3">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="D15" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E15" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F15" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G15" s="3">
-        <v>459</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4404,93 +4295,87 @@
         <v>2009</v>
       </c>
       <c r="B16" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C16" s="3">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G16" s="3">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B17" s="2">
-        <v>21246</v>
+        <v>21090</v>
       </c>
       <c r="C17" s="3">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D17" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3">
-        <v>122</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B18" s="2">
-        <v>21090</v>
+        <v>21533</v>
       </c>
       <c r="C18" s="3">
-        <v>34</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3">
-        <v>4</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B19" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C19" s="3">
-        <v>30</v>
-      </c>
-      <c r="D19" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B20" s="2">
-        <v>21085</v>
+        <v>21086</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3">
@@ -4503,24 +4388,60 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="4">
-        <v>2398</v>
-      </c>
-      <c r="D21" s="4">
-        <v>311</v>
-      </c>
-      <c r="E21" s="4">
-        <v>175</v>
-      </c>
-      <c r="F21" s="4">
-        <v>208</v>
-      </c>
-      <c r="G21" s="4">
-        <v>3092</v>
+      <c r="A21" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21457</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="4">
+        <v>2355</v>
+      </c>
+      <c r="D23" s="4">
+        <v>286</v>
+      </c>
+      <c r="E23" s="4">
+        <v>145</v>
+      </c>
+      <c r="F23" s="4">
+        <v>173</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2959</v>
       </c>
     </row>
   </sheetData>
@@ -4530,7 +4451,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4547,10 +4468,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4558,13 +4479,13 @@
         <v>5000</v>
       </c>
       <c r="B2" s="2">
-        <v>17056</v>
+        <v>17168</v>
       </c>
       <c r="C2" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4583,28 +4504,56 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="B4" s="2">
         <v>21094</v>
       </c>
       <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>5003</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21094</v>
+      </c>
+      <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4">
-        <v>29</v>
-      </c>
-      <c r="D5" s="4">
-        <v>29</v>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>5004</v>
+      </c>
+      <c r="B6" s="2">
+        <v>17183</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4">
+        <v>32</v>
+      </c>
+      <c r="D7" s="4">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4614,7 +4563,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4634,37 +4583,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4681,38 +4630,42 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
+      <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2">
-        <v>3000</v>
+        <v>3003</v>
       </c>
       <c r="B3" s="2">
-        <v>21469</v>
+        <v>21081</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="E3" s="3">
+        <v>20</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>28</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4720,63 +4673,65 @@
         <v>3003</v>
       </c>
       <c r="B4" s="2">
-        <v>21081</v>
+        <v>21515</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>53</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3">
         <v>20</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2</v>
-      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3">
-        <v>55</v>
-      </c>
+      <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3">
-        <v>278</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="B5" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5</v>
+      </c>
       <c r="D5" s="3">
-        <v>64</v>
+        <v>162</v>
       </c>
       <c r="E5" s="3">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="F5" s="3">
+        <v>119</v>
+      </c>
       <c r="G5" s="3">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
       <c r="I5" s="3">
-        <v>69</v>
-      </c>
-      <c r="J5" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="J5" s="3">
+        <v>137</v>
+      </c>
       <c r="K5" s="3">
-        <v>9</v>
-      </c>
-      <c r="L5" s="3"/>
+        <v>175</v>
+      </c>
+      <c r="L5" s="3">
+        <v>14</v>
+      </c>
       <c r="M5" s="3">
-        <v>174</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4784,79 +4739,77 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2">
-        <v>21082</v>
+        <v>21234</v>
       </c>
       <c r="C6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="E6" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3">
-        <v>70</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J6" s="3">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="L6" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M6" s="3">
-        <v>800</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2">
-        <v>3004</v>
+        <v>3006</v>
       </c>
       <c r="B7" s="2">
-        <v>21234</v>
+        <v>21083</v>
       </c>
       <c r="C7" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G7" s="3">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="J7" s="3">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" s="3">
-        <v>516</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4864,77 +4817,77 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C8" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G8" s="3">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="J8" s="3">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="K8" s="3">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L8" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" s="3">
-        <v>386</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2">
-        <v>3006</v>
+        <v>3008</v>
       </c>
       <c r="B9" s="2">
-        <v>21457</v>
+        <v>21195</v>
       </c>
       <c r="C9" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3">
-        <v>19</v>
-      </c>
-      <c r="H9" s="3"/>
+        <v>157</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3</v>
+      </c>
       <c r="I9" s="3">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="J9" s="3">
-        <v>16</v>
-      </c>
-      <c r="K9" s="3">
-        <v>105</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="K9" s="3"/>
       <c r="L9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" s="3">
-        <v>286</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4942,81 +4895,73 @@
         <v>3008</v>
       </c>
       <c r="B10" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C10" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3">
-        <v>157</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3">
-        <v>230</v>
-      </c>
-      <c r="K10" s="3">
-        <v>74</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M10" s="3">
-        <v>784</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="B11" s="2">
-        <v>21246</v>
+        <v>21085</v>
       </c>
       <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>62</v>
+      </c>
+      <c r="E11" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="3">
-        <v>57</v>
-      </c>
-      <c r="E11" s="3">
-        <v>14</v>
-      </c>
       <c r="F11" s="3">
-        <v>43</v>
-      </c>
-      <c r="G11" s="3">
-        <v>52</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="J11" s="3">
-        <v>278</v>
-      </c>
-      <c r="K11" s="3">
-        <v>73</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3">
-        <v>622</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5024,278 +4969,160 @@
         <v>3009</v>
       </c>
       <c r="B12" s="2">
-        <v>21085</v>
+        <v>21086</v>
       </c>
       <c r="C12" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="E12" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3">
-        <v>69</v>
-      </c>
-      <c r="G12" s="3">
-        <v>30</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J12" s="3">
-        <v>24</v>
-      </c>
-      <c r="K12" s="3">
-        <v>61</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M12" s="3">
-        <v>401</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="B13" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C13" s="3">
-        <v>5</v>
-      </c>
+        <v>21081</v>
+      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="3">
-        <v>115</v>
-      </c>
-      <c r="E13" s="3">
-        <v>28</v>
-      </c>
-      <c r="F13" s="3">
-        <v>87</v>
-      </c>
-      <c r="G13" s="3">
-        <v>48</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>67</v>
-      </c>
-      <c r="J13" s="3">
-        <v>35</v>
-      </c>
-      <c r="K13" s="3">
-        <v>60</v>
-      </c>
-      <c r="L13" s="3">
-        <v>17</v>
-      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>462</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="B14" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>21089</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="F14" s="3">
+        <v>19</v>
+      </c>
+      <c r="G14" s="3">
+        <v>17</v>
+      </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3">
-        <v>3</v>
-      </c>
+      <c r="I14" s="3">
+        <v>58</v>
+      </c>
+      <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="B15" s="2">
-        <v>21083</v>
+        <v>21090</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="D15" s="3">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3">
+        <v>48</v>
+      </c>
+      <c r="G15" s="3">
+        <v>36</v>
+      </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3">
-        <v>1</v>
-      </c>
+      <c r="I15" s="3">
+        <v>40</v>
+      </c>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>2</v>
+      </c>
       <c r="M15" s="3">
-        <v>1</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="2">
-        <v>3010</v>
-      </c>
-      <c r="B16" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3">
-        <v>4</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="2">
-        <v>3010</v>
-      </c>
-      <c r="B17" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B18" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3">
-        <v>9</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3">
-        <v>19</v>
-      </c>
-      <c r="G18" s="3">
-        <v>17</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3">
-        <v>58</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3">
-        <v>26</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B19" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
-        <v>30</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="3">
-        <v>48</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="B16" s="2"/>
+      <c r="C16" s="4">
         <v>36</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3">
-        <v>40</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3">
-        <v>34</v>
-      </c>
-      <c r="L19" s="3">
-        <v>2</v>
-      </c>
-      <c r="M19" s="3">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4">
-        <v>36</v>
-      </c>
-      <c r="D20" s="4">
-        <v>860</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D16" s="4">
+        <v>635</v>
+      </c>
+      <c r="E16" s="4">
         <v>216</v>
       </c>
-      <c r="F20" s="4">
-        <v>635</v>
-      </c>
-      <c r="G20" s="4">
-        <v>542</v>
-      </c>
-      <c r="H20" s="4">
+      <c r="F16" s="4">
+        <v>428</v>
+      </c>
+      <c r="G16" s="4">
+        <v>428</v>
+      </c>
+      <c r="H16" s="4">
         <v>7</v>
       </c>
-      <c r="I20" s="4">
-        <v>937</v>
-      </c>
-      <c r="J20" s="4">
-        <v>855</v>
-      </c>
-      <c r="K20" s="4">
-        <v>1017</v>
-      </c>
-      <c r="L20" s="4">
+      <c r="I16" s="4">
+        <v>789</v>
+      </c>
+      <c r="J16" s="4">
+        <v>793</v>
+      </c>
+      <c r="K16" s="4">
+        <v>537</v>
+      </c>
+      <c r="L16" s="4">
         <v>59</v>
       </c>
-      <c r="M20" s="4">
-        <v>5164</v>
+      <c r="M16" s="4">
+        <v>3928</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="43">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>BSCLTH2</t>
-  </si>
-  <si>
-    <t>BSCLTH4</t>
   </si>
   <si>
     <t>BSCLUG</t>
@@ -540,20 +537,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,681 +587,535 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B2" s="2">
-        <v>21092</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C2" s="3">
+        <v>227</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3">
-        <v>2</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="L2" s="3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B3" s="2">
-        <v>21176</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>21469</v>
+      </c>
+      <c r="C3" s="3">
+        <v>130</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>2</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B4" s="2">
-        <v>21092</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>21075</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5</v>
+      </c>
       <c r="D4" s="3">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="E4" s="3">
+        <v>109</v>
+      </c>
+      <c r="F4" s="3">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3">
+        <v>182</v>
+      </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>4</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="L4" s="3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="2">
-        <v>21176</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>21533</v>
+      </c>
+      <c r="C5" s="3">
+        <v>509</v>
+      </c>
       <c r="D5" s="3">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E5" s="3">
+        <v>147</v>
+      </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>24</v>
+      </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3">
+        <v>21</v>
+      </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="K5" s="3">
+        <v>60</v>
+      </c>
+      <c r="L5" s="3">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B6" s="2">
-        <v>21082</v>
+        <v>21086</v>
       </c>
       <c r="C6" s="3">
-        <v>396</v>
-      </c>
-      <c r="D6" s="3"/>
+        <v>661</v>
+      </c>
+      <c r="D6" s="3">
+        <v>49</v>
+      </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>203</v>
+      </c>
       <c r="H6" s="3">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="K6" s="3">
+        <v>25</v>
+      </c>
+      <c r="L6" s="3">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B7" s="2">
-        <v>21469</v>
+        <v>21515</v>
       </c>
       <c r="C7" s="3">
-        <v>397</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
+        <v>82</v>
+      </c>
       <c r="H7" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="B8" s="2">
-        <v>21075</v>
+        <v>21195</v>
       </c>
       <c r="C8" s="3">
-        <v>5</v>
+        <v>709</v>
       </c>
       <c r="D8" s="3">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="E8" s="3">
-        <v>109</v>
-      </c>
-      <c r="F8" s="3">
-        <v>15</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>182</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
+        <v>330</v>
+      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3">
+        <v>31</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="2">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="B9" s="2">
-        <v>21533</v>
+        <v>21246</v>
       </c>
       <c r="C9" s="3">
-        <v>509</v>
+        <v>592</v>
       </c>
       <c r="D9" s="3">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E9" s="3">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>359</v>
+      </c>
       <c r="H9" s="3">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="3">
-        <v>21</v>
-      </c>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3">
+        <v>37</v>
+      </c>
       <c r="L9" s="3">
-        <v>60</v>
-      </c>
-      <c r="M9" s="3">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="2">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B10" s="2">
-        <v>21086</v>
+        <v>21083</v>
       </c>
       <c r="C10" s="3">
-        <v>763</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3">
-        <v>119</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
-        <v>2</v>
-      </c>
-      <c r="G10" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="3">
+        <v>113</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
+        <v>266</v>
+      </c>
       <c r="H10" s="3">
-        <v>433</v>
-      </c>
-      <c r="I10" s="3">
-        <v>56</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>25</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="2">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B11" s="2">
-        <v>21515</v>
+        <v>21457</v>
       </c>
       <c r="C11" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3">
-        <v>19</v>
-      </c>
-      <c r="E11" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="3">
+        <v>76</v>
+      </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3">
+        <v>243</v>
+      </c>
       <c r="H11" s="3">
-        <v>241</v>
-      </c>
-      <c r="I11" s="3">
-        <v>6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="L11" s="3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B12" s="2">
-        <v>21195</v>
+        <v>21089</v>
       </c>
       <c r="C12" s="3">
-        <v>709</v>
+        <v>4</v>
       </c>
       <c r="D12" s="3">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="E12" s="3">
-        <v>221</v>
-      </c>
-      <c r="F12" s="3">
-        <v>11</v>
-      </c>
-      <c r="G12" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>182</v>
+      </c>
       <c r="H12" s="3">
-        <v>330</v>
+        <v>3</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>31</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B13" s="2">
-        <v>21246</v>
+        <v>21234</v>
       </c>
       <c r="C13" s="3">
-        <v>592</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3">
-        <v>200</v>
-      </c>
-      <c r="F13" s="3">
-        <v>10</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>256</v>
+      </c>
       <c r="H13" s="3">
-        <v>359</v>
-      </c>
-      <c r="I13" s="3">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>37</v>
-      </c>
-      <c r="M13" s="3">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B14" s="2">
-        <v>21083</v>
+        <v>21081</v>
       </c>
       <c r="C14" s="3">
-        <v>11</v>
+        <v>449</v>
       </c>
       <c r="D14" s="3">
-        <v>52</v>
-      </c>
-      <c r="E14" s="3">
-        <v>113</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>274</v>
+      </c>
       <c r="H14" s="3">
-        <v>266</v>
-      </c>
-      <c r="I14" s="3">
         <v>17</v>
       </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="K14" s="3">
+        <v>26</v>
+      </c>
+      <c r="L14" s="3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B15" s="2">
-        <v>21457</v>
+        <v>21090</v>
       </c>
       <c r="C15" s="3">
-        <v>24</v>
+        <v>476</v>
       </c>
       <c r="D15" s="3">
-        <v>42</v>
-      </c>
-      <c r="E15" s="3">
-        <v>76</v>
-      </c>
-      <c r="F15" s="3">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3">
+        <v>251</v>
+      </c>
       <c r="H15" s="3">
-        <v>243</v>
-      </c>
-      <c r="I15" s="3">
-        <v>12</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="K15" s="3">
+        <v>17</v>
+      </c>
+      <c r="L15" s="3">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B16" s="2">
-        <v>21089</v>
+        <v>21253</v>
       </c>
       <c r="C16" s="3">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3">
-        <v>22</v>
-      </c>
-      <c r="E16" s="3">
-        <v>74</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>182</v>
-      </c>
-      <c r="I16" s="3">
-        <v>3</v>
-      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="L16" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="B17" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C17" s="3">
-        <v>12</v>
-      </c>
-      <c r="D17" s="3">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3">
-        <v>67</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
+        <v>21085</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>256</v>
-      </c>
-      <c r="I17" s="3">
-        <v>20</v>
-      </c>
-      <c r="J17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3">
+        <v>2</v>
+      </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="L17" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="2">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="B18" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C18" s="3">
-        <v>551</v>
-      </c>
-      <c r="D18" s="3">
-        <v>161</v>
-      </c>
+        <v>21088</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="3">
-        <v>7</v>
-      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3">
-        <v>325</v>
-      </c>
-      <c r="I18" s="3">
-        <v>17</v>
-      </c>
-      <c r="J18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3">
+        <v>6</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3">
-        <v>46</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="2">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="B19" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C19" s="3">
-        <v>476</v>
-      </c>
-      <c r="D19" s="3">
-        <v>108</v>
-      </c>
+        <v>88887</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
-        <v>301</v>
-      </c>
-      <c r="I19" s="3">
-        <v>19</v>
-      </c>
-      <c r="J19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3">
+        <v>11</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3">
-        <v>20</v>
-      </c>
-      <c r="M19" s="3">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B20" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C20" s="3">
-        <v>3</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B21" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3">
-        <v>2</v>
-      </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B22" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3">
-        <v>6</v>
-      </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B23" s="2">
-        <v>88887</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3">
         <v>11</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3">
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="4">
-        <v>4469</v>
-      </c>
-      <c r="D24" s="4">
-        <v>979</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="B20" s="2"/>
+      <c r="C20" s="4">
+        <v>3829</v>
+      </c>
+      <c r="D20" s="4">
+        <v>871</v>
+      </c>
+      <c r="E20" s="4">
         <v>1007</v>
       </c>
-      <c r="F24" s="4">
-        <v>68</v>
-      </c>
-      <c r="G24" s="4">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4">
-        <v>3255</v>
-      </c>
-      <c r="I24" s="4">
+      <c r="F20" s="4">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2652</v>
+      </c>
+      <c r="H20" s="4">
         <v>161</v>
       </c>
-      <c r="J24" s="4">
+      <c r="I20" s="4">
         <v>25</v>
       </c>
-      <c r="K24" s="4">
+      <c r="J20" s="4">
         <v>19</v>
       </c>
-      <c r="L24" s="4">
-        <v>219</v>
-      </c>
-      <c r="M24" s="4">
-        <v>10203</v>
+      <c r="K20" s="4">
+        <v>196</v>
+      </c>
+      <c r="L20" s="4">
+        <v>8775</v>
       </c>
     </row>
   </sheetData>
@@ -1274,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1293,63 +1144,65 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B2" s="2">
-        <v>21092</v>
-      </c>
-      <c r="C2" s="3">
-        <v>13</v>
-      </c>
+        <v>21085</v>
+      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3">
+        <v>7</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B3" s="2">
-        <v>21176</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
+        <v>21086</v>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="F3" s="3">
+        <v>37</v>
+      </c>
+      <c r="G3" s="3">
+        <v>7</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1357,186 +1210,188 @@
         <v>4002</v>
       </c>
       <c r="B4" s="2">
-        <v>21085</v>
+        <v>21515</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="B5" s="2">
-        <v>21086</v>
+        <v>21195</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="3">
-        <v>37</v>
-      </c>
-      <c r="G5" s="3">
-        <v>11</v>
-      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="B6" s="2">
-        <v>21515</v>
+        <v>21246</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>37</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2">
-        <v>4003</v>
+        <v>4005</v>
       </c>
       <c r="B7" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+        <v>21083</v>
+      </c>
+      <c r="C7" s="3">
+        <v>122</v>
+      </c>
+      <c r="D7" s="3">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3">
+        <v>15</v>
+      </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>4</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>4</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B8" s="2">
-        <v>21195</v>
+        <v>21234</v>
       </c>
       <c r="C8" s="3">
-        <v>61</v>
+        <v>710</v>
       </c>
       <c r="D8" s="3">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>75</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>69</v>
+        <v>810</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B9" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>21457</v>
+      </c>
+      <c r="C9" s="3">
+        <v>330</v>
+      </c>
       <c r="D9" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3">
-        <v>2</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3">
-        <v>49</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="B10" s="2">
-        <v>21083</v>
+        <v>21523</v>
       </c>
       <c r="C10" s="3">
-        <v>122</v>
-      </c>
-      <c r="D10" s="3">
-        <v>30</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>24</v>
+      </c>
       <c r="I10" s="3">
-        <v>187</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2">
-        <v>4005</v>
+        <v>4007</v>
       </c>
       <c r="B11" s="2">
-        <v>21234</v>
+        <v>21082</v>
       </c>
       <c r="C11" s="3">
-        <v>721</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>75</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>10</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>821</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2">
-        <v>4005</v>
+        <v>4010</v>
       </c>
       <c r="B12" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C12" s="3">
-        <v>330</v>
-      </c>
-      <c r="D12" s="3">
-        <v>30</v>
-      </c>
+        <v>21089</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="3">
         <v>5</v>
       </c>
@@ -1544,199 +1399,128 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>365</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="B13" s="2">
-        <v>21523</v>
+        <v>21090</v>
       </c>
       <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>194</v>
+      </c>
+      <c r="D13" s="3">
+        <v>21</v>
+      </c>
       <c r="E13" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>24</v>
-      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>73</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2">
-        <v>4007</v>
+        <v>4011</v>
       </c>
       <c r="B14" s="2">
-        <v>21082</v>
+        <v>21075</v>
       </c>
       <c r="C14" s="3">
-        <v>31</v>
-      </c>
-      <c r="D14" s="3">
-        <v>29</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3">
-        <v>38</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>30</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3">
+        <v>13</v>
+      </c>
       <c r="I14" s="3">
-        <v>108</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B15" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>21094</v>
+      </c>
+      <c r="C15" s="3">
+        <v>44</v>
+      </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3">
-        <v>59</v>
-      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B16" s="2">
-        <v>21090</v>
+        <v>21533</v>
       </c>
       <c r="C16" s="3">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="D16" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>24</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I16" s="3">
-        <v>226</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B17" s="2">
-        <v>21075</v>
-      </c>
-      <c r="C17" s="3">
-        <v>117</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>30</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>13</v>
-      </c>
-      <c r="I17" s="3">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B18" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C18" s="3">
-        <v>44</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B19" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C19" s="3">
-        <v>241</v>
-      </c>
-      <c r="D19" s="3">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>8</v>
-      </c>
-      <c r="F19" s="3">
-        <v>24</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3">
-        <v>16</v>
-      </c>
-      <c r="I19" s="3">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4">
-        <v>1876</v>
-      </c>
-      <c r="D20" s="4">
-        <v>235</v>
-      </c>
-      <c r="E20" s="4">
-        <v>155</v>
-      </c>
-      <c r="F20" s="4">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="4">
+        <v>1790</v>
+      </c>
+      <c r="D17" s="4">
+        <v>203</v>
+      </c>
+      <c r="E17" s="4">
+        <v>125</v>
+      </c>
+      <c r="F17" s="4">
         <v>166</v>
       </c>
-      <c r="G20" s="4">
-        <v>40</v>
-      </c>
-      <c r="H20" s="4">
-        <v>116</v>
-      </c>
-      <c r="I20" s="4">
-        <v>2588</v>
+      <c r="G17" s="4">
+        <v>27</v>
+      </c>
+      <c r="H17" s="4">
+        <v>53</v>
+      </c>
+      <c r="I17" s="4">
+        <v>2364</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1771,45 +1555,45 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>60127</v>
+        <v>60138</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1821,18 +1605,18 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M2" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>60129</v>
+        <v>60496</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1840,25 +1624,27 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3">
-        <v>6</v>
-      </c>
+      <c r="L3" s="3"/>
       <c r="M3" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>60131</v>
+        <v>60507</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -1867,18 +1653,18 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M4" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>60138</v>
+        <v>60127</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1886,24 +1672,22 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
+      <c r="L5" s="3"/>
       <c r="M5" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>60496</v>
+        <v>60129</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1911,120 +1695,114 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>67</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3">
-        <v>68</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>60507</v>
+        <v>60131</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
+      <c r="L7" s="3"/>
       <c r="M7" s="3">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>60127</v>
+        <v>60138</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>70</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="3">
+        <v>19</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>60129</v>
+        <v>60496</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3">
-        <v>62</v>
-      </c>
+      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="J9" s="3">
+        <v>25</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>60131</v>
+        <v>60507</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3">
-        <v>100</v>
-      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="J10" s="3">
+        <v>57</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>60138</v>
+        <v>60127</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -2034,20 +1812,20 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>42</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>60496</v>
+        <v>60129</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -2057,20 +1835,20 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>66</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>60507</v>
+        <v>60131</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -2080,20 +1858,20 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>118</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>60127</v>
+        <v>60138</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -2101,45 +1879,47 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3">
-        <v>165</v>
-      </c>
+      <c r="I14" s="3">
+        <v>25</v>
+      </c>
+      <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>165</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>60129</v>
+        <v>60496</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3">
-        <v>207</v>
-      </c>
+      <c r="I15" s="3">
+        <v>64</v>
+      </c>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3">
-        <v>207</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
-        <v>60131</v>
+        <v>60507</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -2147,22 +1927,22 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3">
-        <v>112</v>
-      </c>
+      <c r="I16" s="3">
+        <v>47</v>
+      </c>
+      <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3">
-        <v>112</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
-        <v>60138</v>
+        <v>60127</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -2173,44 +1953,44 @@
       <c r="I17" s="3">
         <v>58</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>1</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2">
-        <v>60496</v>
+        <v>60129</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3">
-        <v>98</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2">
-        <v>60507</v>
+        <v>60131</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -2219,18 +1999,20 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3">
-        <v>65</v>
-      </c>
-      <c r="J19" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>60127</v>
@@ -2238,24 +2020,24 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3">
+        <v>3</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="3">
-        <v>101</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3">
+        <v>30</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3">
-        <v>102</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2">
         <v>60129</v>
@@ -2266,19 +2048,19 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3">
-        <v>91</v>
-      </c>
+      <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3">
+        <v>20</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3">
-        <v>91</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
         <v>60131</v>
@@ -2286,107 +2068,101 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3">
+        <v>3</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3">
-        <v>107</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1</v>
-      </c>
-      <c r="K22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3">
+        <v>19</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>60127</v>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3">
+        <v>15</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3">
-        <v>19</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3">
-        <v>30</v>
-      </c>
+      <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2">
         <v>60129</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3">
+        <v>7</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3">
-        <v>15</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="3">
-        <v>20</v>
-      </c>
+      <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B25" s="2">
         <v>60131</v>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3">
+        <v>29</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3">
-        <v>15</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="3">
-        <v>19</v>
-      </c>
+      <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>60138</v>
-      </c>
-      <c r="C26" s="3">
-        <v>3</v>
-      </c>
-      <c r="D26" s="3"/>
+        <v>60128</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3">
+        <v>6</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -2394,45 +2170,51 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="L26" s="3">
+        <v>20</v>
+      </c>
       <c r="M26" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C27" s="3">
-        <v>103</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>60132</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3">
+        <v>26</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="3">
+        <v>1</v>
+      </c>
       <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
+      <c r="L27" s="3">
+        <v>92</v>
+      </c>
       <c r="M27" s="3">
-        <v>103</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C28" s="3">
-        <v>54</v>
-      </c>
-      <c r="D28" s="3"/>
+        <v>60134</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3">
+        <v>8</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -2440,106 +2222,110 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
+      <c r="L28" s="3">
+        <v>19</v>
+      </c>
       <c r="M28" s="3">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>60131</v>
-      </c>
-      <c r="C29" s="3">
-        <v>81</v>
-      </c>
+        <v>60128</v>
+      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
+      <c r="H29" s="3">
+        <v>70</v>
+      </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B30" s="2">
-        <v>60127</v>
+        <v>60132</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3">
-        <v>3</v>
-      </c>
-      <c r="H30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3">
+        <v>222</v>
+      </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="L30" s="3">
+        <v>2</v>
+      </c>
       <c r="M30" s="3">
-        <v>3</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>60129</v>
+        <v>60134</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3">
-        <v>3</v>
-      </c>
-      <c r="H31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3">
+        <v>141</v>
+      </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3">
-        <v>3</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>60131</v>
+        <v>60128</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3">
-        <v>3</v>
-      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="3">
+        <v>140</v>
+      </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
-        <v>3</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B33" s="2">
         <v>60132</v>
@@ -2548,21 +2334,21 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3">
-        <v>6</v>
-      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="J33" s="3">
+        <v>136</v>
+      </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3">
-        <v>6</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B34" s="2">
         <v>60134</v>
@@ -2571,98 +2357,92 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3">
-        <v>4</v>
-      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="J34" s="3">
+        <v>99</v>
+      </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B35" s="2">
         <v>60128</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="3">
-        <v>6</v>
-      </c>
+      <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="I35" s="3">
+        <v>85</v>
+      </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
-      <c r="L35" s="3">
-        <v>39</v>
-      </c>
+      <c r="L35" s="3"/>
       <c r="M35" s="3">
-        <v>45</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B36" s="2">
         <v>60132</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="3">
-        <v>26</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3">
-        <v>1</v>
-      </c>
+      <c r="I36" s="3">
+        <v>350</v>
+      </c>
+      <c r="J36" s="3"/>
       <c r="K36" s="3"/>
-      <c r="L36" s="3">
-        <v>183</v>
-      </c>
+      <c r="L36" s="3"/>
       <c r="M36" s="3">
-        <v>210</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B37" s="2">
         <v>60134</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="I37" s="3">
+        <v>111</v>
+      </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
-      <c r="L37" s="3">
-        <v>38</v>
-      </c>
+      <c r="L37" s="3"/>
       <c r="M37" s="3">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B38" s="2">
         <v>60128</v>
@@ -2670,22 +2450,24 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3">
+        <v>4</v>
+      </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="3">
-        <v>88</v>
-      </c>
+      <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
+      <c r="K38" s="3">
+        <v>15</v>
+      </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B39" s="2">
         <v>60132</v>
@@ -2693,24 +2475,24 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3">
+        <v>23</v>
+      </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="3">
-        <v>303</v>
-      </c>
+      <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3">
-        <v>2</v>
-      </c>
+      <c r="K39" s="3">
+        <v>77</v>
+      </c>
+      <c r="L39" s="3"/>
       <c r="M39" s="3">
-        <v>305</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B40" s="2">
         <v>60134</v>
@@ -2718,245 +2500,245 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3">
+        <v>16</v>
+      </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="3">
-        <v>170</v>
-      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="3">
+        <v>46</v>
+      </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
-        <v>170</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B41" s="2">
         <v>60128</v>
       </c>
-      <c r="C41" s="3"/>
+      <c r="C41" s="3">
+        <v>35</v>
+      </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3">
-        <v>140</v>
-      </c>
+      <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3">
-        <v>140</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B42" s="2">
         <v>60132</v>
       </c>
-      <c r="C42" s="3"/>
+      <c r="C42" s="3">
+        <v>213</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3">
-        <v>136</v>
-      </c>
+      <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3">
-        <v>136</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B43" s="2">
         <v>60134</v>
       </c>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3">
+        <v>109</v>
+      </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3">
-        <v>99</v>
-      </c>
+      <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B44" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C44" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C44" s="3">
+        <v>137</v>
+      </c>
       <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="3">
-        <v>100</v>
-      </c>
+      <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C45" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C45" s="3">
+        <v>179</v>
+      </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="3">
-        <v>454</v>
-      </c>
+      <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3">
-        <v>454</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B46" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3">
-        <v>2</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C46" s="3">
+        <v>169</v>
+      </c>
+      <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="3">
-        <v>117</v>
-      </c>
+      <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3">
-        <v>119</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B47" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C47" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C47" s="3">
+        <v>268</v>
+      </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3">
-        <v>13</v>
-      </c>
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="3">
-        <v>15</v>
-      </c>
+      <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3">
-        <v>28</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B48" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C48" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C48" s="3">
+        <v>170</v>
+      </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3">
-        <v>60</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="3">
-        <v>77</v>
-      </c>
+      <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3">
-        <v>137</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B49" s="2">
-        <v>60134</v>
+        <v>60135</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="D49" s="3">
+        <v>11</v>
+      </c>
       <c r="E49" s="3"/>
-      <c r="F49" s="3">
-        <v>42</v>
-      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="3">
-        <v>46</v>
-      </c>
-      <c r="L49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3">
+        <v>43</v>
+      </c>
       <c r="M49" s="3">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C50" s="3">
-        <v>94</v>
-      </c>
-      <c r="D50" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3">
+        <v>10</v>
+      </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2964,22 +2746,24 @@
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
+      <c r="L50" s="3">
+        <v>26</v>
+      </c>
       <c r="M50" s="3">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B51" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C51" s="3">
-        <v>414</v>
-      </c>
-      <c r="D51" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3">
+        <v>5</v>
+      </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2987,22 +2771,24 @@
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="L51" s="3">
+        <v>23</v>
+      </c>
       <c r="M51" s="3">
-        <v>414</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B52" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C52" s="3">
-        <v>188</v>
-      </c>
-      <c r="D52" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3">
+        <v>5</v>
+      </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -3010,383 +2796,377 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
+      <c r="L52" s="3">
+        <v>248</v>
+      </c>
       <c r="M52" s="3">
-        <v>188</v>
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B53" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C53" s="3">
-        <v>137</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3">
-        <v>1</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3">
+        <v>15</v>
+      </c>
+      <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
+      <c r="L53" s="3">
+        <v>356</v>
+      </c>
       <c r="M53" s="3">
-        <v>138</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B54" s="2">
         <v>60139</v>
       </c>
-      <c r="C54" s="3">
-        <v>179</v>
-      </c>
+      <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3">
+        <v>80</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
+      <c r="K54" s="3">
+        <v>19</v>
+      </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3">
-        <v>179</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2">
         <v>60306</v>
       </c>
-      <c r="C55" s="3">
-        <v>169</v>
-      </c>
+      <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3">
+        <v>78</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
+      <c r="K55" s="3">
+        <v>26</v>
+      </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3">
-        <v>169</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B56" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C56" s="3">
-        <v>268</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C56" s="3"/>
       <c r="D56" s="3"/>
-      <c r="E56" s="3">
-        <v>5</v>
-      </c>
-      <c r="F56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3">
+        <v>91</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
+      <c r="K56" s="3">
+        <v>37</v>
+      </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3">
-        <v>273</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C57" s="3">
-        <v>170</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3">
+        <v>51</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
+      <c r="K57" s="3">
+        <v>27</v>
+      </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3">
-        <v>170</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B58" s="2">
         <v>60135</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="3">
-        <v>11</v>
-      </c>
+      <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
+      <c r="F58" s="3">
+        <v>45</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3">
-        <v>139</v>
-      </c>
+      <c r="K58" s="3">
+        <v>13</v>
+      </c>
+      <c r="L58" s="3"/>
       <c r="M58" s="3">
-        <v>150</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2">
-        <v>60139</v>
+        <v>60135</v>
       </c>
       <c r="C59" s="3"/>
-      <c r="D59" s="3">
-        <v>10</v>
-      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="I59" s="3">
+        <v>172</v>
+      </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
-      <c r="L59" s="3">
-        <v>148</v>
-      </c>
+      <c r="L59" s="3"/>
       <c r="M59" s="3">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B60" s="2">
-        <v>60306</v>
+        <v>60139</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="3">
-        <v>5</v>
-      </c>
+      <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="I60" s="3">
+        <v>185</v>
+      </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
-      <c r="L60" s="3">
-        <v>90</v>
-      </c>
+      <c r="L60" s="3"/>
       <c r="M60" s="3">
-        <v>95</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B61" s="2">
-        <v>60130</v>
+        <v>60306</v>
       </c>
       <c r="C61" s="3"/>
-      <c r="D61" s="3">
-        <v>5</v>
-      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="I61" s="3">
+        <v>215</v>
+      </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
-      <c r="L61" s="3">
-        <v>248</v>
-      </c>
+      <c r="L61" s="3"/>
       <c r="M61" s="3">
-        <v>253</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B62" s="2">
-        <v>60355</v>
+        <v>60130</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="I62" s="3">
+        <v>204</v>
+      </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
-      <c r="L62" s="3">
-        <v>356</v>
-      </c>
+      <c r="L62" s="3"/>
       <c r="M62" s="3">
-        <v>371</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B63" s="2">
-        <v>60139</v>
+        <v>60355</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="3">
-        <v>80</v>
-      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="I63" s="3">
+        <v>282</v>
+      </c>
       <c r="J63" s="3"/>
-      <c r="K63" s="3">
-        <v>19</v>
-      </c>
+      <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3">
-        <v>99</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B64" s="2">
-        <v>60306</v>
+        <v>60132</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="3">
-        <v>26</v>
-      </c>
+      <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3">
-        <v>104</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B65" s="2">
-        <v>60355</v>
+        <v>60296</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="3">
-        <v>91</v>
-      </c>
-      <c r="G65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3">
+        <v>3</v>
+      </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-      <c r="K65" s="3">
-        <v>37</v>
-      </c>
+      <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3">
-        <v>128</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B66" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
-      <c r="K66" s="3">
-        <v>27</v>
-      </c>
+      <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B67" s="2">
-        <v>60135</v>
+        <v>60496</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="3">
-        <v>45</v>
-      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
+      <c r="H67" s="3">
+        <v>3</v>
+      </c>
       <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3">
-        <v>13</v>
-      </c>
+      <c r="J67" s="3">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B68" s="2">
         <v>60135</v>
@@ -3397,19 +3177,19 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="3">
-        <v>172</v>
-      </c>
-      <c r="J68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3">
+        <v>80</v>
+      </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3">
-        <v>172</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B69" s="2">
         <v>60139</v>
@@ -3420,19 +3200,19 @@
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="3">
-        <v>185</v>
-      </c>
-      <c r="J69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3">
+        <v>71</v>
+      </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3">
-        <v>185</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B70" s="2">
         <v>60306</v>
@@ -3443,517 +3223,191 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="3">
-        <v>215</v>
-      </c>
-      <c r="J70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3">
+        <v>72</v>
+      </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3">
-        <v>215</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="2">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B71" s="2">
         <v>60130</v>
       </c>
       <c r="C71" s="3"/>
-      <c r="D71" s="3">
-        <v>1</v>
-      </c>
+      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
-      <c r="I71" s="3">
-        <v>204</v>
-      </c>
-      <c r="J71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3">
+        <v>102</v>
+      </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3">
-        <v>205</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B72" s="2">
-        <v>60355</v>
+        <v>60139</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3">
-        <v>282</v>
-      </c>
+      <c r="H72" s="3">
+        <v>205</v>
+      </c>
+      <c r="I72" s="3"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3">
-        <v>282</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B73" s="2">
-        <v>60130</v>
+        <v>60306</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="3">
-        <v>3</v>
-      </c>
-      <c r="H73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3">
+        <v>200</v>
+      </c>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3">
-        <v>3</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B74" s="2">
-        <v>60132</v>
+        <v>60355</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
-      <c r="F74" s="3">
-        <v>3</v>
-      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
+      <c r="H74" s="3">
+        <v>342</v>
+      </c>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3">
-        <v>3</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B75" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3">
-        <v>3</v>
-      </c>
-      <c r="H75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3">
+        <v>124</v>
+      </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3">
-        <v>3</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B76" s="2">
-        <v>60202</v>
+        <v>60135</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3">
+        <v>149</v>
+      </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="4">
+        <v>1331</v>
+      </c>
+      <c r="D77" s="4">
+        <v>91</v>
+      </c>
+      <c r="E77" s="4">
+        <v>6</v>
+      </c>
+      <c r="F77" s="4">
+        <v>398</v>
+      </c>
+      <c r="G77" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:13">
-      <c r="A77" s="2">
-        <v>50</v>
-      </c>
-      <c r="B77" s="2">
-        <v>60215</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3">
-        <v>3</v>
-      </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
-      <c r="A78" s="2">
-        <v>50</v>
-      </c>
-      <c r="B78" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3">
-        <v>3</v>
-      </c>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3"/>
-      <c r="M78" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
-      <c r="A79" s="2">
-        <v>50</v>
-      </c>
-      <c r="B79" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3">
-        <v>3</v>
-      </c>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
-      <c r="A80" s="2">
-        <v>50</v>
-      </c>
-      <c r="B80" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
-      <c r="M80" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
-      <c r="A81" s="2">
-        <v>50</v>
-      </c>
-      <c r="B81" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3">
-        <v>1</v>
-      </c>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3"/>
-      <c r="M81" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
-      <c r="A82" s="2">
-        <v>51</v>
-      </c>
-      <c r="B82" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3">
-        <v>80</v>
-      </c>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3"/>
-      <c r="M82" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13">
-      <c r="A83" s="2">
-        <v>51</v>
-      </c>
-      <c r="B83" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3">
-        <v>71</v>
-      </c>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="2">
-        <v>51</v>
-      </c>
-      <c r="B84" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3">
-        <v>72</v>
-      </c>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="2">
-        <v>52</v>
-      </c>
-      <c r="B85" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3">
-        <v>102</v>
-      </c>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="2">
-        <v>53</v>
-      </c>
-      <c r="B86" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3">
-        <v>205</v>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="2">
-        <v>53</v>
-      </c>
-      <c r="B87" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3">
-        <v>200</v>
-      </c>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="2">
-        <v>53</v>
-      </c>
-      <c r="B88" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3">
-        <v>342</v>
-      </c>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="2">
-        <v>54</v>
-      </c>
-      <c r="B89" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3">
-        <v>124</v>
-      </c>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="2">
-        <v>54</v>
-      </c>
-      <c r="B90" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3">
-        <v>149</v>
-      </c>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="4">
-        <v>1860</v>
-      </c>
-      <c r="D91" s="4">
-        <v>91</v>
-      </c>
-      <c r="E91" s="4">
-        <v>6</v>
-      </c>
-      <c r="F91" s="4">
-        <v>513</v>
-      </c>
-      <c r="G91" s="4">
-        <v>37</v>
-      </c>
-      <c r="H91" s="4">
-        <v>1955</v>
-      </c>
-      <c r="I91" s="4">
-        <v>2249</v>
-      </c>
-      <c r="J91" s="4">
-        <v>1414</v>
-      </c>
-      <c r="K91" s="4">
+      <c r="H77" s="4">
+        <v>1543</v>
+      </c>
+      <c r="I77" s="4">
+        <v>1920</v>
+      </c>
+      <c r="J77" s="4">
+        <v>1181</v>
+      </c>
+      <c r="K77" s="4">
         <v>329</v>
       </c>
-      <c r="L91" s="4">
-        <v>1266</v>
-      </c>
-      <c r="M91" s="4">
-        <v>9720</v>
+      <c r="L77" s="4">
+        <v>831</v>
+      </c>
+      <c r="M77" s="4">
+        <v>7633</v>
       </c>
     </row>
   </sheetData>
@@ -3963,7 +3417,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -3979,19 +3433,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4019,15 +3473,15 @@
         <v>21176</v>
       </c>
       <c r="C3" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4038,34 +3492,36 @@
         <v>21229</v>
       </c>
       <c r="C4" s="3">
-        <v>392</v>
+        <v>179</v>
       </c>
       <c r="D4" s="3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>424</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B5" s="2">
-        <v>21092</v>
+        <v>21086</v>
       </c>
       <c r="C5" s="3">
-        <v>61</v>
+        <v>243</v>
       </c>
       <c r="D5" s="3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3">
+        <v>44</v>
+      </c>
       <c r="G5" s="3">
-        <v>67</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4073,41 +3529,37 @@
         <v>2004</v>
       </c>
       <c r="B6" s="2">
-        <v>21086</v>
+        <v>21515</v>
       </c>
       <c r="C6" s="3">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="D6" s="3">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3">
-        <v>53</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>333</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B7" s="2">
-        <v>21515</v>
+        <v>21081</v>
       </c>
       <c r="C7" s="3">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>4</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>97</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4115,66 +3567,62 @@
         <v>2005</v>
       </c>
       <c r="B8" s="2">
-        <v>21081</v>
+        <v>21085</v>
       </c>
       <c r="C8" s="3">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>69</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B9" s="2">
-        <v>21085</v>
+        <v>21089</v>
       </c>
       <c r="C9" s="3">
-        <v>221</v>
-      </c>
-      <c r="D9" s="3">
         <v>50</v>
       </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3">
-        <v>279</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B10" s="2">
-        <v>21089</v>
+        <v>21082</v>
       </c>
       <c r="C10" s="3">
-        <v>50</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>252</v>
+      </c>
+      <c r="D10" s="3">
+        <v>28</v>
+      </c>
       <c r="E10" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F10" s="3">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3">
-        <v>58</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4182,45 +3630,43 @@
         <v>2007</v>
       </c>
       <c r="B11" s="2">
-        <v>21082</v>
+        <v>21234</v>
       </c>
       <c r="C11" s="3">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D11" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3">
-        <v>358</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B12" s="2">
-        <v>21234</v>
+        <v>21083</v>
       </c>
       <c r="C12" s="3">
-        <v>235</v>
-      </c>
-      <c r="D12" s="3">
-        <v>42</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" s="3">
-        <v>317</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4228,43 +3674,45 @@
         <v>2008</v>
       </c>
       <c r="B13" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C13" s="3">
-        <v>64</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>420</v>
+      </c>
+      <c r="D13" s="3">
+        <v>22</v>
+      </c>
       <c r="E13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G13" s="3">
-        <v>85</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B14" s="2">
-        <v>21457</v>
+        <v>21195</v>
       </c>
       <c r="C14" s="3">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E14" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F14" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G14" s="3">
-        <v>459</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4272,93 +3720,87 @@
         <v>2009</v>
       </c>
       <c r="B15" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C15" s="3">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D15" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B16" s="2">
-        <v>21246</v>
+        <v>21090</v>
       </c>
       <c r="C16" s="3">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F16" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G16" s="3">
-        <v>122</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B17" s="2">
-        <v>21090</v>
+        <v>21533</v>
       </c>
       <c r="C17" s="3">
-        <v>34</v>
-      </c>
-      <c r="D17" s="3">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B18" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C18" s="3">
-        <v>30</v>
-      </c>
-      <c r="D18" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B19" s="2">
-        <v>21082</v>
+        <v>21086</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3">
@@ -4372,10 +3814,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B20" s="2">
-        <v>21086</v>
+        <v>21085</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3">
@@ -4389,59 +3831,42 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B21" s="2">
-        <v>21085</v>
+        <v>21457</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B22" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4">
-        <v>2355</v>
-      </c>
-      <c r="D23" s="4">
-        <v>286</v>
-      </c>
-      <c r="E23" s="4">
-        <v>145</v>
-      </c>
-      <c r="F23" s="4">
-        <v>173</v>
-      </c>
-      <c r="G23" s="4">
-        <v>2959</v>
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="4">
+        <v>2070</v>
+      </c>
+      <c r="D22" s="4">
+        <v>256</v>
+      </c>
+      <c r="E22" s="4">
+        <v>137</v>
+      </c>
+      <c r="F22" s="4">
+        <v>155</v>
+      </c>
+      <c r="G22" s="4">
+        <v>2618</v>
       </c>
     </row>
   </sheetData>
@@ -4451,7 +3876,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4468,10 +3893,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4531,29 +3956,15 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2">
-        <v>5004</v>
-      </c>
-      <c r="B6" s="2">
-        <v>17183</v>
-      </c>
-      <c r="C6" s="3">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4">
-        <v>32</v>
-      </c>
-      <c r="D7" s="4">
-        <v>32</v>
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -4563,7 +3974,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4583,60 +3994,62 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2">
-        <v>3000</v>
+        <v>3003</v>
       </c>
       <c r="B2" s="2">
-        <v>21088</v>
+        <v>21081</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="E2" s="3">
+        <v>20</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4644,7 +4057,7 @@
         <v>3003</v>
       </c>
       <c r="B3" s="2">
-        <v>21081</v>
+        <v>21515</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -4653,44 +4066,54 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3">
-        <v>28</v>
-      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="B4" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3">
+        <v>162</v>
+      </c>
       <c r="E4" s="3">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="F4" s="3">
+        <v>119</v>
+      </c>
+      <c r="G4" s="3">
+        <v>70</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
       <c r="I4" s="3">
-        <v>17</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="J4" s="3">
+        <v>137</v>
+      </c>
+      <c r="K4" s="3">
+        <v>117</v>
+      </c>
+      <c r="L4" s="3">
+        <v>14</v>
+      </c>
       <c r="M4" s="3">
-        <v>37</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4698,79 +4121,77 @@
         <v>3004</v>
       </c>
       <c r="B5" s="2">
-        <v>21082</v>
+        <v>21234</v>
       </c>
       <c r="C5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="E5" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3">
-        <v>70</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J5" s="3">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="K5" s="3">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M5" s="3">
-        <v>800</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>3004</v>
+        <v>3006</v>
       </c>
       <c r="B6" s="2">
-        <v>21234</v>
+        <v>21083</v>
       </c>
       <c r="C6" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="J6" s="3">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="K6" s="3">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="3">
-        <v>516</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4778,77 +4199,75 @@
         <v>3006</v>
       </c>
       <c r="B7" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C7" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="J7" s="3">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="K7" s="3">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3">
-        <v>386</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2">
-        <v>3006</v>
+        <v>3008</v>
       </c>
       <c r="B8" s="2">
-        <v>21457</v>
+        <v>21195</v>
       </c>
       <c r="C8" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3">
-        <v>33</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>19</v>
-      </c>
-      <c r="H8" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3</v>
+      </c>
       <c r="I8" s="3">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="J8" s="3">
-        <v>16</v>
-      </c>
-      <c r="K8" s="3">
-        <v>105</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="K8" s="3"/>
       <c r="L8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" s="3">
-        <v>286</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4856,77 +4275,69 @@
         <v>3008</v>
       </c>
       <c r="B9" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3">
-        <v>13</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="H9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J9" s="3">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M9" s="3">
-        <v>616</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="B10" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C10" s="3">
+        <v>21085</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>57</v>
-      </c>
-      <c r="E10" s="3">
-        <v>14</v>
-      </c>
       <c r="F10" s="3">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3">
-        <v>52</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="3">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="J10" s="3">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3">
         <v>6</v>
       </c>
       <c r="M10" s="3">
-        <v>514</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4934,16 +4345,12 @@
         <v>3009</v>
       </c>
       <c r="B11" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>62</v>
-      </c>
+        <v>21086</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3">
         <v>35</v>
@@ -4951,75 +4358,71 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J11" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" s="3">
-        <v>187</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="B12" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C12" s="3">
-        <v>5</v>
-      </c>
+        <v>21081</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3">
-        <v>76</v>
-      </c>
-      <c r="E12" s="3">
-        <v>28</v>
-      </c>
-      <c r="F12" s="3">
-        <v>43</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3">
-        <v>67</v>
-      </c>
-      <c r="J12" s="3">
-        <v>6</v>
-      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3">
-        <v>17</v>
-      </c>
+      <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>242</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="B13" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>21089</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="3">
+        <v>19</v>
+      </c>
+      <c r="G13" s="3">
+        <v>17</v>
+      </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="I13" s="3">
+        <v>58</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -5027,102 +4430,71 @@
         <v>3011</v>
       </c>
       <c r="B14" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
+        <v>21090</v>
+      </c>
+      <c r="C14" s="3"/>
       <c r="D14" s="3">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="E14" s="3">
+        <v>12</v>
+      </c>
       <c r="F14" s="3">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>2</v>
+      </c>
       <c r="M14" s="3">
-        <v>104</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B15" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="4">
         <v>30</v>
       </c>
-      <c r="E15" s="3">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3">
-        <v>48</v>
-      </c>
-      <c r="G15" s="3">
-        <v>36</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>40</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3">
-        <v>2</v>
-      </c>
-      <c r="M15" s="3">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4">
-        <v>36</v>
-      </c>
-      <c r="D16" s="4">
-        <v>635</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D15" s="4">
+        <v>498</v>
+      </c>
+      <c r="E15" s="4">
         <v>216</v>
       </c>
-      <c r="F16" s="4">
-        <v>428</v>
-      </c>
-      <c r="G16" s="4">
-        <v>428</v>
-      </c>
-      <c r="H16" s="4">
-        <v>7</v>
-      </c>
-      <c r="I16" s="4">
-        <v>789</v>
-      </c>
-      <c r="J16" s="4">
-        <v>793</v>
-      </c>
-      <c r="K16" s="4">
-        <v>537</v>
-      </c>
-      <c r="L16" s="4">
-        <v>59</v>
-      </c>
-      <c r="M16" s="4">
-        <v>3928</v>
+      <c r="F15" s="4">
+        <v>406</v>
+      </c>
+      <c r="G15" s="4">
+        <v>359</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>744</v>
+      </c>
+      <c r="J15" s="4">
+        <v>587</v>
+      </c>
+      <c r="K15" s="4">
+        <v>429</v>
+      </c>
+      <c r="L15" s="4">
+        <v>47</v>
+      </c>
+      <c r="M15" s="4">
+        <v>3321</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="39">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -78,9 +78,6 @@
     <t>MCHL</t>
   </si>
   <si>
-    <t>MCOS1</t>
-  </si>
-  <si>
     <t>MFTA</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
   </si>
   <si>
     <t>SPAIS1</t>
-  </si>
-  <si>
-    <t>SPAIS2</t>
   </si>
   <si>
     <t>SPLAD</t>
@@ -531,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -670,7 +664,7 @@
         <v>21086</v>
       </c>
       <c r="C5" s="3">
-        <v>486</v>
+        <v>269</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -680,28 +674,36 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>486</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B6" s="2">
-        <v>21515</v>
+        <v>21195</v>
       </c>
       <c r="C6" s="3">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+        <v>634</v>
+      </c>
+      <c r="D6" s="3">
+        <v>137</v>
+      </c>
+      <c r="E6" s="3">
+        <v>152</v>
+      </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>233</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>4</v>
+      </c>
       <c r="K6" s="3">
-        <v>12</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -709,59 +711,59 @@
         <v>1012</v>
       </c>
       <c r="B7" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C7" s="3">
-        <v>709</v>
+        <v>513</v>
       </c>
       <c r="D7" s="3">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="E7" s="3">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>330</v>
-      </c>
-      <c r="H7" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="H7" s="3">
+        <v>11</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K7" s="3">
-        <v>1428</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B8" s="2">
-        <v>21246</v>
+        <v>21083</v>
       </c>
       <c r="C8" s="3">
-        <v>592</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>359</v>
+        <v>266</v>
       </c>
       <c r="H8" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>37</v>
-      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>1301</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -769,57 +771,57 @@
         <v>1013</v>
       </c>
       <c r="B9" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C9" s="3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="H9" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>459</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B10" s="2">
-        <v>21457</v>
+        <v>21089</v>
       </c>
       <c r="C10" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>243</v>
+        <v>182</v>
       </c>
       <c r="H10" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>397</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -827,57 +829,49 @@
         <v>1014</v>
       </c>
       <c r="B11" s="2">
-        <v>21089</v>
+        <v>21234</v>
       </c>
       <c r="C11" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>182</v>
+        <v>256</v>
       </c>
       <c r="H11" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3">
-        <v>285</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B12" s="2">
-        <v>21234</v>
+        <v>21081</v>
       </c>
       <c r="C12" s="3">
-        <v>12</v>
-      </c>
-      <c r="D12" s="3">
-        <v>59</v>
-      </c>
-      <c r="E12" s="3">
-        <v>67</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3">
-        <v>256</v>
-      </c>
-      <c r="H12" s="3">
-        <v>20</v>
-      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>414</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -885,107 +879,78 @@
         <v>1015</v>
       </c>
       <c r="B13" s="2">
-        <v>21081</v>
+        <v>21090</v>
       </c>
       <c r="C13" s="3">
-        <v>200</v>
+        <v>476</v>
       </c>
       <c r="D13" s="3">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3">
-        <v>118</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3">
-        <v>457</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B14" s="2">
-        <v>21090</v>
+        <v>21253</v>
       </c>
       <c r="C14" s="3">
-        <v>476</v>
-      </c>
-      <c r="D14" s="3">
-        <v>88</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3">
-        <v>86</v>
-      </c>
-      <c r="H14" s="3">
-        <v>19</v>
-      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3">
-        <v>669</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B15" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="2" t="s">
+      <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4">
-        <v>3270</v>
-      </c>
-      <c r="D16" s="4">
-        <v>763</v>
-      </c>
-      <c r="E16" s="4">
-        <v>1007</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="B15" s="2"/>
+      <c r="C15" s="4">
+        <v>2719</v>
+      </c>
+      <c r="D15" s="4">
+        <v>597</v>
+      </c>
+      <c r="E15" s="4">
+        <v>870</v>
+      </c>
+      <c r="F15" s="4">
         <v>15</v>
       </c>
-      <c r="G16" s="4">
-        <v>2046</v>
-      </c>
-      <c r="H16" s="4">
-        <v>99</v>
-      </c>
-      <c r="I16" s="4">
+      <c r="G15" s="4">
+        <v>1633</v>
+      </c>
+      <c r="H15" s="4">
+        <v>82</v>
+      </c>
+      <c r="I15" s="4">
         <v>25</v>
       </c>
-      <c r="J16" s="4">
-        <v>128</v>
-      </c>
-      <c r="K16" s="4">
-        <v>7353</v>
+      <c r="J15" s="4">
+        <v>68</v>
+      </c>
+      <c r="K15" s="4">
+        <v>6009</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1028,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1072,7 +1037,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1104,7 +1069,7 @@
         <v>21234</v>
       </c>
       <c r="C5" s="3">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="D5" s="3">
         <v>23</v>
@@ -1114,7 +1079,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>425</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1149,16 +1114,14 @@
         <v>1</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>48</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3">
         <v>24</v>
       </c>
       <c r="I7" s="3">
-        <v>73</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1168,9 +1131,7 @@
       <c r="B8" s="2">
         <v>21082</v>
       </c>
-      <c r="C8" s="3">
-        <v>31</v>
-      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3">
         <v>29</v>
       </c>
@@ -1183,7 +1144,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1212,9 +1173,7 @@
       <c r="B10" s="2">
         <v>21090</v>
       </c>
-      <c r="C10" s="3">
-        <v>62</v>
-      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3">
         <v>2</v>
@@ -1223,7 +1182,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1278,7 +1237,7 @@
         <v>21533</v>
       </c>
       <c r="C13" s="3">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3">
@@ -1292,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="I13" s="3">
-        <v>289</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1301,13 +1260,13 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="4">
-        <v>1350</v>
+        <v>1152</v>
       </c>
       <c r="D14" s="4">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="E14" s="4">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="F14" s="4">
         <v>54</v>
@@ -1319,7 +1278,7 @@
         <v>53</v>
       </c>
       <c r="I14" s="4">
-        <v>1729</v>
+        <v>1455</v>
       </c>
     </row>
   </sheetData>
@@ -1329,22 +1288,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="8" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="4" max="7" width="6.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1376,13 +1333,10 @@
         <v>24</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>9</v>
       </c>
@@ -1394,17 +1348,16 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3">
-        <v>119</v>
-      </c>
+      <c r="H2" s="3">
+        <v>85</v>
+      </c>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="K2" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>9</v>
       </c>
@@ -1416,17 +1369,16 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>143</v>
-      </c>
+      <c r="H3" s="3">
+        <v>89</v>
+      </c>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="K3" s="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>9</v>
       </c>
@@ -1438,17 +1390,16 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>76</v>
-      </c>
+      <c r="H4" s="3">
+        <v>41</v>
+      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="K4" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>12</v>
       </c>
@@ -1461,23 +1412,20 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3">
         <v>1</v>
       </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="K5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>12</v>
       </c>
       <c r="B6" s="2">
-        <v>60129</v>
+        <v>60131</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1485,729 +1433,691 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2">
-        <v>60131</v>
+        <v>60128</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="3">
+        <v>40</v>
+      </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3">
-        <v>36</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="K7" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3">
+        <v>91</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="J8" s="3">
+        <v>2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>26</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>60</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="K9" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3">
-        <v>8</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>88</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="K10" s="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3">
-        <v>52</v>
-      </c>
-      <c r="H11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3">
+        <v>92</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="K11" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3">
-        <v>151</v>
-      </c>
-      <c r="H12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3">
+        <v>72</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>2</v>
-      </c>
-      <c r="L12" s="3">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="K13" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3">
+        <v>189</v>
+      </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>140</v>
-      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="K14" s="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <v>44</v>
+      </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>136</v>
-      </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="K15" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C16" s="3">
+        <v>82</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3">
-        <v>99</v>
-      </c>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="K16" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C17" s="3">
+        <v>95</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>64</v>
-      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="K17" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C18" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C18" s="3">
+        <v>100</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3">
-        <v>285</v>
-      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="K18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
-        <v>2</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C19" s="3">
+        <v>268</v>
+      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3">
-        <v>78</v>
-      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="K19" s="3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C20" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C20" s="3">
+        <v>170</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2">
-        <v>60132</v>
+        <v>60130</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>5</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3">
-        <v>44</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>130</v>
+      </c>
+      <c r="K21" s="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2">
-        <v>60134</v>
+        <v>60355</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>15</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
-        <v>12</v>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>184</v>
+      </c>
+      <c r="K22" s="3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C23" s="3">
-        <v>9</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="E23" s="3">
+        <v>28</v>
+      </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="I23" s="3">
+        <v>19</v>
+      </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="K23" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2">
+        <v>36</v>
+      </c>
+      <c r="B24" s="2">
+        <v>60306</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3">
         <v>31</v>
       </c>
-      <c r="B24" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C24" s="3">
-        <v>44</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="I24" s="3">
+        <v>26</v>
+      </c>
       <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="K24" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C25" s="3">
-        <v>40</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="E25" s="3">
+        <v>38</v>
+      </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="I25" s="3">
+        <v>37</v>
+      </c>
       <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="K25" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C26" s="3">
-        <v>137</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3">
+        <v>6</v>
+      </c>
       <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="K26" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C27" s="3">
-        <v>179</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3">
+        <v>45</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="I27" s="3">
+        <v>5</v>
+      </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="K27" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C28" s="3">
-        <v>169</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3">
+        <v>151</v>
+      </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="K28" s="3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C29" s="3">
-        <v>268</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="3">
-        <v>5</v>
-      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3">
+        <v>153</v>
+      </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="K29" s="3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C30" s="3">
-        <v>170</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3">
+        <v>185</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="K30" s="3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2">
         <v>60130</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3">
+        <v>204</v>
+      </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3">
-        <v>197</v>
-      </c>
-      <c r="L31" s="3">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2">
         <v>60355</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="3">
-        <v>15</v>
-      </c>
+      <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3">
+        <v>282</v>
+      </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3">
-        <v>311</v>
-      </c>
-      <c r="L32" s="3">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B33" s="2">
-        <v>60139</v>
+        <v>60132</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3">
-        <v>69</v>
-      </c>
+      <c r="E33" s="3">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="3">
-        <v>19</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="J33" s="3"/>
+      <c r="K33" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B34" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3">
-        <v>71</v>
-      </c>
+      <c r="E34" s="3">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3">
-        <v>26</v>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="J34" s="3"/>
+      <c r="K34" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B35" s="2">
-        <v>60355</v>
+        <v>60135</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="3">
-        <v>83</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+      <c r="H35" s="3">
+        <v>38</v>
+      </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="3">
-        <v>37</v>
-      </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="J35" s="3"/>
+      <c r="K35" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B36" s="2">
-        <v>60130</v>
+        <v>60139</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3">
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3">
+        <v>40</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="2">
         <v>51</v>
       </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3">
-        <v>27</v>
-      </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="2">
-        <v>37</v>
-      </c>
       <c r="B37" s="2">
-        <v>60135</v>
+        <v>60306</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3">
-        <v>45</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
+      <c r="H37" s="3">
+        <v>32</v>
+      </c>
       <c r="I37" s="3"/>
-      <c r="J37" s="3">
-        <v>13</v>
-      </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="J37" s="3"/>
+      <c r="K37" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B38" s="2">
-        <v>60135</v>
+        <v>60130</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -2215,18 +2125,17 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="K38" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B39" s="2">
         <v>60139</v>
@@ -2234,21 +2143,20 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3">
+        <v>123</v>
+      </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="3">
-        <v>185</v>
-      </c>
+      <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="K39" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B40" s="2">
         <v>60306</v>
@@ -2256,340 +2164,111 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3">
+        <v>118</v>
+      </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="3">
-        <v>215</v>
-      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="K40" s="3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B41" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3">
-        <v>1</v>
-      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3">
+        <v>208</v>
+      </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="3">
-        <v>204</v>
-      </c>
+      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="K41" s="3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B42" s="2">
-        <v>60355</v>
+        <v>60130</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3">
+        <v>124</v>
+      </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3">
-        <v>282</v>
-      </c>
+      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="K42" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B43" s="2">
-        <v>60132</v>
+        <v>60135</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="2">
-        <v>50</v>
-      </c>
-      <c r="B44" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3">
-        <v>1</v>
-      </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="2">
-        <v>51</v>
-      </c>
-      <c r="B45" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3">
-        <v>65</v>
-      </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="2">
-        <v>51</v>
-      </c>
-      <c r="B46" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3">
-        <v>62</v>
-      </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="2">
-        <v>51</v>
-      </c>
-      <c r="B47" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3">
-        <v>60</v>
-      </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="2">
-        <v>52</v>
-      </c>
-      <c r="B48" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3">
-        <v>102</v>
-      </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="2">
-        <v>53</v>
-      </c>
-      <c r="B49" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3">
-        <v>194</v>
-      </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="2">
-        <v>53</v>
-      </c>
-      <c r="B50" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3">
-        <v>183</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="2">
-        <v>53</v>
-      </c>
-      <c r="B51" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3">
-        <v>306</v>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="2">
-        <v>54</v>
-      </c>
-      <c r="B52" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3">
-        <v>124</v>
-      </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="2">
-        <v>54</v>
-      </c>
-      <c r="B53" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
+      <c r="K43" s="3">
         <v>149</v>
       </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="2" t="s">
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="4">
-        <v>1016</v>
-      </c>
-      <c r="D54" s="4">
-        <v>63</v>
-      </c>
-      <c r="E54" s="4">
-        <v>6</v>
-      </c>
-      <c r="F54" s="4">
-        <v>323</v>
-      </c>
-      <c r="G54" s="4">
-        <v>1264</v>
-      </c>
-      <c r="H54" s="4">
-        <v>1563</v>
-      </c>
-      <c r="I54" s="4">
-        <v>1005</v>
-      </c>
-      <c r="J54" s="4">
-        <v>182</v>
-      </c>
-      <c r="K54" s="4">
-        <v>510</v>
-      </c>
-      <c r="L54" s="4">
-        <v>5932</v>
+      <c r="B44" s="2"/>
+      <c r="C44" s="4">
+        <v>715</v>
+      </c>
+      <c r="D44" s="4">
+        <v>23</v>
+      </c>
+      <c r="E44" s="4">
+        <v>197</v>
+      </c>
+      <c r="F44" s="4">
+        <v>913</v>
+      </c>
+      <c r="G44" s="4">
+        <v>1251</v>
+      </c>
+      <c r="H44" s="4">
+        <v>681</v>
+      </c>
+      <c r="I44" s="4">
+        <v>93</v>
+      </c>
+      <c r="J44" s="4">
+        <v>316</v>
+      </c>
+      <c r="K44" s="4">
+        <v>4189</v>
       </c>
     </row>
   </sheetData>
@@ -2615,16 +2294,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>10</v>
@@ -2654,18 +2333,14 @@
       <c r="B3" s="2">
         <v>21086</v>
       </c>
-      <c r="C3" s="3">
-        <v>93</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3">
         <v>37</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>12</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>142</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2675,16 +2350,14 @@
       <c r="B4" s="2">
         <v>21515</v>
       </c>
-      <c r="C4" s="3">
-        <v>54</v>
-      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3">
         <v>14</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2695,15 +2368,15 @@
         <v>21081</v>
       </c>
       <c r="C5" s="3">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>62</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2714,15 +2387,15 @@
         <v>21085</v>
       </c>
       <c r="C6" s="3">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>262</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2998,19 +2671,19 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="4">
-        <v>1693</v>
+        <v>1344</v>
       </c>
       <c r="D20" s="4">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="E20" s="4">
         <v>137</v>
       </c>
       <c r="F20" s="4">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G20" s="4">
-        <v>2185</v>
+        <v>1795</v>
       </c>
     </row>
   </sheetData>
@@ -3037,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -3118,7 +2791,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -3126,11 +2799,11 @@
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="7.7109375" customWidth="1"/>
-    <col min="10" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="13" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="12" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3138,466 +2811,348 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="B2" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3">
+        <v>162</v>
+      </c>
+      <c r="E2" s="3">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3">
+        <v>75</v>
+      </c>
+      <c r="G2" s="3">
+        <v>70</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>85</v>
+      </c>
+      <c r="J2" s="3">
+        <v>137</v>
+      </c>
       <c r="K2" s="3">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
       <c r="B3" s="2">
-        <v>21082</v>
+        <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G3" s="3">
-        <v>70</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J3" s="3">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="K3" s="3">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3">
-        <v>14</v>
-      </c>
-      <c r="M3" s="3">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
-        <v>3004</v>
+        <v>3006</v>
       </c>
       <c r="B4" s="2">
-        <v>21234</v>
+        <v>21083</v>
       </c>
       <c r="C4" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>77</v>
-      </c>
-      <c r="J4" s="3">
-        <v>72</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3">
-        <v>2</v>
-      </c>
-      <c r="M4" s="3">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
         <v>3006</v>
       </c>
       <c r="B5" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C5" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3">
-        <v>3</v>
-      </c>
-      <c r="M5" s="3">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
-        <v>3006</v>
+        <v>3008</v>
       </c>
       <c r="B6" s="2">
-        <v>21457</v>
+        <v>21195</v>
       </c>
       <c r="C6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3">
-        <v>33</v>
-      </c>
-      <c r="G6" s="3">
-        <v>19</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>48</v>
-      </c>
-      <c r="J6" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="J6" s="3">
+        <v>8</v>
+      </c>
       <c r="K6" s="3">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2">
         <v>3008</v>
       </c>
       <c r="B7" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C7" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>34</v>
-      </c>
-      <c r="H7" s="3">
-        <v>3</v>
-      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J7" s="3">
-        <v>39</v>
-      </c>
-      <c r="K7" s="3"/>
+        <v>132</v>
+      </c>
+      <c r="K7" s="3">
+        <v>6</v>
+      </c>
       <c r="L7" s="3">
-        <v>3</v>
-      </c>
-      <c r="M7" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="B8" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C8" s="3">
-        <v>6</v>
-      </c>
+        <v>21085</v>
+      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3">
-        <v>57</v>
-      </c>
-      <c r="E8" s="3">
-        <v>14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3">
-        <v>92</v>
-      </c>
-      <c r="J8" s="3">
-        <v>151</v>
-      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3">
-        <v>6</v>
-      </c>
-      <c r="M8" s="3">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="2">
-        <v>3009</v>
+        <v>3011</v>
       </c>
       <c r="B9" s="2">
-        <v>21085</v>
+        <v>21089</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>17</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3">
-        <v>4</v>
-      </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="L9" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="2">
-        <v>3009</v>
+        <v>3011</v>
       </c>
       <c r="B10" s="2">
-        <v>21086</v>
+        <v>21090</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>30</v>
+      </c>
       <c r="E10" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <v>36</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3">
-        <v>6</v>
-      </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="2">
-        <v>3010</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
-        <v>2</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B12" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="L10" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4">
+        <v>467</v>
+      </c>
+      <c r="E11" s="4">
+        <v>142</v>
+      </c>
+      <c r="F11" s="4">
+        <v>209</v>
+      </c>
+      <c r="G11" s="4">
+        <v>219</v>
+      </c>
+      <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
-        <v>9</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3">
-        <v>6</v>
-      </c>
-      <c r="G12" s="3">
-        <v>17</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3">
-        <v>58</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B13" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
-        <v>30</v>
-      </c>
-      <c r="E13" s="3">
-        <v>12</v>
-      </c>
-      <c r="F13" s="3">
-        <v>16</v>
-      </c>
-      <c r="G13" s="3">
-        <v>36</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>40</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>2</v>
-      </c>
-      <c r="M13" s="3">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4">
-        <v>30</v>
-      </c>
-      <c r="D14" s="4">
-        <v>498</v>
-      </c>
-      <c r="E14" s="4">
-        <v>176</v>
-      </c>
-      <c r="F14" s="4">
-        <v>295</v>
-      </c>
-      <c r="G14" s="4">
-        <v>277</v>
-      </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>609</v>
-      </c>
-      <c r="J14" s="4">
-        <v>409</v>
-      </c>
-      <c r="K14" s="4">
-        <v>213</v>
-      </c>
-      <c r="L14" s="4">
-        <v>31</v>
-      </c>
-      <c r="M14" s="4">
-        <v>2543</v>
+      <c r="I11" s="4">
+        <v>511</v>
+      </c>
+      <c r="J11" s="4">
+        <v>349</v>
+      </c>
+      <c r="K11" s="4">
+        <v>29</v>
+      </c>
+      <c r="L11" s="4">
+        <v>1956</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -525,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -664,7 +664,7 @@
         <v>21086</v>
       </c>
       <c r="C5" s="3">
-        <v>269</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -674,7 +674,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>269</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -685,25 +685,23 @@
         <v>21195</v>
       </c>
       <c r="C6" s="3">
-        <v>634</v>
+        <v>592</v>
       </c>
       <c r="D6" s="3">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3">
-        <v>4</v>
-      </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="3">
-        <v>1160</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -714,27 +712,25 @@
         <v>21246</v>
       </c>
       <c r="C7" s="3">
-        <v>513</v>
+        <v>432</v>
       </c>
       <c r="D7" s="3">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>247</v>
+        <v>100</v>
       </c>
       <c r="H7" s="3">
         <v>11</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>4</v>
-      </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="3">
-        <v>1009</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -809,11 +805,11 @@
         <v>22</v>
       </c>
       <c r="E10" s="3">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3">
         <v>3</v>
@@ -821,7 +817,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>285</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -838,11 +834,11 @@
         <v>59</v>
       </c>
       <c r="E11" s="3">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="H11" s="3">
         <v>20</v>
@@ -850,7 +846,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3">
-        <v>414</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -858,99 +854,78 @@
         <v>1015</v>
       </c>
       <c r="B12" s="2">
-        <v>21081</v>
+        <v>21090</v>
       </c>
       <c r="C12" s="3">
-        <v>32</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>476</v>
+      </c>
+      <c r="D12" s="3">
+        <v>44</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>19</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>32</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B13" s="2">
-        <v>21090</v>
+        <v>21253</v>
       </c>
       <c r="C13" s="3">
-        <v>476</v>
-      </c>
-      <c r="D13" s="3">
-        <v>44</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>19</v>
-      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3">
-        <v>539</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B14" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C14" s="3">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="2" t="s">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="4">
-        <v>2719</v>
-      </c>
-      <c r="D15" s="4">
-        <v>597</v>
-      </c>
-      <c r="E15" s="4">
-        <v>870</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="B14" s="2"/>
+      <c r="C14" s="4">
+        <v>2331</v>
+      </c>
+      <c r="D14" s="4">
+        <v>442</v>
+      </c>
+      <c r="E14" s="4">
+        <v>653</v>
+      </c>
+      <c r="F14" s="4">
         <v>15</v>
       </c>
-      <c r="G15" s="4">
-        <v>1633</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="G14" s="4">
+        <v>1022</v>
+      </c>
+      <c r="H14" s="4">
         <v>82</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I14" s="4">
         <v>25</v>
       </c>
-      <c r="J15" s="4">
-        <v>68</v>
-      </c>
-      <c r="K15" s="4">
-        <v>6009</v>
+      <c r="J14" s="4">
+        <v>60</v>
+      </c>
+      <c r="K14" s="4">
+        <v>4630</v>
       </c>
     </row>
   </sheetData>
@@ -960,7 +935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1005,39 +980,39 @@
         <v>4004</v>
       </c>
       <c r="B2" s="2">
-        <v>21195</v>
+        <v>21246</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3">
-        <v>8</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3">
+        <v>2</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B3" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>21083</v>
+      </c>
+      <c r="C3" s="3">
+        <v>122</v>
+      </c>
       <c r="D3" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>2</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>11</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1045,20 +1020,20 @@
         <v>4005</v>
       </c>
       <c r="B4" s="2">
-        <v>21083</v>
+        <v>21234</v>
       </c>
       <c r="C4" s="3">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D4" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>152</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1066,85 +1041,81 @@
         <v>4005</v>
       </c>
       <c r="B5" s="2">
-        <v>21234</v>
+        <v>21457</v>
       </c>
       <c r="C5" s="3">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="D5" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>392</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="B6" s="2">
-        <v>21457</v>
+        <v>21523</v>
       </c>
       <c r="C6" s="3">
-        <v>330</v>
-      </c>
-      <c r="D6" s="3">
-        <v>30</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>24</v>
+      </c>
       <c r="I6" s="3">
-        <v>360</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="B7" s="2">
-        <v>21523</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
+        <v>21082</v>
+      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="E7" s="3">
+        <v>13</v>
+      </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
-        <v>24</v>
-      </c>
+      <c r="G7" s="3">
+        <v>10</v>
+      </c>
+      <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="B8" s="2">
-        <v>21082</v>
+        <v>21089</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>29</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>10</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1152,37 +1123,43 @@
         <v>4010</v>
       </c>
       <c r="B9" s="2">
-        <v>21089</v>
+        <v>21090</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B10" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>21075</v>
+      </c>
+      <c r="C10" s="3">
+        <v>117</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3">
+        <v>14</v>
+      </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>13</v>
+      </c>
       <c r="I10" s="3">
-        <v>2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1190,24 +1167,18 @@
         <v>4011</v>
       </c>
       <c r="B11" s="2">
-        <v>21075</v>
+        <v>21094</v>
       </c>
       <c r="C11" s="3">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>30</v>
-      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3">
-        <v>13</v>
-      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>162</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1215,70 +1186,49 @@
         <v>4011</v>
       </c>
       <c r="B12" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C12" s="3">
-        <v>44</v>
-      </c>
+        <v>21533</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="E12" s="3">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>24</v>
+      </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>16</v>
+      </c>
       <c r="I12" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B13" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C13" s="3">
-        <v>169</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>24</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>16</v>
-      </c>
-      <c r="I13" s="3">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2" t="s">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4">
-        <v>1152</v>
-      </c>
-      <c r="D14" s="4">
-        <v>129</v>
-      </c>
-      <c r="E14" s="4">
-        <v>55</v>
-      </c>
-      <c r="F14" s="4">
-        <v>54</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="B13" s="2"/>
+      <c r="C13" s="4">
+        <v>681</v>
+      </c>
+      <c r="D13" s="4">
+        <v>83</v>
+      </c>
+      <c r="E13" s="4">
+        <v>30</v>
+      </c>
+      <c r="F13" s="4">
+        <v>38</v>
+      </c>
+      <c r="G13" s="4">
         <v>12</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H13" s="4">
         <v>53</v>
       </c>
-      <c r="I14" s="4">
-        <v>1455</v>
+      <c r="I13" s="4">
+        <v>897</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1349,12 +1299,12 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>85</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1370,12 +1320,12 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3">
-        <v>89</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1391,41 +1341,41 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2">
-        <v>60127</v>
+        <v>60132</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3">
+        <v>2</v>
+      </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2">
-        <v>60131</v>
+        <v>60128</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1433,216 +1383,214 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>40</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>56</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>91</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>40</v>
+      </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>2</v>
-      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>93</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>60</v>
-      </c>
-      <c r="G9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>35</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3">
-        <v>88</v>
-      </c>
+      <c r="G10" s="3">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2">
-        <v>60132</v>
+        <v>60134</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>2</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3">
-        <v>92</v>
-      </c>
+      <c r="G11" s="3">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3">
-        <v>92</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C12" s="3">
+        <v>31</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3">
-        <v>72</v>
-      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C13" s="3">
+        <v>23</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3">
-        <v>43</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C14" s="3">
+        <v>23</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3">
-        <v>189</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3">
-        <v>189</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
-        <v>2</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C15" s="3">
+        <v>192</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3">
-        <v>44</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3">
-        <v>46</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C16" s="3">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1652,469 +1600,461 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3">
-        <v>82</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C17" s="3">
-        <v>95</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>88</v>
+      </c>
       <c r="K17" s="3">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C18" s="3">
-        <v>100</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="3">
+        <v>114</v>
+      </c>
       <c r="K18" s="3">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C19" s="3">
-        <v>268</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="I19" s="3">
+        <v>19</v>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3">
-        <v>268</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C20" s="3">
-        <v>170</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="3">
+        <v>4</v>
+      </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="I20" s="3">
+        <v>26</v>
+      </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3">
-        <v>170</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2">
-        <v>60130</v>
+        <v>60355</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="3">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3">
+        <v>4</v>
+      </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3">
-        <v>130</v>
-      </c>
+      <c r="I21" s="3">
+        <v>37</v>
+      </c>
+      <c r="J21" s="3"/>
       <c r="K21" s="3">
-        <v>135</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2">
-        <v>60355</v>
+        <v>60130</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="3">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
         <v>15</v>
       </c>
-      <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3">
-        <v>184</v>
-      </c>
+      <c r="J22" s="3"/>
       <c r="K22" s="3">
-        <v>199</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2">
-        <v>60139</v>
+        <v>60135</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3">
-        <v>19</v>
-      </c>
+      <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2">
-        <v>60306</v>
+        <v>60135</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3">
-        <v>31</v>
-      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3">
+        <v>117</v>
+      </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="3">
-        <v>26</v>
-      </c>
+      <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3">
-        <v>57</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2">
-        <v>60355</v>
+        <v>60139</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3">
-        <v>38</v>
-      </c>
+      <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3">
+        <v>132</v>
+      </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="3">
-        <v>37</v>
-      </c>
+      <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3">
-        <v>75</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2">
-        <v>60130</v>
+        <v>60306</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3">
-        <v>51</v>
-      </c>
+      <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3">
+        <v>139</v>
+      </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="3">
-        <v>6</v>
-      </c>
+      <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3">
-        <v>57</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2">
-        <v>60135</v>
+        <v>60130</v>
       </c>
       <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3">
-        <v>45</v>
-      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3">
+        <v>176</v>
+      </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="3">
-        <v>5</v>
-      </c>
+      <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3">
-        <v>50</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3">
-        <v>151</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2">
-        <v>60139</v>
+        <v>60132</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="E29" s="3">
+        <v>3</v>
+      </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="3">
-        <v>153</v>
-      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3">
-        <v>153</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
       <c r="F30" s="3"/>
-      <c r="G30" s="3">
-        <v>185</v>
-      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3">
-        <v>185</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2">
-        <v>60130</v>
+        <v>60135</v>
       </c>
       <c r="C31" s="3"/>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3">
-        <v>204</v>
-      </c>
-      <c r="H31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3">
+        <v>14</v>
+      </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3">
-        <v>205</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B32" s="2">
-        <v>60355</v>
+        <v>60139</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3">
-        <v>282</v>
-      </c>
-      <c r="H32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3">
+        <v>8</v>
+      </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3">
-        <v>282</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2">
-        <v>60132</v>
+        <v>60306</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="3">
-        <v>3</v>
-      </c>
+      <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="3">
+        <v>13</v>
+      </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B34" s="2">
-        <v>60355</v>
+        <v>60130</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="3">
-        <v>1</v>
-      </c>
+      <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="H34" s="3">
+        <v>102</v>
+      </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B35" s="2">
-        <v>60135</v>
+        <v>60139</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="3">
+        <v>68</v>
+      </c>
       <c r="G35" s="3"/>
-      <c r="H35" s="3">
-        <v>38</v>
-      </c>
+      <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B36" s="2">
-        <v>60139</v>
+        <v>60306</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3">
+        <v>49</v>
+      </c>
       <c r="G36" s="3"/>
-      <c r="H36" s="3">
-        <v>40</v>
-      </c>
+      <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B37" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3">
+        <v>98</v>
+      </c>
       <c r="G37" s="3"/>
-      <c r="H37" s="3">
-        <v>32</v>
-      </c>
+      <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3">
-        <v>32</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2">
         <v>60130</v>
@@ -2122,153 +2062,69 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3">
+        <v>119</v>
+      </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="3">
-        <v>102</v>
-      </c>
+      <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39" s="2">
-        <v>60139</v>
+        <v>60135</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="2">
-        <v>53</v>
-      </c>
-      <c r="B40" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>118</v>
-      </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="2">
-        <v>53</v>
-      </c>
-      <c r="B41" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>208</v>
-      </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="2">
-        <v>54</v>
-      </c>
-      <c r="B42" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>124</v>
-      </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="2">
-        <v>54</v>
-      </c>
-      <c r="B43" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>149</v>
-      </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="2" t="s">
+      <c r="A40" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="4">
-        <v>715</v>
-      </c>
-      <c r="D44" s="4">
-        <v>23</v>
-      </c>
-      <c r="E44" s="4">
-        <v>197</v>
-      </c>
-      <c r="F44" s="4">
-        <v>913</v>
-      </c>
-      <c r="G44" s="4">
-        <v>1251</v>
-      </c>
-      <c r="H44" s="4">
-        <v>681</v>
-      </c>
-      <c r="I44" s="4">
-        <v>93</v>
-      </c>
-      <c r="J44" s="4">
-        <v>316</v>
-      </c>
-      <c r="K44" s="4">
-        <v>4189</v>
+      <c r="B40" s="2"/>
+      <c r="C40" s="4">
+        <v>381</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4">
+        <v>38</v>
+      </c>
+      <c r="F40" s="4">
+        <v>478</v>
+      </c>
+      <c r="G40" s="4">
+        <v>960</v>
+      </c>
+      <c r="H40" s="4">
+        <v>387</v>
+      </c>
+      <c r="I40" s="4">
+        <v>82</v>
+      </c>
+      <c r="J40" s="4">
+        <v>204</v>
+      </c>
+      <c r="K40" s="4">
+        <v>2533</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +2134,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2311,19 +2167,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="B2" s="2">
-        <v>21085</v>
+        <v>21086</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
+      <c r="D2" s="3">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2331,276 +2187,268 @@
         <v>2004</v>
       </c>
       <c r="B3" s="2">
-        <v>21086</v>
+        <v>21515</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B4" s="2">
-        <v>21515</v>
+        <v>21085</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B5" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C5" s="3">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
+        <v>21089</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3">
+        <v>4</v>
+      </c>
       <c r="G5" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B6" s="2">
-        <v>21085</v>
+        <v>21082</v>
       </c>
       <c r="C6" s="3">
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="D6" s="3">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="E6" s="3">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3">
+        <v>42</v>
+      </c>
       <c r="G6" s="3">
-        <v>72</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B7" s="2">
-        <v>21089</v>
+        <v>21234</v>
       </c>
       <c r="C7" s="3">
-        <v>50</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>235</v>
+      </c>
+      <c r="D7" s="3">
+        <v>42</v>
+      </c>
       <c r="E7" s="3">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F7" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G7" s="3">
-        <v>58</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B8" s="2">
-        <v>21082</v>
+        <v>21083</v>
       </c>
       <c r="C8" s="3">
-        <v>252</v>
-      </c>
-      <c r="D8" s="3">
-        <v>28</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F8" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G8" s="3">
-        <v>358</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B9" s="2">
-        <v>21234</v>
+        <v>21457</v>
       </c>
       <c r="C9" s="3">
-        <v>235</v>
+        <v>420</v>
       </c>
       <c r="D9" s="3">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F9" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3">
-        <v>317</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B10" s="2">
-        <v>21083</v>
+        <v>21195</v>
       </c>
       <c r="C10" s="3">
-        <v>64</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="D10" s="3">
+        <v>14</v>
+      </c>
       <c r="E10" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G10" s="3">
-        <v>85</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B11" s="2">
-        <v>21457</v>
+        <v>21246</v>
       </c>
       <c r="C11" s="3">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="D11" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3">
-        <v>459</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B12" s="2">
-        <v>21195</v>
+        <v>21090</v>
       </c>
       <c r="C12" s="3">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F12" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G12" s="3">
-        <v>165</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B13" s="2">
-        <v>21246</v>
+        <v>21533</v>
       </c>
       <c r="C13" s="3">
-        <v>75</v>
-      </c>
-      <c r="D13" s="3">
-        <v>20</v>
-      </c>
-      <c r="E13" s="3">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3">
-        <v>14</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>122</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B14" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C14" s="3">
-        <v>34</v>
-      </c>
+        <v>21082</v>
+      </c>
+      <c r="C14" s="3"/>
       <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B15" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C15" s="3">
-        <v>30</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>21086</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B16" s="2">
-        <v>21082</v>
+        <v>21085</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3">
@@ -2614,76 +2462,42 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B17" s="2">
-        <v>21086</v>
+        <v>21457</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B18" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B19" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
-        <v>3</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="2" t="s">
+      <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4">
-        <v>1344</v>
-      </c>
-      <c r="D20" s="4">
-        <v>203</v>
-      </c>
-      <c r="E20" s="4">
-        <v>137</v>
-      </c>
-      <c r="F20" s="4">
+      <c r="B18" s="2"/>
+      <c r="C18" s="4">
+        <v>1217</v>
+      </c>
+      <c r="D18" s="4">
+        <v>150</v>
+      </c>
+      <c r="E18" s="4">
+        <v>131</v>
+      </c>
+      <c r="F18" s="4">
         <v>111</v>
       </c>
-      <c r="G20" s="4">
-        <v>1795</v>
+      <c r="G18" s="4">
+        <v>1609</v>
       </c>
     </row>
   </sheetData>
@@ -2848,18 +2662,14 @@
       <c r="B2" s="2">
         <v>21082</v>
       </c>
-      <c r="C2" s="3">
-        <v>5</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3">
         <v>162</v>
       </c>
       <c r="E2" s="3">
         <v>32</v>
       </c>
-      <c r="F2" s="3">
-        <v>75</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3">
         <v>70</v>
       </c>
@@ -2867,16 +2677,14 @@
         <v>1</v>
       </c>
       <c r="I2" s="3">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3">
-        <v>137</v>
-      </c>
-      <c r="K2" s="3">
-        <v>14</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="3">
-        <v>581</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2886,33 +2694,27 @@
       <c r="B3" s="2">
         <v>21234</v>
       </c>
-      <c r="C3" s="3">
-        <v>6</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3">
         <v>84</v>
       </c>
       <c r="E3" s="3">
         <v>26</v>
       </c>
-      <c r="F3" s="3">
-        <v>55</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3">
         <v>48</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J3" s="3">
-        <v>72</v>
-      </c>
-      <c r="K3" s="3">
-        <v>2</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="3">
-        <v>370</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2990,11 +2792,9 @@
       <c r="B6" s="2">
         <v>21195</v>
       </c>
-      <c r="C6" s="3">
-        <v>4</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3">
         <v>13</v>
@@ -3003,16 +2803,14 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="J6" s="3">
         <v>8</v>
       </c>
-      <c r="K6" s="3">
-        <v>3</v>
-      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3">
-        <v>217</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3022,11 +2820,9 @@
       <c r="B7" s="2">
         <v>21246</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
         <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>43</v>
       </c>
       <c r="E7" s="3">
         <v>14</v>
@@ -3035,16 +2831,14 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="J7" s="3">
         <v>132</v>
       </c>
-      <c r="K7" s="3">
-        <v>6</v>
-      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>293</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -3077,20 +2871,18 @@
         <v>21089</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>9</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -3101,22 +2893,20 @@
         <v>21090</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3">
-        <v>30</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3">
         <v>12</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>78</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3125,34 +2915,34 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4">
-        <v>467</v>
+        <v>349</v>
       </c>
       <c r="E11" s="4">
         <v>142</v>
       </c>
       <c r="F11" s="4">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="G11" s="4">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
       </c>
       <c r="I11" s="4">
-        <v>511</v>
+        <v>371</v>
       </c>
       <c r="J11" s="4">
-        <v>349</v>
+        <v>277</v>
       </c>
       <c r="K11" s="4">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="L11" s="4">
-        <v>1956</v>
+        <v>1432</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -8,18 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Babyshop" sheetId="1" r:id="rId1"/>
-    <sheet name="Lifestyle" sheetId="2" r:id="rId2"/>
-    <sheet name="Max" sheetId="3" r:id="rId3"/>
-    <sheet name="Shoe Mart" sheetId="4" r:id="rId4"/>
-    <sheet name="Shoexpress" sheetId="5" r:id="rId5"/>
-    <sheet name="Splash" sheetId="6" r:id="rId6"/>
+    <sheet name="Max" sheetId="2" r:id="rId2"/>
+    <sheet name="Shoe Mart" sheetId="3" r:id="rId3"/>
+    <sheet name="Shoexpress" sheetId="4" r:id="rId4"/>
+    <sheet name="Splash" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="22">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -54,33 +53,12 @@
     <t>Total</t>
   </si>
   <si>
-    <t>LSCOSM</t>
-  </si>
-  <si>
-    <t>LSFAC</t>
-  </si>
-  <si>
-    <t>LSHFU</t>
-  </si>
-  <si>
-    <t>MACC01</t>
-  </si>
-  <si>
     <t>MCHL</t>
   </si>
   <si>
-    <t>MLAD</t>
-  </si>
-  <si>
     <t>MLIN</t>
   </si>
   <si>
-    <t>MMEN2</t>
-  </si>
-  <si>
-    <t>MXKIDS</t>
-  </si>
-  <si>
     <t>SMACC</t>
   </si>
   <si>
@@ -103,9 +81,6 @@
   </si>
   <si>
     <t>SP-HWNTR</t>
-  </si>
-  <si>
-    <t>SPACC</t>
   </si>
   <si>
     <t>SPAIS1</t>
@@ -554,7 +529,7 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -564,7 +539,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>227</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -637,7 +612,7 @@
         <v>21195</v>
       </c>
       <c r="C5" s="3">
-        <v>526</v>
+        <v>124</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -647,7 +622,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>526</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -658,7 +633,7 @@
         <v>21246</v>
       </c>
       <c r="C6" s="3">
-        <v>343</v>
+        <v>228</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -670,7 +645,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3">
-        <v>354</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -680,26 +655,20 @@
       <c r="B7" s="2">
         <v>21083</v>
       </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>52</v>
-      </c>
-      <c r="E7" s="3">
-        <v>71</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>179</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3">
         <v>17</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3">
-        <v>325</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -709,26 +678,20 @@
       <c r="B8" s="2">
         <v>21457</v>
       </c>
-      <c r="C8" s="3">
-        <v>5</v>
-      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3">
-        <v>42</v>
-      </c>
-      <c r="E8" s="3">
-        <v>41</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>161</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3">
         <v>12</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>261</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -739,9 +702,7 @@
         <v>21089</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>12</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -751,7 +712,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -762,9 +723,7 @@
         <v>21234</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3">
-        <v>47</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -774,7 +733,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -829,19 +788,19 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="4">
-        <v>2100</v>
+        <v>1375</v>
       </c>
       <c r="D13" s="4">
-        <v>336</v>
+        <v>199</v>
       </c>
       <c r="E13" s="4">
-        <v>368</v>
+        <v>256</v>
       </c>
       <c r="F13" s="4">
         <v>15</v>
       </c>
       <c r="G13" s="4">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="H13" s="4">
         <v>82</v>
@@ -853,7 +812,7 @@
         <v>60</v>
       </c>
       <c r="K13" s="4">
-        <v>3532</v>
+        <v>2218</v>
       </c>
     </row>
   </sheetData>
@@ -863,16 +822,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="6" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -886,132 +845,54 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>4005</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2">
-        <v>21083</v>
+        <v>60130</v>
       </c>
       <c r="C2" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>49</v>
+      </c>
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>4005</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C3" s="3">
-        <v>330</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2">
-        <v>4006</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21523</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>24</v>
-      </c>
-      <c r="F4" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21075</v>
-      </c>
-      <c r="C5" s="3">
-        <v>34</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C6" s="3">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>16</v>
-      </c>
-      <c r="F7" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4">
-        <v>425</v>
-      </c>
-      <c r="D8" s="4">
-        <v>36</v>
-      </c>
-      <c r="E8" s="4">
-        <v>53</v>
-      </c>
-      <c r="F8" s="4">
-        <v>514</v>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>106</v>
+      </c>
+      <c r="E4" s="4">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1021,407 +902,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="6" width="6.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2">
-        <v>28</v>
-      </c>
-      <c r="B2" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C5" s="3">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2">
-        <v>35</v>
-      </c>
-      <c r="B6" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
-        <v>15</v>
-      </c>
-      <c r="I6" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
-        <v>13</v>
-      </c>
-      <c r="I7" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>50</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2">
-        <v>38</v>
-      </c>
-      <c r="B9" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>53</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2">
-        <v>38</v>
-      </c>
-      <c r="B10" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>151</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="2">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3">
-        <v>177</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>52</v>
-      </c>
-      <c r="B13" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3">
-        <v>102</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="2">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>6</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="2">
-        <v>53</v>
-      </c>
-      <c r="B16" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3">
-        <v>10</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="2">
-        <v>54</v>
-      </c>
-      <c r="B17" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="2">
-        <v>54</v>
-      </c>
-      <c r="B18" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3">
-        <v>39</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="4">
-        <v>24</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4">
-        <v>86</v>
-      </c>
-      <c r="F19" s="4">
-        <v>491</v>
-      </c>
-      <c r="G19" s="4">
-        <v>115</v>
-      </c>
-      <c r="H19" s="4">
-        <v>28</v>
-      </c>
-      <c r="I19" s="4">
-        <v>745</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1437,16 +918,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>10</v>
@@ -1454,295 +935,223 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B2" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C2" s="3">
+        <v>252</v>
+      </c>
       <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3">
+        <v>42</v>
+      </c>
       <c r="G2" s="3">
-        <v>1</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B3" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+        <v>21234</v>
+      </c>
+      <c r="C3" s="3">
+        <v>235</v>
+      </c>
+      <c r="D3" s="3">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3">
+        <v>17</v>
+      </c>
       <c r="F3" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" s="3">
-        <v>4</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B4" s="2">
-        <v>21082</v>
+        <v>21083</v>
       </c>
       <c r="C4" s="3">
-        <v>252</v>
-      </c>
-      <c r="D4" s="3">
-        <v>28</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G4" s="3">
-        <v>358</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B5" s="2">
-        <v>21234</v>
+        <v>21457</v>
       </c>
       <c r="C5" s="3">
-        <v>235</v>
+        <v>420</v>
       </c>
       <c r="D5" s="3">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="3">
-        <v>317</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B6" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C6" s="3">
-        <v>64</v>
-      </c>
+        <v>21195</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3">
-        <v>12</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B7" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C7" s="3">
-        <v>420</v>
-      </c>
-      <c r="D7" s="3">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3">
-        <v>11</v>
-      </c>
+        <v>21246</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
       <c r="F7" s="3">
         <v>6</v>
       </c>
       <c r="G7" s="3">
-        <v>459</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B8" s="2">
-        <v>21195</v>
+        <v>21090</v>
       </c>
       <c r="C8" s="3">
-        <v>75</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8</v>
+      </c>
       <c r="F8" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B9" s="2">
-        <v>21246</v>
+        <v>21533</v>
       </c>
       <c r="C9" s="3">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>14</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B10" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C10" s="3">
-        <v>34</v>
-      </c>
+        <v>21082</v>
+      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="B11" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C11" s="3">
-        <v>30</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+        <v>21457</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B12" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B13" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B14" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B15" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4">
-        <v>1148</v>
-      </c>
-      <c r="D16" s="4">
-        <v>102</v>
-      </c>
-      <c r="E16" s="4">
-        <v>101</v>
-      </c>
-      <c r="F16" s="4">
-        <v>111</v>
-      </c>
-      <c r="G16" s="4">
-        <v>1462</v>
+      <c r="B12" s="2"/>
+      <c r="C12" s="4">
+        <v>1035</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46</v>
+      </c>
+      <c r="E12" s="4">
+        <v>70</v>
+      </c>
+      <c r="F12" s="4">
+        <v>77</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1228</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +1159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1769,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -1848,20 +1257,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="4" width="9.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1869,25 +1277,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>3004</v>
       </c>
@@ -1895,23 +1300,22 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="D2" s="3">
         <v>32</v>
       </c>
       <c r="E2" s="3">
-        <v>70</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="F2" s="3">
+        <v>7</v>
+      </c>
       <c r="G2" s="3">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
@@ -1919,21 +1323,20 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D3" s="3">
         <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="G3" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>3006</v>
       </c>
@@ -1941,23 +1344,20 @@
         <v>21083</v>
       </c>
       <c r="C4" s="3">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3">
         <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>29</v>
-      </c>
-      <c r="F4" s="3">
-        <v>54</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>3006</v>
       </c>
@@ -1965,98 +1365,55 @@
         <v>21457</v>
       </c>
       <c r="C5" s="3">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3">
         <v>20</v>
       </c>
       <c r="E5" s="3">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3">
-        <v>36</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>3008</v>
+        <v>3011</v>
       </c>
       <c r="B6" s="2">
-        <v>21195</v>
+        <v>21090</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>6</v>
-      </c>
-      <c r="H6" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2">
-        <v>3008</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>106</v>
-      </c>
-      <c r="H7" s="3">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B8" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="4">
-        <v>339</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="B7" s="2"/>
+      <c r="C7" s="4">
+        <v>189</v>
+      </c>
+      <c r="D7" s="4">
         <v>103</v>
       </c>
-      <c r="E9" s="4">
-        <v>167</v>
-      </c>
-      <c r="F9" s="4">
-        <v>90</v>
-      </c>
-      <c r="G9" s="4">
-        <v>119</v>
-      </c>
-      <c r="H9" s="4">
-        <v>818</v>
+      <c r="E7" s="4">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4">
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="17">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -53,12 +53,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>MCHL</t>
-  </si>
-  <si>
-    <t>MLIN</t>
-  </si>
-  <si>
     <t>SMACC</t>
   </si>
   <si>
@@ -75,15 +69,6 @@
   </si>
   <si>
     <t>SP-HLAD</t>
-  </si>
-  <si>
-    <t>SP-HLIN</t>
-  </si>
-  <si>
-    <t>SP-HWNTR</t>
-  </si>
-  <si>
-    <t>SPAIS1</t>
   </si>
 </sst>
 </file>
@@ -473,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -523,23 +508,33 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B2" s="2">
-        <v>21082</v>
+        <v>21075</v>
       </c>
       <c r="C2" s="3">
-        <v>30</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="D2" s="3">
+        <v>34</v>
+      </c>
+      <c r="E2" s="3">
+        <v>109</v>
+      </c>
+      <c r="F2" s="3">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3">
+        <v>182</v>
+      </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="I2" s="3">
+        <v>4</v>
+      </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>30</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -547,272 +542,170 @@
         <v>1003</v>
       </c>
       <c r="B3" s="2">
-        <v>21075</v>
+        <v>21533</v>
       </c>
       <c r="C3" s="3">
-        <v>5</v>
+        <v>509</v>
       </c>
       <c r="D3" s="3">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3">
-        <v>109</v>
-      </c>
-      <c r="F3" s="3">
-        <v>15</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="J3" s="3">
+        <v>60</v>
+      </c>
       <c r="K3" s="3">
-        <v>349</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="B4" s="2">
-        <v>21533</v>
+        <v>21246</v>
       </c>
       <c r="C4" s="3">
-        <v>509</v>
-      </c>
-      <c r="D4" s="3">
-        <v>105</v>
-      </c>
-      <c r="E4" s="3">
-        <v>147</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>24</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>21</v>
-      </c>
-      <c r="J4" s="3">
-        <v>60</v>
-      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>866</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B5" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C5" s="3">
-        <v>124</v>
-      </c>
+        <v>21083</v>
+      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>14</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3">
-        <v>124</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B6" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C6" s="3">
-        <v>228</v>
-      </c>
+        <v>21457</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3">
-        <v>239</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B7" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
+        <v>21090</v>
+      </c>
+      <c r="C7" s="3">
+        <v>406</v>
+      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3">
-        <v>27</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B8" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
+        <v>21253</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>12</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B10" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3">
-        <v>20</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C11" s="3">
-        <v>476</v>
-      </c>
-      <c r="D11" s="3">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3">
-        <v>19</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B12" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C12" s="3">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="2" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="4">
-        <v>1375</v>
-      </c>
-      <c r="D13" s="4">
-        <v>199</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="B9" s="2"/>
+      <c r="C9" s="4">
+        <v>1151</v>
+      </c>
+      <c r="D9" s="4">
+        <v>139</v>
+      </c>
+      <c r="E9" s="4">
         <v>256</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F9" s="4">
         <v>15</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G9" s="4">
         <v>206</v>
       </c>
-      <c r="H13" s="4">
-        <v>82</v>
-      </c>
-      <c r="I13" s="4">
+      <c r="H9" s="4">
+        <v>45</v>
+      </c>
+      <c r="I9" s="4">
         <v>25</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J9" s="4">
         <v>60</v>
       </c>
-      <c r="K13" s="4">
-        <v>2218</v>
+      <c r="K9" s="4">
+        <v>1897</v>
       </c>
     </row>
   </sheetData>
@@ -822,16 +715,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="4" width="6.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -839,61 +731,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>39</v>
-      </c>
-      <c r="B3" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
-        <v>57</v>
-      </c>
-      <c r="E3" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>106</v>
-      </c>
-      <c r="E4" s="4">
-        <v>107</v>
-      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -902,7 +748,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -918,16 +764,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>10</v>
@@ -944,16 +790,14 @@
         <v>252</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3">
-        <v>318</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -967,16 +811,14 @@
         <v>235</v>
       </c>
       <c r="D3" s="3">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3">
-        <v>17</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="3">
-        <v>273</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1025,133 +867,97 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B6" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+        <v>21090</v>
+      </c>
+      <c r="C6" s="3">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3">
         <v>3</v>
       </c>
+      <c r="E6" s="3">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B7" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>21533</v>
+      </c>
+      <c r="C7" s="3">
+        <v>30</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>6</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B8" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C8" s="3">
-        <v>34</v>
-      </c>
+        <v>21082</v>
+      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="B9" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C9" s="3">
-        <v>30</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+        <v>21457</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B10" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4">
+      <c r="B10" s="2"/>
+      <c r="C10" s="4">
         <v>1035</v>
       </c>
-      <c r="D12" s="4">
-        <v>46</v>
-      </c>
-      <c r="E12" s="4">
-        <v>70</v>
-      </c>
-      <c r="F12" s="4">
-        <v>77</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1228</v>
+      <c r="D10" s="4">
+        <v>34</v>
+      </c>
+      <c r="E10" s="4">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4">
+        <v>59</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +967,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1178,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -1186,7 +992,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>5000</v>
+        <v>5001</v>
       </c>
       <c r="B2" s="2">
         <v>17168</v>
@@ -1200,56 +1006,42 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="B3" s="2">
-        <v>17168</v>
+        <v>21094</v>
       </c>
       <c r="C3" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="B4" s="2">
         <v>21094</v>
       </c>
       <c r="C4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2">
-        <v>5003</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4">
-        <v>27</v>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1259,17 +1051,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" customWidth="1"/>
+    <col min="2" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1277,22 +1067,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
         <v>3004</v>
       </c>
@@ -1300,22 +1081,13 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
-        <v>32</v>
-      </c>
-      <c r="E2" s="3">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
         <v>3004</v>
       </c>
@@ -1323,97 +1095,22 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3">
-        <v>26</v>
-      </c>
-      <c r="E3" s="3">
         <v>14</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>3006</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C4" s="3">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3">
-        <v>25</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <v>3006</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C5" s="3">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4">
-        <v>189</v>
-      </c>
-      <c r="D7" s="4">
-        <v>103</v>
-      </c>
-      <c r="E7" s="4">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4">
-        <v>7</v>
-      </c>
-      <c r="G7" s="4">
-        <v>332</v>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -11,14 +11,13 @@
     <sheet name="Max" sheetId="2" r:id="rId2"/>
     <sheet name="Shoe Mart" sheetId="3" r:id="rId3"/>
     <sheet name="Shoexpress" sheetId="4" r:id="rId4"/>
-    <sheet name="Splash" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="9">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -27,27 +26,6 @@
   </si>
   <si>
     <t>BSBAS1</t>
-  </si>
-  <si>
-    <t>BSBAS2</t>
-  </si>
-  <si>
-    <t>BSCLTH1</t>
-  </si>
-  <si>
-    <t>BSCLTH2</t>
-  </si>
-  <si>
-    <t>BSCLUG</t>
-  </si>
-  <si>
-    <t>BSECOM</t>
-  </si>
-  <si>
-    <t>BSLIQ</t>
-  </si>
-  <si>
-    <t>BSTOY1</t>
   </si>
   <si>
     <t>Total</t>
@@ -66,9 +44,6 @@
   </si>
   <si>
     <t>SXDMF1</t>
-  </si>
-  <si>
-    <t>SP-HLAD</t>
   </si>
 </sst>
 </file>
@@ -458,20 +433,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="6" width="9.7109375" customWidth="1"/>
-    <col min="7" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,228 +455,59 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="2">
-        <v>21075</v>
+        <v>21246</v>
       </c>
       <c r="C2" s="3">
-        <v>5</v>
+        <v>191</v>
       </c>
       <c r="D2" s="3">
-        <v>34</v>
-      </c>
-      <c r="E2" s="3">
-        <v>109</v>
-      </c>
-      <c r="F2" s="3">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3">
-        <v>182</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3">
-        <v>4</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="B3" s="2">
-        <v>21533</v>
+        <v>21090</v>
       </c>
       <c r="C3" s="3">
-        <v>509</v>
+        <v>263</v>
       </c>
       <c r="D3" s="3">
-        <v>105</v>
-      </c>
-      <c r="E3" s="3">
-        <v>147</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>21</v>
-      </c>
-      <c r="J3" s="3">
-        <v>60</v>
-      </c>
-      <c r="K3" s="3">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B4" s="2">
-        <v>21246</v>
+        <v>21253</v>
       </c>
       <c r="C4" s="3">
-        <v>228</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
-        <v>12</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C7" s="3">
-        <v>406</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
-        <v>19</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B8" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="4">
-        <v>1151</v>
-      </c>
-      <c r="D9" s="4">
-        <v>139</v>
-      </c>
-      <c r="E9" s="4">
-        <v>256</v>
-      </c>
-      <c r="F9" s="4">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4">
-        <v>206</v>
-      </c>
-      <c r="H9" s="4">
-        <v>45</v>
-      </c>
-      <c r="I9" s="4">
-        <v>25</v>
-      </c>
-      <c r="J9" s="4">
-        <v>60</v>
-      </c>
-      <c r="K9" s="4">
-        <v>1897</v>
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4">
+        <v>457</v>
+      </c>
+      <c r="D5" s="4">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -731,12 +533,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="4"/>
@@ -764,19 +566,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -787,17 +589,15 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>252</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3">
-        <v>291</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -808,17 +608,15 @@
         <v>21234</v>
       </c>
       <c r="C3" s="3">
-        <v>235</v>
-      </c>
-      <c r="D3" s="3">
-        <v>4</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3">
-        <v>245</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -832,14 +630,12 @@
         <v>64</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>12</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3">
         <v>9</v>
       </c>
       <c r="G4" s="3">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -852,17 +648,13 @@
       <c r="C5" s="3">
         <v>420</v>
       </c>
-      <c r="D5" s="3">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3">
-        <v>11</v>
-      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="3">
         <v>6</v>
       </c>
       <c r="G5" s="3">
-        <v>459</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -876,14 +668,12 @@
         <v>34</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3">
-        <v>8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -941,23 +731,23 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>1035</v>
+        <v>961</v>
       </c>
       <c r="D10" s="4">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G10" s="4">
-        <v>1160</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -984,10 +774,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1034,7 +824,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
@@ -1042,75 +832,6 @@
       </c>
       <c r="D5" s="4">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2">
-        <v>3004</v>
-      </c>
-      <c r="B2" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C2" s="3">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
-        <v>3004</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C3" s="3">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4">
-        <v>36</v>
-      </c>
-      <c r="D4" s="4">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -9,15 +9,14 @@
   <sheets>
     <sheet name="Babyshop" sheetId="1" r:id="rId1"/>
     <sheet name="Max" sheetId="2" r:id="rId2"/>
-    <sheet name="Shoe Mart" sheetId="3" r:id="rId3"/>
-    <sheet name="Shoexpress" sheetId="4" r:id="rId4"/>
+    <sheet name="Shoexpress" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -25,22 +24,13 @@
     <t>DEST_ID</t>
   </si>
   <si>
-    <t>BSBAS1</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
-    <t>SMACC</t>
+    <t>MLIN</t>
   </si>
   <si>
-    <t>SMKID</t>
-  </si>
-  <si>
-    <t>SMLAD</t>
-  </si>
-  <si>
-    <t>SMMEN</t>
+    <t>MMEN2</t>
   </si>
   <si>
     <t>SXDMF1</t>
@@ -133,10 +123,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -433,90 +423,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B2" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C2" s="3">
-        <v>191</v>
-      </c>
-      <c r="D2" s="3">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C3" s="3">
-        <v>263</v>
-      </c>
-      <c r="D3" s="3">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4">
-        <v>457</v>
-      </c>
-      <c r="D5" s="4">
-        <v>457</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -533,15 +439,110 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="4"/>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>59</v>
+      </c>
+      <c r="B2" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2179</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>59</v>
+      </c>
+      <c r="B3" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>1247</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>2030</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5456</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5457</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -549,213 +550,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="7" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B2" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C2" s="3">
-        <v>213</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C3" s="3">
-        <v>200</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C4" s="3">
-        <v>64</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B5" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C5" s="3">
-        <v>420</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
-        <v>6</v>
-      </c>
-      <c r="G5" s="3">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B6" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C6" s="3">
-        <v>34</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C7" s="3">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B8" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4">
-        <v>961</v>
-      </c>
-      <c r="D10" s="4">
-        <v>5</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4">
-        <v>22</v>
-      </c>
-      <c r="G10" s="4">
-        <v>989</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -774,10 +568,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -787,10 +581,10 @@
       <c r="B2" s="2">
         <v>17168</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
     </row>
@@ -801,10 +595,10 @@
       <c r="B3" s="2">
         <v>21094</v>
       </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
         <v>1</v>
       </c>
     </row>
@@ -815,22 +609,22 @@
       <c r="B4" s="2">
         <v>21094</v>
       </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>4</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
     </row>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -8,15 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Babyshop" sheetId="1" r:id="rId1"/>
-    <sheet name="Max" sheetId="2" r:id="rId2"/>
-    <sheet name="Shoexpress" sheetId="3" r:id="rId3"/>
+    <sheet name="Lifestyle" sheetId="2" r:id="rId2"/>
+    <sheet name="Max" sheetId="3" r:id="rId3"/>
+    <sheet name="Shoe Mart" sheetId="4" r:id="rId4"/>
+    <sheet name="Shoexpress" sheetId="5" r:id="rId5"/>
+    <sheet name="Splash" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="44">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -24,7 +27,76 @@
     <t>DEST_ID</t>
   </si>
   <si>
+    <t>BSBAS1</t>
+  </si>
+  <si>
+    <t>BSBAS2</t>
+  </si>
+  <si>
+    <t>BSCLTH1</t>
+  </si>
+  <si>
+    <t>BSCLTH4</t>
+  </si>
+  <si>
+    <t>BSCLUG</t>
+  </si>
+  <si>
+    <t>BSLIQ</t>
+  </si>
+  <si>
+    <t>BSNUF1</t>
+  </si>
+  <si>
+    <t>BSNUF2</t>
+  </si>
+  <si>
+    <t>BSTOY1</t>
+  </si>
+  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>LSCOSM</t>
+  </si>
+  <si>
+    <t>LSFAC</t>
+  </si>
+  <si>
+    <t>LSHDR</t>
+  </si>
+  <si>
+    <t>LSHDR1</t>
+  </si>
+  <si>
+    <t>LSHFR</t>
+  </si>
+  <si>
+    <t>LSHFU</t>
+  </si>
+  <si>
+    <t>LSTEEN</t>
+  </si>
+  <si>
+    <t>MACC01</t>
+  </si>
+  <si>
+    <t>MCHL</t>
+  </si>
+  <si>
+    <t>MCOS1</t>
+  </si>
+  <si>
+    <t>MFTA</t>
+  </si>
+  <si>
+    <t>MHOM</t>
+  </si>
+  <si>
+    <t>MHOM1</t>
+  </si>
+  <si>
+    <t>MLAD</t>
   </si>
   <si>
     <t>MLIN</t>
@@ -33,7 +105,52 @@
     <t>MMEN2</t>
   </si>
   <si>
-    <t>SXDMF1</t>
+    <t>MTOY</t>
+  </si>
+  <si>
+    <t>MXKIDS</t>
+  </si>
+  <si>
+    <t>SMACC</t>
+  </si>
+  <si>
+    <t>SMKID</t>
+  </si>
+  <si>
+    <t>SMLAD</t>
+  </si>
+  <si>
+    <t>SMLUG</t>
+  </si>
+  <si>
+    <t>SMMEN</t>
+  </si>
+  <si>
+    <t>SP-ECOM</t>
+  </si>
+  <si>
+    <t>SP-HLAD</t>
+  </si>
+  <si>
+    <t>SP-HLIN</t>
+  </si>
+  <si>
+    <t>SP-HMEN</t>
+  </si>
+  <si>
+    <t>SP-HWNTR</t>
+  </si>
+  <si>
+    <t>SPACC</t>
+  </si>
+  <si>
+    <t>SPAIS1</t>
+  </si>
+  <si>
+    <t>SPAIS2</t>
+  </si>
+  <si>
+    <t>SPLAD</t>
   </si>
 </sst>
 </file>
@@ -123,10 +240,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -423,6 +540,4307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="2">
+        <v>21092</v>
+      </c>
+      <c r="C2" s="3">
+        <v>360</v>
+      </c>
+      <c r="D2" s="3">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3">
+        <v>29</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>31</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3">
+        <v>16</v>
+      </c>
+      <c r="L2" s="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21176</v>
+      </c>
+      <c r="C3" s="3">
+        <v>391</v>
+      </c>
+      <c r="D3" s="3">
+        <v>73</v>
+      </c>
+      <c r="E3" s="3">
+        <v>190</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>135</v>
+      </c>
+      <c r="H3" s="3">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>23</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3">
+        <v>38</v>
+      </c>
+      <c r="L3" s="3">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B4" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C4" s="3">
+        <v>194</v>
+      </c>
+      <c r="D4" s="3">
+        <v>56</v>
+      </c>
+      <c r="E4" s="3">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>66</v>
+      </c>
+      <c r="H4" s="3">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21088</v>
+      </c>
+      <c r="C5" s="3">
+        <v>290</v>
+      </c>
+      <c r="D5" s="3">
+        <v>67</v>
+      </c>
+      <c r="E5" s="3">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>59</v>
+      </c>
+      <c r="H5" s="3">
+        <v>6</v>
+      </c>
+      <c r="I5" s="3">
+        <v>6</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B6" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C6" s="3">
+        <v>264</v>
+      </c>
+      <c r="D6" s="3">
+        <v>79</v>
+      </c>
+      <c r="E6" s="3">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>66</v>
+      </c>
+      <c r="H6" s="3">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>36</v>
+      </c>
+      <c r="L6" s="3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21229</v>
+      </c>
+      <c r="C7" s="3">
+        <v>343</v>
+      </c>
+      <c r="D7" s="3">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3">
+        <v>94</v>
+      </c>
+      <c r="H7" s="3">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3">
+        <v>5</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>29</v>
+      </c>
+      <c r="L7" s="3">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4">
+        <v>1842</v>
+      </c>
+      <c r="D8" s="4">
+        <v>380</v>
+      </c>
+      <c r="E8" s="4">
+        <v>280</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4">
+        <v>451</v>
+      </c>
+      <c r="H8" s="4">
+        <v>57</v>
+      </c>
+      <c r="I8" s="4">
+        <v>43</v>
+      </c>
+      <c r="J8" s="4">
+        <v>5</v>
+      </c>
+      <c r="K8" s="4">
+        <v>167</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3232</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2">
+        <v>4000</v>
+      </c>
+      <c r="B2" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C2" s="3">
+        <v>255</v>
+      </c>
+      <c r="D2" s="3">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2">
+        <v>4000</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21088</v>
+      </c>
+      <c r="C3" s="3">
+        <v>84</v>
+      </c>
+      <c r="D3" s="3">
+        <v>38</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2">
+        <v>4000</v>
+      </c>
+      <c r="B4" s="2">
+        <v>21469</v>
+      </c>
+      <c r="C4" s="3">
+        <v>288</v>
+      </c>
+      <c r="D4" s="3">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>9</v>
+      </c>
+      <c r="H4" s="3">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2">
+        <v>4001</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21092</v>
+      </c>
+      <c r="C5" s="3">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
+        <v>87</v>
+      </c>
+      <c r="J5" s="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2">
+        <v>4001</v>
+      </c>
+      <c r="B6" s="2">
+        <v>21176</v>
+      </c>
+      <c r="C6" s="3">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3">
+        <v>76</v>
+      </c>
+      <c r="G6" s="3">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3">
+        <v>127</v>
+      </c>
+      <c r="J6" s="3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2">
+        <v>4001</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21229</v>
+      </c>
+      <c r="C7" s="3">
+        <v>188</v>
+      </c>
+      <c r="D7" s="3">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3">
+        <v>9</v>
+      </c>
+      <c r="H7" s="3">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3">
+        <v>81</v>
+      </c>
+      <c r="J7" s="3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2">
+        <v>4002</v>
+      </c>
+      <c r="B8" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C8" s="3">
+        <v>83</v>
+      </c>
+      <c r="D8" s="3">
+        <v>64</v>
+      </c>
+      <c r="E8" s="3">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3">
+        <v>6</v>
+      </c>
+      <c r="I8" s="3">
+        <v>41</v>
+      </c>
+      <c r="J8" s="3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2">
+        <v>4002</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C9" s="3">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>7</v>
+      </c>
+      <c r="I9" s="3">
+        <v>36</v>
+      </c>
+      <c r="J9" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2">
+        <v>4002</v>
+      </c>
+      <c r="B10" s="2">
+        <v>21515</v>
+      </c>
+      <c r="C10" s="3">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3">
+        <v>43</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>7</v>
+      </c>
+      <c r="I10" s="3">
+        <v>16</v>
+      </c>
+      <c r="J10" s="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2">
+        <v>4003</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21081</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
+        <v>28</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="4">
+        <v>1122</v>
+      </c>
+      <c r="D12" s="4">
+        <v>228</v>
+      </c>
+      <c r="E12" s="4">
+        <v>192</v>
+      </c>
+      <c r="F12" s="4">
+        <v>132</v>
+      </c>
+      <c r="G12" s="4">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4">
+        <v>61</v>
+      </c>
+      <c r="I12" s="4">
+        <v>443</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N124"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="7" width="6.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="10" width="6.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3">
+        <v>348</v>
+      </c>
+      <c r="N2" s="3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3">
+        <v>426</v>
+      </c>
+      <c r="N3" s="3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3">
+        <v>371</v>
+      </c>
+      <c r="N4" s="3">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3">
+        <v>642</v>
+      </c>
+      <c r="N5" s="3">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3">
+        <v>541</v>
+      </c>
+      <c r="N6" s="3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3">
+        <v>577</v>
+      </c>
+      <c r="N7" s="3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3">
+        <v>637</v>
+      </c>
+      <c r="N8" s="3">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3">
+        <v>313</v>
+      </c>
+      <c r="N9" s="3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3">
+        <v>379</v>
+      </c>
+      <c r="N10" s="3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="2">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3">
+        <v>379</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="2">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
+        <v>186</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="2">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
+        <v>109</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="2">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3">
+        <v>287</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3">
+        <v>421</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="2">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3">
+        <v>379</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
+        <v>2</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="2">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3">
+        <v>177</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="2">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3">
+        <v>140</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="2">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
+        <v>124</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="2">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3">
+        <v>51</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="2">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3">
+        <v>146</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="2">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3">
+        <v>125</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="2">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3">
+        <v>186</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="2">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3">
+        <v>141</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="2">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3">
+        <v>52</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="2">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3">
+        <v>182</v>
+      </c>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="2">
+        <v>9</v>
+      </c>
+      <c r="B27" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3">
+        <v>105</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="2">
+        <v>9</v>
+      </c>
+      <c r="B28" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3">
+        <v>218</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="2">
+        <v>10</v>
+      </c>
+      <c r="B29" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3">
+        <v>521</v>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="2">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3">
+        <v>136</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="2">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3">
+        <v>53</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="2">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2">
+        <v>60137</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3">
+        <v>9</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="2">
+        <v>11</v>
+      </c>
+      <c r="B33" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3">
+        <v>468</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="2">
+        <v>11</v>
+      </c>
+      <c r="B34" s="2">
+        <v>60202</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3">
+        <v>7</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="2">
+        <v>12</v>
+      </c>
+      <c r="B35" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
+        <v>393</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="2">
+        <v>12</v>
+      </c>
+      <c r="B36" s="2">
+        <v>60496</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3">
+        <v>5</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="2">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2">
+        <v>60507</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3">
+        <v>2</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="2">
+        <v>13</v>
+      </c>
+      <c r="B38" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3">
+        <v>106</v>
+      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3">
+        <v>34</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="2">
+        <v>13</v>
+      </c>
+      <c r="B39" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3">
+        <v>40</v>
+      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3">
+        <v>9</v>
+      </c>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="2">
+        <v>13</v>
+      </c>
+      <c r="B40" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3">
+        <v>24</v>
+      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3">
+        <v>14</v>
+      </c>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="2">
+        <v>14</v>
+      </c>
+      <c r="B41" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3">
+        <v>102</v>
+      </c>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3">
+        <v>20</v>
+      </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="2">
+        <v>14</v>
+      </c>
+      <c r="B42" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
+        <v>113</v>
+      </c>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>29</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="2">
+        <v>14</v>
+      </c>
+      <c r="B43" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3">
+        <v>106</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3">
+        <v>21</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="2">
+        <v>15</v>
+      </c>
+      <c r="B44" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
+        <v>130</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3">
+        <v>34</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="2">
+        <v>15</v>
+      </c>
+      <c r="B45" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3">
+        <v>46</v>
+      </c>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3">
+        <v>23</v>
+      </c>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="2">
+        <v>15</v>
+      </c>
+      <c r="B46" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3">
+        <v>95</v>
+      </c>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3">
+        <v>47</v>
+      </c>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="2">
+        <v>16</v>
+      </c>
+      <c r="B47" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C47" s="3">
+        <v>295</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3">
+        <v>2</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="2">
+        <v>16</v>
+      </c>
+      <c r="B48" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C48" s="3">
+        <v>132</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="2">
+        <v>16</v>
+      </c>
+      <c r="B49" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C49" s="3">
+        <v>65</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="2">
+        <v>17</v>
+      </c>
+      <c r="B50" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C50" s="3">
+        <v>330</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="2">
+        <v>17</v>
+      </c>
+      <c r="B51" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C51" s="3">
+        <v>323</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3">
+        <v>7</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="2">
+        <v>17</v>
+      </c>
+      <c r="B52" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C52" s="3">
+        <v>379</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="2">
+        <v>18</v>
+      </c>
+      <c r="B53" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C53" s="3">
+        <v>462</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="2">
+        <v>18</v>
+      </c>
+      <c r="B54" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C54" s="3">
+        <v>109</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="2">
+        <v>18</v>
+      </c>
+      <c r="B55" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C55" s="3">
+        <v>161</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3">
+        <v>2</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="2">
+        <v>19</v>
+      </c>
+      <c r="B56" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3">
+        <v>5</v>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="2">
+        <v>19</v>
+      </c>
+      <c r="B57" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="2">
+        <v>19</v>
+      </c>
+      <c r="B58" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3">
+        <v>7</v>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="2">
+        <v>19</v>
+      </c>
+      <c r="B59" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3">
+        <v>13</v>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="2">
+        <v>19</v>
+      </c>
+      <c r="B60" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3">
+        <v>9</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="2">
+        <v>19</v>
+      </c>
+      <c r="B61" s="2">
+        <v>60132</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3">
+        <v>7</v>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="2">
+        <v>19</v>
+      </c>
+      <c r="B62" s="2">
+        <v>60134</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="2">
+        <v>19</v>
+      </c>
+      <c r="B63" s="2">
+        <v>60135</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3">
+        <v>2</v>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="2">
+        <v>19</v>
+      </c>
+      <c r="B64" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3">
+        <v>8</v>
+      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="2">
+        <v>19</v>
+      </c>
+      <c r="B65" s="2">
+        <v>60139</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3">
+        <v>11</v>
+      </c>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="2">
+        <v>19</v>
+      </c>
+      <c r="B66" s="2">
+        <v>60140</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3">
+        <v>8</v>
+      </c>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" s="2">
+        <v>19</v>
+      </c>
+      <c r="B67" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="2">
+        <v>19</v>
+      </c>
+      <c r="B68" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3">
+        <v>15</v>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="2">
+        <v>19</v>
+      </c>
+      <c r="B69" s="2">
+        <v>60306</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3">
+        <v>6</v>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="2">
+        <v>19</v>
+      </c>
+      <c r="B70" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3">
+        <v>4</v>
+      </c>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="2">
+        <v>19</v>
+      </c>
+      <c r="B71" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3">
+        <v>10</v>
+      </c>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="2">
+        <v>21</v>
+      </c>
+      <c r="B72" s="2">
+        <v>60138</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3">
+        <v>32</v>
+      </c>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" s="2">
+        <v>21</v>
+      </c>
+      <c r="B73" s="2">
+        <v>60202</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3">
+        <v>10</v>
+      </c>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="2">
+        <v>21</v>
+      </c>
+      <c r="B74" s="2">
+        <v>60224</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3">
+        <v>47</v>
+      </c>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" s="2">
+        <v>21</v>
+      </c>
+      <c r="B75" s="2">
+        <v>60227</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3">
+        <v>46</v>
+      </c>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" s="2">
+        <v>21</v>
+      </c>
+      <c r="B76" s="2">
+        <v>60448</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3">
+        <v>1</v>
+      </c>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" s="2">
+        <v>22</v>
+      </c>
+      <c r="B77" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3">
+        <v>46</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" s="2">
+        <v>22</v>
+      </c>
+      <c r="B78" s="2">
+        <v>60131</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3">
+        <v>1</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3">
+        <v>33</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" s="2">
+        <v>22</v>
+      </c>
+      <c r="B79" s="2">
+        <v>60215</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3">
+        <v>10</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" s="2">
+        <v>22</v>
+      </c>
+      <c r="B80" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3">
+        <v>38</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" s="2">
+        <v>22</v>
+      </c>
+      <c r="B81" s="2">
+        <v>60496</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3">
+        <v>10</v>
+      </c>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="2">
+        <v>22</v>
+      </c>
+      <c r="B82" s="2">
+        <v>60507</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3">
+        <v>10</v>
+      </c>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" s="2">
+        <v>23</v>
+      </c>
+      <c r="B83" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3">
+        <v>2</v>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3">
+        <v>32</v>
+      </c>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" s="2">
+        <v>23</v>
+      </c>
+      <c r="B84" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3">
+        <v>56</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" s="2">
+        <v>23</v>
+      </c>
+      <c r="B85" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3">
+        <v>39</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" s="2">
+        <v>23</v>
+      </c>
+      <c r="B86" s="2">
+        <v>60132</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3">
+        <v>2</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3">
+        <v>41</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" s="2">
+        <v>23</v>
+      </c>
+      <c r="B87" s="2">
+        <v>60134</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3">
+        <v>24</v>
+      </c>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" s="2">
+        <v>23</v>
+      </c>
+      <c r="B88" s="2">
+        <v>60135</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3">
+        <v>24</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" s="2">
+        <v>23</v>
+      </c>
+      <c r="B89" s="2">
+        <v>60139</v>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3">
+        <v>51</v>
+      </c>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" s="2">
+        <v>23</v>
+      </c>
+      <c r="B90" s="2">
+        <v>60140</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3">
+        <v>4</v>
+      </c>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" s="2">
+        <v>23</v>
+      </c>
+      <c r="B91" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3">
+        <v>39</v>
+      </c>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" s="2">
+        <v>23</v>
+      </c>
+      <c r="B92" s="2">
+        <v>60306</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3">
+        <v>15</v>
+      </c>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93" s="2">
+        <v>23</v>
+      </c>
+      <c r="B93" s="2">
+        <v>60355</v>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3">
+        <v>15</v>
+      </c>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" s="2">
+        <v>23</v>
+      </c>
+      <c r="B94" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3">
+        <v>16</v>
+      </c>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" s="2">
+        <v>27</v>
+      </c>
+      <c r="B95" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3">
+        <v>15</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3">
+        <v>328</v>
+      </c>
+      <c r="N95" s="3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" s="2">
+        <v>27</v>
+      </c>
+      <c r="B96" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3">
+        <v>2</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3">
+        <v>261</v>
+      </c>
+      <c r="N96" s="3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" s="2">
+        <v>27</v>
+      </c>
+      <c r="B97" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3">
+        <v>1</v>
+      </c>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3">
+        <v>146</v>
+      </c>
+      <c r="N97" s="3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98" s="2">
+        <v>28</v>
+      </c>
+      <c r="B98" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3">
+        <v>338</v>
+      </c>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3">
+        <v>1</v>
+      </c>
+      <c r="N98" s="3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="A99" s="2">
+        <v>28</v>
+      </c>
+      <c r="B99" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3">
+        <v>152</v>
+      </c>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" s="2">
+        <v>28</v>
+      </c>
+      <c r="B100" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3">
+        <v>499</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3">
+        <v>1</v>
+      </c>
+      <c r="N100" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101" s="2">
+        <v>29</v>
+      </c>
+      <c r="B101" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3">
+        <v>100</v>
+      </c>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" s="2">
+        <v>29</v>
+      </c>
+      <c r="B102" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3">
+        <v>83</v>
+      </c>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" s="2">
+        <v>29</v>
+      </c>
+      <c r="B103" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3">
+        <v>41</v>
+      </c>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="A104" s="2">
+        <v>30</v>
+      </c>
+      <c r="B104" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3">
+        <v>70</v>
+      </c>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3">
+        <v>24</v>
+      </c>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" s="2">
+        <v>30</v>
+      </c>
+      <c r="B105" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3">
+        <v>33</v>
+      </c>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3">
+        <v>20</v>
+      </c>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="A106" s="2">
+        <v>30</v>
+      </c>
+      <c r="B106" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3">
+        <v>73</v>
+      </c>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3">
+        <v>20</v>
+      </c>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
+      <c r="A107" s="2">
+        <v>31</v>
+      </c>
+      <c r="B107" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3">
+        <v>285</v>
+      </c>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
+      <c r="A108" s="2">
+        <v>31</v>
+      </c>
+      <c r="B108" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3">
+        <v>419</v>
+      </c>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
+      <c r="A109" s="2">
+        <v>31</v>
+      </c>
+      <c r="B109" s="2">
+        <v>60296</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3">
+        <v>313</v>
+      </c>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" s="2">
+        <v>32</v>
+      </c>
+      <c r="B110" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3">
+        <v>230</v>
+      </c>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
+      <c r="A111" s="2">
+        <v>32</v>
+      </c>
+      <c r="B111" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3">
+        <v>125</v>
+      </c>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
+      <c r="A112" s="2">
+        <v>32</v>
+      </c>
+      <c r="B112" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3">
+        <v>132</v>
+      </c>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
+      <c r="A113" s="2">
+        <v>33</v>
+      </c>
+      <c r="B113" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C113" s="3">
+        <v>246</v>
+      </c>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3">
+        <v>1</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
+      <c r="A114" s="2">
+        <v>33</v>
+      </c>
+      <c r="B114" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C114" s="3">
+        <v>49</v>
+      </c>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
+      <c r="A115" s="2">
+        <v>33</v>
+      </c>
+      <c r="B115" s="2">
+        <v>60510</v>
+      </c>
+      <c r="C115" s="3">
+        <v>147</v>
+      </c>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3">
+        <v>2</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
+      <c r="A116" s="2">
+        <v>34</v>
+      </c>
+      <c r="B116" s="2">
+        <v>60136</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3">
+        <v>1</v>
+      </c>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3">
+        <v>170</v>
+      </c>
+      <c r="N116" s="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
+      <c r="A117" s="2">
+        <v>36</v>
+      </c>
+      <c r="B117" s="2">
+        <v>60132</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3">
+        <v>24</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="3"/>
+      <c r="M117" s="3">
+        <v>1056</v>
+      </c>
+      <c r="N117" s="3">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
+      <c r="A118" s="2">
+        <v>37</v>
+      </c>
+      <c r="B118" s="2">
+        <v>60139</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3">
+        <v>8</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3">
+        <v>541</v>
+      </c>
+      <c r="N118" s="3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="A119" s="2">
+        <v>38</v>
+      </c>
+      <c r="B119" s="2">
+        <v>60130</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3">
+        <v>4</v>
+      </c>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
+      <c r="A120" s="2">
+        <v>38</v>
+      </c>
+      <c r="B120" s="2">
+        <v>60272</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3">
+        <v>3</v>
+      </c>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" s="2">
+        <v>59</v>
+      </c>
+      <c r="B121" s="2">
+        <v>60127</v>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3">
+        <v>39</v>
+      </c>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="A122" s="2">
+        <v>59</v>
+      </c>
+      <c r="B122" s="2">
+        <v>60128</v>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3">
+        <v>9</v>
+      </c>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="2">
+        <v>59</v>
+      </c>
+      <c r="B123" s="2">
+        <v>60129</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3">
+        <v>14</v>
+      </c>
+      <c r="L123" s="3"/>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
+      <c r="A124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" s="2"/>
+      <c r="C124" s="4">
+        <v>2698</v>
+      </c>
+      <c r="D124" s="4">
+        <v>168</v>
+      </c>
+      <c r="E124" s="4">
+        <v>15</v>
+      </c>
+      <c r="F124" s="4">
+        <v>945</v>
+      </c>
+      <c r="G124" s="4">
+        <v>115</v>
+      </c>
+      <c r="H124" s="4">
+        <v>6</v>
+      </c>
+      <c r="I124" s="4">
+        <v>3196</v>
+      </c>
+      <c r="J124" s="4">
+        <v>3099</v>
+      </c>
+      <c r="K124" s="4">
+        <v>1498</v>
+      </c>
+      <c r="L124" s="4">
+        <v>934</v>
+      </c>
+      <c r="M124" s="4">
+        <v>6739</v>
+      </c>
+      <c r="N124" s="4">
+        <v>19413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="8" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="2">
+        <v>21088</v>
+      </c>
+      <c r="C2" s="3">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3">
+        <v>177</v>
+      </c>
+      <c r="E2" s="3">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21469</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3">
+        <v>230</v>
+      </c>
+      <c r="E3" s="3">
+        <v>21</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B4" s="2">
+        <v>21176</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>65</v>
+      </c>
+      <c r="E4" s="3">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21229</v>
+      </c>
+      <c r="C5" s="3">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
+        <v>166</v>
+      </c>
+      <c r="E5" s="3">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B6" s="2">
+        <v>21092</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>97</v>
+      </c>
+      <c r="E6" s="3">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C7" s="3">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3">
+        <v>171</v>
+      </c>
+      <c r="E7" s="3">
+        <v>107</v>
+      </c>
+      <c r="F7" s="3">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B8" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C8" s="3">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3">
+        <v>134</v>
+      </c>
+      <c r="E8" s="3">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>28</v>
+      </c>
+      <c r="H8" s="3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21515</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>7</v>
+      </c>
+      <c r="H9" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B10" s="2">
+        <v>21081</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>82</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C11" s="3">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>159</v>
+      </c>
+      <c r="E11" s="3">
+        <v>18</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>17</v>
+      </c>
+      <c r="H11" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C12" s="3">
+        <v>12</v>
+      </c>
+      <c r="D12" s="3">
+        <v>14</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B13" s="2">
+        <v>21082</v>
+      </c>
+      <c r="C13" s="3">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3">
+        <v>137</v>
+      </c>
+      <c r="E13" s="3">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B14" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C14" s="3">
+        <v>33</v>
+      </c>
+      <c r="D14" s="3">
+        <v>113</v>
+      </c>
+      <c r="E14" s="3">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C15" s="3">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3">
+        <v>49</v>
+      </c>
+      <c r="E15" s="3">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3">
+        <v>32</v>
+      </c>
+      <c r="H15" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21457</v>
+      </c>
+      <c r="C16" s="3">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <v>63</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B17" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C17" s="3">
+        <v>24</v>
+      </c>
+      <c r="D17" s="3">
+        <v>44</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3">
+        <v>11</v>
+      </c>
+      <c r="H17" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B18" s="2">
+        <v>21533</v>
+      </c>
+      <c r="C18" s="3">
+        <v>21</v>
+      </c>
+      <c r="D18" s="3">
+        <v>147</v>
+      </c>
+      <c r="E18" s="3">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3">
+        <v>6</v>
+      </c>
+      <c r="H18" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="4">
+        <v>294</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1856</v>
+      </c>
+      <c r="E19" s="4">
+        <v>322</v>
+      </c>
+      <c r="F19" s="4">
+        <v>16</v>
+      </c>
+      <c r="G19" s="4">
+        <v>241</v>
+      </c>
+      <c r="H19" s="4">
+        <v>2729</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -439,33 +4857,35 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="5" width="7.7109375" customWidth="1"/>
+    <col min="2" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="12" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,159 +4893,294 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2">
-        <v>59</v>
+        <v>3000</v>
       </c>
       <c r="B2" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C2" s="4">
+        <v>21088</v>
+      </c>
+      <c r="C2" s="3">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3">
+        <v>87</v>
+      </c>
+      <c r="H2" s="3">
+        <v>171</v>
+      </c>
+      <c r="I2" s="3">
+        <v>53</v>
+      </c>
+      <c r="J2" s="3">
+        <v>44</v>
+      </c>
+      <c r="K2" s="3">
+        <v>12</v>
+      </c>
+      <c r="L2" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="2">
+        <v>3000</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21469</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3">
+        <v>26</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <v>65</v>
+      </c>
+      <c r="H3" s="3">
+        <v>214</v>
+      </c>
+      <c r="I3" s="3">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3">
+        <v>42</v>
+      </c>
+      <c r="K3" s="3">
+        <v>7</v>
+      </c>
+      <c r="L3" s="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2">
+        <v>3001</v>
+      </c>
+      <c r="B4" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>162</v>
+      </c>
+      <c r="E4" s="3">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3">
+        <v>95</v>
+      </c>
+      <c r="G4" s="3">
+        <v>119</v>
+      </c>
+      <c r="H4" s="3">
+        <v>213</v>
+      </c>
+      <c r="I4" s="3">
+        <v>158</v>
+      </c>
+      <c r="J4" s="3">
+        <v>88</v>
+      </c>
+      <c r="K4" s="3">
+        <v>18</v>
+      </c>
+      <c r="L4" s="3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2">
+        <v>3001</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21229</v>
+      </c>
+      <c r="C5" s="3">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>135</v>
+      </c>
+      <c r="E5" s="3">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3">
+        <v>71</v>
+      </c>
+      <c r="H5" s="3">
+        <v>53</v>
+      </c>
+      <c r="I5" s="3">
+        <v>83</v>
+      </c>
+      <c r="J5" s="3">
+        <v>108</v>
+      </c>
+      <c r="K5" s="3">
+        <v>13</v>
+      </c>
+      <c r="L5" s="3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2">
+        <v>3002</v>
+      </c>
+      <c r="B6" s="2">
+        <v>21092</v>
+      </c>
+      <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
-        <v>2179</v>
-      </c>
-      <c r="E2" s="4">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>59</v>
-      </c>
-      <c r="B3" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
-        <v>1247</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>59</v>
-      </c>
-      <c r="B4" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>2030</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3">
+      <c r="D6" s="3">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <v>87</v>
+      </c>
+      <c r="J6" s="3">
+        <v>52</v>
+      </c>
+      <c r="K6" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="3">
-        <v>5456</v>
-      </c>
-      <c r="E5" s="3">
-        <v>5457</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="L6" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2">
+        <v>3002</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21176</v>
+      </c>
+      <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2">
-        <v>5001</v>
-      </c>
-      <c r="B2" s="2">
-        <v>17168</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
-        <v>5002</v>
-      </c>
-      <c r="B3" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2">
-        <v>5003</v>
-      </c>
-      <c r="B4" s="2">
-        <v>21094</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
+      <c r="D7" s="3">
+        <v>72</v>
+      </c>
+      <c r="E7" s="3">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3">
+        <v>68</v>
+      </c>
+      <c r="G7" s="3">
+        <v>58</v>
+      </c>
+      <c r="H7" s="3">
+        <v>43</v>
+      </c>
+      <c r="I7" s="3">
+        <v>169</v>
+      </c>
+      <c r="J7" s="3">
+        <v>120</v>
+      </c>
+      <c r="K7" s="3">
+        <v>6</v>
+      </c>
+      <c r="L7" s="3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4">
+        <v>40</v>
+      </c>
+      <c r="D8" s="4">
+        <v>437</v>
+      </c>
+      <c r="E8" s="4">
+        <v>120</v>
+      </c>
+      <c r="F8" s="4">
+        <v>246</v>
+      </c>
+      <c r="G8" s="4">
+        <v>427</v>
+      </c>
+      <c r="H8" s="4">
+        <v>724</v>
+      </c>
+      <c r="I8" s="4">
+        <v>581</v>
+      </c>
+      <c r="J8" s="4">
+        <v>454</v>
+      </c>
+      <c r="K8" s="4">
+        <v>57</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3086</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="47">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -36,10 +36,16 @@
     <t>BSCLTH1</t>
   </si>
   <si>
+    <t>BSCLTH2</t>
+  </si>
+  <si>
     <t>BSCLTH4</t>
   </si>
   <si>
     <t>BSCLUG</t>
+  </si>
+  <si>
+    <t>BSECOM</t>
   </si>
   <si>
     <t>BSLIQ</t>
@@ -120,10 +126,10 @@
     <t>SMLAD</t>
   </si>
   <si>
-    <t>SMLUG</t>
+    <t>SMMEN</t>
   </si>
   <si>
-    <t>SMMEN</t>
+    <t>SXDMF1</t>
   </si>
   <si>
     <t>SP-ECOM</t>
@@ -139,6 +145,9 @@
   </si>
   <si>
     <t>SP-HWNTR</t>
+  </si>
+  <si>
+    <t>SP-PERFUME</t>
   </si>
   <si>
     <t>SPACC</t>
@@ -540,20 +549,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="6" width="9.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="5" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="9" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,8 +599,14 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -601,33 +616,25 @@
       <c r="C2" s="3">
         <v>360</v>
       </c>
-      <c r="D2" s="3">
-        <v>35</v>
-      </c>
-      <c r="E2" s="3">
-        <v>29</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3">
         <v>1</v>
       </c>
-      <c r="G2" s="3">
-        <v>31</v>
-      </c>
-      <c r="H2" s="3">
-        <v>6</v>
-      </c>
-      <c r="I2" s="3">
-        <v>2</v>
-      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3">
         <v>16</v>
       </c>
-      <c r="L2" s="3">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" s="3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
@@ -637,214 +644,944 @@
       <c r="C3" s="3">
         <v>391</v>
       </c>
-      <c r="D3" s="3">
-        <v>73</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>190</v>
-      </c>
-      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
-        <v>135</v>
-      </c>
-      <c r="H3" s="3">
-        <v>12</v>
-      </c>
-      <c r="I3" s="3">
-        <v>23</v>
-      </c>
-      <c r="J3" s="3">
-        <v>2</v>
-      </c>
-      <c r="K3" s="3">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3">
         <v>38</v>
       </c>
-      <c r="L3" s="3">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" s="3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="2">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="2">
-        <v>21085</v>
+        <v>21082</v>
       </c>
       <c r="C4" s="3">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="D4" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3">
-        <v>12</v>
+        <v>213</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>66</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="I4" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3">
         <v>24</v>
       </c>
-      <c r="L4" s="3">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" s="3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="2">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B5" s="2">
-        <v>21088</v>
+        <v>21469</v>
       </c>
       <c r="C5" s="3">
-        <v>290</v>
+        <v>476</v>
       </c>
       <c r="D5" s="3">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E5" s="3">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
-        <v>6</v>
-      </c>
-      <c r="I5" s="3">
-        <v>6</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="3">
-        <v>24</v>
-      </c>
-      <c r="L5" s="3">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3">
+        <v>33</v>
+      </c>
+      <c r="N5" s="3">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="2">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="2">
-        <v>21087</v>
+        <v>21075</v>
       </c>
       <c r="C6" s="3">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>66</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F6" s="3">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="I6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
         <v>1</v>
       </c>
-      <c r="K6" s="3">
-        <v>36</v>
-      </c>
-      <c r="L6" s="3">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3">
+        <v>9</v>
+      </c>
+      <c r="N6" s="3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21533</v>
+      </c>
+      <c r="C7" s="3">
+        <v>507</v>
+      </c>
+      <c r="D7" s="3">
+        <v>105</v>
+      </c>
+      <c r="E7" s="3">
+        <v>148</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>24</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>10</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3">
+        <v>61</v>
+      </c>
+      <c r="N7" s="3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B8" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21515</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B10" s="2">
+        <v>21533</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3">
+        <v>6</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21075</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21082</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B13" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3">
+        <v>3</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B14" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21457</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
+        <v>7</v>
+      </c>
+      <c r="L16" s="3">
+        <v>3</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B17" s="2">
+        <v>21081</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B18" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B19" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B20" s="2">
+        <v>21469</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3">
+        <v>19</v>
+      </c>
+      <c r="L20" s="3">
+        <v>2</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C21" s="3">
+        <v>82</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21088</v>
+      </c>
+      <c r="C22" s="3">
+        <v>113</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B23" s="2">
+        <v>21088</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="2">
         <v>1008</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B24" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C24" s="3">
+        <v>74</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B25" s="2">
         <v>21229</v>
       </c>
-      <c r="C7" s="3">
-        <v>343</v>
-      </c>
-      <c r="D7" s="3">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="C25" s="3">
+        <v>73</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3">
+        <v>4</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B26" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C26" s="3">
+        <v>226</v>
+      </c>
+      <c r="D26" s="3">
+        <v>56</v>
+      </c>
+      <c r="E26" s="3">
+        <v>174</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
+        <v>80</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3">
+        <v>2</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3">
+        <v>24</v>
+      </c>
+      <c r="N26" s="3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B27" s="2">
+        <v>21515</v>
+      </c>
+      <c r="C27" s="3">
+        <v>107</v>
+      </c>
+      <c r="D27" s="3">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B28" s="2">
+        <v>21195</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3">
+        <v>2</v>
+      </c>
+      <c r="N28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B29" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C29" s="3">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B30" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C30" s="3">
+        <v>342</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45</v>
+      </c>
+      <c r="E30" s="3">
+        <v>165</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3">
+        <v>71</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3">
+        <v>15</v>
+      </c>
+      <c r="N30" s="3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B31" s="2">
+        <v>21457</v>
+      </c>
+      <c r="C31" s="3">
+        <v>488</v>
+      </c>
+      <c r="D31" s="3">
+        <v>57</v>
+      </c>
+      <c r="E31" s="3">
+        <v>165</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3">
+        <v>69</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3">
+        <v>4</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3">
+        <v>23</v>
+      </c>
+      <c r="N31" s="3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B32" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C32" s="3">
+        <v>55</v>
+      </c>
+      <c r="D32" s="3">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3">
+        <v>43</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3">
+        <v>46</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3">
+        <v>2</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3">
+        <v>27</v>
+      </c>
+      <c r="N32" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B33" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C33" s="3">
+        <v>641</v>
+      </c>
+      <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>359</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>154</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3">
+        <v>7</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3">
+        <v>14</v>
+      </c>
+      <c r="N33" s="3">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B34" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C34" s="3">
+        <v>184</v>
+      </c>
+      <c r="D34" s="3">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>73</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3">
+        <v>7</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3">
+        <v>21</v>
+      </c>
+      <c r="N34" s="3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="3">
-        <v>4</v>
-      </c>
-      <c r="G7" s="3">
-        <v>94</v>
-      </c>
-      <c r="H7" s="3">
-        <v>12</v>
-      </c>
-      <c r="I7" s="3">
-        <v>5</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3">
-        <v>29</v>
-      </c>
-      <c r="L7" s="3">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="2" t="s">
+      <c r="B35" s="2"/>
+      <c r="C35" s="4">
+        <v>4482</v>
+      </c>
+      <c r="D35" s="4">
+        <v>600</v>
+      </c>
+      <c r="E35" s="4">
+        <v>1726</v>
+      </c>
+      <c r="F35" s="4">
+        <v>15</v>
+      </c>
+      <c r="G35" s="4">
+        <v>19</v>
+      </c>
+      <c r="H35" s="4">
+        <v>930</v>
+      </c>
+      <c r="I35" s="4">
+        <v>3</v>
+      </c>
+      <c r="J35" s="4">
+        <v>40</v>
+      </c>
+      <c r="K35" s="4">
+        <v>61</v>
+      </c>
+      <c r="L35" s="4">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4">
-        <v>1842</v>
-      </c>
-      <c r="D8" s="4">
-        <v>380</v>
-      </c>
-      <c r="E8" s="4">
-        <v>280</v>
-      </c>
-      <c r="F8" s="4">
-        <v>7</v>
-      </c>
-      <c r="G8" s="4">
-        <v>451</v>
-      </c>
-      <c r="H8" s="4">
-        <v>57</v>
-      </c>
-      <c r="I8" s="4">
-        <v>43</v>
-      </c>
-      <c r="J8" s="4">
-        <v>5</v>
-      </c>
-      <c r="K8" s="4">
-        <v>167</v>
-      </c>
-      <c r="L8" s="4">
-        <v>3232</v>
+      <c r="M35" s="4">
+        <v>307</v>
+      </c>
+      <c r="N35" s="4">
+        <v>8194</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -875,28 +1612,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -907,22 +1644,18 @@
         <v>21087</v>
       </c>
       <c r="C2" s="3">
-        <v>255</v>
-      </c>
-      <c r="D2" s="3">
-        <v>19</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
         <v>3</v>
       </c>
-      <c r="H2" s="3">
-        <v>5</v>
-      </c>
+      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3">
-        <v>282</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -935,22 +1668,18 @@
       <c r="C3" s="3">
         <v>84</v>
       </c>
-      <c r="D3" s="3">
-        <v>38</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
         <v>2</v>
       </c>
-      <c r="H3" s="3">
-        <v>22</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3">
         <v>20</v>
       </c>
       <c r="J3" s="3">
-        <v>166</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -960,23 +1689,17 @@
       <c r="B4" s="2">
         <v>21469</v>
       </c>
-      <c r="C4" s="3">
-        <v>288</v>
-      </c>
-      <c r="D4" s="3">
-        <v>21</v>
-      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
         <v>9</v>
       </c>
-      <c r="H4" s="3">
-        <v>3</v>
-      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
-        <v>321</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -990,14 +1713,10 @@
         <v>92</v>
       </c>
       <c r="D5" s="3">
-        <v>15</v>
-      </c>
-      <c r="E5" s="3">
-        <v>44</v>
-      </c>
-      <c r="F5" s="3">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="3">
         <v>3</v>
       </c>
@@ -1006,7 +1725,7 @@
         <v>87</v>
       </c>
       <c r="J5" s="3">
-        <v>247</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1022,23 +1741,19 @@
       <c r="D6" s="3">
         <v>29</v>
       </c>
-      <c r="E6" s="3">
-        <v>29</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3">
         <v>6</v>
       </c>
-      <c r="H6" s="3">
-        <v>4</v>
-      </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="J6" s="3">
-        <v>318</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1049,28 +1764,20 @@
         <v>21229</v>
       </c>
       <c r="C7" s="3">
-        <v>188</v>
-      </c>
-      <c r="D7" s="3">
-        <v>25</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3">
         <v>37</v>
       </c>
-      <c r="F7" s="3">
-        <v>10</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
         <v>9</v>
       </c>
-      <c r="H7" s="3">
-        <v>7</v>
-      </c>
-      <c r="I7" s="3">
-        <v>81</v>
-      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>357</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1086,23 +1793,19 @@
       <c r="D8" s="3">
         <v>64</v>
       </c>
-      <c r="E8" s="3">
-        <v>15</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3">
         <v>7</v>
       </c>
       <c r="G8" s="3">
         <v>19</v>
       </c>
-      <c r="H8" s="3">
-        <v>6</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3">
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1118,23 +1821,19 @@
       <c r="D9" s="3">
         <v>11</v>
       </c>
-      <c r="E9" s="3">
-        <v>24</v>
-      </c>
+      <c r="E9" s="3"/>
       <c r="F9" s="3">
         <v>3</v>
       </c>
       <c r="G9" s="3">
         <v>8</v>
       </c>
-      <c r="H9" s="3">
-        <v>7</v>
-      </c>
+      <c r="H9" s="3"/>
       <c r="I9" s="3">
         <v>36</v>
       </c>
       <c r="J9" s="3">
-        <v>119</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1150,23 +1849,19 @@
       <c r="D10" s="3">
         <v>6</v>
       </c>
-      <c r="E10" s="3">
-        <v>43</v>
-      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3">
         <v>2</v>
       </c>
       <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="H10" s="3">
-        <v>7</v>
-      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3">
         <v>16</v>
       </c>
       <c r="J10" s="3">
-        <v>134</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1192,33 +1887,397 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="2">
+        <v>4004</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21195</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
+        <v>485</v>
+      </c>
+      <c r="E12" s="3">
+        <v>53</v>
+      </c>
+      <c r="F12" s="3">
+        <v>54</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>48</v>
+      </c>
+      <c r="I12" s="3">
+        <v>46</v>
+      </c>
+      <c r="J12" s="3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2">
+        <v>4004</v>
+      </c>
+      <c r="B13" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
+        <v>18</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
+        <v>42</v>
+      </c>
+      <c r="J13" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2">
+        <v>4005</v>
+      </c>
+      <c r="B14" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C14" s="3">
+        <v>59</v>
+      </c>
+      <c r="D14" s="3">
+        <v>15</v>
+      </c>
+      <c r="E14" s="3">
+        <v>65</v>
+      </c>
+      <c r="F14" s="3">
+        <v>49</v>
+      </c>
+      <c r="G14" s="3">
+        <v>15</v>
+      </c>
+      <c r="H14" s="3">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
+        <v>74</v>
+      </c>
+      <c r="J14" s="3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2">
+        <v>4005</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C15" s="3">
+        <v>420</v>
+      </c>
+      <c r="D15" s="3">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3">
+        <v>36</v>
+      </c>
+      <c r="F15" s="3">
+        <v>38</v>
+      </c>
+      <c r="G15" s="3">
+        <v>6</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3">
+        <v>105</v>
+      </c>
+      <c r="J15" s="3">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2">
+        <v>4005</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21457</v>
+      </c>
+      <c r="C16" s="3">
+        <v>175</v>
+      </c>
+      <c r="D16" s="3">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>18</v>
+      </c>
+      <c r="F16" s="3">
+        <v>38</v>
+      </c>
+      <c r="G16" s="3">
+        <v>5</v>
+      </c>
+      <c r="H16" s="3">
+        <v>7</v>
+      </c>
+      <c r="I16" s="3">
+        <v>60</v>
+      </c>
+      <c r="J16" s="3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2">
+        <v>4006</v>
+      </c>
+      <c r="B17" s="2">
+        <v>21523</v>
+      </c>
+      <c r="C17" s="3">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2">
+        <v>4007</v>
+      </c>
+      <c r="B18" s="2">
+        <v>21082</v>
+      </c>
+      <c r="C18" s="3">
+        <v>42</v>
+      </c>
+      <c r="D18" s="3">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3">
+        <v>79</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>89</v>
+      </c>
+      <c r="J18" s="3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2">
+        <v>4010</v>
+      </c>
+      <c r="B19" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4">
-        <v>1122</v>
-      </c>
-      <c r="D12" s="4">
-        <v>228</v>
-      </c>
-      <c r="E12" s="4">
-        <v>192</v>
-      </c>
-      <c r="F12" s="4">
-        <v>132</v>
-      </c>
-      <c r="G12" s="4">
-        <v>64</v>
-      </c>
-      <c r="H12" s="4">
-        <v>61</v>
-      </c>
-      <c r="I12" s="4">
-        <v>443</v>
-      </c>
-      <c r="J12" s="4">
-        <v>2242</v>
+      <c r="F19" s="3">
+        <v>33</v>
+      </c>
+      <c r="G19" s="3">
+        <v>5</v>
+      </c>
+      <c r="H19" s="3">
+        <v>3</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2">
+        <v>4010</v>
+      </c>
+      <c r="B20" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C20" s="3">
+        <v>136</v>
+      </c>
+      <c r="D20" s="3">
+        <v>31</v>
+      </c>
+      <c r="E20" s="3">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3">
+        <v>42</v>
+      </c>
+      <c r="G20" s="3">
+        <v>24</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2</v>
+      </c>
+      <c r="I20" s="3">
+        <v>78</v>
+      </c>
+      <c r="J20" s="3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21075</v>
+      </c>
+      <c r="C21" s="3">
+        <v>13</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>27</v>
+      </c>
+      <c r="J21" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21094</v>
+      </c>
+      <c r="C22" s="3">
+        <v>14</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <v>14</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3">
+        <v>26</v>
+      </c>
+      <c r="J22" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B23" s="2">
+        <v>21533</v>
+      </c>
+      <c r="C23" s="3">
+        <v>171</v>
+      </c>
+      <c r="D23" s="3">
+        <v>97</v>
+      </c>
+      <c r="E23" s="3">
+        <v>46</v>
+      </c>
+      <c r="F23" s="3">
+        <v>27</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>12</v>
+      </c>
+      <c r="I23" s="3">
+        <v>70</v>
+      </c>
+      <c r="J23" s="3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="4">
+        <v>1821</v>
+      </c>
+      <c r="D24" s="4">
+        <v>815</v>
+      </c>
+      <c r="E24" s="4">
+        <v>357</v>
+      </c>
+      <c r="F24" s="4">
+        <v>453</v>
+      </c>
+      <c r="G24" s="4">
+        <v>129</v>
+      </c>
+      <c r="H24" s="4">
+        <v>96</v>
+      </c>
+      <c r="I24" s="4">
+        <v>943</v>
+      </c>
+      <c r="J24" s="4">
+        <v>4614</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +2287,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1253,40 +2312,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1309,10 +2368,10 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3">
-        <v>348</v>
+        <v>92</v>
       </c>
       <c r="N2" s="3">
-        <v>363</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1335,10 +2394,10 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3">
-        <v>426</v>
+        <v>120</v>
       </c>
       <c r="N3" s="3">
-        <v>434</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1361,10 +2420,10 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3">
-        <v>371</v>
+        <v>124</v>
       </c>
       <c r="N4" s="3">
-        <v>375</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1387,10 +2446,10 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3">
-        <v>642</v>
+        <v>442</v>
       </c>
       <c r="N5" s="3">
-        <v>665</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1413,10 +2472,10 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3">
-        <v>541</v>
+        <v>369</v>
       </c>
       <c r="N6" s="3">
-        <v>561</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1439,10 +2498,10 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3">
-        <v>577</v>
+        <v>387</v>
       </c>
       <c r="N7" s="3">
-        <v>595</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1467,10 +2526,10 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>637</v>
+        <v>533</v>
       </c>
       <c r="N8" s="3">
-        <v>649</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1493,10 +2552,10 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>313</v>
+        <v>251</v>
       </c>
       <c r="N9" s="3">
-        <v>318</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1521,10 +2580,10 @@
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3">
-        <v>379</v>
+        <v>291</v>
       </c>
       <c r="N10" s="3">
-        <v>396</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1541,14 +2600,14 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3">
-        <v>379</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1565,7 +2624,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1574,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3">
-        <v>187</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1591,14 +2650,14 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1615,14 +2674,14 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3">
-        <v>287</v>
+        <v>211</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3">
-        <v>287</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1639,14 +2698,14 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>421</v>
+        <v>332</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3">
-        <v>421</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1663,7 +2722,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3">
-        <v>379</v>
+        <v>289</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3">
@@ -1672,7 +2731,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3">
-        <v>381</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1763,12 +2822,12 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1787,12 +2846,12 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3">
-        <v>146</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1811,12 +2870,12 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3">
-        <v>125</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1978,13 +3037,13 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3">
-        <v>521</v>
+        <v>181</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3">
-        <v>521</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2004,13 +3063,13 @@
         <v>1</v>
       </c>
       <c r="J30" s="3">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3">
-        <v>137</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2028,13 +3087,13 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2042,7 +3101,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="2">
-        <v>60137</v>
+        <v>60130</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -2052,13 +3111,13 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3">
-        <v>9</v>
+        <v>244</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3">
-        <v>9</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2066,7 +3125,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="2">
-        <v>60138</v>
+        <v>60131</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -2074,15 +3133,17 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="I33" s="3">
+        <v>4</v>
+      </c>
       <c r="J33" s="3">
-        <v>468</v>
+        <v>342</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3">
-        <v>468</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2090,7 +3151,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="2">
-        <v>60202</v>
+        <v>60138</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -2100,13 +3161,13 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3">
-        <v>7</v>
+        <v>378</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3">
-        <v>7</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2114,7 +3175,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>60131</v>
+        <v>60137</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -2122,17 +3183,15 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="3">
-        <v>4</v>
-      </c>
+      <c r="I35" s="3"/>
       <c r="J35" s="3">
-        <v>393</v>
+        <v>9</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3">
-        <v>397</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2140,7 +3199,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="2">
-        <v>60496</v>
+        <v>60202</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -2150,13 +3209,13 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2164,7 +3223,7 @@
         <v>12</v>
       </c>
       <c r="B37" s="2">
-        <v>60507</v>
+        <v>60496</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -2174,13 +3233,13 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2194,7 +3253,7 @@
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -2206,7 +3265,7 @@
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3">
-        <v>140</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2220,7 +3279,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -2232,7 +3291,7 @@
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2246,7 +3305,7 @@
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -2258,7 +3317,7 @@
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2272,7 +3331,7 @@
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
@@ -2284,7 +3343,7 @@
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3">
-        <v>122</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2298,7 +3357,7 @@
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -2310,7 +3369,7 @@
       </c>
       <c r="M42" s="3"/>
       <c r="N42" s="3">
-        <v>142</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2324,7 +3383,7 @@
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -2336,7 +3395,7 @@
       </c>
       <c r="M43" s="3"/>
       <c r="N43" s="3">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2425,7 +3484,7 @@
         <v>60224</v>
       </c>
       <c r="C47" s="3">
-        <v>295</v>
+        <v>96</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3">
@@ -2440,7 +3499,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3">
-        <v>297</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2451,7 +3510,7 @@
         <v>60227</v>
       </c>
       <c r="C48" s="3">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2464,7 +3523,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3">
-        <v>132</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2475,7 +3534,7 @@
         <v>60448</v>
       </c>
       <c r="C49" s="3">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2488,7 +3547,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2499,7 +3558,7 @@
         <v>60129</v>
       </c>
       <c r="C50" s="3">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2512,7 +3571,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3">
-        <v>330</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2523,7 +3582,7 @@
         <v>60131</v>
       </c>
       <c r="C51" s="3">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3">
@@ -2538,7 +3597,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3">
-        <v>330</v>
+        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2549,7 +3608,7 @@
         <v>60138</v>
       </c>
       <c r="C52" s="3">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -2562,7 +3621,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3">
-        <v>379</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -2670,14 +3729,14 @@
         <v>19</v>
       </c>
       <c r="B57" s="2">
-        <v>60128</v>
+        <v>60129</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -2686,7 +3745,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -2694,7 +3753,7 @@
         <v>19</v>
       </c>
       <c r="B58" s="2">
-        <v>60129</v>
+        <v>60131</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -2718,14 +3777,14 @@
         <v>19</v>
       </c>
       <c r="B59" s="2">
-        <v>60130</v>
+        <v>60134</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -2734,7 +3793,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -2742,14 +3801,14 @@
         <v>19</v>
       </c>
       <c r="B60" s="2">
-        <v>60131</v>
+        <v>60135</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2758,7 +3817,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -2766,14 +3825,14 @@
         <v>19</v>
       </c>
       <c r="B61" s="2">
-        <v>60132</v>
+        <v>60138</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2782,7 +3841,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -2790,14 +3849,14 @@
         <v>19</v>
       </c>
       <c r="B62" s="2">
-        <v>60134</v>
+        <v>60139</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -2806,7 +3865,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -2814,14 +3873,14 @@
         <v>19</v>
       </c>
       <c r="B63" s="2">
-        <v>60135</v>
+        <v>60306</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -2830,7 +3889,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -2838,14 +3897,14 @@
         <v>19</v>
       </c>
       <c r="B64" s="2">
-        <v>60138</v>
+        <v>60448</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2854,84 +3913,86 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B65" s="2">
-        <v>60139</v>
+        <v>60129</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
-      <c r="G65" s="3">
-        <v>11</v>
-      </c>
+      <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
+      <c r="L65" s="3">
+        <v>46</v>
+      </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B66" s="2">
-        <v>60140</v>
+        <v>60131</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="3">
-        <v>8</v>
-      </c>
-      <c r="H66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3">
+        <v>1</v>
+      </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
+      <c r="L66" s="3">
+        <v>33</v>
+      </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B67" s="2">
-        <v>60272</v>
+        <v>60215</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="3">
-        <v>1</v>
-      </c>
+      <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
+      <c r="L67" s="3">
+        <v>10</v>
+      </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B68" s="2">
         <v>60296</v>
@@ -2940,97 +4001,99 @@
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="3">
-        <v>15</v>
-      </c>
+      <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
+      <c r="L68" s="3">
+        <v>38</v>
+      </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B69" s="2">
-        <v>60306</v>
+        <v>60496</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3">
-        <v>6</v>
-      </c>
+      <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
+      <c r="L69" s="3">
+        <v>10</v>
+      </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B70" s="2">
-        <v>60448</v>
+        <v>60507</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3">
-        <v>4</v>
-      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
+      <c r="L70" s="3">
+        <v>10</v>
+      </c>
       <c r="M70" s="3"/>
       <c r="N70" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B71" s="2">
-        <v>60510</v>
+        <v>60127</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="3">
-        <v>10</v>
-      </c>
-      <c r="H71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3">
+        <v>2</v>
+      </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
+      <c r="L71" s="3">
+        <v>32</v>
+      </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B72" s="2">
-        <v>60138</v>
+        <v>60128</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -3042,19 +4105,19 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B73" s="2">
-        <v>60202</v>
+        <v>60130</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
@@ -3066,43 +4129,45 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B74" s="2">
-        <v>60224</v>
+        <v>60132</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
+      <c r="H74" s="3">
+        <v>2</v>
+      </c>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B75" s="2">
-        <v>60227</v>
+        <v>60134</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
@@ -3114,19 +4179,19 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B76" s="2">
-        <v>60448</v>
+        <v>60135</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
@@ -3138,69 +4203,69 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B77" s="2">
-        <v>60129</v>
+        <v>60139</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
+      <c r="H77" s="3">
+        <v>1</v>
+      </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B78" s="2">
-        <v>60131</v>
+        <v>60140</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3">
-        <v>1</v>
-      </c>
+      <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B79" s="2">
-        <v>60215</v>
+        <v>60272</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
@@ -3212,19 +4277,19 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B80" s="2">
-        <v>60296</v>
+        <v>60306</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -3236,19 +4301,19 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B81" s="2">
-        <v>60496</v>
+        <v>60355</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
@@ -3260,19 +4325,19 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B82" s="2">
-        <v>60507</v>
+        <v>60510</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -3284,48 +4349,50 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B83" s="2">
-        <v>60127</v>
+        <v>60130</v>
       </c>
       <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
+      <c r="D83" s="3">
+        <v>15</v>
+      </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
-      <c r="H83" s="3">
-        <v>2</v>
-      </c>
+      <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
-      <c r="L83" s="3">
-        <v>32</v>
-      </c>
-      <c r="M83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3">
+        <v>328</v>
+      </c>
       <c r="N83" s="3">
-        <v>34</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B84" s="2">
-        <v>60128</v>
+        <v>60272</v>
       </c>
       <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+      <c r="D84" s="3">
+        <v>2</v>
+      </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -3333,20 +4400,20 @@
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
-      <c r="L84" s="3">
-        <v>56</v>
-      </c>
-      <c r="M84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3">
+        <v>261</v>
+      </c>
       <c r="N84" s="3">
-        <v>56</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B85" s="2">
-        <v>60130</v>
+        <v>60510</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
@@ -3356,47 +4423,49 @@
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3">
-        <v>39</v>
-      </c>
-      <c r="M85" s="3"/>
+      <c r="K85" s="3">
+        <v>1</v>
+      </c>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3">
+        <v>146</v>
+      </c>
       <c r="N85" s="3">
-        <v>39</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B86" s="2">
-        <v>60132</v>
+        <v>60127</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3">
-        <v>2</v>
-      </c>
-      <c r="I86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3">
+        <v>338</v>
+      </c>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
-      <c r="L86" s="3">
-        <v>41</v>
-      </c>
-      <c r="M86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3">
+        <v>1</v>
+      </c>
       <c r="N86" s="3">
-        <v>43</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B87" s="2">
-        <v>60134</v>
+        <v>60128</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
@@ -3404,23 +4473,23 @@
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+      <c r="I87" s="3">
+        <v>152</v>
+      </c>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
-      <c r="L87" s="3">
-        <v>24</v>
-      </c>
+      <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="3">
-        <v>24</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B88" s="2">
-        <v>60135</v>
+        <v>60296</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -3428,49 +4497,49 @@
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
+      <c r="I88" s="3">
+        <v>499</v>
+      </c>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
-      <c r="L88" s="3">
-        <v>24</v>
-      </c>
-      <c r="M88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3">
+        <v>1</v>
+      </c>
       <c r="N88" s="3">
-        <v>24</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B89" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="3">
-        <v>1</v>
-      </c>
+      <c r="H89" s="3"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3">
-        <v>51</v>
-      </c>
+      <c r="K89" s="3">
+        <v>100</v>
+      </c>
+      <c r="L89" s="3"/>
       <c r="M89" s="3"/>
       <c r="N89" s="3">
-        <v>52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B90" s="2">
-        <v>60140</v>
+        <v>60272</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
@@ -3480,21 +4549,21 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3">
-        <v>4</v>
-      </c>
+      <c r="K90" s="3">
+        <v>83</v>
+      </c>
+      <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B91" s="2">
-        <v>60272</v>
+        <v>60510</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
@@ -3504,66 +4573,70 @@
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3">
-        <v>39</v>
-      </c>
+      <c r="K91" s="3">
+        <v>41</v>
+      </c>
+      <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B92" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3">
+        <v>74</v>
+      </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3">
-        <v>15</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B93" s="2">
-        <v>60355</v>
+        <v>60272</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3">
+        <v>36</v>
+      </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B94" s="2">
         <v>60510</v>
@@ -3571,78 +4644,76 @@
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3">
+        <v>73</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="3">
-        <v>16</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B95" s="2">
-        <v>60130</v>
+        <v>60127</v>
       </c>
       <c r="C95" s="3"/>
-      <c r="D95" s="3">
-        <v>15</v>
-      </c>
+      <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
+      <c r="J95" s="3">
+        <v>285</v>
+      </c>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-      <c r="M95" s="3">
-        <v>328</v>
-      </c>
+      <c r="M95" s="3"/>
       <c r="N95" s="3">
-        <v>343</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B96" s="2">
-        <v>60272</v>
+        <v>60129</v>
       </c>
       <c r="C96" s="3"/>
-      <c r="D96" s="3">
-        <v>2</v>
-      </c>
+      <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
+      <c r="J96" s="3">
+        <v>419</v>
+      </c>
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
-      <c r="M96" s="3">
-        <v>261</v>
-      </c>
+      <c r="M96" s="3"/>
       <c r="N96" s="3">
-        <v>263</v>
+        <v>419</v>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B97" s="2">
-        <v>60510</v>
+        <v>60296</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
@@ -3651,24 +4722,22 @@
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3">
-        <v>1</v>
-      </c>
+      <c r="J97" s="3">
+        <v>313</v>
+      </c>
+      <c r="K97" s="3"/>
       <c r="L97" s="3"/>
-      <c r="M97" s="3">
-        <v>146</v>
-      </c>
+      <c r="M97" s="3"/>
       <c r="N97" s="3">
-        <v>147</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B98" s="2">
-        <v>60127</v>
+        <v>60128</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -3676,25 +4745,23 @@
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="3">
-        <v>338</v>
-      </c>
-      <c r="J98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3">
+        <v>230</v>
+      </c>
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
-      <c r="M98" s="3">
-        <v>1</v>
-      </c>
+      <c r="M98" s="3"/>
       <c r="N98" s="3">
-        <v>339</v>
+        <v>230</v>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B99" s="2">
-        <v>60128</v>
+        <v>60272</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
@@ -3702,23 +4769,23 @@
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
-      <c r="I99" s="3">
-        <v>152</v>
-      </c>
-      <c r="J99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3">
+        <v>125</v>
+      </c>
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
       <c r="N99" s="3">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B100" s="2">
-        <v>60296</v>
+        <v>60510</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -3726,51 +4793,53 @@
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
-      <c r="I100" s="3">
-        <v>499</v>
-      </c>
-      <c r="J100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3">
+        <v>132</v>
+      </c>
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
-      <c r="M100" s="3">
-        <v>1</v>
-      </c>
+      <c r="M100" s="3"/>
       <c r="N100" s="3">
-        <v>500</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B101" s="2">
         <v>60130</v>
       </c>
-      <c r="C101" s="3"/>
+      <c r="C101" s="3">
+        <v>246</v>
+      </c>
       <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
+      <c r="E101" s="3">
+        <v>1</v>
+      </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
-      <c r="K101" s="3">
-        <v>100</v>
-      </c>
+      <c r="K101" s="3"/>
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
       <c r="N101" s="3">
-        <v>100</v>
+        <v>247</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B102" s="2">
         <v>60272</v>
       </c>
-      <c r="C102" s="3"/>
+      <c r="C102" s="3">
+        <v>49</v>
+      </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -3778,575 +4847,79 @@
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
-      <c r="K102" s="3">
-        <v>83</v>
-      </c>
+      <c r="K102" s="3"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B103" s="2">
         <v>60510</v>
       </c>
-      <c r="C103" s="3"/>
+      <c r="C103" s="3">
+        <v>147</v>
+      </c>
       <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
+      <c r="E103" s="3">
+        <v>2</v>
+      </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
-      <c r="K103" s="3">
-        <v>41</v>
-      </c>
+      <c r="K103" s="3"/>
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
       <c r="N103" s="3">
-        <v>41</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:14">
-      <c r="A104" s="2">
-        <v>30</v>
-      </c>
-      <c r="B104" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3">
-        <v>70</v>
-      </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3">
-        <v>24</v>
-      </c>
-      <c r="M104" s="3"/>
-      <c r="N104" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
-      <c r="A105" s="2">
-        <v>30</v>
-      </c>
-      <c r="B105" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3">
-        <v>33</v>
-      </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
-      <c r="L105" s="3">
-        <v>20</v>
-      </c>
-      <c r="M105" s="3"/>
-      <c r="N105" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
-      <c r="A106" s="2">
-        <v>30</v>
-      </c>
-      <c r="B106" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3">
-        <v>73</v>
-      </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
-      <c r="L106" s="3">
-        <v>20</v>
-      </c>
-      <c r="M106" s="3"/>
-      <c r="N106" s="3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
-      <c r="A107" s="2">
-        <v>31</v>
-      </c>
-      <c r="B107" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3"/>
-      <c r="J107" s="3">
-        <v>285</v>
-      </c>
-      <c r="K107" s="3"/>
-      <c r="L107" s="3"/>
-      <c r="M107" s="3"/>
-      <c r="N107" s="3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
-      <c r="A108" s="2">
-        <v>31</v>
-      </c>
-      <c r="B108" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3"/>
-      <c r="J108" s="3">
-        <v>419</v>
-      </c>
-      <c r="K108" s="3"/>
-      <c r="L108" s="3"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="3">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
-      <c r="A109" s="2">
-        <v>31</v>
-      </c>
-      <c r="B109" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3">
-        <v>313</v>
-      </c>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
-      <c r="A110" s="2">
-        <v>32</v>
-      </c>
-      <c r="B110" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3">
-        <v>230</v>
-      </c>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
-      <c r="A111" s="2">
-        <v>32</v>
-      </c>
-      <c r="B111" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3">
-        <v>125</v>
-      </c>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
-      <c r="A112" s="2">
-        <v>32</v>
-      </c>
-      <c r="B112" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3">
-        <v>132</v>
-      </c>
-      <c r="K112" s="3"/>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" s="2">
-        <v>33</v>
-      </c>
-      <c r="B113" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C113" s="3">
-        <v>246</v>
-      </c>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3">
-        <v>1</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="A114" s="2">
-        <v>33</v>
-      </c>
-      <c r="B114" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C114" s="3">
-        <v>49</v>
-      </c>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="3"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
-      <c r="A115" s="2">
-        <v>33</v>
-      </c>
-      <c r="B115" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C115" s="3">
-        <v>147</v>
-      </c>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3">
-        <v>2</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" s="2">
-        <v>34</v>
-      </c>
-      <c r="B116" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3">
-        <v>1</v>
-      </c>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3">
-        <v>170</v>
-      </c>
-      <c r="N116" s="3">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
-      <c r="A117" s="2">
-        <v>36</v>
-      </c>
-      <c r="B117" s="2">
-        <v>60132</v>
-      </c>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3">
-        <v>24</v>
-      </c>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="3"/>
-      <c r="M117" s="3">
-        <v>1056</v>
-      </c>
-      <c r="N117" s="3">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
-      <c r="A118" s="2">
+      <c r="A104" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" s="4">
+        <v>2258</v>
+      </c>
+      <c r="D104" s="4">
+        <v>136</v>
+      </c>
+      <c r="E104" s="4">
+        <v>15</v>
+      </c>
+      <c r="F104" s="4">
+        <v>690</v>
+      </c>
+      <c r="G104" s="4">
         <v>37</v>
       </c>
-      <c r="B118" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3">
-        <v>8</v>
-      </c>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3">
-        <v>541</v>
-      </c>
-      <c r="N118" s="3">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
-      <c r="A119" s="2">
-        <v>38</v>
-      </c>
-      <c r="B119" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3">
-        <v>4</v>
-      </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
-      <c r="A120" s="2">
-        <v>38</v>
-      </c>
-      <c r="B120" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3">
-        <v>3</v>
-      </c>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" s="2">
-        <v>59</v>
-      </c>
-      <c r="B121" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="3"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3">
-        <v>39</v>
-      </c>
-      <c r="L121" s="3"/>
-      <c r="M121" s="3"/>
-      <c r="N121" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
-      <c r="A122" s="2">
-        <v>59</v>
-      </c>
-      <c r="B122" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="3"/>
-      <c r="J122" s="3"/>
-      <c r="K122" s="3">
-        <v>9</v>
-      </c>
-      <c r="L122" s="3"/>
-      <c r="M122" s="3"/>
-      <c r="N122" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="A123" s="2">
-        <v>59</v>
-      </c>
-      <c r="B123" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="3"/>
-      <c r="J123" s="3"/>
-      <c r="K123" s="3">
-        <v>14</v>
-      </c>
-      <c r="L123" s="3"/>
-      <c r="M123" s="3"/>
-      <c r="N123" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
-      <c r="A124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B124" s="2"/>
-      <c r="C124" s="4">
-        <v>2698</v>
-      </c>
-      <c r="D124" s="4">
-        <v>168</v>
-      </c>
-      <c r="E124" s="4">
-        <v>15</v>
-      </c>
-      <c r="F124" s="4">
-        <v>945</v>
-      </c>
-      <c r="G124" s="4">
-        <v>115</v>
-      </c>
-      <c r="H124" s="4">
+      <c r="H104" s="4">
         <v>6</v>
       </c>
-      <c r="I124" s="4">
-        <v>3196</v>
-      </c>
-      <c r="J124" s="4">
-        <v>3099</v>
-      </c>
-      <c r="K124" s="4">
-        <v>1498</v>
-      </c>
-      <c r="L124" s="4">
-        <v>934</v>
-      </c>
-      <c r="M124" s="4">
-        <v>6739</v>
-      </c>
-      <c r="N124" s="4">
-        <v>19413</v>
+      <c r="I104" s="4">
+        <v>2558</v>
+      </c>
+      <c r="J104" s="4">
+        <v>2752</v>
+      </c>
+      <c r="K104" s="4">
+        <v>1233</v>
+      </c>
+      <c r="L104" s="4">
+        <v>798</v>
+      </c>
+      <c r="M104" s="4">
+        <v>3347</v>
+      </c>
+      <c r="N104" s="4">
+        <v>13830</v>
       </c>
     </row>
   </sheetData>
@@ -4356,15 +4929,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="8" width="7.7109375" customWidth="1"/>
+    <col min="3" max="7" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4372,86 +4945,63 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>2000</v>
       </c>
       <c r="B2" s="2">
         <v>21088</v>
       </c>
-      <c r="C2" s="3">
-        <v>19</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>177</v>
-      </c>
-      <c r="E2" s="3">
-        <v>16</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>2000</v>
       </c>
       <c r="B3" s="2">
         <v>21469</v>
       </c>
-      <c r="C3" s="3">
-        <v>13</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>230</v>
-      </c>
-      <c r="E3" s="3">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3">
-        <v>3</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>2001</v>
       </c>
       <c r="B4" s="2">
         <v>21176</v>
       </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3">
         <v>65</v>
       </c>
@@ -4459,16 +5009,13 @@
         <v>11</v>
       </c>
       <c r="F4" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>2001</v>
       </c>
@@ -4476,7 +5023,7 @@
         <v>21229</v>
       </c>
       <c r="C5" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3">
         <v>166</v>
@@ -4485,16 +5032,13 @@
         <v>19</v>
       </c>
       <c r="F5" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3">
-        <v>14</v>
-      </c>
-      <c r="H5" s="3">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>2002</v>
       </c>
@@ -4512,39 +5056,29 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>3</v>
-      </c>
-      <c r="H6" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>2003</v>
       </c>
       <c r="B7" s="2">
         <v>21087</v>
       </c>
-      <c r="C7" s="3">
-        <v>17</v>
-      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3">
         <v>171</v>
       </c>
       <c r="E7" s="3">
         <v>107</v>
       </c>
-      <c r="F7" s="3">
-        <v>6</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>20</v>
-      </c>
-      <c r="H7" s="3">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>2004</v>
       </c>
@@ -4561,16 +5095,13 @@
         <v>24</v>
       </c>
       <c r="F8" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3">
-        <v>28</v>
-      </c>
-      <c r="H8" s="3">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="2">
         <v>2004</v>
       </c>
@@ -4586,15 +5117,14 @@
       <c r="E9" s="3">
         <v>5</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>7</v>
+      </c>
       <c r="G9" s="3">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>2005</v>
       </c>
@@ -4610,15 +5140,14 @@
       <c r="E10" s="3">
         <v>10</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
       <c r="G10" s="3">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11" s="2">
         <v>2005</v>
       </c>
@@ -4634,15 +5163,14 @@
       <c r="E11" s="3">
         <v>18</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3">
+        <v>17</v>
+      </c>
       <c r="G11" s="3">
-        <v>17</v>
-      </c>
-      <c r="H11" s="3">
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>2006</v>
       </c>
@@ -4658,15 +5186,14 @@
       <c r="E12" s="3">
         <v>4</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
       <c r="G12" s="3">
-        <v>2</v>
-      </c>
-      <c r="H12" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13" s="2">
         <v>2007</v>
       </c>
@@ -4682,15 +5209,14 @@
       <c r="E13" s="3">
         <v>12</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3">
+        <v>16</v>
+      </c>
       <c r="G13" s="3">
-        <v>16</v>
-      </c>
-      <c r="H13" s="3">
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14" s="2">
         <v>2007</v>
       </c>
@@ -4706,15 +5232,14 @@
       <c r="E14" s="3">
         <v>11</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3">
+        <v>13</v>
+      </c>
       <c r="G14" s="3">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15" s="2">
         <v>2008</v>
       </c>
@@ -4730,15 +5255,14 @@
       <c r="E15" s="3">
         <v>19</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3">
+        <v>32</v>
+      </c>
       <c r="G15" s="3">
-        <v>32</v>
-      </c>
-      <c r="H15" s="3">
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16" s="2">
         <v>2008</v>
       </c>
@@ -4754,15 +5278,14 @@
       <c r="E16" s="3">
         <v>5</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3">
+        <v>6</v>
+      </c>
       <c r="G16" s="3">
-        <v>6</v>
-      </c>
-      <c r="H16" s="3">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17" s="2">
         <v>2009</v>
       </c>
@@ -4778,15 +5301,14 @@
       <c r="E17" s="3">
         <v>16</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3">
+        <v>11</v>
+      </c>
       <c r="G17" s="3">
-        <v>11</v>
-      </c>
-      <c r="H17" s="3">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -4802,36 +5324,66 @@
       <c r="E18" s="3">
         <v>13</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3">
+        <v>6</v>
+      </c>
       <c r="G18" s="3">
-        <v>6</v>
-      </c>
-      <c r="H18" s="3">
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="4">
-        <v>294</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1856</v>
-      </c>
-      <c r="E19" s="4">
-        <v>322</v>
-      </c>
-      <c r="F19" s="4">
-        <v>16</v>
-      </c>
-      <c r="G19" s="4">
-        <v>241</v>
-      </c>
-      <c r="H19" s="4">
-        <v>2729</v>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B19" s="2">
+        <v>21195</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B20" s="2">
+        <v>21246</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="4">
+        <v>210</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1738</v>
+      </c>
+      <c r="E21" s="4">
+        <v>285</v>
+      </c>
+      <c r="F21" s="4">
+        <v>178</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2411</v>
       </c>
     </row>
   </sheetData>
@@ -4841,15 +5393,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4857,15 +5411,91 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="B2" s="2">
+        <v>17056</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B3" s="2">
+        <v>17168</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>5002</v>
+      </c>
+      <c r="B4" s="2">
+        <v>17183</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>53</v>
+      </c>
+      <c r="E4" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>5003</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21094</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>109</v>
+      </c>
+      <c r="E6" s="4">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4874,18 +5504,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="6" width="9.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="12" width="7.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="13" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4893,37 +5524,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>46</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
         <v>3000</v>
       </c>
@@ -4933,33 +5567,30 @@
       <c r="C2" s="3">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
-        <v>14</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3">
         <v>21</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>87</v>
-      </c>
-      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3">
         <v>171</v>
       </c>
-      <c r="I2" s="3">
-        <v>53</v>
-      </c>
       <c r="J2" s="3">
-        <v>44</v>
-      </c>
-      <c r="K2" s="3">
+        <v>11</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3">
         <v>12</v>
       </c>
-      <c r="L2" s="3">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
         <v>3000</v>
       </c>
@@ -4969,33 +5600,28 @@
       <c r="C3" s="3">
         <v>13</v>
       </c>
-      <c r="D3" s="3">
-        <v>22</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3">
         <v>26</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>65</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
         <v>214</v>
       </c>
-      <c r="I3" s="3">
-        <v>31</v>
-      </c>
       <c r="J3" s="3">
-        <v>42</v>
-      </c>
-      <c r="K3" s="3">
+        <v>3</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
         <v>7</v>
       </c>
-      <c r="L3" s="3">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
         <v>3001</v>
       </c>
@@ -5006,34 +5632,31 @@
         <v>7</v>
       </c>
       <c r="D4" s="3">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3">
         <v>22</v>
       </c>
-      <c r="F4" s="3">
-        <v>95</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3">
         <v>119</v>
       </c>
-      <c r="H4" s="3">
-        <v>213</v>
-      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="J4" s="3">
-        <v>88</v>
-      </c>
-      <c r="K4" s="3">
+        <v>61</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>18</v>
       </c>
-      <c r="L4" s="3">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="3">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>3001</v>
       </c>
@@ -5044,34 +5667,33 @@
         <v>10</v>
       </c>
       <c r="D5" s="3">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3">
         <v>29</v>
       </c>
-      <c r="F5" s="3">
-        <v>53</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3">
         <v>71</v>
       </c>
-      <c r="H5" s="3">
-        <v>53</v>
-      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="J5" s="3">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="K5" s="3">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3">
         <v>13</v>
       </c>
-      <c r="L5" s="3">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
         <v>3002</v>
       </c>
@@ -5081,35 +5703,32 @@
       <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
-        <v>32</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3">
         <v>10</v>
       </c>
-      <c r="F6" s="3">
-        <v>30</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3">
         <v>27</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3">
         <v>30</v>
       </c>
-      <c r="I6" s="3">
-        <v>87</v>
-      </c>
       <c r="J6" s="3">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="K6" s="3">
+        <v>22</v>
+      </c>
+      <c r="L6" s="3">
         <v>1</v>
       </c>
-      <c r="L6" s="3">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
         <v>3002</v>
       </c>
@@ -5119,68 +5738,672 @@
       <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="3">
-        <v>72</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3">
         <v>12</v>
       </c>
-      <c r="F7" s="3">
-        <v>68</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
         <v>58</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3">
         <v>43</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
+        <v>46</v>
+      </c>
+      <c r="K7" s="3">
+        <v>43</v>
+      </c>
+      <c r="L7" s="3">
+        <v>6</v>
+      </c>
+      <c r="M7" s="3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="2">
+        <v>3003</v>
+      </c>
+      <c r="B8" s="2">
+        <v>30095</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
+        <v>139</v>
+      </c>
+      <c r="J8" s="3">
+        <v>475</v>
+      </c>
+      <c r="K8" s="3">
+        <v>136</v>
+      </c>
+      <c r="L8" s="3">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="2">
+        <v>3003</v>
+      </c>
+      <c r="B9" s="2">
+        <v>39906</v>
+      </c>
+      <c r="C9" s="3">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33</v>
+      </c>
+      <c r="G9" s="3">
+        <v>18</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>82</v>
+      </c>
+      <c r="J9" s="3">
+        <v>40</v>
+      </c>
+      <c r="K9" s="3">
+        <v>92</v>
+      </c>
+      <c r="L9" s="3">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="2">
+        <v>3004</v>
+      </c>
+      <c r="B10" s="2">
+        <v>21082</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>147</v>
+      </c>
+      <c r="E10" s="3">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3">
+        <v>94</v>
+      </c>
+      <c r="G10" s="3">
+        <v>79</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3">
         <v>169</v>
       </c>
-      <c r="J7" s="3">
-        <v>120</v>
-      </c>
-      <c r="K7" s="3">
+      <c r="J10" s="3">
+        <v>132</v>
+      </c>
+      <c r="K10" s="3">
+        <v>172</v>
+      </c>
+      <c r="L10" s="3">
+        <v>13</v>
+      </c>
+      <c r="M10" s="3">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="2">
+        <v>3004</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C11" s="3">
         <v>6</v>
       </c>
-      <c r="L7" s="3">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="2" t="s">
+      <c r="D11" s="3">
+        <v>118</v>
+      </c>
+      <c r="E11" s="3">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3">
+        <v>54</v>
+      </c>
+      <c r="G11" s="3">
+        <v>51</v>
+      </c>
+      <c r="H11" s="3">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3">
+        <v>69</v>
+      </c>
+      <c r="J11" s="3">
+        <v>135</v>
+      </c>
+      <c r="K11" s="3">
+        <v>184</v>
+      </c>
+      <c r="L11" s="3">
+        <v>9</v>
+      </c>
+      <c r="M11" s="3">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="2">
+        <v>3006</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21083</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
+        <v>205</v>
+      </c>
+      <c r="J12" s="3">
+        <v>85</v>
+      </c>
+      <c r="K12" s="3">
+        <v>62</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="2">
+        <v>3006</v>
+      </c>
+      <c r="B13" s="2">
+        <v>21457</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3">
+        <v>15</v>
+      </c>
+      <c r="F13" s="3">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="4">
-        <v>40</v>
-      </c>
-      <c r="D8" s="4">
-        <v>437</v>
-      </c>
-      <c r="E8" s="4">
-        <v>120</v>
-      </c>
-      <c r="F8" s="4">
-        <v>246</v>
-      </c>
-      <c r="G8" s="4">
-        <v>427</v>
-      </c>
-      <c r="H8" s="4">
-        <v>724</v>
-      </c>
-      <c r="I8" s="4">
-        <v>581</v>
-      </c>
-      <c r="J8" s="4">
-        <v>454</v>
-      </c>
-      <c r="K8" s="4">
-        <v>57</v>
-      </c>
-      <c r="L8" s="4">
-        <v>3086</v>
+      <c r="G13" s="3">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3</v>
+      </c>
+      <c r="I13" s="3">
+        <v>24</v>
+      </c>
+      <c r="J13" s="3">
+        <v>42</v>
+      </c>
+      <c r="K13" s="3">
+        <v>66</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="2">
+        <v>3008</v>
+      </c>
+      <c r="B14" s="2">
+        <v>21081</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>9</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="2">
+        <v>3008</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3">
+        <v>92</v>
+      </c>
+      <c r="E15" s="3">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>77</v>
+      </c>
+      <c r="G15" s="3">
+        <v>48</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3">
+        <v>38</v>
+      </c>
+      <c r="J15" s="3">
+        <v>123</v>
+      </c>
+      <c r="K15" s="3">
+        <v>110</v>
+      </c>
+      <c r="L15" s="3">
+        <v>7</v>
+      </c>
+      <c r="M15" s="3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="2">
+        <v>3008</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21515</v>
+      </c>
+      <c r="C16" s="3">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3">
+        <v>41</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>13</v>
+      </c>
+      <c r="G16" s="3">
+        <v>8</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3">
+        <v>5</v>
+      </c>
+      <c r="J16" s="3">
+        <v>30</v>
+      </c>
+      <c r="K16" s="3">
+        <v>33</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2">
+        <v>3009</v>
+      </c>
+      <c r="B17" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>62</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3">
+        <v>83</v>
+      </c>
+      <c r="G17" s="3">
+        <v>58</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3">
+        <v>184</v>
+      </c>
+      <c r="J17" s="3">
+        <v>145</v>
+      </c>
+      <c r="K17" s="3">
+        <v>85</v>
+      </c>
+      <c r="L17" s="3">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2">
+        <v>3009</v>
+      </c>
+      <c r="B18" s="2">
+        <v>21533</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>117</v>
+      </c>
+      <c r="E18" s="3">
+        <v>35</v>
+      </c>
+      <c r="F18" s="3">
+        <v>74</v>
+      </c>
+      <c r="G18" s="3">
+        <v>59</v>
+      </c>
+      <c r="H18" s="3">
+        <v>6</v>
+      </c>
+      <c r="I18" s="3">
+        <v>303</v>
+      </c>
+      <c r="J18" s="3">
+        <v>74</v>
+      </c>
+      <c r="K18" s="3">
+        <v>127</v>
+      </c>
+      <c r="L18" s="3">
+        <v>9</v>
+      </c>
+      <c r="M18" s="3">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="2">
+        <v>3010</v>
+      </c>
+      <c r="B19" s="2">
+        <v>21075</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
+        <v>21</v>
+      </c>
+      <c r="E19" s="3">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
+        <v>43</v>
+      </c>
+      <c r="J19" s="3">
+        <v>19</v>
+      </c>
+      <c r="K19" s="3">
+        <v>23</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="2">
+        <v>3010</v>
+      </c>
+      <c r="B20" s="2">
+        <v>30923</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3">
+        <v>42</v>
+      </c>
+      <c r="J20" s="3">
+        <v>47</v>
+      </c>
+      <c r="K20" s="3">
+        <v>77</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="2">
+        <v>3011</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21212</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3">
+        <v>20</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="2">
+        <v>3012</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21089</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>18</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3">
+        <v>27</v>
+      </c>
+      <c r="G22" s="3">
+        <v>19</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>30</v>
+      </c>
+      <c r="J22" s="3">
+        <v>48</v>
+      </c>
+      <c r="K22" s="3">
+        <v>44</v>
+      </c>
+      <c r="L22" s="3">
+        <v>2</v>
+      </c>
+      <c r="M22" s="3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="2">
+        <v>3012</v>
+      </c>
+      <c r="B23" s="2">
+        <v>21090</v>
+      </c>
+      <c r="C23" s="3">
+        <v>9</v>
+      </c>
+      <c r="D23" s="3">
+        <v>117</v>
+      </c>
+      <c r="E23" s="3">
+        <v>21</v>
+      </c>
+      <c r="F23" s="3">
+        <v>32</v>
+      </c>
+      <c r="G23" s="3">
+        <v>55</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3">
+        <v>36</v>
+      </c>
+      <c r="J23" s="3">
+        <v>74</v>
+      </c>
+      <c r="K23" s="3">
+        <v>144</v>
+      </c>
+      <c r="L23" s="3">
+        <v>7</v>
+      </c>
+      <c r="M23" s="3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="4">
+        <v>132</v>
+      </c>
+      <c r="D24" s="4">
+        <v>932</v>
+      </c>
+      <c r="E24" s="4">
+        <v>296</v>
+      </c>
+      <c r="F24" s="4">
+        <v>640</v>
+      </c>
+      <c r="G24" s="4">
+        <v>717</v>
+      </c>
+      <c r="H24" s="4">
+        <v>36</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2063</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1646</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1431</v>
+      </c>
+      <c r="L24" s="4">
+        <v>125</v>
+      </c>
+      <c r="M24" s="4">
+        <v>8018</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="44">
   <si>
     <t>WAVE_NBR</t>
   </si>
@@ -46,15 +46,6 @@
   </si>
   <si>
     <t>BSECOM</t>
-  </si>
-  <si>
-    <t>BSLIQ</t>
-  </si>
-  <si>
-    <t>BSNUF1</t>
-  </si>
-  <si>
-    <t>BSNUF2</t>
   </si>
   <si>
     <t>BSTOY1</t>
@@ -96,9 +87,6 @@
     <t>MFTA</t>
   </si>
   <si>
-    <t>MHOM</t>
-  </si>
-  <si>
     <t>MHOM1</t>
   </si>
   <si>
@@ -124,6 +112,9 @@
   </si>
   <si>
     <t>SMLAD</t>
+  </si>
+  <si>
+    <t>SMLUG</t>
   </si>
   <si>
     <t>SMMEN</t>
@@ -549,20 +540,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="4" width="8.7109375" customWidth="1"/>
     <col min="5" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" customWidth="1"/>
+    <col min="8" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,17 +585,8 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -614,7 +594,7 @@
         <v>21092</v>
       </c>
       <c r="C2" s="3">
-        <v>360</v>
+        <v>212</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -625,16 +605,11 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3">
-        <v>16</v>
-      </c>
-      <c r="N2" s="3">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="K2" s="3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
@@ -642,12 +617,10 @@
         <v>21176</v>
       </c>
       <c r="C3" s="3">
-        <v>391</v>
+        <v>233</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
         <v>1</v>
@@ -655,16 +628,11 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3">
-        <v>38</v>
-      </c>
-      <c r="N3" s="3">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="K3" s="3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>1001</v>
       </c>
@@ -672,33 +640,24 @@
         <v>21082</v>
       </c>
       <c r="C4" s="3">
-        <v>258</v>
-      </c>
-      <c r="D4" s="3">
-        <v>55</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3">
-        <v>117</v>
-      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3">
         <v>1</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3">
-        <v>24</v>
-      </c>
-      <c r="N4" s="3">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="K4" s="3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
@@ -706,35 +665,24 @@
         <v>21469</v>
       </c>
       <c r="C5" s="3">
-        <v>476</v>
-      </c>
-      <c r="D5" s="3">
-        <v>91</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3">
-        <v>248</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
         <v>7</v>
       </c>
-      <c r="H5" s="3">
-        <v>125</v>
-      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3">
-        <v>33</v>
-      </c>
-      <c r="N5" s="3">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="J5" s="3"/>
+      <c r="K5" s="3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
@@ -761,18 +709,13 @@
         <v>1</v>
       </c>
       <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3">
         <v>9</v>
       </c>
-      <c r="N6" s="3">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="K6" s="3">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>1002</v>
       </c>
@@ -797,49 +740,43 @@
         <v>1</v>
       </c>
       <c r="J7" s="3">
-        <v>10</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3">
         <v>61</v>
       </c>
-      <c r="N7" s="3">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="K7" s="3">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B8" s="2">
-        <v>21086</v>
+        <v>21088</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21088</v>
+      </c>
+      <c r="C9" s="3">
         <v>2</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="2">
-        <v>1003</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -848,70 +785,63 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="2">
-        <v>21533</v>
+        <v>21229</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <v>4</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3">
-        <v>6</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="2">
-        <v>21075</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>21086</v>
+      </c>
+      <c r="C11" s="3">
+        <v>209</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3">
+        <v>24</v>
+      </c>
       <c r="K11" s="3">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="B12" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>21515</v>
+      </c>
+      <c r="C12" s="3">
+        <v>59</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -920,20 +850,15 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="B13" s="2">
-        <v>21083</v>
+        <v>21195</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -942,26 +867,23 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
       <c r="K13" s="3">
-        <v>3</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="B14" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>21246</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -970,618 +892,218 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3">
-        <v>1</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="B15" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+        <v>21083</v>
+      </c>
+      <c r="C15" s="3">
+        <v>342</v>
+      </c>
+      <c r="D15" s="3">
+        <v>45</v>
+      </c>
+      <c r="E15" s="3">
+        <v>165</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <v>71</v>
+      </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3">
+        <v>15</v>
+      </c>
       <c r="K15" s="3">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="B16" s="2">
         <v>21457</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="C16" s="3">
+        <v>488</v>
+      </c>
+      <c r="D16" s="3">
+        <v>57</v>
+      </c>
+      <c r="E16" s="3">
+        <v>165</v>
+      </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>69</v>
+      </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>23</v>
+      </c>
       <c r="K16" s="3">
-        <v>7</v>
-      </c>
-      <c r="L16" s="3">
-        <v>3</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="B17" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+        <v>21089</v>
+      </c>
+      <c r="C17" s="3">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3">
+        <v>14</v>
+      </c>
+      <c r="E17" s="3">
+        <v>32</v>
+      </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>46</v>
+      </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>27</v>
+      </c>
       <c r="K17" s="3">
-        <v>4</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="B18" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C18" s="3">
+        <v>641</v>
+      </c>
+      <c r="D18" s="3">
+        <v>100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>235</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>154</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3">
+        <v>14</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B19" s="2">
         <v>21090</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3">
+      <c r="C19" s="3">
+        <v>184</v>
+      </c>
+      <c r="D19" s="3">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>73</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3">
         <v>1</v>
       </c>
-      <c r="L18" s="3">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="2">
-        <v>1005</v>
-      </c>
-      <c r="B19" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3">
+        <v>33</v>
+      </c>
       <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3">
+        <v>21</v>
+      </c>
       <c r="K19" s="3">
-        <v>2</v>
-      </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="B20" s="2">
-        <v>21469</v>
-      </c>
-      <c r="C20" s="3"/>
+        <v>21253</v>
+      </c>
+      <c r="C20" s="3">
+        <v>40</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3">
+        <v>11</v>
+      </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="I20" s="3">
+        <v>23</v>
+      </c>
+      <c r="J20" s="3">
+        <v>21</v>
+      </c>
       <c r="K20" s="3">
-        <v>19</v>
-      </c>
-      <c r="L20" s="3">
-        <v>2</v>
-      </c>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B21" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C21" s="3">
-        <v>82</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B22" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C22" s="3">
-        <v>113</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B23" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="4">
+        <v>3663</v>
+      </c>
+      <c r="D21" s="4">
+        <v>391</v>
+      </c>
+      <c r="E21" s="4">
         <v>1008</v>
       </c>
-      <c r="B24" s="2">
-        <v>21087</v>
-      </c>
-      <c r="C24" s="3">
-        <v>74</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3">
-        <v>1</v>
-      </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B25" s="2">
-        <v>21229</v>
-      </c>
-      <c r="C25" s="3">
-        <v>73</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3">
-        <v>4</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>1</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="2">
-        <v>1009</v>
-      </c>
-      <c r="B26" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C26" s="3">
-        <v>226</v>
-      </c>
-      <c r="D26" s="3">
-        <v>56</v>
-      </c>
-      <c r="E26" s="3">
-        <v>174</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3">
-        <v>80</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3">
-        <v>2</v>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3">
-        <v>24</v>
-      </c>
-      <c r="N26" s="3">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="2">
-        <v>1009</v>
-      </c>
-      <c r="B27" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C27" s="3">
-        <v>107</v>
-      </c>
-      <c r="D27" s="3">
-        <v>6</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B28" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3">
-        <v>2</v>
-      </c>
-      <c r="N28" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B29" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C29" s="3">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B30" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C30" s="3">
-        <v>342</v>
-      </c>
-      <c r="D30" s="3">
-        <v>45</v>
-      </c>
-      <c r="E30" s="3">
-        <v>165</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3">
-        <v>71</v>
-      </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3">
+      <c r="F21" s="4">
         <v>15</v>
       </c>
-      <c r="N30" s="3">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B31" s="2">
-        <v>21457</v>
-      </c>
-      <c r="C31" s="3">
-        <v>488</v>
-      </c>
-      <c r="D31" s="3">
-        <v>57</v>
-      </c>
-      <c r="E31" s="3">
-        <v>165</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3">
-        <v>2</v>
-      </c>
-      <c r="H31" s="3">
-        <v>69</v>
-      </c>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3">
-        <v>4</v>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3">
-        <v>23</v>
-      </c>
-      <c r="N31" s="3">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B32" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C32" s="3">
-        <v>55</v>
-      </c>
-      <c r="D32" s="3">
-        <v>14</v>
-      </c>
-      <c r="E32" s="3">
-        <v>43</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3">
-        <v>46</v>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3">
-        <v>2</v>
-      </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3">
-        <v>27</v>
-      </c>
-      <c r="N32" s="3">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B33" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C33" s="3">
-        <v>641</v>
-      </c>
-      <c r="D33" s="3">
-        <v>100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>359</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3">
-        <v>2</v>
-      </c>
-      <c r="H33" s="3">
-        <v>154</v>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3">
-        <v>7</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3">
-        <v>14</v>
-      </c>
-      <c r="N33" s="3">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B34" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C34" s="3">
-        <v>184</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="G21" s="4">
+        <v>30</v>
+      </c>
+      <c r="H21" s="4">
+        <v>608</v>
+      </c>
+      <c r="I21" s="4">
         <v>26</v>
       </c>
-      <c r="E34" s="3">
-        <v>73</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3">
-        <v>33</v>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3">
-        <v>7</v>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3">
-        <v>21</v>
-      </c>
-      <c r="N34" s="3">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="4">
-        <v>4482</v>
-      </c>
-      <c r="D35" s="4">
-        <v>600</v>
-      </c>
-      <c r="E35" s="4">
-        <v>1726</v>
-      </c>
-      <c r="F35" s="4">
-        <v>15</v>
-      </c>
-      <c r="G35" s="4">
-        <v>19</v>
-      </c>
-      <c r="H35" s="4">
-        <v>930</v>
-      </c>
-      <c r="I35" s="4">
-        <v>3</v>
-      </c>
-      <c r="J35" s="4">
-        <v>40</v>
-      </c>
-      <c r="K35" s="4">
-        <v>61</v>
-      </c>
-      <c r="L35" s="4">
-        <v>11</v>
-      </c>
-      <c r="M35" s="4">
-        <v>307</v>
-      </c>
-      <c r="N35" s="4">
-        <v>8194</v>
+      <c r="J21" s="4">
+        <v>217</v>
+      </c>
+      <c r="K21" s="4">
+        <v>5958</v>
       </c>
     </row>
   </sheetData>
@@ -1612,28 +1134,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1643,9 +1165,7 @@
       <c r="B2" s="2">
         <v>21087</v>
       </c>
-      <c r="C2" s="3">
-        <v>213</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1655,7 +1175,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3">
-        <v>216</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1665,9 +1185,7 @@
       <c r="B3" s="2">
         <v>21088</v>
       </c>
-      <c r="C3" s="3">
-        <v>84</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1679,7 +1197,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="3">
-        <v>106</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1710,22 +1228,18 @@
         <v>21092</v>
       </c>
       <c r="C5" s="3">
-        <v>92</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
         <v>3</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="3">
-        <v>87</v>
-      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1738,22 +1252,16 @@
       <c r="C6" s="3">
         <v>47</v>
       </c>
-      <c r="D6" s="3">
-        <v>29</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3">
         <v>6</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>85</v>
-      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3">
-        <v>169</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1763,13 +1271,9 @@
       <c r="B7" s="2">
         <v>21229</v>
       </c>
-      <c r="C7" s="3">
-        <v>178</v>
-      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>37</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
         <v>9</v>
@@ -1777,7 +1281,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>224</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1790,13 +1294,9 @@
       <c r="C8" s="3">
         <v>83</v>
       </c>
-      <c r="D8" s="3">
-        <v>64</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>7</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3">
         <v>19</v>
       </c>
@@ -1805,7 +1305,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>214</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1818,22 +1318,16 @@
       <c r="C9" s="3">
         <v>30</v>
       </c>
-      <c r="D9" s="3">
-        <v>11</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>3</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3">
         <v>8</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>36</v>
-      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3">
-        <v>88</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1847,12 +1341,10 @@
         <v>55</v>
       </c>
       <c r="D10" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3">
-        <v>2</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3">
         <v>5</v>
       </c>
@@ -1861,7 +1353,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1874,16 +1366,14 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>28</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
         <v>35</v>
       </c>
       <c r="J11" s="3">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1906,14 +1396,12 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="3">
-        <v>48</v>
-      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3">
         <v>46</v>
       </c>
       <c r="J12" s="3">
-        <v>687</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1951,23 +1439,19 @@
       <c r="D14" s="3">
         <v>15</v>
       </c>
-      <c r="E14" s="3">
-        <v>65</v>
-      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="3">
         <v>49</v>
       </c>
       <c r="G14" s="3">
         <v>15</v>
       </c>
-      <c r="H14" s="3">
-        <v>10</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3">
         <v>74</v>
       </c>
       <c r="J14" s="3">
-        <v>287</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1983,23 +1467,19 @@
       <c r="D15" s="3">
         <v>23</v>
       </c>
-      <c r="E15" s="3">
-        <v>36</v>
-      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3">
         <v>38</v>
       </c>
       <c r="G15" s="3">
         <v>6</v>
       </c>
-      <c r="H15" s="3">
-        <v>4</v>
-      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3">
         <v>105</v>
       </c>
       <c r="J15" s="3">
-        <v>632</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2015,23 +1495,19 @@
       <c r="D16" s="3">
         <v>26</v>
       </c>
-      <c r="E16" s="3">
-        <v>18</v>
-      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3">
         <v>38</v>
       </c>
       <c r="G16" s="3">
         <v>5</v>
       </c>
-      <c r="H16" s="3">
-        <v>7</v>
-      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3">
         <v>60</v>
       </c>
       <c r="J16" s="3">
-        <v>329</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2052,14 +1528,12 @@
         <v>12</v>
       </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>2</v>
-      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3">
         <v>5</v>
       </c>
       <c r="J17" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2084,14 +1558,12 @@
       <c r="G18" s="3">
         <v>3</v>
       </c>
-      <c r="H18" s="3">
-        <v>5</v>
-      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3">
         <v>89</v>
       </c>
       <c r="J18" s="3">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2109,7 +1581,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G19" s="3">
         <v>5</v>
@@ -2121,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2252,32 +1724,32 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="4">
-        <v>1821</v>
+        <v>1330</v>
       </c>
       <c r="D24" s="4">
-        <v>815</v>
+        <v>708</v>
       </c>
       <c r="E24" s="4">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="F24" s="4">
-        <v>453</v>
+        <v>403</v>
       </c>
       <c r="G24" s="4">
         <v>129</v>
       </c>
       <c r="H24" s="4">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="I24" s="4">
-        <v>943</v>
+        <v>735</v>
       </c>
       <c r="J24" s="4">
-        <v>4614</v>
+        <v>3526</v>
       </c>
     </row>
   </sheetData>
@@ -2287,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2295,16 +1767,16 @@
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="6.7109375" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="7" width="6.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="10" width="6.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2312,52 +1784,49 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>60224</v>
+        <v>60129</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -2366,24 +1835,23 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="L2" s="3">
+        <v>102</v>
+      </c>
       <c r="M2" s="3">
-        <v>92</v>
-      </c>
-      <c r="N2" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>60227</v>
+        <v>60131</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -2392,24 +1860,23 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>89</v>
+      </c>
       <c r="M3" s="3">
-        <v>120</v>
-      </c>
-      <c r="N3" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>60448</v>
+        <v>60138</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -2418,50 +1885,50 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>97</v>
+      </c>
       <c r="M4" s="3">
-        <v>124</v>
-      </c>
-      <c r="N4" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>60129</v>
+        <v>60127</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>322</v>
+      </c>
       <c r="M5" s="3">
-        <v>442</v>
-      </c>
-      <c r="N5" s="3">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2">
-        <v>60131</v>
+        <v>60128</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -2470,276 +1937,255 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>157</v>
+      </c>
       <c r="M6" s="3">
-        <v>369</v>
-      </c>
-      <c r="N6" s="3">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>60138</v>
+        <v>60296</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="3">
+        <v>2</v>
+      </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>183</v>
+      </c>
       <c r="M7" s="3">
-        <v>387</v>
-      </c>
-      <c r="N7" s="3">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>60127</v>
+        <v>60224</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>11</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>29</v>
+      </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>533</v>
-      </c>
-      <c r="N8" s="3">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>60128</v>
+        <v>60227</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>5</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>22</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>251</v>
-      </c>
-      <c r="N9" s="3">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>60296</v>
+        <v>60448</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3">
-        <v>15</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>14</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3">
-        <v>2</v>
-      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3">
-        <v>291</v>
-      </c>
-      <c r="N10" s="3">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2">
-        <v>60224</v>
+        <v>60129</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>156</v>
-      </c>
+      <c r="H11" s="3">
+        <v>130</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2">
-        <v>60227</v>
+        <v>60131</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3">
-        <v>80</v>
-      </c>
+      <c r="H12" s="3">
+        <v>216</v>
+      </c>
+      <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>1</v>
-      </c>
-      <c r="N12" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2">
-        <v>60448</v>
+        <v>60138</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>55</v>
-      </c>
-      <c r="J13" s="3"/>
+      <c r="H13" s="3">
+        <v>215</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="M13" s="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2">
-        <v>60129</v>
+        <v>60130</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>211</v>
-      </c>
+      <c r="H14" s="3">
+        <v>148</v>
+      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="M14" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2">
-        <v>60131</v>
+        <v>60272</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <v>332</v>
-      </c>
+      <c r="H15" s="3">
+        <v>124</v>
+      </c>
+      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="M15" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>60138</v>
+        <v>60510</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3">
-        <v>289</v>
-      </c>
+      <c r="H16" s="3">
+        <v>104</v>
+      </c>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3">
-        <v>2</v>
-      </c>
+      <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="M16" s="3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2">
-        <v>60130</v>
+        <v>60129</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -2747,23 +2193,22 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="3">
-        <v>177</v>
-      </c>
-      <c r="J17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3">
+        <v>116</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="M17" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2">
-        <v>60272</v>
+        <v>60131</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -2771,23 +2216,22 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3">
-        <v>140</v>
-      </c>
-      <c r="J18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3">
+        <v>78</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="M18" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2">
-        <v>60510</v>
+        <v>60138</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -2795,23 +2239,22 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="3">
-        <v>124</v>
-      </c>
-      <c r="J19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3">
+        <v>41</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="M19" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2">
-        <v>60224</v>
+        <v>60127</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -2820,22 +2263,21 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3">
-        <v>28</v>
-      </c>
+      <c r="J20" s="3">
+        <v>182</v>
+      </c>
+      <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="M20" s="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2">
-        <v>60227</v>
+        <v>60128</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -2844,22 +2286,21 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3">
-        <v>43</v>
-      </c>
+      <c r="J21" s="3">
+        <v>105</v>
+      </c>
+      <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="M21" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2">
-        <v>60448</v>
+        <v>60296</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -2868,22 +2309,21 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3">
-        <v>49</v>
-      </c>
+      <c r="J22" s="3">
+        <v>218</v>
+      </c>
+      <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="M22" s="3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B23" s="2">
-        <v>60129</v>
+        <v>60130</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -2891,20 +2331,19 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="I23" s="3">
+        <v>159</v>
+      </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="3">
-        <v>186</v>
-      </c>
+      <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="M23" s="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" s="2">
         <v>60131</v>
@@ -2914,21 +2353,22 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="H24" s="3">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
+        <v>218</v>
+      </c>
       <c r="J24" s="3"/>
-      <c r="K24" s="3">
-        <v>141</v>
-      </c>
+      <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="M24" s="3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25" s="2">
         <v>60138</v>
@@ -2939,23 +2379,22 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="I25" s="3">
+        <v>249</v>
+      </c>
       <c r="J25" s="3"/>
-      <c r="K25" s="3">
-        <v>52</v>
-      </c>
+      <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="M25" s="3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B26" s="2">
-        <v>60127</v>
+        <v>60137</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -2963,23 +2402,22 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3">
+        <v>9</v>
+      </c>
       <c r="J26" s="3"/>
-      <c r="K26" s="3">
-        <v>182</v>
-      </c>
+      <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="M26" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B27" s="2">
-        <v>60128</v>
+        <v>60202</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -2987,23 +2425,22 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="I27" s="3">
+        <v>7</v>
+      </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="3">
-        <v>105</v>
-      </c>
+      <c r="K27" s="3"/>
       <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="M27" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B28" s="2">
-        <v>60296</v>
+        <v>60496</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -3011,531 +2448,506 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="I28" s="3">
+        <v>5</v>
+      </c>
       <c r="J28" s="3"/>
-      <c r="K28" s="3">
-        <v>218</v>
-      </c>
+      <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="M28" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B29" s="2">
-        <v>60224</v>
+        <v>60129</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3">
+        <v>9</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3">
-        <v>181</v>
-      </c>
-      <c r="K29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3">
+        <v>20</v>
+      </c>
       <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="M29" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B30" s="2">
-        <v>60227</v>
+        <v>60131</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3">
+        <v>8</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3">
-        <v>59</v>
-      </c>
-      <c r="K30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3">
+        <v>29</v>
+      </c>
       <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="M30" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B31" s="2">
-        <v>60448</v>
+        <v>60138</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3">
+        <v>14</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3">
-        <v>22</v>
-      </c>
-      <c r="K31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3">
+        <v>21</v>
+      </c>
       <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="M31" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2">
-        <v>60130</v>
+        <v>60127</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3">
+        <v>128</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3">
-        <v>244</v>
-      </c>
-      <c r="K32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3">
+        <v>34</v>
+      </c>
       <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="M32" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B33" s="2">
-        <v>60131</v>
+        <v>60128</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3">
+        <v>45</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3">
-        <v>342</v>
-      </c>
-      <c r="K33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3">
+        <v>23</v>
+      </c>
       <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="M33" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B34" s="2">
-        <v>60138</v>
+        <v>60296</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3">
+        <v>87</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3">
-        <v>378</v>
-      </c>
-      <c r="K34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3">
+        <v>47</v>
+      </c>
       <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="M34" s="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B35" s="2">
-        <v>60137</v>
-      </c>
-      <c r="C35" s="3"/>
+        <v>60129</v>
+      </c>
+      <c r="C35" s="3">
+        <v>213</v>
+      </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3">
-        <v>9</v>
-      </c>
+      <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="M35" s="3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B36" s="2">
-        <v>60202</v>
-      </c>
-      <c r="C36" s="3"/>
+        <v>60131</v>
+      </c>
+      <c r="C36" s="3">
+        <v>217</v>
+      </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3">
-        <v>7</v>
-      </c>
+      <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="M36" s="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B37" s="2">
-        <v>60496</v>
-      </c>
-      <c r="C37" s="3"/>
+        <v>60138</v>
+      </c>
+      <c r="C37" s="3">
+        <v>258</v>
+      </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3">
-        <v>5</v>
-      </c>
+      <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="M37" s="3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B38" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C38" s="3"/>
+        <v>60127</v>
+      </c>
+      <c r="C38" s="3">
+        <v>462</v>
+      </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3">
-        <v>25</v>
-      </c>
+      <c r="E38" s="3">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
-      <c r="L38" s="3">
-        <v>34</v>
-      </c>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="L38" s="3"/>
+      <c r="M38" s="3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B39" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C39" s="3"/>
+        <v>60128</v>
+      </c>
+      <c r="C39" s="3">
+        <v>109</v>
+      </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3">
-        <v>8</v>
-      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-      <c r="L39" s="3">
-        <v>9</v>
-      </c>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B40" s="2">
-        <v>60448</v>
-      </c>
-      <c r="C40" s="3"/>
+        <v>60296</v>
+      </c>
+      <c r="C40" s="3">
+        <v>161</v>
+      </c>
       <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>11</v>
-      </c>
+      <c r="E40" s="3">
+        <v>2</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3">
-        <v>14</v>
-      </c>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B41" s="2">
-        <v>60129</v>
+        <v>60131</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>55</v>
-      </c>
-      <c r="G41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
-      <c r="L41" s="3">
-        <v>20</v>
-      </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="L41" s="3"/>
+      <c r="M41" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B42" s="2">
-        <v>60131</v>
+        <v>60127</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>66</v>
-      </c>
-      <c r="G42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3">
+        <v>2</v>
+      </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3">
-        <v>29</v>
-      </c>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="K42" s="3">
+        <v>32</v>
+      </c>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B43" s="2">
-        <v>60138</v>
+        <v>60128</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>71</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3">
-        <v>21</v>
-      </c>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="K43" s="3">
+        <v>56</v>
+      </c>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B44" s="2">
-        <v>60127</v>
+        <v>60130</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3">
-        <v>130</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3">
-        <v>34</v>
-      </c>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="K44" s="3">
+        <v>39</v>
+      </c>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B45" s="2">
-        <v>60128</v>
+        <v>60132</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="3">
-        <v>46</v>
-      </c>
-      <c r="G45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3">
+        <v>2</v>
+      </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3">
+      <c r="K45" s="3">
+        <v>41</v>
+      </c>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="2">
         <v>23</v>
       </c>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="2">
-        <v>15</v>
-      </c>
       <c r="B46" s="2">
-        <v>60296</v>
+        <v>60134</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="3">
-        <v>95</v>
-      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3">
-        <v>47</v>
-      </c>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="K46" s="3">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B47" s="2">
-        <v>60224</v>
-      </c>
-      <c r="C47" s="3">
-        <v>96</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="3">
-        <v>2</v>
-      </c>
+      <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
+      <c r="K47" s="3">
+        <v>24</v>
+      </c>
       <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="M47" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B48" s="2">
-        <v>60227</v>
-      </c>
-      <c r="C48" s="3">
-        <v>65</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3">
+        <v>1</v>
+      </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
+      <c r="K48" s="3">
+        <v>51</v>
+      </c>
       <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="M48" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B49" s="2">
-        <v>60448</v>
-      </c>
-      <c r="C49" s="3">
-        <v>30</v>
-      </c>
+        <v>60140</v>
+      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3543,23 +2955,22 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
+      <c r="K49" s="3">
+        <v>4</v>
+      </c>
       <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="M49" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B50" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C50" s="3">
-        <v>285</v>
-      </c>
+        <v>60272</v>
+      </c>
+      <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3567,49 +2978,45 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
+      <c r="K50" s="3">
+        <v>39</v>
+      </c>
       <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="M50" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B51" s="2">
-        <v>60131</v>
-      </c>
-      <c r="C51" s="3">
-        <v>278</v>
-      </c>
+        <v>60306</v>
+      </c>
+      <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="3">
-        <v>7</v>
-      </c>
+      <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
+      <c r="K51" s="3">
+        <v>15</v>
+      </c>
       <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="M51" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B52" s="2">
-        <v>60138</v>
-      </c>
-      <c r="C52" s="3">
-        <v>330</v>
-      </c>
+        <v>60355</v>
+      </c>
+      <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3617,50 +3024,48 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
+      <c r="K52" s="3">
+        <v>15</v>
+      </c>
       <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="M52" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B53" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C53" s="3">
-        <v>462</v>
-      </c>
+        <v>60510</v>
+      </c>
+      <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="3">
-        <v>1</v>
-      </c>
+      <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
+      <c r="K53" s="3">
+        <v>16</v>
+      </c>
       <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="M53" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B54" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C54" s="3">
-        <v>109</v>
-      </c>
-      <c r="D54" s="3"/>
+        <v>60132</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3">
+        <v>22</v>
+      </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -3668,260 +3073,265 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="L54" s="3">
+        <v>1063</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B55" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C55" s="3">
-        <v>161</v>
-      </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3">
-        <v>2</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3">
+        <v>8</v>
+      </c>
+      <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
+      <c r="J55" s="3">
+        <v>1</v>
+      </c>
       <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="L55" s="3">
+        <v>487</v>
+      </c>
+      <c r="M55" s="3">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B56" s="2">
-        <v>60127</v>
+        <v>60139</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3">
+        <v>8</v>
+      </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3">
-        <v>5</v>
-      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="L56" s="3">
+        <v>544</v>
+      </c>
+      <c r="M56" s="3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B57" s="2">
-        <v>60129</v>
+        <v>60130</v>
       </c>
       <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3">
+        <v>15</v>
+      </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3">
-        <v>3</v>
-      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="L57" s="3">
+        <v>157</v>
+      </c>
+      <c r="M57" s="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B58" s="2">
-        <v>60131</v>
+        <v>60272</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3">
+        <v>2</v>
+      </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3">
-        <v>7</v>
-      </c>
+      <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
+      <c r="L58" s="3">
+        <v>143</v>
+      </c>
+      <c r="M58" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B59" s="2">
-        <v>60134</v>
+        <v>60510</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="3">
-        <v>4</v>
-      </c>
+      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
+      <c r="J59" s="3">
+        <v>1</v>
+      </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="L59" s="3">
+        <v>62</v>
+      </c>
+      <c r="M59" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B60" s="2">
-        <v>60135</v>
+        <v>60127</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3">
-        <v>2</v>
-      </c>
-      <c r="H60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3">
+        <v>338</v>
+      </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="L60" s="3">
+        <v>1</v>
+      </c>
+      <c r="M60" s="3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B61" s="2">
-        <v>60138</v>
+        <v>60128</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="3">
-        <v>4</v>
-      </c>
-      <c r="H61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3">
+        <v>152</v>
+      </c>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="M61" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B62" s="2">
-        <v>60139</v>
+        <v>60296</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="3">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3">
+        <v>499</v>
+      </c>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="L62" s="3">
+        <v>1</v>
+      </c>
+      <c r="M62" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B63" s="2">
-        <v>60306</v>
+        <v>60130</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-      <c r="G63" s="3">
-        <v>6</v>
-      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
+      <c r="J63" s="3">
+        <v>65</v>
+      </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="M63" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B64" s="2">
-        <v>60448</v>
+        <v>60272</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
-      <c r="G64" s="3">
-        <v>3</v>
-      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
+      <c r="J64" s="3">
+        <v>50</v>
+      </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="M64" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B65" s="2">
-        <v>60129</v>
+        <v>60510</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -3930,96 +3340,96 @@
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
+      <c r="J65" s="3">
+        <v>22</v>
+      </c>
       <c r="K65" s="3"/>
-      <c r="L65" s="3">
-        <v>46</v>
-      </c>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="L65" s="3"/>
+      <c r="M65" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B66" s="2">
-        <v>60131</v>
+        <v>60130</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3">
+        <v>74</v>
+      </c>
       <c r="G66" s="3"/>
-      <c r="H66" s="3">
-        <v>1</v>
-      </c>
+      <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3">
-        <v>33</v>
-      </c>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="K66" s="3">
+        <v>24</v>
+      </c>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B67" s="2">
-        <v>60215</v>
+        <v>60272</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3">
+        <v>36</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3">
-        <v>10</v>
-      </c>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="K67" s="3">
+        <v>20</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B68" s="2">
-        <v>60296</v>
+        <v>60510</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
+      <c r="F68" s="3">
+        <v>73</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3">
-        <v>38</v>
-      </c>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+      <c r="K68" s="3">
+        <v>20</v>
+      </c>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B69" s="2">
-        <v>60496</v>
+        <v>60127</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
@@ -4027,23 +3437,22 @@
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="I69" s="3">
+        <v>285</v>
+      </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
-      <c r="L69" s="3">
-        <v>10</v>
-      </c>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="L69" s="3"/>
+      <c r="M69" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B70" s="2">
-        <v>60507</v>
+        <v>60129</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -4051,46 +3460,42 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="I70" s="3">
+        <v>419</v>
+      </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
-      <c r="L70" s="3">
-        <v>10</v>
-      </c>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="L70" s="3"/>
+      <c r="M70" s="3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B71" s="2">
-        <v>60127</v>
+        <v>60296</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="3">
-        <v>2</v>
-      </c>
-      <c r="I71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3">
+        <v>313</v>
+      </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
-      <c r="L71" s="3">
+      <c r="L71" s="3"/>
+      <c r="M71" s="3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="2">
         <v>32</v>
-      </c>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" s="2">
-        <v>23</v>
       </c>
       <c r="B72" s="2">
         <v>60128</v>
@@ -4101,23 +3506,22 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="I72" s="3">
+        <v>230</v>
+      </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
-      <c r="L72" s="3">
-        <v>56</v>
-      </c>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="L72" s="3"/>
+      <c r="M72" s="3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B73" s="2">
-        <v>60130</v>
+        <v>60272</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
@@ -4125,75 +3529,74 @@
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="I73" s="3">
+        <v>125</v>
+      </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
-      <c r="L73" s="3">
-        <v>39</v>
-      </c>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="L73" s="3"/>
+      <c r="M73" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B74" s="2">
-        <v>60132</v>
+        <v>60510</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="3">
-        <v>2</v>
-      </c>
-      <c r="I74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3">
+        <v>132</v>
+      </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
-      <c r="L74" s="3">
-        <v>41</v>
-      </c>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="L74" s="3"/>
+      <c r="M74" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B75" s="2">
-        <v>60134</v>
-      </c>
-      <c r="C75" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C75" s="3">
+        <v>246</v>
+      </c>
       <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
+      <c r="E75" s="3">
+        <v>1</v>
+      </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
-      <c r="L75" s="3">
-        <v>24</v>
-      </c>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="L75" s="3"/>
+      <c r="M75" s="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B76" s="2">
-        <v>60135</v>
-      </c>
-      <c r="C76" s="3"/>
+        <v>60272</v>
+      </c>
+      <c r="C76" s="3">
+        <v>49</v>
+      </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -4202,49 +3605,47 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
-      <c r="L76" s="3">
-        <v>24</v>
-      </c>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="L76" s="3"/>
+      <c r="M76" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B77" s="2">
-        <v>60139</v>
-      </c>
-      <c r="C77" s="3"/>
+        <v>60510</v>
+      </c>
+      <c r="C77" s="3">
+        <v>147</v>
+      </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
+      <c r="E77" s="3">
+        <v>2</v>
+      </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="3">
-        <v>1</v>
-      </c>
+      <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
-      <c r="L77" s="3">
-        <v>51</v>
-      </c>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="L77" s="3"/>
+      <c r="M77" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B78" s="2">
-        <v>60140</v>
+        <v>60134</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
+      <c r="D78" s="3">
+        <v>14</v>
+      </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -4253,22 +3654,23 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3">
-        <v>4</v>
-      </c>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+        <v>367</v>
+      </c>
+      <c r="M78" s="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B79" s="2">
-        <v>60272</v>
+        <v>60306</v>
       </c>
       <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
+      <c r="D79" s="3">
+        <v>13</v>
+      </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -4277,22 +3679,23 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3">
-        <v>39</v>
-      </c>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
+        <v>415</v>
+      </c>
+      <c r="M79" s="3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B80" s="2">
-        <v>60306</v>
+        <v>60355</v>
       </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
+      <c r="D80" s="3">
+        <v>12</v>
+      </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -4301,625 +3704,49 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3">
-        <v>15</v>
-      </c>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
-      <c r="A81" s="2">
-        <v>23</v>
-      </c>
-      <c r="B81" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3">
-        <v>15</v>
-      </c>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
-      <c r="A82" s="2">
-        <v>23</v>
-      </c>
-      <c r="B82" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3">
-        <v>16</v>
-      </c>
-      <c r="M82" s="3"/>
-      <c r="N82" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="A83" s="2">
-        <v>27</v>
-      </c>
-      <c r="B83" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3">
-        <v>15</v>
-      </c>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3">
-        <v>328</v>
-      </c>
-      <c r="N83" s="3">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" s="2">
-        <v>27</v>
-      </c>
-      <c r="B84" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3">
-        <v>2</v>
-      </c>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3">
-        <v>261</v>
-      </c>
-      <c r="N84" s="3">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" s="2">
-        <v>27</v>
-      </c>
-      <c r="B85" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3">
-        <v>1</v>
-      </c>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3">
-        <v>146</v>
-      </c>
-      <c r="N85" s="3">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
-      <c r="A86" s="2">
-        <v>28</v>
-      </c>
-      <c r="B86" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3">
-        <v>338</v>
-      </c>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3">
-        <v>1</v>
-      </c>
-      <c r="N86" s="3">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
-      <c r="A87" s="2">
-        <v>28</v>
-      </c>
-      <c r="B87" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3">
-        <v>152</v>
-      </c>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14">
-      <c r="A88" s="2">
-        <v>28</v>
-      </c>
-      <c r="B88" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3">
-        <v>499</v>
-      </c>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3">
-        <v>1</v>
-      </c>
-      <c r="N88" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14">
-      <c r="A89" s="2">
-        <v>29</v>
-      </c>
-      <c r="B89" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3">
-        <v>100</v>
-      </c>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
-      <c r="A90" s="2">
-        <v>29</v>
-      </c>
-      <c r="B90" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3">
-        <v>83</v>
-      </c>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14">
-      <c r="A91" s="2">
-        <v>29</v>
-      </c>
-      <c r="B91" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3">
-        <v>41</v>
-      </c>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
-      <c r="A92" s="2">
-        <v>30</v>
-      </c>
-      <c r="B92" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3">
-        <v>74</v>
-      </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3">
-        <v>24</v>
-      </c>
-      <c r="M92" s="3"/>
-      <c r="N92" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
-      <c r="A93" s="2">
-        <v>30</v>
-      </c>
-      <c r="B93" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3">
-        <v>36</v>
-      </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3">
-        <v>20</v>
-      </c>
-      <c r="M93" s="3"/>
-      <c r="N93" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
-      <c r="A94" s="2">
-        <v>30</v>
-      </c>
-      <c r="B94" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3">
-        <v>73</v>
-      </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3">
-        <v>20</v>
-      </c>
-      <c r="M94" s="3"/>
-      <c r="N94" s="3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14">
-      <c r="A95" s="2">
-        <v>31</v>
-      </c>
-      <c r="B95" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3">
-        <v>285</v>
-      </c>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
-      <c r="A96" s="2">
-        <v>31</v>
-      </c>
-      <c r="B96" s="2">
-        <v>60129</v>
-      </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3">
-        <v>419</v>
-      </c>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="3">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
-      <c r="A97" s="2">
-        <v>31</v>
-      </c>
-      <c r="B97" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3">
-        <v>313</v>
-      </c>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
-      <c r="A98" s="2">
-        <v>32</v>
-      </c>
-      <c r="B98" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3">
-        <v>230</v>
-      </c>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
-      <c r="A99" s="2">
-        <v>32</v>
-      </c>
-      <c r="B99" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="3">
-        <v>125</v>
-      </c>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
-      <c r="N99" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
-      <c r="A100" s="2">
-        <v>32</v>
-      </c>
-      <c r="B100" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="3">
-        <v>132</v>
-      </c>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-      <c r="M100" s="3"/>
-      <c r="N100" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
-      <c r="A101" s="2">
-        <v>33</v>
-      </c>
-      <c r="B101" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C101" s="3">
-        <v>246</v>
-      </c>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3">
-        <v>1</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
-      <c r="N101" s="3">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
-      <c r="A102" s="2">
-        <v>33</v>
-      </c>
-      <c r="B102" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C102" s="3">
-        <v>49</v>
-      </c>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
-      <c r="N102" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
-      <c r="A103" s="2">
-        <v>33</v>
-      </c>
-      <c r="B103" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C103" s="3">
-        <v>147</v>
-      </c>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3">
-        <v>2</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
-      <c r="A104" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" s="4">
-        <v>2258</v>
-      </c>
-      <c r="D104" s="4">
-        <v>136</v>
-      </c>
-      <c r="E104" s="4">
-        <v>15</v>
-      </c>
-      <c r="F104" s="4">
-        <v>690</v>
-      </c>
-      <c r="G104" s="4">
-        <v>37</v>
-      </c>
-      <c r="H104" s="4">
+        <v>509</v>
+      </c>
+      <c r="M80" s="3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="4">
+        <v>1862</v>
+      </c>
+      <c r="D81" s="4">
+        <v>144</v>
+      </c>
+      <c r="E81" s="4">
         <v>6</v>
       </c>
-      <c r="I104" s="4">
-        <v>2558</v>
-      </c>
-      <c r="J104" s="4">
-        <v>2752</v>
-      </c>
-      <c r="K104" s="4">
-        <v>1233</v>
-      </c>
-      <c r="L104" s="4">
-        <v>798</v>
-      </c>
-      <c r="M104" s="4">
-        <v>3347</v>
-      </c>
-      <c r="N104" s="4">
-        <v>13830</v>
+      <c r="F81" s="4">
+        <v>474</v>
+      </c>
+      <c r="G81" s="4">
+        <v>6</v>
+      </c>
+      <c r="H81" s="4">
+        <v>1995</v>
+      </c>
+      <c r="I81" s="4">
+        <v>2152</v>
+      </c>
+      <c r="J81" s="4">
+        <v>883</v>
+      </c>
+      <c r="K81" s="4">
+        <v>594</v>
+      </c>
+      <c r="L81" s="4">
+        <v>4699</v>
+      </c>
+      <c r="M81" s="4">
+        <v>12815</v>
       </c>
     </row>
   </sheetData>
@@ -4929,15 +3756,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="7" width="7.7109375" customWidth="1"/>
+    <col min="3" max="8" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4945,22 +3772,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>2000</v>
       </c>
@@ -4969,15 +3799,16 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>2000</v>
       </c>
@@ -4986,15 +3817,16 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>2001</v>
       </c>
@@ -5008,46 +3840,40 @@
       <c r="E4" s="3">
         <v>11</v>
       </c>
-      <c r="F4" s="3">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>2001</v>
       </c>
       <c r="B5" s="2">
         <v>21229</v>
       </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3">
         <v>166</v>
       </c>
       <c r="E5" s="3">
         <v>19</v>
       </c>
-      <c r="F5" s="3">
-        <v>14</v>
-      </c>
-      <c r="G5" s="3">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>2002</v>
       </c>
       <c r="B6" s="2">
         <v>21092</v>
       </c>
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3">
         <v>97</v>
       </c>
@@ -5055,11 +3881,12 @@
         <v>11</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>2003</v>
       </c>
@@ -5068,109 +3895,104 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E7" s="3">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>2004</v>
       </c>
       <c r="B8" s="2">
         <v>21086</v>
       </c>
-      <c r="C8" s="3">
-        <v>37</v>
-      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3">
         <v>134</v>
       </c>
       <c r="E8" s="3">
         <v>24</v>
       </c>
-      <c r="F8" s="3">
-        <v>28</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>2004</v>
       </c>
       <c r="B9" s="2">
         <v>21515</v>
       </c>
-      <c r="C9" s="3">
-        <v>4</v>
-      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="3">
         <v>8</v>
       </c>
       <c r="E9" s="3">
         <v>5</v>
       </c>
-      <c r="F9" s="3">
-        <v>7</v>
-      </c>
-      <c r="G9" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>2005</v>
       </c>
       <c r="B10" s="2">
         <v>21081</v>
       </c>
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="3">
         <v>82</v>
       </c>
       <c r="E10" s="3">
         <v>10</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>2005</v>
       </c>
       <c r="B11" s="2">
         <v>21085</v>
       </c>
-      <c r="C11" s="3">
-        <v>26</v>
-      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="3">
         <v>159</v>
       </c>
       <c r="E11" s="3">
         <v>18</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
         <v>17</v>
       </c>
-      <c r="G11" s="3">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>2006</v>
       </c>
@@ -5186,14 +4008,15 @@
       <c r="E12" s="3">
         <v>4</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>2007</v>
       </c>
@@ -5209,14 +4032,15 @@
       <c r="E13" s="3">
         <v>12</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
         <v>16</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>2007</v>
       </c>
@@ -5232,14 +4056,15 @@
       <c r="E14" s="3">
         <v>11</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
         <v>13</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>2008</v>
       </c>
@@ -5255,14 +4080,15 @@
       <c r="E15" s="3">
         <v>19</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3">
         <v>32</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>2008</v>
       </c>
@@ -5278,14 +4104,15 @@
       <c r="E16" s="3">
         <v>5</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3">
         <v>6</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>2009</v>
       </c>
@@ -5301,14 +4128,15 @@
       <c r="E17" s="3">
         <v>16</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3">
         <v>11</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -5324,14 +4152,15 @@
       <c r="E18" s="3">
         <v>13</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3"/>
+      <c r="G18" s="3">
         <v>6</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>2010</v>
       </c>
@@ -5344,46 +4173,199 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B20" s="2">
+        <v>21469</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B21" s="2">
+        <v>21087</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21229</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B23" s="2">
+        <v>21086</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B24" s="2">
+        <v>21081</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B25" s="2">
+        <v>21085</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2">
         <v>2017</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B26" s="2">
         <v>21246</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3">
         <v>21</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="4">
-        <v>210</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1738</v>
-      </c>
-      <c r="E21" s="4">
-        <v>285</v>
-      </c>
-      <c r="F21" s="4">
-        <v>178</v>
-      </c>
-      <c r="G21" s="4">
-        <v>2411</v>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B27" s="2">
+        <v>21082</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B28" s="2">
+        <v>21234</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3">
+        <v>2</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="4">
+        <v>133</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1531</v>
+      </c>
+      <c r="E29" s="4">
+        <v>201</v>
+      </c>
+      <c r="F29" s="4">
+        <v>11</v>
+      </c>
+      <c r="G29" s="4">
+        <v>106</v>
+      </c>
+      <c r="H29" s="4">
+        <v>1982</v>
       </c>
     </row>
   </sheetData>
@@ -5411,13 +4393,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5484,7 +4466,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
@@ -5524,37 +4506,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -5568,17 +4550,11 @@
         <v>8</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="3">
-        <v>21</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3">
-        <v>171</v>
-      </c>
+      <c r="I2" s="3"/>
       <c r="J2" s="3">
         <v>11</v>
       </c>
@@ -5587,7 +4563,7 @@
         <v>12</v>
       </c>
       <c r="M2" s="3">
-        <v>224</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5601,15 +4577,11 @@
         <v>13</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>26</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3">
-        <v>214</v>
-      </c>
+      <c r="I3" s="3"/>
       <c r="J3" s="3">
         <v>3</v>
       </c>
@@ -5618,7 +4590,7 @@
         <v>7</v>
       </c>
       <c r="M3" s="3">
-        <v>263</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5628,32 +4600,24 @@
       <c r="B4" s="2">
         <v>21087</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>7</v>
-      </c>
-      <c r="D4" s="3">
-        <v>60</v>
-      </c>
-      <c r="E4" s="3">
-        <v>22</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>119</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>187</v>
-      </c>
-      <c r="J4" s="3">
-        <v>61</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M4" s="3">
-        <v>474</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5663,34 +4627,24 @@
       <c r="B5" s="2">
         <v>21229</v>
       </c>
-      <c r="C5" s="3">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3">
-        <v>51</v>
-      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
+        <v>2</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <v>2</v>
+      </c>
+      <c r="M5" s="3">
         <v>29</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3">
-        <v>71</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3">
-        <v>21</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3">
-        <v>13</v>
-      </c>
-      <c r="M5" s="3">
-        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5700,32 +4654,24 @@
       <c r="B6" s="2">
         <v>21092</v>
       </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3">
         <v>10</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>27</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>30</v>
-      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3">
-        <v>19</v>
-      </c>
-      <c r="K6" s="3">
-        <v>22</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3">
         <v>1</v>
       </c>
       <c r="M6" s="3">
-        <v>110</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5735,32 +4681,24 @@
       <c r="B7" s="2">
         <v>21176</v>
       </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3">
         <v>12</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>58</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>43</v>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>46</v>
-      </c>
-      <c r="K7" s="3">
-        <v>43</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="3">
         <v>6</v>
       </c>
       <c r="M7" s="3">
-        <v>209</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5790,7 +4728,7 @@
         <v>139</v>
       </c>
       <c r="J8" s="3">
-        <v>475</v>
+        <v>274</v>
       </c>
       <c r="K8" s="3">
         <v>136</v>
@@ -5799,7 +4737,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="3">
-        <v>839</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6015,25 +4953,19 @@
         <v>2</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3">
-        <v>9</v>
-      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3">
         <v>1</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3">
-        <v>10</v>
-      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="3">
         <v>1</v>
       </c>
       <c r="M14" s="3">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -6052,9 +4984,7 @@
       <c r="E15" s="3">
         <v>8</v>
       </c>
-      <c r="F15" s="3">
-        <v>77</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3">
         <v>48</v>
       </c>
@@ -6063,16 +4993,16 @@
         <v>38</v>
       </c>
       <c r="J15" s="3">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="K15" s="3">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="L15" s="3">
         <v>7</v>
       </c>
       <c r="M15" s="3">
-        <v>507</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6091,9 +5021,7 @@
       <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="F16" s="3">
-        <v>13</v>
-      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3">
         <v>8</v>
       </c>
@@ -6102,14 +5030,14 @@
         <v>5</v>
       </c>
       <c r="J16" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K16" s="3">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3">
-        <v>145</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -6129,7 +5057,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="3">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="G17" s="3">
         <v>58</v>
@@ -6139,16 +5067,16 @@
         <v>184</v>
       </c>
       <c r="J17" s="3">
-        <v>145</v>
+        <v>31</v>
       </c>
       <c r="K17" s="3">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="L17" s="3">
         <v>5</v>
       </c>
       <c r="M17" s="3">
-        <v>639</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -6168,7 +5096,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="3">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="G18" s="3">
         <v>59</v>
@@ -6180,16 +5108,16 @@
         <v>303</v>
       </c>
       <c r="J18" s="3">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="K18" s="3">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="L18" s="3">
         <v>9</v>
       </c>
       <c r="M18" s="3">
-        <v>806</v>
+        <v>702</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -6369,41 +5297,41 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="4">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D24" s="4">
-        <v>932</v>
+        <v>821</v>
       </c>
       <c r="E24" s="4">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="F24" s="4">
-        <v>640</v>
+        <v>446</v>
       </c>
       <c r="G24" s="4">
-        <v>717</v>
+        <v>441</v>
       </c>
       <c r="H24" s="4">
         <v>36</v>
       </c>
       <c r="I24" s="4">
-        <v>2063</v>
+        <v>1389</v>
       </c>
       <c r="J24" s="4">
-        <v>1646</v>
+        <v>1025</v>
       </c>
       <c r="K24" s="4">
-        <v>1431</v>
+        <v>1241</v>
       </c>
       <c r="L24" s="4">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="M24" s="4">
-        <v>8018</v>
+        <v>5853</v>
       </c>
     </row>
   </sheetData>

--- a/Balance_Pick_Summary.xlsx
+++ b/Balance_Pick_Summary.xlsx
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -585,7 +585,7 @@
         <v>21082</v>
       </c>
       <c r="C2" s="3">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -608,7 +608,7 @@
         <v>21469</v>
       </c>
       <c r="C3" s="3">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -618,7 +618,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3">
-        <v>92</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -632,9 +632,7 @@
         <v>96</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>5</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3">
         <v>15</v>
       </c>
@@ -647,7 +645,7 @@
         <v>9</v>
       </c>
       <c r="K4" s="3">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -661,9 +659,7 @@
         <v>507</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>5</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -674,26 +670,26 @@
         <v>61</v>
       </c>
       <c r="K5" s="3">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B6" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
+        <v>21195</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>2</v>
+      </c>
       <c r="K6" s="3">
         <v>2</v>
       </c>
@@ -703,41 +699,47 @@
         <v>1011</v>
       </c>
       <c r="B7" s="2">
-        <v>21195</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>21246</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>2</v>
-      </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B8" s="2">
-        <v>21246</v>
+        <v>21083</v>
       </c>
       <c r="C8" s="3">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+        <v>330</v>
+      </c>
+      <c r="D8" s="3">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3">
+        <v>165</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>71</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -745,13 +747,13 @@
         <v>1012</v>
       </c>
       <c r="B9" s="2">
-        <v>21083</v>
+        <v>21457</v>
       </c>
       <c r="C9" s="3">
-        <v>342</v>
+        <v>465</v>
       </c>
       <c r="D9" s="3">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3">
         <v>165</v>
@@ -759,43 +761,39 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="3">
-        <v>7</v>
-      </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="3">
-        <v>630</v>
+        <v>756</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B10" s="2">
-        <v>21457</v>
+        <v>21089</v>
       </c>
       <c r="C10" s="3">
-        <v>488</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3">
-        <v>57</v>
-      </c>
-      <c r="E10" s="3">
-        <v>165</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K10" s="3">
-        <v>792</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -803,295 +801,113 @@
         <v>1013</v>
       </c>
       <c r="B11" s="2">
-        <v>21089</v>
+        <v>21234</v>
       </c>
       <c r="C11" s="3">
-        <v>55</v>
+        <v>620</v>
       </c>
       <c r="D11" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K11" s="3">
-        <v>133</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B12" s="2">
-        <v>21234</v>
+        <v>21090</v>
       </c>
       <c r="C12" s="3">
-        <v>641</v>
-      </c>
-      <c r="D12" s="3">
-        <v>88</v>
-      </c>
-      <c r="E12" s="3"/>
+        <v>184</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
+        <v>73</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K12" s="3">
-        <v>876</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B13" s="2">
-        <v>21090</v>
+        <v>21253</v>
       </c>
       <c r="C13" s="3">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>73</v>
-      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>33</v>
-      </c>
-      <c r="I13" s="3"/>
+      <c r="G13" s="3">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
+        <v>23</v>
+      </c>
       <c r="J13" s="3">
         <v>21</v>
       </c>
       <c r="K13" s="3">
-        <v>311</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B14" s="2">
-        <v>21253</v>
-      </c>
-      <c r="C14" s="3">
-        <v>40</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3">
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="4">
+        <v>2313</v>
+      </c>
+      <c r="D14" s="4">
+        <v>128</v>
+      </c>
+      <c r="E14" s="4">
+        <v>403</v>
+      </c>
+      <c r="F14" s="4">
+        <v>15</v>
+      </c>
+      <c r="G14" s="4">
         <v>11</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>23</v>
-      </c>
-      <c r="J14" s="3">
-        <v>21</v>
-      </c>
-      <c r="K14" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="2">
-        <v>1030</v>
-      </c>
-      <c r="B15" s="2">
-        <v>21088</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="2">
-        <v>1031</v>
-      </c>
-      <c r="B16" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C16" s="3">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="2">
-        <v>1032</v>
-      </c>
-      <c r="B17" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="2">
-        <v>1032</v>
-      </c>
-      <c r="B18" s="2">
-        <v>21083</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="2">
-        <v>1032</v>
-      </c>
-      <c r="B19" s="2">
-        <v>21086</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="2">
-        <v>1032</v>
-      </c>
-      <c r="B20" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C20" s="3">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="2">
-        <v>1032</v>
-      </c>
-      <c r="B21" s="2">
-        <v>21234</v>
-      </c>
-      <c r="C21" s="3">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4">
-        <v>2540</v>
-      </c>
-      <c r="D22" s="4">
-        <v>209</v>
-      </c>
-      <c r="E22" s="4">
-        <v>413</v>
-      </c>
-      <c r="F22" s="4">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4">
-        <v>11</v>
-      </c>
-      <c r="H22" s="4">
-        <v>343</v>
-      </c>
-      <c r="I22" s="4">
+      <c r="H14" s="4">
+        <v>239</v>
+      </c>
+      <c r="I14" s="4">
         <v>26</v>
       </c>
-      <c r="J22" s="4">
-        <v>175</v>
-      </c>
-      <c r="K22" s="4">
-        <v>3732</v>
+      <c r="J14" s="4">
+        <v>132</v>
+      </c>
+      <c r="K14" s="4">
+        <v>3267</v>
       </c>
     </row>
   </sheetData>
@@ -1273,10 +1089,10 @@
         <v>15</v>
       </c>
       <c r="H7" s="3">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="I7" s="3">
-        <v>197</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1362,21 +1178,19 @@
       <c r="C11" s="3">
         <v>42</v>
       </c>
-      <c r="D11" s="3">
-        <v>2</v>
-      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
       </c>
       <c r="H11" s="3">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3">
-        <v>215</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1414,17 +1228,13 @@
         <v>31</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3">
-        <v>13</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3">
         <v>24</v>
       </c>
-      <c r="H13" s="3">
-        <v>19</v>
-      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>223</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1447,11 +1257,9 @@
       <c r="G14" s="3">
         <v>2</v>
       </c>
-      <c r="H14" s="3">
-        <v>27</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1474,11 +1282,9 @@
       <c r="G15" s="3">
         <v>3</v>
       </c>
-      <c r="H15" s="3">
-        <v>6</v>
-      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1496,14 +1302,14 @@
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3">
-        <v>296</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1515,22 +1321,22 @@
         <v>1207</v>
       </c>
       <c r="D17" s="4">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E17" s="4">
         <v>67</v>
       </c>
       <c r="F17" s="4">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="G17" s="4">
         <v>97</v>
       </c>
       <c r="H17" s="4">
-        <v>473</v>
+        <v>325</v>
       </c>
       <c r="I17" s="4">
-        <v>2809</v>
+        <v>2589</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1613,10 +1419,10 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L2" s="3">
-        <v>93</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1637,10 +1443,10 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="L3" s="3">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1663,10 +1469,10 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="L4" s="3">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1681,14 +1487,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1703,14 +1509,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1725,7 +1531,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3">
@@ -1734,7 +1540,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1749,14 +1555,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1771,14 +1577,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1793,14 +1599,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1817,12 +1623,12 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1839,12 +1645,12 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1861,12 +1667,12 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1883,12 +1689,12 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3">
-        <v>178</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1905,12 +1711,12 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1927,12 +1733,12 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3">
-        <v>215</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1948,13 +1754,13 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1968,17 +1774,15 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3">
-        <v>4</v>
-      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3">
-        <v>83</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1994,162 +1798,158 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
-        <v>60137</v>
+        <v>60127</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3">
+        <v>8</v>
+      </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="3">
-        <v>8</v>
-      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3">
+        <v>34</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2">
-        <v>60202</v>
+        <v>60128</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3">
-        <v>2</v>
-      </c>
+      <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="J21" s="3">
+        <v>23</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>60496</v>
+        <v>60296</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
+      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="3">
+        <v>47</v>
+      </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C23" s="3"/>
+        <v>60129</v>
+      </c>
+      <c r="C23" s="3">
+        <v>81</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3">
-        <v>28</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3">
-        <v>34</v>
-      </c>
+      <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C24" s="3"/>
+        <v>60131</v>
+      </c>
+      <c r="C24" s="3">
+        <v>74</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3">
-        <v>5</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3">
-        <v>23</v>
-      </c>
+      <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C25" s="3"/>
+        <v>60138</v>
+      </c>
+      <c r="C25" s="3">
+        <v>98</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3">
-        <v>16</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>47</v>
-      </c>
+      <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3">
-        <v>63</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" s="2">
-        <v>60129</v>
+        <v>60127</v>
       </c>
       <c r="C26" s="3">
-        <v>108</v>
+        <v>462</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2160,18 +1960,18 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3">
-        <v>108</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2">
-        <v>60131</v>
+        <v>60128</v>
       </c>
       <c r="C27" s="3">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2182,18 +1982,18 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2">
-        <v>60138</v>
+        <v>60296</v>
       </c>
       <c r="C28" s="3">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2204,73 +2004,73 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B29" s="2">
-        <v>60127</v>
-      </c>
-      <c r="C29" s="3">
-        <v>462</v>
-      </c>
+        <v>60128</v>
+      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
+      <c r="J29" s="3">
+        <v>34</v>
+      </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3">
-        <v>462</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B30" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C30" s="3">
-        <v>109</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="J30" s="3">
+        <v>20</v>
+      </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3">
-        <v>109</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B31" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C31" s="3">
-        <v>161</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
+      <c r="J31" s="3">
+        <v>22</v>
+      </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3">
-        <v>161</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2278,7 +2078,7 @@
         <v>23</v>
       </c>
       <c r="B32" s="2">
-        <v>60127</v>
+        <v>60135</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -2288,11 +2088,11 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2300,7 +2100,7 @@
         <v>23</v>
       </c>
       <c r="B33" s="2">
-        <v>60128</v>
+        <v>60139</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -2322,7 +2122,7 @@
         <v>23</v>
       </c>
       <c r="B34" s="2">
-        <v>60130</v>
+        <v>60140</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -2332,11 +2132,11 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2344,7 +2144,7 @@
         <v>23</v>
       </c>
       <c r="B35" s="2">
-        <v>60134</v>
+        <v>60306</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -2354,11 +2154,11 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2366,7 +2166,7 @@
         <v>23</v>
       </c>
       <c r="B36" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -2385,314 +2185,314 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2">
-        <v>60139</v>
+        <v>60132</v>
       </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3">
+        <v>22</v>
+      </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3">
-        <v>34</v>
-      </c>
-      <c r="K37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3">
+        <v>750</v>
+      </c>
       <c r="L37" s="3">
-        <v>34</v>
+        <v>772</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2">
-        <v>60140</v>
+        <v>60135</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3">
+        <v>8</v>
+      </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3">
-        <v>4</v>
-      </c>
-      <c r="K38" s="3"/>
+      <c r="I38" s="3">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3">
+        <v>337</v>
+      </c>
       <c r="L38" s="3">
-        <v>4</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B39" s="2">
-        <v>60306</v>
+        <v>60139</v>
       </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3">
+        <v>8</v>
+      </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3">
-        <v>15</v>
-      </c>
-      <c r="K39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3">
+        <v>393</v>
+      </c>
       <c r="L39" s="3">
-        <v>15</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B40" s="2">
-        <v>60355</v>
+        <v>60127</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="G40" s="3">
+        <v>287</v>
+      </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3">
-        <v>15</v>
-      </c>
-      <c r="K40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3">
+        <v>1</v>
+      </c>
       <c r="L40" s="3">
-        <v>15</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2">
-        <v>60132</v>
+        <v>60128</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3">
-        <v>22</v>
-      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="G41" s="3">
+        <v>129</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3">
-        <v>908</v>
-      </c>
+      <c r="K41" s="3"/>
       <c r="L41" s="3">
-        <v>930</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" s="2">
-        <v>60135</v>
+        <v>60296</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>8</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="G42" s="3">
+        <v>384</v>
+      </c>
       <c r="H42" s="3"/>
-      <c r="I42" s="3">
-        <v>1</v>
-      </c>
+      <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3">
-        <v>402</v>
+        <v>1</v>
       </c>
       <c r="L42" s="3">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B43" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3">
-        <v>8</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3">
+        <v>27</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3">
-        <v>467</v>
-      </c>
+      <c r="J43" s="3">
+        <v>24</v>
+      </c>
+      <c r="K43" s="3"/>
       <c r="L43" s="3">
-        <v>475</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B44" s="2">
-        <v>60127</v>
+        <v>60272</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3">
-        <v>301</v>
-      </c>
+      <c r="F44" s="3">
+        <v>14</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3">
-        <v>1</v>
-      </c>
+      <c r="J44" s="3">
+        <v>20</v>
+      </c>
+      <c r="K44" s="3"/>
       <c r="L44" s="3">
-        <v>302</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2">
-        <v>60128</v>
+        <v>60510</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3">
-        <v>138</v>
-      </c>
+      <c r="F45" s="3">
+        <v>56</v>
+      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
+      <c r="J45" s="3">
+        <v>20</v>
+      </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3">
-        <v>138</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2">
-        <v>60296</v>
+        <v>60127</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="3">
-        <v>425</v>
-      </c>
-      <c r="H46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3">
+        <v>285</v>
+      </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="3">
-        <v>1</v>
-      </c>
+      <c r="K46" s="3"/>
       <c r="L46" s="3">
-        <v>426</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2">
-        <v>60130</v>
+        <v>60129</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="3">
-        <v>74</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="3">
+        <v>419</v>
+      </c>
       <c r="I47" s="3"/>
-      <c r="J47" s="3">
-        <v>24</v>
-      </c>
+      <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3">
-        <v>98</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" s="2">
-        <v>60272</v>
+        <v>60296</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3">
-        <v>36</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
+      <c r="H48" s="3">
+        <v>313</v>
+      </c>
       <c r="I48" s="3"/>
-      <c r="J48" s="3">
-        <v>20</v>
-      </c>
+      <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3">
-        <v>56</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B49" s="2">
-        <v>60510</v>
+        <v>60128</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="3">
-        <v>73</v>
-      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
+      <c r="H49" s="3">
+        <v>154</v>
+      </c>
       <c r="I49" s="3"/>
-      <c r="J49" s="3">
-        <v>20</v>
-      </c>
+      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3">
-        <v>93</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B50" s="2">
-        <v>60127</v>
+        <v>60272</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -2700,21 +2500,21 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3">
-        <v>285</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B51" s="2">
-        <v>60129</v>
+        <v>60510</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -2722,157 +2522,161 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3">
-        <v>419</v>
+        <v>85</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3">
-        <v>419</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B52" s="2">
-        <v>60296</v>
-      </c>
-      <c r="C52" s="3"/>
+        <v>60130</v>
+      </c>
+      <c r="C52" s="3">
+        <v>246</v>
+      </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3">
-        <v>313</v>
-      </c>
+      <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3">
-        <v>313</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B53" s="2">
-        <v>60128</v>
-      </c>
-      <c r="C53" s="3"/>
+        <v>60272</v>
+      </c>
+      <c r="C53" s="3">
+        <v>49</v>
+      </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3">
-        <v>172</v>
-      </c>
+      <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3">
-        <v>172</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B54" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C54" s="3"/>
+        <v>60510</v>
+      </c>
+      <c r="C54" s="3">
+        <v>147</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="3">
-        <v>86</v>
-      </c>
+      <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3">
-        <v>86</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B55" s="2">
-        <v>60510</v>
+        <v>60134</v>
       </c>
       <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="D55" s="3">
+        <v>14</v>
+      </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="3">
-        <v>94</v>
-      </c>
+      <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
+      <c r="K55" s="3">
+        <v>296</v>
+      </c>
       <c r="L55" s="3">
-        <v>94</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B56" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C56" s="3">
-        <v>246</v>
-      </c>
-      <c r="D56" s="3"/>
+        <v>60306</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3">
+        <v>13</v>
+      </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
+      <c r="K56" s="3">
+        <v>352</v>
+      </c>
       <c r="L56" s="3">
-        <v>246</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B57" s="2">
-        <v>60272</v>
-      </c>
-      <c r="C57" s="3">
-        <v>49</v>
-      </c>
-      <c r="D57" s="3"/>
+        <v>60355</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3">
+        <v>12</v>
+      </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
+      <c r="K57" s="3">
+        <v>424</v>
+      </c>
       <c r="L57" s="3">
-        <v>49</v>
+        <v>436</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B58" s="2">
-        <v>60510</v>
-      </c>
-      <c r="C58" s="3">
-        <v>147</v>
-      </c>
+        <v>60130</v>
+      </c>
+      <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -2880,45 +2684,47 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
+      <c r="K58" s="3">
+        <v>1</v>
+      </c>
       <c r="L58" s="3">
-        <v>147</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B59" s="2">
-        <v>60134</v>
+        <v>60136</v>
       </c>
       <c r="C59" s="3"/>
-      <c r="D59" s="3">
-        <v>14</v>
-      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="I59" s="3">
+        <v>1</v>
+      </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3">
-        <v>355</v>
+        <v>172</v>
       </c>
       <c r="L59" s="3">
-        <v>369</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B60" s="2">
-        <v>60306</v>
+        <v>60140</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -2927,119 +2733,119 @@
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3">
-        <v>409</v>
+        <v>212</v>
       </c>
       <c r="L60" s="3">
-        <v>422</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B61" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3">
-        <v>12</v>
-      </c>
-      <c r="E61" s="3"/>
+        <v>60132</v>
+      </c>
+      <c r="C61" s="3">
+        <v>507</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3">
+        <v>1</v>
+      </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
-      <c r="K61" s="3">
-        <v>495</v>
-      </c>
+      <c r="K61" s="3"/>
       <c r="L61" s="3">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B62" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C62" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="C62" s="3">
+        <v>240</v>
+      </c>
       <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
-      <c r="K62" s="3">
-        <v>1</v>
-      </c>
+      <c r="K62" s="3"/>
       <c r="L62" s="3">
-        <v>1</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B63" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C63" s="3"/>
+        <v>60139</v>
+      </c>
+      <c r="C63" s="3">
+        <v>289</v>
+      </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="3">
-        <v>1</v>
-      </c>
+      <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="3">
-        <v>172</v>
-      </c>
+      <c r="K63" s="3"/>
       <c r="L63" s="3">
-        <v>173</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B64" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3">
-        <v>6</v>
-      </c>
-      <c r="E64" s="3"/>
+        <v>60134</v>
+      </c>
+      <c r="C64" s="3">
+        <v>263</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3">
+        <v>1</v>
+      </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="3">
-        <v>212</v>
-      </c>
+      <c r="K64" s="3"/>
       <c r="L64" s="3">
-        <v>218</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B65" s="2">
-        <v>60132</v>
+        <v>60306</v>
       </c>
       <c r="C65" s="3">
-        <v>507</v>
+        <v>326</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -3048,23 +2854,21 @@
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3">
-        <v>508</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B66" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C66" s="3">
-        <v>240</v>
+        <v>388</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="3">
-        <v>5</v>
-      </c>
+      <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
@@ -3072,18 +2876,18 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3">
-        <v>245</v>
+        <v>388</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B67" s="2">
-        <v>60139</v>
+        <v>60136</v>
       </c>
       <c r="C67" s="3">
-        <v>289</v>
+        <v>48</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3094,23 +2898,21 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3">
-        <v>289</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B68" s="2">
-        <v>60134</v>
+        <v>60140</v>
       </c>
       <c r="C68" s="3">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="3">
-        <v>1</v>
-      </c>
+      <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
@@ -3118,343 +2920,345 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3">
-        <v>264</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B69" s="2">
-        <v>60306</v>
-      </c>
-      <c r="C69" s="3">
-        <v>326</v>
-      </c>
+        <v>60132</v>
+      </c>
+      <c r="C69" s="3"/>
       <c r="D69" s="3"/>
-      <c r="E69" s="3">
-        <v>2</v>
-      </c>
-      <c r="F69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3">
+        <v>173</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
+      <c r="J69" s="3">
+        <v>35</v>
+      </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3">
-        <v>328</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B70" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C70" s="3">
-        <v>388</v>
-      </c>
+        <v>60134</v>
+      </c>
+      <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3">
+        <v>163</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
+      <c r="J70" s="3">
+        <v>36</v>
+      </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3">
-        <v>388</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B71" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C71" s="3">
-        <v>48</v>
-      </c>
+        <v>60139</v>
+      </c>
+      <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3">
+        <v>97</v>
+      </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
+      <c r="J71" s="3">
+        <v>18</v>
+      </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3">
-        <v>48</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B72" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C72" s="3">
-        <v>145</v>
-      </c>
+        <v>60135</v>
+      </c>
+      <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3">
+        <v>69</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
+      <c r="J72" s="3">
+        <v>22</v>
+      </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3">
-        <v>145</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B73" s="2">
-        <v>60132</v>
+        <v>60306</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B74" s="2">
-        <v>60134</v>
+        <v>60355</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3">
-        <v>199</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B75" s="2">
-        <v>60139</v>
+        <v>60136</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="3">
-        <v>115</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B76" s="2">
-        <v>60135</v>
+        <v>60140</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="3">
-        <v>91</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B77" s="2">
-        <v>60306</v>
+        <v>60132</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="3">
-        <v>124</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3">
+        <v>904</v>
+      </c>
       <c r="I77" s="3"/>
-      <c r="J77" s="3">
-        <v>46</v>
-      </c>
+      <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3">
-        <v>170</v>
+        <v>905</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B78" s="2">
-        <v>60355</v>
+        <v>60135</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-      <c r="F78" s="3">
-        <v>138</v>
-      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
+      <c r="H78" s="3">
+        <v>331</v>
+      </c>
       <c r="I78" s="3"/>
-      <c r="J78" s="3">
-        <v>26</v>
-      </c>
+      <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3">
-        <v>164</v>
+        <v>331</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B79" s="2">
-        <v>60136</v>
+        <v>60139</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="3">
-        <v>26</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
+      <c r="H79" s="3">
+        <v>327</v>
+      </c>
       <c r="I79" s="3"/>
-      <c r="J79" s="3">
-        <v>16</v>
-      </c>
+      <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3">
-        <v>42</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B80" s="2">
-        <v>60140</v>
+        <v>60134</v>
       </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
+      <c r="D80" s="3">
+        <v>1</v>
+      </c>
       <c r="E80" s="3"/>
-      <c r="F80" s="3">
-        <v>29</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
+      <c r="H80" s="3">
+        <v>297</v>
+      </c>
       <c r="I80" s="3"/>
-      <c r="J80" s="3">
-        <v>24</v>
-      </c>
+      <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3">
-        <v>53</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B81" s="2">
-        <v>60132</v>
+        <v>60306</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="3">
-        <v>1</v>
-      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="3">
-        <v>904</v>
+        <v>488</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3">
-        <v>905</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B82" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+      <c r="D82" s="3">
+        <v>1</v>
+      </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3">
-        <v>331</v>
+        <v>569</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3">
-        <v>331</v>
+        <v>570</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B83" s="2">
-        <v>60139</v>
+        <v>60136</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
@@ -3462,135 +3266,131 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3">
-        <v>327</v>
+        <v>146</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3">
-        <v>327</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B84" s="2">
-        <v>60134</v>
+        <v>60140</v>
       </c>
       <c r="C84" s="3"/>
-      <c r="D84" s="3">
-        <v>1</v>
-      </c>
+      <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3">
-        <v>297</v>
+        <v>119</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3">
-        <v>298</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B85" s="2">
-        <v>60306</v>
+        <v>60132</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="3">
-        <v>488</v>
-      </c>
-      <c r="I85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3">
+        <v>167</v>
+      </c>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3">
-        <v>488</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B86" s="2">
-        <v>60355</v>
+        <v>60134</v>
       </c>
       <c r="C86" s="3"/>
-      <c r="D86" s="3">
-        <v>1</v>
-      </c>
+      <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3">
-        <v>569</v>
-      </c>
-      <c r="I86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3">
+        <v>131</v>
+      </c>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3">
-        <v>570</v>
+        <v>131</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B87" s="2">
-        <v>60136</v>
+        <v>60139</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="3">
-        <v>146</v>
-      </c>
-      <c r="I87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3">
+        <v>72</v>
+      </c>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3">
-        <v>146</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B88" s="2">
-        <v>60140</v>
+        <v>60135</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="3">
-        <v>119</v>
-      </c>
-      <c r="I88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3">
+        <v>107</v>
+      </c>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B89" s="2">
-        <v>60132</v>
+        <v>60140</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
@@ -3599,20 +3399,20 @@
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3">
-        <v>167</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B90" s="2">
-        <v>60134</v>
+        <v>60306</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
@@ -3621,39 +3421,39 @@
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B91" s="2">
-        <v>60139</v>
+        <v>60132</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
+      <c r="G91" s="3">
+        <v>591</v>
+      </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="3">
-        <v>72</v>
-      </c>
+      <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3">
-        <v>72</v>
+        <v>591</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B92" s="2">
         <v>60135</v>
@@ -3662,297 +3462,209 @@
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
+      <c r="G92" s="3">
+        <v>321</v>
+      </c>
       <c r="H92" s="3"/>
-      <c r="I92" s="3">
-        <v>107</v>
-      </c>
+      <c r="I92" s="3"/>
       <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
+      <c r="K92" s="3">
+        <v>1</v>
+      </c>
       <c r="L92" s="3">
-        <v>107</v>
+        <v>322</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B93" s="2">
-        <v>60140</v>
+        <v>60139</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
+      <c r="G93" s="3">
+        <v>358</v>
+      </c>
       <c r="H93" s="3"/>
-      <c r="I93" s="3">
-        <v>43</v>
-      </c>
+      <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3">
-        <v>43</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B94" s="2">
-        <v>60306</v>
+        <v>60134</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
+      <c r="G94" s="3">
+        <v>272</v>
+      </c>
       <c r="H94" s="3"/>
-      <c r="I94" s="3">
-        <v>63</v>
-      </c>
+      <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="3">
-        <v>63</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B95" s="2">
-        <v>60132</v>
+        <v>60306</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3">
-        <v>591</v>
+        <v>508</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3">
-        <v>591</v>
+        <v>508</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B96" s="2">
-        <v>60135</v>
+        <v>60355</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3">
-        <v>321</v>
+        <v>686</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
+      <c r="I96" s="3">
+        <v>2</v>
+      </c>
       <c r="J96" s="3"/>
-      <c r="K96" s="3">
-        <v>1</v>
-      </c>
+      <c r="K96" s="3"/>
       <c r="L96" s="3">
-        <v>322</v>
+        <v>688</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B97" s="2">
-        <v>60139</v>
+        <v>60130</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3">
-        <v>358</v>
+        <v>15</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3">
-        <v>358</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B98" s="2">
-        <v>60134</v>
+        <v>60136</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3">
-        <v>272</v>
+        <v>50</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="3">
-        <v>272</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B99" s="2">
-        <v>60306</v>
+        <v>60140</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3">
-        <v>508</v>
+        <v>155</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="3">
-        <v>508</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100" spans="1:12">
-      <c r="A100" s="2">
-        <v>58</v>
-      </c>
-      <c r="B100" s="2">
-        <v>60355</v>
-      </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3">
-        <v>686</v>
-      </c>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3">
-        <v>2</v>
-      </c>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" s="2">
-        <v>59</v>
-      </c>
-      <c r="B101" s="2">
-        <v>60130</v>
-      </c>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3">
-        <v>15</v>
-      </c>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" s="2">
-        <v>59</v>
-      </c>
-      <c r="B102" s="2">
-        <v>60136</v>
-      </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3">
-        <v>50</v>
-      </c>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" s="2">
-        <v>59</v>
-      </c>
-      <c r="B103" s="2">
-        <v>60140</v>
-      </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3">
-        <v>155</v>
-      </c>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
-      <c r="A104" s="2" t="s">
+      <c r="A100" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B104" s="2"/>
-      <c r="C104" s="4">
-        <v>3725</v>
-      </c>
-      <c r="D104" s="4">
+      <c r="B100" s="2"/>
+      <c r="C100" s="4">
+        <v>3633</v>
+      </c>
+      <c r="D100" s="4">
         <v>116</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E100" s="4">
         <v>9</v>
       </c>
-      <c r="F104" s="4">
-        <v>1051</v>
-      </c>
-      <c r="G104" s="4">
-        <v>4295</v>
-      </c>
-      <c r="H104" s="4">
-        <v>4760</v>
-      </c>
-      <c r="I104" s="4">
-        <v>1169</v>
-      </c>
-      <c r="J104" s="4">
-        <v>551</v>
-      </c>
-      <c r="K104" s="4">
-        <v>3610</v>
-      </c>
-      <c r="L104" s="4">
-        <v>19286</v>
+      <c r="F100" s="4">
+        <v>924</v>
+      </c>
+      <c r="G100" s="4">
+        <v>4140</v>
+      </c>
+      <c r="H100" s="4">
+        <v>4625</v>
+      </c>
+      <c r="I100" s="4">
+        <v>996</v>
+      </c>
+      <c r="J100" s="4">
+        <v>544</v>
+      </c>
+      <c r="K100" s="4">
+        <v>3021</v>
+      </c>
+      <c r="L100" s="4">
+        <v>18008</v>
       </c>
     </row>
   </sheetData>
@@ -3962,7 +3674,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -3995,19 +3707,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B2" s="2">
-        <v>21088</v>
+        <v>21176</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4015,339 +3727,335 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2">
-        <v>21176</v>
+        <v>21229</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
-        <v>62</v>
-      </c>
-      <c r="E3" s="3">
-        <v>6</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>68</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B4" s="2">
-        <v>21229</v>
+        <v>21092</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>157</v>
-      </c>
-      <c r="E4" s="3">
-        <v>15</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>172</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B5" s="2">
-        <v>21092</v>
+        <v>21086</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>97</v>
-      </c>
-      <c r="E5" s="3"/>
+        <v>134</v>
+      </c>
+      <c r="E5" s="3">
+        <v>24</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>97</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B6" s="2">
-        <v>21087</v>
+        <v>21515</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B7" s="2">
-        <v>21086</v>
+        <v>21081</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E7" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>158</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B8" s="2">
-        <v>21515</v>
+        <v>21085</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="E8" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>13</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B9" s="2">
-        <v>21081</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>21089</v>
+      </c>
+      <c r="C9" s="3">
+        <v>12</v>
+      </c>
       <c r="D9" s="3">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
       <c r="G9" s="3">
-        <v>92</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B10" s="2">
-        <v>21085</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>21082</v>
+      </c>
+      <c r="C10" s="3">
+        <v>23</v>
+      </c>
       <c r="D10" s="3">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="E10" s="3">
-        <v>18</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F10" s="3">
+        <v>16</v>
+      </c>
       <c r="G10" s="3">
-        <v>177</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B11" s="2">
-        <v>21089</v>
+        <v>21234</v>
       </c>
       <c r="C11" s="3">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="E11" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F11" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G11" s="3">
-        <v>32</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B12" s="2">
-        <v>21082</v>
+        <v>21083</v>
       </c>
       <c r="C12" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D12" s="3">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="E12" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3">
-        <v>188</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B13" s="2">
-        <v>21234</v>
+        <v>21457</v>
       </c>
       <c r="C13" s="3">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F13" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G13" s="3">
-        <v>170</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B14" s="2">
-        <v>21083</v>
+        <v>21090</v>
       </c>
       <c r="C14" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E14" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B15" s="2">
-        <v>21457</v>
+        <v>21533</v>
       </c>
       <c r="C15" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="E15" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3">
         <v>6</v>
       </c>
       <c r="G15" s="3">
-        <v>81</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B16" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C16" s="3">
-        <v>24</v>
-      </c>
+        <v>21195</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="3">
-        <v>44</v>
-      </c>
-      <c r="E16" s="3">
-        <v>16</v>
-      </c>
-      <c r="F16" s="3">
-        <v>11</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="3">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="B17" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C17" s="3">
-        <v>21</v>
-      </c>
-      <c r="D17" s="3">
-        <v>147</v>
-      </c>
+        <v>21469</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="3">
-        <v>13</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>187</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B18" s="2">
-        <v>21195</v>
+        <v>21087</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B19" s="2">
-        <v>21469</v>
+        <v>21229</v>
       </c>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
         <v>1</v>
@@ -4355,27 +4063,27 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="B20" s="2">
-        <v>21087</v>
+        <v>21246</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
+      <c r="D20" s="3">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="B21" s="2">
-        <v>21229</v>
+        <v>21082</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
@@ -4389,74 +4097,40 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B22" s="2">
-        <v>21246</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3">
-        <v>21</v>
-      </c>
+        <v>21533</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="2">
-        <v>2018</v>
-      </c>
-      <c r="B23" s="2">
-        <v>21082</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B24" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C24" s="3">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2" t="s">
+      <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="4">
+      <c r="B23" s="2"/>
+      <c r="C23" s="4">
         <v>136</v>
       </c>
-      <c r="D25" s="4">
-        <v>1307</v>
-      </c>
-      <c r="E25" s="4">
-        <v>160</v>
-      </c>
-      <c r="F25" s="4">
+      <c r="D23" s="4">
+        <v>1246</v>
+      </c>
+      <c r="E23" s="4">
+        <v>139</v>
+      </c>
+      <c r="F23" s="4">
         <v>86</v>
       </c>
-      <c r="G25" s="4">
-        <v>1689</v>
+      <c r="G23" s="4">
+        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -4525,10 +4199,10 @@
         <v>17183</v>
       </c>
       <c r="C4" s="3">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4551,10 +4225,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D6" s="4">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -4564,7 +4238,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4632,7 +4306,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3">
         <v>9</v>
@@ -4644,16 +4318,14 @@
         <v>139</v>
       </c>
       <c r="J2" s="3">
-        <v>26</v>
-      </c>
-      <c r="K2" s="3">
-        <v>42</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="3">
         <v>5</v>
       </c>
       <c r="M2" s="3">
-        <v>289</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4673,7 +4345,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3">
         <v>18</v>
@@ -4687,14 +4359,12 @@
       <c r="J3" s="3">
         <v>6</v>
       </c>
-      <c r="K3" s="3">
-        <v>45</v>
-      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="3">
         <v>5</v>
       </c>
       <c r="M3" s="3">
-        <v>251</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4804,7 +4474,7 @@
         <v>205</v>
       </c>
       <c r="J6" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3">
         <v>62</v>
@@ -4813,7 +4483,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="3">
-        <v>431</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4845,7 +4515,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="3">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K7" s="3">
         <v>66</v>
@@ -4854,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="3">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4862,13 +4532,13 @@
         <v>3008</v>
       </c>
       <c r="B8" s="2">
-        <v>21081</v>
+        <v>21085</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>8</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -4877,7 +4547,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4885,53 +4555,55 @@
         <v>3008</v>
       </c>
       <c r="B9" s="2">
-        <v>21085</v>
+        <v>21515</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>26</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>38</v>
-      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="B10" s="2">
-        <v>21515</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>21086</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5</v>
+      </c>
       <c r="D10" s="3">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <v>58</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3">
-        <v>5</v>
+        <v>184</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="L10" s="3">
+        <v>5</v>
+      </c>
       <c r="M10" s="3">
-        <v>17</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4939,65 +4611,67 @@
         <v>3009</v>
       </c>
       <c r="B11" s="2">
-        <v>21086</v>
+        <v>21533</v>
       </c>
       <c r="C11" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="E11" s="3">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>184</v>
+        <v>303</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M11" s="3">
-        <v>326</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="B12" s="2">
-        <v>21533</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
+        <v>21075</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3">
-        <v>35</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="F12" s="3">
+        <v>23</v>
+      </c>
       <c r="G12" s="3">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>23</v>
+      </c>
       <c r="L12" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M12" s="3">
-        <v>525</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5005,205 +4679,147 @@
         <v>3010</v>
       </c>
       <c r="B13" s="2">
-        <v>21075</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>30923</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5</v>
+      </c>
       <c r="D13" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E13" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3">
-        <v>23</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2">
-        <v>3010</v>
+        <v>3012</v>
       </c>
       <c r="B14" s="2">
-        <v>30923</v>
+        <v>21089</v>
       </c>
       <c r="C14" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3">
+        <v>18</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>27</v>
+      </c>
+      <c r="G14" s="3">
+        <v>19</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>30</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
         <v>2</v>
       </c>
-      <c r="F14" s="3">
-        <v>20</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>42</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3">
-        <v>77</v>
-      </c>
-      <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>161</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="B15" s="2">
-        <v>21212</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+        <v>21090</v>
+      </c>
+      <c r="C15" s="3">
+        <v>9</v>
+      </c>
+      <c r="D15" s="3">
+        <v>117</v>
+      </c>
+      <c r="E15" s="3">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3">
+        <v>32</v>
+      </c>
+      <c r="G15" s="3">
+        <v>55</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>20</v>
-      </c>
-      <c r="J15" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2</v>
+      </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>7</v>
+      </c>
       <c r="M15" s="3">
-        <v>20</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B16" s="2">
-        <v>21089</v>
-      </c>
-      <c r="C16" s="3">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3">
-        <v>18</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3">
-        <v>19</v>
-      </c>
-      <c r="H16" s="3">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3">
+      <c r="A16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="4">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4">
+        <v>686</v>
+      </c>
+      <c r="E16" s="4">
+        <v>176</v>
+      </c>
+      <c r="F16" s="4">
+        <v>316</v>
+      </c>
+      <c r="G16" s="4">
+        <v>384</v>
+      </c>
+      <c r="H16" s="4">
         <v>30</v>
       </c>
-      <c r="J16" s="3">
-        <v>3</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3">
-        <v>2</v>
-      </c>
-      <c r="M16" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B17" s="2">
-        <v>21090</v>
-      </c>
-      <c r="C17" s="3">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3">
-        <v>117</v>
-      </c>
-      <c r="E17" s="3">
-        <v>21</v>
-      </c>
-      <c r="F17" s="3">
-        <v>32</v>
-      </c>
-      <c r="G17" s="3">
-        <v>55</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3">
-        <v>36</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3">
-        <v>7</v>
-      </c>
-      <c r="M17" s="3">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4">
-        <v>75</v>
-      </c>
-      <c r="D18" s="4">
-        <v>723</v>
-      </c>
-      <c r="E18" s="4">
-        <v>176</v>
-      </c>
-      <c r="F18" s="4">
-        <v>373</v>
-      </c>
-      <c r="G18" s="4">
-        <v>384</v>
-      </c>
-      <c r="H18" s="4">
-        <v>30</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1389</v>
-      </c>
-      <c r="J18" s="4">
-        <v>431</v>
-      </c>
-      <c r="K18" s="4">
-        <v>671</v>
-      </c>
-      <c r="L18" s="4">
+      <c r="I16" s="4">
+        <v>1326</v>
+      </c>
+      <c r="J16" s="4">
+        <v>371</v>
+      </c>
+      <c r="K16" s="4">
+        <v>584</v>
+      </c>
+      <c r="L16" s="4">
         <v>60</v>
       </c>
-      <c r="M18" s="4">
-        <v>4312</v>
+      <c r="M16" s="4">
+        <v>4008</v>
       </c>
     </row>
   </sheetData>
